--- a/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>22.86156608971377</v>
+        <v>10.84497634995303</v>
       </c>
       <c r="C21" t="n">
-        <v>79.66060406260559</v>
+        <v>37.78907200371703</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.35877988040659</v>
+        <v>6.041675371934871</v>
       </c>
       <c r="C2" t="n">
-        <v>7.515278676009333</v>
+        <v>6.078000036992003</v>
       </c>
       <c r="D2" t="n">
-        <v>24.96584411899639</v>
+        <v>42.91121040492384</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1448409963388</v>
+        <v>18.14760631300229</v>
       </c>
       <c r="C3" t="n">
-        <v>39.1373722297991</v>
+        <v>17.24439842509522</v>
       </c>
       <c r="D3" t="n">
-        <v>86.42325040484673</v>
+        <v>92.67698328089891</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.3489877655599</v>
+        <v>35.90153179660161</v>
       </c>
       <c r="C4" t="n">
-        <v>68.0380611474167</v>
+        <v>42.44880723622359</v>
       </c>
       <c r="D4" t="n">
-        <v>118.5911956821977</v>
+        <v>111.3930215146601</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.1541029985003</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="C5" t="n">
-        <v>119.0123654473196</v>
+        <v>72.5511553438393</v>
       </c>
       <c r="D5" t="n">
-        <v>91.13073064671019</v>
+        <v>72.08482518432207</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.72838434775569</v>
+        <v>40.45291415348983</v>
       </c>
       <c r="C6" t="n">
-        <v>129.6505835705381</v>
+        <v>78.41022564278425</v>
       </c>
       <c r="D6" t="n">
-        <v>58.00263611460582</v>
+        <v>45.72588107299945</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.30829414132927</v>
+        <v>28.62579956042849</v>
       </c>
       <c r="C7" t="n">
-        <v>102.2264432001076</v>
+        <v>60.7250224984822</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>66.50849822420017</v>
+        <v>37.1346069131356</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.659862521386895</v>
+        <v>7.730939431724142</v>
       </c>
       <c r="C21" t="n">
-        <v>92.87583307181609</v>
+        <v>96.63674289655178</v>
       </c>
       <c r="D21" t="n">
-        <v>7.659862521386895</v>
+        <v>8.697306860689659</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.826672624704819</v>
+        <v>6.516841260790327</v>
       </c>
       <c r="C2" t="n">
-        <v>11.18996033300514</v>
+        <v>7.743044143394593</v>
       </c>
       <c r="D2" t="n">
-        <v>21.75258388299658</v>
+        <v>40.97422218444488</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.4224956701914</v>
+        <v>19.29134238844982</v>
       </c>
       <c r="C3" t="n">
-        <v>33.96356182841841</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D3" t="n">
-        <v>85.66730467257668</v>
+        <v>103.8492721552276</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.62602054460675</v>
+        <v>35.42931115085889</v>
       </c>
       <c r="C4" t="n">
-        <v>81.50273091116171</v>
+        <v>42.7678752401038</v>
       </c>
       <c r="D4" t="n">
-        <v>130.1414574226614</v>
+        <v>130.3839491056104</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.58392856651115</v>
+        <v>48.74377351585415</v>
       </c>
       <c r="C5" t="n">
-        <v>120.7304239297515</v>
+        <v>75.47185476397355</v>
       </c>
       <c r="D5" t="n">
-        <v>109.3912379457009</v>
+        <v>92.38245896962486</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.5434969841878</v>
+        <v>49.83154997215961</v>
       </c>
       <c r="C6" t="n">
-        <v>157.3437228119321</v>
+        <v>95.91969594802613</v>
       </c>
       <c r="D6" t="n">
-        <v>69.83662294159687</v>
+        <v>56.91584140600459</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.59071868498287</v>
+        <v>38.62686342359076</v>
       </c>
       <c r="C7" t="n">
-        <v>140.2544405241078</v>
+        <v>86.95535766054849</v>
       </c>
       <c r="D7" t="n">
-        <v>47.78951474732623</v>
+        <v>43.47767883027424</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.19593293468863</v>
+        <v>22.69800692218626</v>
       </c>
       <c r="C8" t="n">
-        <v>98.46929473595507</v>
+        <v>58.0801941832413</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>11.20468654856884</v>
       </c>
       <c r="C9" t="n">
-        <v>58.46405753560178</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>37.72365553568369</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.833517344552555</v>
+        <v>7.923188896208778</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8565358111141</v>
+        <v>105.9726514867924</v>
       </c>
       <c r="D21" t="n">
-        <v>8.812707012621624</v>
+        <v>9.903986120260972</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.677267047210058</v>
+        <v>9.392380286529235</v>
       </c>
       <c r="C2" t="n">
-        <v>16.58171872472863</v>
+        <v>8.645270283597412</v>
       </c>
       <c r="D2" t="n">
-        <v>40.57563261652067</v>
+        <v>31.94508854848696</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.51085296357361</v>
+        <v>20.28781630826034</v>
       </c>
       <c r="C3" t="n">
-        <v>37.94945750766045</v>
+        <v>25.18182861393069</v>
       </c>
       <c r="D3" t="n">
-        <v>82.95277227033425</v>
+        <v>109.9655603526852</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.34073287329843</v>
+        <v>35.50588747179015</v>
       </c>
       <c r="C4" t="n">
-        <v>81.89837523597318</v>
+        <v>46.5073522455799</v>
       </c>
       <c r="D4" t="n">
-        <v>138.2585474413741</v>
+        <v>146.6053664228805</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.0502587260284</v>
+        <v>50.56000676871075</v>
       </c>
       <c r="C5" t="n">
-        <v>133.0759013106552</v>
+        <v>76.23270923476484</v>
       </c>
       <c r="D5" t="n">
-        <v>126.3509295365645</v>
+        <v>113.88273369263</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.017722183068</v>
+        <v>57.03659637362695</v>
       </c>
       <c r="C6" t="n">
-        <v>170.4255109710208</v>
+        <v>107.2706629045278</v>
       </c>
       <c r="D6" t="n">
-        <v>82.95866275655973</v>
+        <v>69.19259644761097</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.97484407925062</v>
+        <v>48.50815406683489</v>
       </c>
       <c r="C7" t="n">
-        <v>175.5875403999505</v>
+        <v>110.0715891047439</v>
       </c>
       <c r="D7" t="n">
-        <v>54.97590794241288</v>
+        <v>49.0471335564664</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.53940576245478</v>
+        <v>31.2097595180061</v>
       </c>
       <c r="C8" t="n">
-        <v>135.4370045393687</v>
+        <v>84.61683462903258</v>
       </c>
       <c r="D8" t="n">
-        <v>41.30703465618455</v>
+        <v>41.22358610132356</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8656237377052</v>
+        <v>16.30781111524376</v>
       </c>
       <c r="C9" t="n">
-        <v>84.09061785955626</v>
+        <v>52.80624551602742</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>37.38593432542277</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>50.39310965898878</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>34.08137155292803</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.991492361475165</v>
+        <v>8.100837108259562</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8851468799147</v>
+        <v>114.4243241541663</v>
       </c>
       <c r="D21" t="n">
-        <v>9.989365451843955</v>
+        <v>11.1386510238569</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.000842878984005</v>
+        <v>8.319330045787471</v>
       </c>
       <c r="C2" t="n">
-        <v>11.54044426342126</v>
+        <v>5.670574739729576</v>
       </c>
       <c r="D2" t="n">
-        <v>33.2567034813607</v>
+        <v>25.93384735538374</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.10895829963817</v>
+        <v>24.94130042639022</v>
       </c>
       <c r="C3" t="n">
-        <v>58.35508354043041</v>
+        <v>37.09533700496573</v>
       </c>
       <c r="D3" t="n">
-        <v>91.9848511494049</v>
+        <v>120.4555345725624</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.60277739487432</v>
+        <v>24.28745645536184</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4485802231747</v>
+        <v>65.28131359389165</v>
       </c>
       <c r="D4" t="n">
-        <v>135.6677152498667</v>
+        <v>137.4672587917511</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.43417883165113</v>
+        <v>32.12769362147687</v>
       </c>
       <c r="C5" t="n">
-        <v>101.8317806230004</v>
+        <v>64.08358139471056</v>
       </c>
       <c r="D5" t="n">
-        <v>83.52218593879741</v>
+        <v>73.0420291959627</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.89439752076462</v>
+        <v>30.10823859384119</v>
       </c>
       <c r="C6" t="n">
-        <v>115.6430073263446</v>
+        <v>72.49323222928874</v>
       </c>
       <c r="D6" t="n">
-        <v>36.18623863083319</v>
+        <v>32.28182801104362</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="C7" t="n">
-        <v>95.21970983489813</v>
+        <v>59.46740368934205</v>
       </c>
       <c r="D7" t="n">
-        <v>29.04500583014188</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C8" t="n">
-        <v>61.91882770684633</v>
+        <v>38.88702656521616</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>38.38437174064178</v>
+        <v>28.73281006019139</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.603594911662541</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.245077073163208</v>
+        <v>4.867505117655686</v>
       </c>
       <c r="C2" t="n">
-        <v>5.397648877948964</v>
+        <v>3.038509144643878</v>
       </c>
       <c r="D2" t="n">
-        <v>23.20458873757761</v>
+        <v>18.29290497323082</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.53740120931728</v>
+        <v>27.57238427377167</v>
       </c>
       <c r="C3" t="n">
-        <v>52.76893910326606</v>
+        <v>29.69786805346602</v>
       </c>
       <c r="D3" t="n">
-        <v>97.67407909551517</v>
+        <v>115.8069591929537</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.79644373451819</v>
+        <v>34.9953786655818</v>
       </c>
       <c r="C4" t="n">
-        <v>131.0093223932156</v>
+        <v>81.68140899333463</v>
       </c>
       <c r="D4" t="n">
-        <v>147.741248516694</v>
+        <v>161.5887998850953</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.62485887045326</v>
+        <v>35.95650966803944</v>
       </c>
       <c r="C5" t="n">
-        <v>147.1394371739907</v>
+        <v>92.35791527701869</v>
       </c>
       <c r="D5" t="n">
-        <v>105.513334513926</v>
+        <v>98.61655689159213</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.68434456978482</v>
+        <v>36.38749691020379</v>
       </c>
       <c r="C6" t="n">
-        <v>139.9550074743126</v>
+        <v>88.03037139669877</v>
       </c>
       <c r="D6" t="n">
-        <v>45.48437113775474</v>
+        <v>41.21769561509809</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>122.1686843164731</v>
+        <v>78.87066531607601</v>
       </c>
       <c r="D7" t="n">
-        <v>31.85967649821749</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>82.78096642209104</v>
+        <v>52.82293522699963</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15624642035802</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.571017310973149</v>
+        <v>5.790347959647687</v>
       </c>
       <c r="C2" t="n">
-        <v>8.135743225093318</v>
+        <v>3.389974822764236</v>
       </c>
       <c r="D2" t="n">
-        <v>21.86450312128071</v>
+        <v>24.00864010735575</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.99190933865455</v>
+        <v>22.14822820780804</v>
       </c>
       <c r="C3" t="n">
-        <v>36.62900684544849</v>
+        <v>19.67422399310608</v>
       </c>
       <c r="D3" t="n">
-        <v>93.60473486141214</v>
+        <v>104.3303285303085</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.3820073346058</v>
+        <v>43.85270645329653</v>
       </c>
       <c r="C4" t="n">
-        <v>131.1880004753885</v>
+        <v>78.43967807391167</v>
       </c>
       <c r="D4" t="n">
-        <v>160.5805449928338</v>
+        <v>180.7711682783737</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.17173339944774</v>
+        <v>44.10501561328796</v>
       </c>
       <c r="C5" t="n">
-        <v>191.3426275577034</v>
+        <v>122.1048707156971</v>
       </c>
       <c r="D5" t="n">
-        <v>129.737959116216</v>
+        <v>130.2288329683394</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.15856976866503</v>
+        <v>42.86801350593698</v>
       </c>
       <c r="C6" t="n">
-        <v>183.7890607212284</v>
+        <v>117.816596743547</v>
       </c>
       <c r="D6" t="n">
-        <v>63.23535137824131</v>
+        <v>59.16993413495527</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.87101550231194</v>
+        <v>29.40432548989622</v>
       </c>
       <c r="C7" t="n">
-        <v>157.5017841923158</v>
+        <v>103.0648557395344</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2669375645639</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C8" t="n">
-        <v>117.8293594637022</v>
+        <v>77.35681035612741</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>67.11718180083317</v>
+        <v>48.7015583645715</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>39.57424995818893</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>36.10868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.758711048933538</v>
+        <v>3.34579617607313</v>
       </c>
       <c r="C2" t="n">
-        <v>3.944662275663684</v>
+        <v>1.512873212244335</v>
       </c>
       <c r="D2" t="n">
-        <v>15.25635932399543</v>
+        <v>16.5728829953904</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.17353266394021</v>
+        <v>23.02689240310894</v>
       </c>
       <c r="C3" t="n">
-        <v>36.92843989524377</v>
+        <v>18.00034415736527</v>
       </c>
       <c r="D3" t="n">
-        <v>93.1384047018949</v>
+        <v>103.584200275081</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.03214529899544</v>
+        <v>49.02160811615598</v>
       </c>
       <c r="C4" t="n">
-        <v>130.0010675009542</v>
+        <v>75.38938795681682</v>
       </c>
       <c r="D4" t="n">
-        <v>171.1991281619673</v>
+        <v>192.6277353025624</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.6934423410303</v>
+        <v>46.43666641087414</v>
       </c>
       <c r="C5" t="n">
-        <v>232.4533126730386</v>
+        <v>144.7096116059799</v>
       </c>
       <c r="D5" t="n">
-        <v>136.3402124272758</v>
+        <v>141.8870869562703</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.87302005544945</v>
+        <v>36.46800022195202</v>
       </c>
       <c r="C6" t="n">
-        <v>214.8230874001744</v>
+        <v>147.7235770580176</v>
       </c>
       <c r="D6" t="n">
-        <v>61.14226527278711</v>
+        <v>57.80137783523521</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.084692344472483</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>159.8373619807189</v>
+        <v>107.1371452167502</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>84.11614329986671</v>
+        <v>60.91744504851459</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>30.17499743772996</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>25.19655482949439</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.006111470403733</v>
+        <v>4.946044933995431</v>
       </c>
       <c r="C2" t="n">
-        <v>6.292021036517808</v>
+        <v>7.738135404873359</v>
       </c>
       <c r="D2" t="n">
-        <v>14.7291608068149</v>
+        <v>19.53776106221577</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.59367962362884</v>
+        <v>17.3278469799562</v>
       </c>
       <c r="C3" t="n">
-        <v>26.35992585902686</v>
+        <v>11.61407534123977</v>
       </c>
       <c r="D3" t="n">
-        <v>84.86718029361553</v>
+        <v>94.46376410262809</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.78590655167874</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="C4" t="n">
-        <v>113.2053277766997</v>
+        <v>59.8188693674624</v>
       </c>
       <c r="D4" t="n">
-        <v>176.8913013511903</v>
+        <v>199.2771125034261</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.16101629015904</v>
+        <v>58.46307578789757</v>
       </c>
       <c r="C5" t="n">
-        <v>235.0304003966864</v>
+        <v>143.2124463570035</v>
       </c>
       <c r="D5" t="n">
-        <v>161.2766041151448</v>
+        <v>172.6648774844078</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.88939097125216</v>
+        <v>47.13468902859362</v>
       </c>
       <c r="C6" t="n">
-        <v>284.2169421271559</v>
+        <v>188.7400143937451</v>
       </c>
       <c r="D6" t="n">
-        <v>80.62406671586082</v>
+        <v>82.75740447718914</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.5287043486993</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="C7" t="n">
-        <v>220.8019309190373</v>
+        <v>154.507453694363</v>
       </c>
       <c r="D7" t="n">
-        <v>42.10028680121597</v>
+        <v>41.68108053150257</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>133.2673421129833</v>
+        <v>95.79894098040376</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>55.80155776168444</v>
+        <v>46.70468353413349</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.053816197284327</v>
+        <v>3.240749171718721</v>
       </c>
       <c r="C2" t="n">
-        <v>3.953498005001906</v>
+        <v>3.879866927183394</v>
       </c>
       <c r="D2" t="n">
-        <v>10.54397034361074</v>
+        <v>13.81220845104838</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91979978788802</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="C3" t="n">
-        <v>25.75124228239384</v>
+        <v>20.78850763742621</v>
       </c>
       <c r="D3" t="n">
-        <v>79.12886496229292</v>
+        <v>90.49259463894975</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.48036203147973</v>
+        <v>42.85721428119026</v>
       </c>
       <c r="C4" t="n">
-        <v>96.94562229896403</v>
+        <v>47.20930185411637</v>
       </c>
       <c r="D4" t="n">
-        <v>178.6653194527643</v>
+        <v>201.357435888725</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.13709449235862</v>
+        <v>64.47628047640929</v>
       </c>
       <c r="C5" t="n">
-        <v>233.3368856068607</v>
+        <v>134.8921345635118</v>
       </c>
       <c r="D5" t="n">
-        <v>178.3590141690393</v>
+        <v>193.306122966197</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.0478943199924</v>
+        <v>56.75483478250812</v>
       </c>
       <c r="C6" t="n">
-        <v>324.5491013130234</v>
+        <v>211.683458241993</v>
       </c>
       <c r="D6" t="n">
-        <v>95.35617276578846</v>
+        <v>103.4065039406123</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.67221943996858</v>
+        <v>20.78065365579224</v>
       </c>
       <c r="C7" t="n">
-        <v>277.2151175004676</v>
+        <v>198.4043387943506</v>
       </c>
       <c r="D7" t="n">
-        <v>47.37030847761284</v>
+        <v>47.72962813736718</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>171.7371259038945</v>
+        <v>126.257663504661</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>61.4593697812588</v>
+        <v>57.68749510154256</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.77932775072272</v>
+        <v>5.596943661911066</v>
       </c>
       <c r="C2" t="n">
-        <v>12.95317920983241</v>
+        <v>3.720823799095411</v>
       </c>
       <c r="D2" t="n">
-        <v>17.14622365467054</v>
+        <v>15.23770611761474</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.13654504634832</v>
+        <v>14.22061549601505</v>
       </c>
       <c r="C3" t="n">
-        <v>20.97994843975434</v>
+        <v>18.06906649666254</v>
       </c>
       <c r="D3" t="n">
-        <v>71.23070468162733</v>
+        <v>81.80903619488672</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.57947749187965</v>
+        <v>38.33921134624644</v>
       </c>
       <c r="C4" t="n">
-        <v>82.8300538073034</v>
+        <v>49.23857435879452</v>
       </c>
       <c r="D4" t="n">
-        <v>176.8657759108799</v>
+        <v>200.4385200375501</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.86711387369075</v>
+        <v>64.47628047640929</v>
       </c>
       <c r="C5" t="n">
-        <v>210.46216409791</v>
+        <v>113.440947225719</v>
       </c>
       <c r="D5" t="n">
-        <v>191.8335014098268</v>
+        <v>215.3463589265379</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.82275530055039</v>
+        <v>68.95108651236625</v>
       </c>
       <c r="C6" t="n">
-        <v>343.1453663268665</v>
+        <v>213.6557893798249</v>
       </c>
       <c r="D6" t="n">
-        <v>118.7021331727776</v>
+        <v>130.7373782791393</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.88908787161589</v>
+        <v>37.36924461445059</v>
       </c>
       <c r="C7" t="n">
-        <v>352.3728129990822</v>
+        <v>243.9780489731918</v>
       </c>
       <c r="D7" t="n">
-        <v>57.97023844036566</v>
+        <v>60.7250224984822</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.42692138262712</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>240.999426438507</v>
+        <v>183.3364750295706</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>112.7124904291678</v>
+        <v>95.96092935160446</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>43.70249905454677</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.75891633757857</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.797220193577415</v>
+        <v>4.28434698133308</v>
       </c>
       <c r="C2" t="n">
-        <v>6.520768251607315</v>
+        <v>2.034181243199391</v>
       </c>
       <c r="D2" t="n">
-        <v>18.90846078379357</v>
+        <v>8.208392555207581</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>3.913246349127786</v>
+      </c>
+      <c r="C2" t="n">
         <v>2.053816197284327</v>
       </c>
-      <c r="C2" t="n">
-        <v>7.668431317871836</v>
-      </c>
       <c r="D2" t="n">
-        <v>12.75584792127881</v>
+        <v>11.21450402561132</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.53339210304228</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="C3" t="n">
-        <v>32.3044082082413</v>
+        <v>19.70367642423349</v>
       </c>
       <c r="D3" t="n">
-        <v>78.40237166115028</v>
+        <v>87.85169331452583</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.77689089589127</v>
+        <v>50.33616829214247</v>
       </c>
       <c r="C4" t="n">
-        <v>119.6760268953904</v>
+        <v>70.11838453271569</v>
       </c>
       <c r="D4" t="n">
-        <v>180.1457949907685</v>
+        <v>206.6667274732918</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.3668391506856</v>
+        <v>41.82245220091413</v>
       </c>
       <c r="C5" t="n">
-        <v>301.5192636668017</v>
+        <v>175.8064701379976</v>
       </c>
       <c r="D5" t="n">
-        <v>174.284761196415</v>
+        <v>195.3923368377215</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.66418553188536</v>
+        <v>23.18495378349268</v>
       </c>
       <c r="C6" t="n">
-        <v>289.2483991114208</v>
+        <v>206.7325045694764</v>
       </c>
       <c r="D6" t="n">
-        <v>90.56622571676827</v>
+        <v>99.70335160019334</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.910702016642545</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>169.4791061841269</v>
+        <v>128.9358712418463</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>83.03131208667398</v>
+        <v>70.68092596724911</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>25.20146356801562</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>33.28124717396686</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>21.1890607007589</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.35653864755762</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.9264920953685</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.53116656572653</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.202681995431348</v>
+        <v>6.661158173314608</v>
       </c>
       <c r="C2" t="n">
-        <v>5.602834148136546</v>
+        <v>2.52701859073129</v>
       </c>
       <c r="D2" t="n">
-        <v>32.51548396465436</v>
+        <v>15.27893952119311</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.31602494977624</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="C3" t="n">
-        <v>16.42954783057037</v>
+        <v>5.203262832508095</v>
       </c>
       <c r="D3" t="n">
-        <v>19.02136176978195</v>
+        <v>10.35743827980385</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39664358861125</v>
+        <v>13.39951074075891</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13536937567065</v>
+        <v>70.1503797604437</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576075716307206</v>
+        <v>1.576413028324577</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.497386233154638</v>
+        <v>4.614214209960009</v>
       </c>
       <c r="C2" t="n">
-        <v>5.399612373357456</v>
+        <v>4.59850624669206</v>
       </c>
       <c r="D2" t="n">
-        <v>30.50977340487812</v>
+        <v>13.45779752981528</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.79417713947344</v>
+        <v>17.65182372235765</v>
       </c>
       <c r="C3" t="n">
-        <v>19.82148614874311</v>
+        <v>8.163232160812228</v>
       </c>
       <c r="D3" t="n">
-        <v>41.73409490753191</v>
+        <v>20.6854241284803</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.34529745445439</v>
+        <v>10.70792221021996</v>
       </c>
       <c r="C4" t="n">
-        <v>25.60201663134832</v>
+        <v>8.602073384610552</v>
       </c>
       <c r="D4" t="n">
-        <v>25.04045694451915</v>
+        <v>20.49692856926491</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>39.82655911818034</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43527972005641</v>
+        <v>15.44664142810605</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11261317505158</v>
+        <v>86.17599954627588</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249532572643456</v>
+        <v>3.251924511180222</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.977460860531329</v>
+        <v>4.863578126838698</v>
       </c>
       <c r="C2" t="n">
-        <v>9.36292785540183</v>
+        <v>5.432991795301848</v>
       </c>
       <c r="D2" t="n">
-        <v>27.04911274740812</v>
+        <v>27.41235939797944</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.69461971071701</v>
+        <v>16.74370709592935</v>
       </c>
       <c r="C3" t="n">
-        <v>20.51852701875834</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D3" t="n">
-        <v>56.45540173271283</v>
+        <v>26.64954143177967</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.39781310886498</v>
+        <v>24.28745645536184</v>
       </c>
       <c r="C4" t="n">
-        <v>39.25812719742145</v>
+        <v>15.68538307075129</v>
       </c>
       <c r="D4" t="n">
-        <v>40.30467025014855</v>
+        <v>26.06147455693583</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.59091430696535</v>
+        <v>9.915651812892786</v>
       </c>
       <c r="C5" t="n">
-        <v>29.30516897176729</v>
+        <v>11.48644813968768</v>
       </c>
       <c r="D5" t="n">
-        <v>31.63681976935347</v>
+        <v>30.18874190558942</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.93593402397924</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.82369599052563</v>
       </c>
     </row>
     <row r="11">
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72290644499124</v>
+        <v>16.74970518175311</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0097293144466</v>
+        <v>102.173201608694</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180726611247811</v>
+        <v>5.024911554525933</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.17421131200819</v>
+        <v>5.014767273292708</v>
       </c>
       <c r="C2" t="n">
-        <v>9.258862598751669</v>
+        <v>4.405101948955438</v>
       </c>
       <c r="D2" t="n">
-        <v>23.91341058004381</v>
+        <v>34.43283723104838</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8369731278328</v>
+        <v>16.75352457297182</v>
       </c>
       <c r="C3" t="n">
-        <v>29.46224860444678</v>
+        <v>18.23105486786327</v>
       </c>
       <c r="D3" t="n">
-        <v>64.45664552232434</v>
+        <v>41.55247158224626</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.90756115154733</v>
+        <v>28.97137475232337</v>
       </c>
       <c r="C4" t="n">
-        <v>45.49909735331843</v>
+        <v>26.77618688562751</v>
       </c>
       <c r="D4" t="n">
-        <v>58.49154647132072</v>
+        <v>32.9022925601276</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.35363446217388</v>
+        <v>23.34105166846792</v>
       </c>
       <c r="C5" t="n">
-        <v>52.62167694762905</v>
+        <v>21.27938148954962</v>
       </c>
       <c r="D5" t="n">
-        <v>38.28816046562561</v>
+        <v>32.88854809226815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.35096695650162</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>30.02773528209295</v>
+        <v>15.41638419978766</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68184129502858</v>
+        <v>37.95731148929444</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
         <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.56104526967722</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>46.09305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.91411459030757</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04105117055726</v>
+        <v>18.08908690071179</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6963814460164</v>
+        <v>118.0097573998817</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013683723519088</v>
+        <v>6.891080724080684</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.062292073724055</v>
+        <v>6.197773256910113</v>
       </c>
       <c r="C2" t="n">
-        <v>7.994371555681777</v>
+        <v>5.432991795301848</v>
       </c>
       <c r="D2" t="n">
-        <v>32.06878875922206</v>
+        <v>41.80576248994193</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.2689421177014</v>
+        <v>15.39871274111122</v>
       </c>
       <c r="C3" t="n">
-        <v>31.06740610089032</v>
+        <v>16.55717503212245</v>
       </c>
       <c r="D3" t="n">
-        <v>64.25538724295374</v>
+        <v>56.37686191637309</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.25818395068368</v>
+        <v>22.50067563363265</v>
       </c>
       <c r="C4" t="n">
-        <v>50.65523629602267</v>
+        <v>31.65154598491717</v>
       </c>
       <c r="D4" t="n">
-        <v>66.83836545282711</v>
+        <v>39.52614432068083</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.93576979306323</v>
+        <v>20.69033286700153</v>
       </c>
       <c r="C5" t="n">
-        <v>51.61538555077607</v>
+        <v>27.51347941151687</v>
       </c>
       <c r="D5" t="n">
-        <v>40.12893741108838</v>
+        <v>30.33600406122645</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.47801332097696</v>
+        <v>11.63272854762046</v>
       </c>
       <c r="C6" t="n">
-        <v>38.7220929509027</v>
+        <v>17.02645043475243</v>
       </c>
       <c r="D6" t="n">
-        <v>32.56358960216246</v>
+        <v>30.67176177607885</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>20.84054026575129</v>
+        <v>14.13323995033708</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.91876128692155</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5983,10 +5983,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -5997,10 +5997,10 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048213628352539</v>
+        <v>7.075897522312748</v>
       </c>
       <c r="C21" t="n">
-        <v>66.07700276580505</v>
+        <v>67.22102646197111</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405133517720337</v>
+        <v>5.306923141734561</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.417864669110647</v>
+        <v>5.580253950938871</v>
       </c>
       <c r="C2" t="n">
-        <v>5.473243451175968</v>
+        <v>3.612831551628263</v>
       </c>
       <c r="D2" t="n">
-        <v>27.06678420608456</v>
+        <v>36.1636584336355</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.66931525458484</v>
+        <v>19.41896959000191</v>
       </c>
       <c r="C3" t="n">
-        <v>31.15576339427253</v>
+        <v>19.68895020866978</v>
       </c>
       <c r="D3" t="n">
-        <v>75.66820430482291</v>
+        <v>79.00123776074084</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.36701907713484</v>
+        <v>27.61852641587127</v>
       </c>
       <c r="C4" t="n">
-        <v>67.52755234120836</v>
+        <v>38.09671966329748</v>
       </c>
       <c r="D4" t="n">
-        <v>84.99971623368884</v>
+        <v>60.92922602096554</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.07798434145878</v>
+        <v>28.51977080836985</v>
       </c>
       <c r="C5" t="n">
-        <v>76.40451508300804</v>
+        <v>47.09934611124073</v>
       </c>
       <c r="D5" t="n">
-        <v>55.49328898255097</v>
+        <v>38.31270415823178</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.65539086027615</v>
+        <v>21.45413258090555</v>
       </c>
       <c r="C6" t="n">
-        <v>64.24164277509429</v>
+        <v>33.24786775202249</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>41.32176087174825</v>
+        <v>20.60099382591507</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>24.11663235482289</v>
+        <v>19.19316761802514</v>
       </c>
       <c r="D8" t="n">
         <v>32.04424506661589</v>
@@ -6168,7 +6168,7 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
         <v>31.50624732468863</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.5935407549086</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.266122439104093</v>
+        <v>7.305390418732499</v>
       </c>
       <c r="C21" t="n">
-        <v>75.38602030570496</v>
+        <v>77.61977319903281</v>
       </c>
       <c r="D21" t="n">
-        <v>5.449591829328069</v>
+        <v>6.392216616390938</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.514075944126835</v>
+        <v>4.869468613064179</v>
       </c>
       <c r="C2" t="n">
-        <v>13.08669689760998</v>
+        <v>4.633849164044945</v>
       </c>
       <c r="D2" t="n">
-        <v>32.82964323001334</v>
+        <v>29.5633686179842</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.19531103988288</v>
+        <v>19.48769192929919</v>
       </c>
       <c r="C3" t="n">
-        <v>25.25545969174919</v>
+        <v>16.18411090450867</v>
       </c>
       <c r="D3" t="n">
-        <v>79.76209223153211</v>
+        <v>90.29133635957915</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.16580185549325</v>
+        <v>33.93607289269949</v>
       </c>
       <c r="C4" t="n">
-        <v>73.61536985524283</v>
+        <v>44.96306310679967</v>
       </c>
       <c r="D4" t="n">
-        <v>103.8630166230871</v>
+        <v>88.19039627249097</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.86462629446773</v>
+        <v>35.85833489761475</v>
       </c>
       <c r="C5" t="n">
-        <v>103.5498391054324</v>
+        <v>60.91744504851459</v>
       </c>
       <c r="D5" t="n">
-        <v>73.48381566287377</v>
+        <v>52.27806525114266</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.3497485290859</v>
+        <v>31.43654323768712</v>
       </c>
       <c r="C6" t="n">
-        <v>94.51088799243196</v>
+        <v>56.59382815901164</v>
       </c>
       <c r="D6" t="n">
-        <v>46.61141750223008</v>
+        <v>38.48058301565798</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="C7" t="n">
-        <v>69.46846755250429</v>
+        <v>36.4110588551057</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>40.80634332701867</v>
+        <v>24.20008090968387</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.29062268265283</v>
+        <v>24.4062479275757</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>22.12466626290612</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.470819171349954</v>
+        <v>7.524227637473119</v>
       </c>
       <c r="C21" t="n">
-        <v>84.04671567768699</v>
+        <v>87.469146285625</v>
       </c>
       <c r="D21" t="n">
-        <v>6.53696677493121</v>
+        <v>7.524227637473119</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497634995303</v>
+        <v>10.84497621975275</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907200371703</v>
+        <v>37.78907155003716</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.041675371934871</v>
+        <v>6.301838513560276</v>
       </c>
       <c r="C2" t="n">
-        <v>6.078000036992003</v>
+        <v>10.04229726674062</v>
       </c>
       <c r="D2" t="n">
-        <v>42.91121040492384</v>
+        <v>24.1627744969225</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.14760631300229</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="C3" t="n">
-        <v>17.24439842509522</v>
+        <v>37.85619147575701</v>
       </c>
       <c r="D3" t="n">
-        <v>92.67698328089891</v>
+        <v>66.14034283510762</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.90153179660161</v>
+        <v>37.94356702143497</v>
       </c>
       <c r="C4" t="n">
-        <v>42.44880723622359</v>
+        <v>61.42697210701868</v>
       </c>
       <c r="D4" t="n">
-        <v>111.3930215146601</v>
+        <v>83.48095253521902</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.12955930589413</v>
+        <v>44.20319038371264</v>
       </c>
       <c r="C5" t="n">
-        <v>72.5511553438393</v>
+        <v>102.9853341754904</v>
       </c>
       <c r="D5" t="n">
-        <v>72.08482518432207</v>
+        <v>63.05274630525141</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.45291415348983</v>
+        <v>38.96360288614742</v>
       </c>
       <c r="C6" t="n">
-        <v>78.41022564278425</v>
+        <v>156.659444662072</v>
       </c>
       <c r="D6" t="n">
-        <v>45.72588107299945</v>
+        <v>45.08185457901354</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.62579956042849</v>
+        <v>25.27214940272139</v>
       </c>
       <c r="C7" t="n">
-        <v>60.7250224984822</v>
+        <v>168.4011472048639</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.0207398749762</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>37.1346069131356</v>
+        <v>116.4941825859265</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>27.73437264497238</v>
+        <v>57.79843259212245</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.18589447346791</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.730939431724142</v>
+        <v>7.643989832300453</v>
       </c>
       <c r="C21" t="n">
-        <v>96.63674289655178</v>
+        <v>92.68337671664298</v>
       </c>
       <c r="D21" t="n">
-        <v>8.697306860689659</v>
+        <v>7.643989832300453</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.516841260790327</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="C2" t="n">
-        <v>7.743044143394593</v>
+        <v>11.1408729477928</v>
       </c>
       <c r="D2" t="n">
-        <v>40.97422218444488</v>
+        <v>22.39268338616549</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.29134238844982</v>
+        <v>19.10481032464293</v>
       </c>
       <c r="C3" t="n">
-        <v>20.66578917439536</v>
+        <v>38.17525947963722</v>
       </c>
       <c r="D3" t="n">
-        <v>103.8492721552276</v>
+        <v>68.79597037509524</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.42931115085889</v>
+        <v>35.68456555396306</v>
       </c>
       <c r="C4" t="n">
-        <v>42.7678752401038</v>
+        <v>77.18893149870122</v>
       </c>
       <c r="D4" t="n">
-        <v>130.3839491056104</v>
+        <v>93.72941681985148</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.74377351585415</v>
+        <v>49.33282213840224</v>
       </c>
       <c r="C5" t="n">
-        <v>75.47185476397355</v>
+        <v>106.519625910779</v>
       </c>
       <c r="D5" t="n">
-        <v>92.38245896962486</v>
+        <v>76.10999077173399</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.83154997215961</v>
+        <v>47.81896717845365</v>
       </c>
       <c r="C6" t="n">
-        <v>95.91969594802613</v>
+        <v>160.4431003142393</v>
       </c>
       <c r="D6" t="n">
-        <v>56.91584140600459</v>
+        <v>52.40765594810324</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.62686342359076</v>
+        <v>34.43480072645687</v>
       </c>
       <c r="C7" t="n">
-        <v>86.95535766054849</v>
+        <v>193.9128430474215</v>
       </c>
       <c r="D7" t="n">
-        <v>43.47767883027424</v>
+        <v>42.16017341117502</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.69800692218626</v>
+        <v>19.44351328260808</v>
       </c>
       <c r="C8" t="n">
-        <v>58.0801941832413</v>
+        <v>163.8929617469625</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.20468654856884</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>96.73749178566366</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>48.54251523648354</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
         <v>36.42774856607789</v>
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.923188896208778</v>
+        <v>7.814338148235011</v>
       </c>
       <c r="C21" t="n">
-        <v>105.9726514867924</v>
+        <v>100.6096036585258</v>
       </c>
       <c r="D21" t="n">
-        <v>9.903986120260972</v>
+        <v>8.791130416764387</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.392380286529235</v>
+        <v>7.087236676957724</v>
       </c>
       <c r="C2" t="n">
-        <v>8.645270283597412</v>
+        <v>13.78570126303371</v>
       </c>
       <c r="D2" t="n">
-        <v>31.94508854848696</v>
+        <v>23.89573912136737</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.28781630826034</v>
+        <v>19.65949777754238</v>
       </c>
       <c r="C3" t="n">
-        <v>25.18182861393069</v>
+        <v>40.05039759474863</v>
       </c>
       <c r="D3" t="n">
-        <v>109.9655603526852</v>
+        <v>69.57155106145022</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.50588747179015</v>
+        <v>34.9953786655818</v>
       </c>
       <c r="C4" t="n">
-        <v>46.5073522455799</v>
+        <v>83.94041046080653</v>
       </c>
       <c r="D4" t="n">
-        <v>146.6053664228805</v>
+        <v>103.1355415742402</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.56000676871075</v>
+        <v>50.53546307610458</v>
       </c>
       <c r="C5" t="n">
-        <v>76.23270923476484</v>
+        <v>120.1659189998096</v>
       </c>
       <c r="D5" t="n">
-        <v>113.88273369263</v>
+        <v>87.05647767408593</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.03659637362695</v>
+        <v>54.98376192404687</v>
       </c>
       <c r="C6" t="n">
-        <v>107.2706629045278</v>
+        <v>164.6695241810218</v>
       </c>
       <c r="D6" t="n">
-        <v>69.19259644761097</v>
+        <v>61.42402686390595</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.50815406683489</v>
+        <v>43.59745205019235</v>
       </c>
       <c r="C7" t="n">
-        <v>110.0715891047439</v>
+        <v>209.0042687571035</v>
       </c>
       <c r="D7" t="n">
-        <v>49.0471335564664</v>
+        <v>45.87314322863646</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.2097595180061</v>
+        <v>26.28629478120835</v>
       </c>
       <c r="C8" t="n">
-        <v>84.61683462903258</v>
+        <v>201.7786056538469</v>
       </c>
       <c r="D8" t="n">
-        <v>41.22358610132356</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.30781111524376</v>
+        <v>13.42343636016663</v>
       </c>
       <c r="C9" t="n">
-        <v>52.80624551602742</v>
+        <v>140.55780056472</v>
       </c>
       <c r="D9" t="n">
-        <v>37.38593432542277</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>37.72365553568369</v>
+        <v>73.88142348309373</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>42.11403126907541</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.382120841130262</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.100837108259562</v>
+        <v>7.96872602886142</v>
       </c>
       <c r="C21" t="n">
-        <v>114.4243241541663</v>
+        <v>107.5778013896292</v>
       </c>
       <c r="D21" t="n">
-        <v>11.1386510238569</v>
+        <v>9.960907536076775</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.319330045787471</v>
+        <v>6.581636609270617</v>
       </c>
       <c r="C2" t="n">
-        <v>5.670574739729576</v>
+        <v>9.594620313604079</v>
       </c>
       <c r="D2" t="n">
-        <v>25.93384735538374</v>
+        <v>19.78417973598172</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.94130042639022</v>
+        <v>23.69448084199677</v>
       </c>
       <c r="C3" t="n">
-        <v>37.09533700496573</v>
+        <v>59.56263321665398</v>
       </c>
       <c r="D3" t="n">
-        <v>120.4555345725624</v>
+        <v>75.63384313517427</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.28745645536184</v>
+        <v>24.27469373520663</v>
       </c>
       <c r="C4" t="n">
-        <v>65.28131359389165</v>
+        <v>104.2969491083641</v>
       </c>
       <c r="D4" t="n">
-        <v>137.4672587917511</v>
+        <v>98.60477591914113</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.12769362147687</v>
+        <v>30.97414006898687</v>
       </c>
       <c r="C5" t="n">
-        <v>64.08358139471056</v>
+        <v>98.3956636581366</v>
       </c>
       <c r="D5" t="n">
-        <v>73.0420291959627</v>
+        <v>60.08295949990481</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.10823859384119</v>
+        <v>27.04911274740813</v>
       </c>
       <c r="C6" t="n">
-        <v>72.49323222928874</v>
+        <v>137.6606630894878</v>
       </c>
       <c r="D6" t="n">
-        <v>32.28182801104362</v>
+        <v>30.18874190558942</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>59.46740368934205</v>
+        <v>141.8713789930023</v>
       </c>
       <c r="D7" t="n">
-        <v>28.98511922018283</v>
+        <v>27.78738702100172</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>38.88702656521616</v>
+        <v>103.5596565824748</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>26.45319189093031</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>28.73281006019139</v>
+        <v>56.35624521458389</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.8983245115816</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.603594911662541</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.867505117655686</v>
+        <v>3.901465376676824</v>
       </c>
       <c r="C2" t="n">
-        <v>3.038509144643878</v>
+        <v>4.967643383488861</v>
       </c>
       <c r="D2" t="n">
-        <v>18.29290497323082</v>
+        <v>14.16269238146448</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.57238427377167</v>
+        <v>23.79265561242145</v>
       </c>
       <c r="C3" t="n">
-        <v>29.69786805346602</v>
+        <v>49.48990177108171</v>
       </c>
       <c r="D3" t="n">
-        <v>115.8069591929537</v>
+        <v>74.37720607373835</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.9953786655818</v>
+        <v>33.02991976167969</v>
       </c>
       <c r="C4" t="n">
-        <v>81.68140899333463</v>
+        <v>128.9417617280718</v>
       </c>
       <c r="D4" t="n">
-        <v>161.5887998850953</v>
+        <v>111.6099877572986</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.95650966803944</v>
+        <v>34.72932503773092</v>
       </c>
       <c r="C5" t="n">
-        <v>92.35791527701869</v>
+        <v>141.273494641116</v>
       </c>
       <c r="D5" t="n">
-        <v>98.61655689159213</v>
+        <v>74.31830121148356</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.38749691020379</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="C6" t="n">
-        <v>88.03037139669877</v>
+        <v>152.4732724511637</v>
       </c>
       <c r="D6" t="n">
-        <v>41.21769561509809</v>
+        <v>36.58875518957439</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>16.10949807898591</v>
       </c>
       <c r="C7" t="n">
-        <v>78.87066531607601</v>
+        <v>170.3175187235536</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>30.12296480940488</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>52.82293522699963</v>
+        <v>132.1825108997905</v>
       </c>
       <c r="D8" t="n">
-        <v>28.78975142703771</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.215624642035802</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>60.4609323660398</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.790347959647687</v>
+        <v>3.61675854244525</v>
       </c>
       <c r="C2" t="n">
-        <v>3.389974822764236</v>
+        <v>7.532950134685777</v>
       </c>
       <c r="D2" t="n">
-        <v>24.00864010735575</v>
+        <v>17.37791611287279</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.14822820780804</v>
+        <v>18.55994034878595</v>
       </c>
       <c r="C3" t="n">
-        <v>19.67422399310608</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D3" t="n">
-        <v>104.3303285303085</v>
+        <v>68.89414514551991</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.85270645329653</v>
+        <v>38.79866927183395</v>
       </c>
       <c r="C4" t="n">
-        <v>78.43967807391167</v>
+        <v>126.1212005737707</v>
       </c>
       <c r="D4" t="n">
-        <v>180.7711682783737</v>
+        <v>121.5521467582061</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.10501561328796</v>
+        <v>41.1843161931537</v>
       </c>
       <c r="C5" t="n">
-        <v>122.1048707156971</v>
+        <v>186.4584327290755</v>
       </c>
       <c r="D5" t="n">
-        <v>130.2288329683394</v>
+        <v>93.60964359993338</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.86801350593698</v>
+        <v>38.27932473628739</v>
       </c>
       <c r="C6" t="n">
-        <v>117.816596743547</v>
+        <v>186.7274316000391</v>
       </c>
       <c r="D6" t="n">
-        <v>59.16993413495527</v>
+        <v>48.38249036069132</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.40432548989622</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="C7" t="n">
-        <v>103.0648557395344</v>
+        <v>193.4936367777081</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>77.35681035612741</v>
+        <v>174.5743767691678</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54217107911827</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>48.7015583645715</v>
+        <v>103.393741220457</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>36.30012136452581</v>
+        <v>48.40016181936776</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>30.74146586308036</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>29.50740899884213</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>20.03256190515617</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.34579617607313</v>
+        <v>2.202060100625596</v>
       </c>
       <c r="C2" t="n">
-        <v>1.512873212244335</v>
+        <v>3.631484758008952</v>
       </c>
       <c r="D2" t="n">
-        <v>16.5728829953904</v>
+        <v>12.13341987678633</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.02689240310894</v>
+        <v>17.81872083207961</v>
       </c>
       <c r="C3" t="n">
-        <v>18.00034415736527</v>
+        <v>34.35135217159589</v>
       </c>
       <c r="D3" t="n">
-        <v>103.584200275081</v>
+        <v>69.21812188792136</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.02160811615598</v>
+        <v>42.33394275482671</v>
       </c>
       <c r="C4" t="n">
-        <v>75.38938795681682</v>
+        <v>124.1429789497134</v>
       </c>
       <c r="D4" t="n">
-        <v>192.6277353025624</v>
+        <v>129.1204398102448</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.43666641087414</v>
+        <v>42.19060759000669</v>
       </c>
       <c r="C5" t="n">
-        <v>144.7096116059799</v>
+        <v>226.1946710584652</v>
       </c>
       <c r="D5" t="n">
-        <v>141.8870869562703</v>
+        <v>99.15651812892787</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.46800022195202</v>
+        <v>30.02773528209295</v>
       </c>
       <c r="C6" t="n">
-        <v>147.7235770580176</v>
+        <v>225.2482662715712</v>
       </c>
       <c r="D6" t="n">
-        <v>57.80137783523521</v>
+        <v>47.17494068446774</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.306166415004762</v>
       </c>
       <c r="C7" t="n">
-        <v>107.1371452167502</v>
+        <v>211.0404134957113</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>3.67173641388307</v>
       </c>
       <c r="C8" t="n">
-        <v>60.91744504851459</v>
+        <v>127.5093918275757</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>27.62343515439249</v>
+        <v>36.94218436310322</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>22.91890015564179</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.50125647070939</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>22.7451308119901</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.946044933995431</v>
+        <v>2.863758053287946</v>
       </c>
       <c r="C2" t="n">
-        <v>7.738135404873359</v>
+        <v>3.966260725157114</v>
       </c>
       <c r="D2" t="n">
-        <v>19.53776106221577</v>
+        <v>15.92591125829176</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3278469799562</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C3" t="n">
-        <v>11.61407534123977</v>
+        <v>24.1166323548229</v>
       </c>
       <c r="D3" t="n">
-        <v>94.46376410262809</v>
+        <v>63.57798132702344</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.22206457427158</v>
+        <v>38.79866927183395</v>
       </c>
       <c r="C4" t="n">
-        <v>59.8188693674624</v>
+        <v>106.6963404975434</v>
       </c>
       <c r="D4" t="n">
-        <v>199.2771125034261</v>
+        <v>133.0003067374281</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.46307578789757</v>
+        <v>50.85453107998479</v>
       </c>
       <c r="C5" t="n">
-        <v>143.2124463570035</v>
+        <v>229.0662830933871</v>
       </c>
       <c r="D5" t="n">
-        <v>172.6648774844078</v>
+        <v>117.6133749687679</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.13468902859362</v>
+        <v>39.68813269188156</v>
       </c>
       <c r="C6" t="n">
-        <v>188.7400143937451</v>
+        <v>284.2169421271559</v>
       </c>
       <c r="D6" t="n">
-        <v>82.75740447718914</v>
+        <v>62.51082157250717</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>16.10949807898591</v>
       </c>
       <c r="C7" t="n">
-        <v>154.507453694363</v>
+        <v>262.4830114505399</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>95.79894098040376</v>
+        <v>187.0082114434537</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>46.70468353413349</v>
+        <v>78.21093085882212</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.240749171718721</v>
+        <v>1.915389770985527</v>
       </c>
       <c r="C2" t="n">
-        <v>3.879866927183394</v>
+        <v>2.265873701401639</v>
       </c>
       <c r="D2" t="n">
-        <v>13.81220845104838</v>
+        <v>12.18152551429442</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.35729941108361</v>
+        <v>11.71715885018568</v>
       </c>
       <c r="C3" t="n">
-        <v>20.78850763742621</v>
+        <v>20.70996782108647</v>
       </c>
       <c r="D3" t="n">
-        <v>90.49259463894975</v>
+        <v>62.01700247727101</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.85721428119026</v>
+        <v>34.42105625859742</v>
       </c>
       <c r="C4" t="n">
-        <v>47.20930185411637</v>
+        <v>89.61982092987432</v>
       </c>
       <c r="D4" t="n">
-        <v>201.357435888725</v>
+        <v>134.2638160327938</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.47628047640929</v>
+        <v>55.14967728606459</v>
       </c>
       <c r="C5" t="n">
-        <v>134.8921345635118</v>
+        <v>224.8202242725196</v>
       </c>
       <c r="D5" t="n">
-        <v>193.306122966197</v>
+        <v>130.8669689760999</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.75483478250812</v>
+        <v>46.0478943199924</v>
       </c>
       <c r="C6" t="n">
-        <v>211.683458241993</v>
+        <v>322.6572734869397</v>
       </c>
       <c r="D6" t="n">
-        <v>103.4065039406123</v>
+        <v>72.97625209977816</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.78065365579224</v>
+        <v>14.3727863901733</v>
       </c>
       <c r="C7" t="n">
-        <v>198.4043387943506</v>
+        <v>316.500733633608</v>
       </c>
       <c r="D7" t="n">
-        <v>47.72962813736718</v>
+        <v>41.32176087174825</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>126.257663504661</v>
+        <v>231.4028426294944</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>57.68749510154256</v>
+        <v>84.97811778419538</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.596943661911066</v>
+        <v>2.581014714464864</v>
       </c>
       <c r="C2" t="n">
-        <v>3.720823799095411</v>
+        <v>3.677626900108552</v>
       </c>
       <c r="D2" t="n">
-        <v>15.23770611761474</v>
+        <v>15.58033606639688</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.22061549601505</v>
+        <v>9.267698328089891</v>
       </c>
       <c r="C3" t="n">
-        <v>18.06906649666254</v>
+        <v>15.42816517223863</v>
       </c>
       <c r="D3" t="n">
-        <v>81.80903619488672</v>
+        <v>58.02128932098649</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.33921134624644</v>
+        <v>28.76717122984004</v>
       </c>
       <c r="C4" t="n">
-        <v>49.23857435879452</v>
+        <v>73.32182729167303</v>
       </c>
       <c r="D4" t="n">
-        <v>200.4385200375501</v>
+        <v>132.5153233715302</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.47628047640929</v>
+        <v>53.70159942230054</v>
       </c>
       <c r="C5" t="n">
-        <v>113.440947225719</v>
+        <v>199.9820073550753</v>
       </c>
       <c r="D5" t="n">
-        <v>215.3463589265379</v>
+        <v>143.9978445204009</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.95108651236625</v>
+        <v>56.11080828852221</v>
       </c>
       <c r="C6" t="n">
-        <v>213.6557893798249</v>
+        <v>336.8661080105039</v>
       </c>
       <c r="D6" t="n">
-        <v>130.7373782791393</v>
+        <v>89.68068928753766</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.36924461445059</v>
+        <v>27.12863431145211</v>
       </c>
       <c r="C7" t="n">
-        <v>243.9780489731918</v>
+        <v>374.0517658042602</v>
       </c>
       <c r="D7" t="n">
-        <v>60.7250224984822</v>
+        <v>48.80758711663017</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>183.3364750295706</v>
+        <v>301.0823859384118</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>95.96092935160446</v>
+        <v>155.5343617930051</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>54.52135875534661</v>
       </c>
       <c r="D10" t="n">
-        <v>27.75891633757857</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.28434698133308</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C2" t="n">
-        <v>2.034181243199391</v>
+        <v>16.04372098280137</v>
       </c>
       <c r="D2" t="n">
-        <v>8.208392555207581</v>
+        <v>7.829437941368313</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.913246349127786</v>
+        <v>1.88691908756237</v>
       </c>
       <c r="C2" t="n">
-        <v>2.053816197284327</v>
+        <v>2.148063976892021</v>
       </c>
       <c r="D2" t="n">
-        <v>11.21450402561132</v>
+        <v>11.59149514404209</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.54659679155399</v>
+        <v>12.4976482750619</v>
       </c>
       <c r="C3" t="n">
-        <v>19.70367642423349</v>
+        <v>17.72054606165493</v>
       </c>
       <c r="D3" t="n">
-        <v>87.85169331452583</v>
+        <v>63.9755891472434</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.33616829214247</v>
+        <v>40.48334833232148</v>
       </c>
       <c r="C4" t="n">
-        <v>70.11838453271569</v>
+        <v>107.0919848223548</v>
       </c>
       <c r="D4" t="n">
-        <v>206.6667274732918</v>
+        <v>135.0040538017959</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.82245220091413</v>
+        <v>32.10314992887071</v>
       </c>
       <c r="C5" t="n">
-        <v>175.8064701379976</v>
+        <v>291.7508740095459</v>
       </c>
       <c r="D5" t="n">
-        <v>195.3923368377215</v>
+        <v>130.9896874391307</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.18495378349268</v>
+        <v>16.82519215538184</v>
       </c>
       <c r="C6" t="n">
-        <v>206.7325045694764</v>
+        <v>305.7918296756839</v>
       </c>
       <c r="D6" t="n">
-        <v>99.70335160019334</v>
+        <v>71.00392096194632</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.246279805045708</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>128.9358712418463</v>
+        <v>211.699166205261</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>70.68092596724911</v>
+        <v>114.574865824124</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>23.94973524510094</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>41.60155896745857</v>
       </c>
       <c r="D9" t="n">
-        <v>21.1890607007589</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.06125357275758</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>18.79065105928395</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.41424077792992</v>
+        <v>14.74879576089983</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.661158173314608</v>
+        <v>6.182065293642165</v>
       </c>
       <c r="C2" t="n">
-        <v>2.52701859073129</v>
+        <v>6.179120050529424</v>
       </c>
       <c r="D2" t="n">
-        <v>15.27893952119311</v>
+        <v>15.95929068023615</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.105709956889166</v>
+        <v>10.56360529769568</v>
       </c>
       <c r="C3" t="n">
-        <v>5.203262832508095</v>
+        <v>40.42837046088366</v>
       </c>
       <c r="D3" t="n">
-        <v>10.35743827980385</v>
+        <v>9.714393533522189</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39951074075891</v>
+        <v>13.39705142259507</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1503797604437</v>
+        <v>70.13750450652715</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576413028324577</v>
+        <v>1.576123696775891</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.614214209960009</v>
+        <v>4.676064315327558</v>
       </c>
       <c r="C2" t="n">
-        <v>4.59850624669206</v>
+        <v>10.33289458719768</v>
       </c>
       <c r="D2" t="n">
-        <v>13.45779752981528</v>
+        <v>22.23658550119025</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.65182372235765</v>
+        <v>17.01859645311846</v>
       </c>
       <c r="C3" t="n">
-        <v>8.163232160812228</v>
+        <v>30.21328559819559</v>
       </c>
       <c r="D3" t="n">
-        <v>20.6854241284803</v>
+        <v>20.76887268334127</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.70792221021996</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="C4" t="n">
-        <v>8.602073384610552</v>
+        <v>62.14168443571036</v>
       </c>
       <c r="D4" t="n">
-        <v>20.49692856926491</v>
+        <v>20.16509784522949</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44664142810605</v>
+        <v>15.43625152363723</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17599954627588</v>
+        <v>86.11803481608139</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251924511180222</v>
+        <v>3.249737162870996</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.863578126838698</v>
+        <v>5.321072557017713</v>
       </c>
       <c r="C2" t="n">
-        <v>5.432991795301848</v>
+        <v>5.574363464713389</v>
       </c>
       <c r="D2" t="n">
-        <v>27.41235939797944</v>
+        <v>24.10386963466769</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.74370709592935</v>
+        <v>16.51790512395258</v>
       </c>
       <c r="C3" t="n">
-        <v>14.16661937228147</v>
+        <v>36.15285920888879</v>
       </c>
       <c r="D3" t="n">
-        <v>26.64954143177967</v>
+        <v>33.73775985644163</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.28745645536184</v>
+        <v>23.67484588791183</v>
       </c>
       <c r="C4" t="n">
-        <v>15.68538307075129</v>
+        <v>69.9779946110084</v>
       </c>
       <c r="D4" t="n">
-        <v>26.06147455693583</v>
+        <v>26.03594911662541</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.915651812892786</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C5" t="n">
-        <v>11.48644813968768</v>
+        <v>66.66066911835844</v>
       </c>
       <c r="D5" t="n">
-        <v>30.18874190558942</v>
+        <v>30.2132855981956</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.03524510636165</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.82369599052563</v>
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74970518175311</v>
+        <v>16.72089844565903</v>
       </c>
       <c r="C21" t="n">
-        <v>102.173201608694</v>
+        <v>101.1614355962371</v>
       </c>
       <c r="D21" t="n">
-        <v>5.024911554525933</v>
+        <v>4.180224611414758</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.014767273292708</v>
+        <v>6.223298697220531</v>
       </c>
       <c r="C2" t="n">
-        <v>4.405101948955438</v>
+        <v>5.544911033585985</v>
       </c>
       <c r="D2" t="n">
-        <v>34.43283723104838</v>
+        <v>20.58626761035137</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.75352457297182</v>
+        <v>17.5291052593268</v>
       </c>
       <c r="C3" t="n">
-        <v>18.23105486786327</v>
+        <v>27.88163480060942</v>
       </c>
       <c r="D3" t="n">
-        <v>41.55247158224626</v>
+        <v>44.55171081872026</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.97137475232337</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="C4" t="n">
-        <v>26.77618688562751</v>
+        <v>81.1964256274367</v>
       </c>
       <c r="D4" t="n">
-        <v>32.9022925601276</v>
+        <v>36.4886169237412</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.34105166846792</v>
+        <v>22.87472150895069</v>
       </c>
       <c r="C5" t="n">
-        <v>21.27938148954962</v>
+        <v>99.81919782929447</v>
       </c>
       <c r="D5" t="n">
-        <v>32.88854809226815</v>
+        <v>32.71674224402496</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.861655689159212</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="C6" t="n">
-        <v>15.41638419978766</v>
+        <v>59.53219903782235</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95731148929444</v>
+        <v>37.43403996293088</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>41.60155896745857</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.26838664282043</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
-        <v>46.09305471438775</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08908690071179</v>
+        <v>18.0319019900767</v>
       </c>
       <c r="C21" t="n">
-        <v>118.0097573998817</v>
+        <v>116.7780319357348</v>
       </c>
       <c r="D21" t="n">
-        <v>6.891080724080684</v>
+        <v>6.010633996692233</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.197773256910113</v>
+        <v>6.871252182023426</v>
       </c>
       <c r="C2" t="n">
-        <v>5.432991795301848</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="D2" t="n">
-        <v>41.80576248994193</v>
+        <v>24.96977110981337</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.39871274111122</v>
+        <v>17.38184310368978</v>
       </c>
       <c r="C3" t="n">
-        <v>16.55717503212245</v>
+        <v>22.81090790817464</v>
       </c>
       <c r="D3" t="n">
-        <v>56.37686191637309</v>
+        <v>46.8931790933489</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.50067563363265</v>
+        <v>22.5772519545639</v>
       </c>
       <c r="C4" t="n">
-        <v>31.65154598491717</v>
+        <v>61.93748091322701</v>
       </c>
       <c r="D4" t="n">
-        <v>39.52614432068083</v>
+        <v>42.47433267653401</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.69033286700153</v>
+        <v>19.46314823669302</v>
       </c>
       <c r="C5" t="n">
-        <v>27.51347941151687</v>
+        <v>93.65873098514572</v>
       </c>
       <c r="D5" t="n">
-        <v>30.33600406122645</v>
+        <v>30.92505268377453</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.63272854762046</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="C6" t="n">
-        <v>17.02645043475243</v>
+        <v>73.6605302496382</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>30.14849024971531</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>14.13323995033708</v>
+        <v>34.07548106670254</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.075897522312748</v>
+        <v>7.040857200889293</v>
       </c>
       <c r="C21" t="n">
-        <v>67.22102646197111</v>
+        <v>66.00803625833711</v>
       </c>
       <c r="D21" t="n">
-        <v>5.306923141734561</v>
+        <v>4.400535750555808</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.580253950938871</v>
+        <v>5.8787052530299</v>
       </c>
       <c r="C2" t="n">
-        <v>3.612831551628263</v>
+        <v>8.612872609357268</v>
       </c>
       <c r="D2" t="n">
-        <v>36.1636584336355</v>
+        <v>20.32119573020473</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.41896959000191</v>
+        <v>21.26956401250715</v>
       </c>
       <c r="C3" t="n">
-        <v>19.68895020866978</v>
+        <v>19.87057353395544</v>
       </c>
       <c r="D3" t="n">
-        <v>79.00123776074084</v>
+        <v>56.53394154905258</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.61852641587127</v>
+        <v>29.25215459573796</v>
       </c>
       <c r="C4" t="n">
-        <v>38.09671966329748</v>
+        <v>59.0786315984603</v>
       </c>
       <c r="D4" t="n">
-        <v>60.92922602096554</v>
+        <v>57.18974901548945</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.51977080836985</v>
+        <v>27.83254741539708</v>
       </c>
       <c r="C5" t="n">
-        <v>47.09934611124073</v>
+        <v>106.3478200625358</v>
       </c>
       <c r="D5" t="n">
-        <v>38.31270415823178</v>
+        <v>39.41717032550945</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.45413258090555</v>
+        <v>19.56230475482195</v>
       </c>
       <c r="C6" t="n">
-        <v>33.24786775202249</v>
+        <v>117.2530735613093</v>
       </c>
       <c r="D6" t="n">
-        <v>34.05290086950487</v>
+        <v>33.65038431076368</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.30049691295753</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>20.60099382591507</v>
+        <v>75.45712854840984</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>19.19316761802514</v>
+        <v>33.79666471869644</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>22.85312305945724</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
         <v>35.00617789032851</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.5935407549086</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.305390418732499</v>
+        <v>7.256073863931927</v>
       </c>
       <c r="C21" t="n">
-        <v>77.61977319903281</v>
+        <v>75.28176633829375</v>
       </c>
       <c r="D21" t="n">
-        <v>6.392216616390938</v>
+        <v>5.442055397948945</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.869468613064179</v>
+        <v>4.370740779306799</v>
       </c>
       <c r="C2" t="n">
-        <v>4.633849164044945</v>
+        <v>12.03328161095315</v>
       </c>
       <c r="D2" t="n">
-        <v>29.5633686179842</v>
+        <v>26.92344904126453</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.48769192929919</v>
+        <v>20.89159114637213</v>
       </c>
       <c r="C3" t="n">
-        <v>16.18411090450867</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D3" t="n">
-        <v>90.29133635957915</v>
+        <v>59.40064484545326</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.93607289269949</v>
+        <v>35.5952265128766</v>
       </c>
       <c r="C4" t="n">
-        <v>44.96306310679967</v>
+        <v>53.78210273404877</v>
       </c>
       <c r="D4" t="n">
-        <v>88.19039627249097</v>
+        <v>71.27979206683966</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.85833489761475</v>
+        <v>36.17740290149497</v>
       </c>
       <c r="C5" t="n">
-        <v>60.91744504851459</v>
+        <v>106.9368686850839</v>
       </c>
       <c r="D5" t="n">
-        <v>52.27806525114266</v>
+        <v>51.07542431344032</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.43654323768712</v>
+        <v>29.26295382048468</v>
       </c>
       <c r="C6" t="n">
-        <v>56.59382815901164</v>
+        <v>145.5499876408151</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.74450891718435</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="C7" t="n">
-        <v>36.4110588551057</v>
+        <v>125.8217675239755</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>24.20008090968387</v>
+        <v>68.34436643114171</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>24.4062479275757</v>
+        <v>33.39218466454675</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>22.12466626290612</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.524227637473119</v>
+        <v>7.457787539084732</v>
       </c>
       <c r="C21" t="n">
-        <v>87.469146285625</v>
+        <v>83.90010981470324</v>
       </c>
       <c r="D21" t="n">
-        <v>7.524227637473119</v>
+        <v>6.52556409669914</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497621975275</v>
+        <v>22.86156608971377</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907155003716</v>
+        <v>79.66060406260559</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.301838513560276</v>
+        <v>1.007273144557228</v>
       </c>
       <c r="C2" t="n">
-        <v>10.04229726674062</v>
+        <v>2.93640738340221</v>
       </c>
       <c r="D2" t="n">
-        <v>24.1627744969225</v>
+        <v>16.68283873826605</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.65673246087889</v>
+        <v>9.606401286055039</v>
       </c>
       <c r="C3" t="n">
-        <v>37.85619147575701</v>
+        <v>28.37250865273282</v>
       </c>
       <c r="D3" t="n">
-        <v>66.14034283510762</v>
+        <v>78.58890372495716</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.94356702143497</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="C4" t="n">
-        <v>61.42697210701868</v>
+        <v>89.50495644847746</v>
       </c>
       <c r="D4" t="n">
-        <v>83.48095253521902</v>
+        <v>87.0162260182118</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.20319038371264</v>
+        <v>15.16800203061322</v>
       </c>
       <c r="C5" t="n">
-        <v>102.9853341754904</v>
+        <v>96.13764393836894</v>
       </c>
       <c r="D5" t="n">
-        <v>63.05274630525141</v>
+        <v>52.79348279587224</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.96360288614742</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="C6" t="n">
-        <v>156.659444662072</v>
+        <v>60.01521890831177</v>
       </c>
       <c r="D6" t="n">
-        <v>45.08185457901354</v>
+        <v>30.14849024971531</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.27214940272139</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>168.4011472048639</v>
+        <v>34.49468733641593</v>
       </c>
       <c r="D7" t="n">
-        <v>38.38731698375453</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>116.4941825859265</v>
+        <v>28.45595720759379</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>57.79843259212245</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.643989832300453</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.68337671664298</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.643989832300453</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.42062998577414</v>
+        <v>1.750456156672063</v>
       </c>
       <c r="C2" t="n">
-        <v>11.1408729477928</v>
+        <v>5.01378552558846</v>
       </c>
       <c r="D2" t="n">
-        <v>22.39268338616549</v>
+        <v>23.54132820013427</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.10481032464293</v>
+        <v>6.268459091615885</v>
       </c>
       <c r="C3" t="n">
-        <v>38.17525947963722</v>
+        <v>18.25068982194821</v>
       </c>
       <c r="D3" t="n">
-        <v>68.79597037509524</v>
+        <v>74.45574589007809</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.68456555396306</v>
+        <v>18.07201173977529</v>
       </c>
       <c r="C4" t="n">
-        <v>77.18893149870122</v>
+        <v>79.72871280958772</v>
       </c>
       <c r="D4" t="n">
-        <v>93.72941681985148</v>
+        <v>105.7646619262131</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.33282213840224</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="C5" t="n">
-        <v>106.519625910779</v>
+        <v>134.2539985557513</v>
       </c>
       <c r="D5" t="n">
-        <v>76.10999077173399</v>
+        <v>70.98035901704441</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.81896717845365</v>
+        <v>15.57739082328414</v>
       </c>
       <c r="C6" t="n">
-        <v>160.4431003142393</v>
+        <v>109.6052589452267</v>
       </c>
       <c r="D6" t="n">
-        <v>52.40765594810324</v>
+        <v>38.9233512302733</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.43480072645687</v>
+        <v>9.102764713776425</v>
       </c>
       <c r="C7" t="n">
-        <v>193.9128430474215</v>
+        <v>61.62332164786803</v>
       </c>
       <c r="D7" t="n">
-        <v>42.16017341117502</v>
+        <v>31.62013005838127</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.44351328260808</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>163.8929617469625</v>
+        <v>37.96909246174539</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>96.73749178566366</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>48.54251523648354</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.50740899884213</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.814338148235011</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6096036585258</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.791130416764387</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.087236676957724</v>
+        <v>0.9149888603580273</v>
       </c>
       <c r="C2" t="n">
-        <v>13.78570126303371</v>
+        <v>2.029272504678157</v>
       </c>
       <c r="D2" t="n">
-        <v>23.89573912136737</v>
+        <v>15.91805727665778</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.65949777754238</v>
+        <v>6.720063035569417</v>
       </c>
       <c r="C3" t="n">
-        <v>40.05039759474863</v>
+        <v>20.18473279931442</v>
       </c>
       <c r="D3" t="n">
-        <v>69.57155106145022</v>
+        <v>77.96549393276045</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.9953786655818</v>
+        <v>19.64182631886593</v>
       </c>
       <c r="C4" t="n">
-        <v>83.94041046080653</v>
+        <v>73.47497993353554</v>
       </c>
       <c r="D4" t="n">
-        <v>103.1355415742402</v>
+        <v>117.7360934317987</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.53546307610458</v>
+        <v>20.51852701875834</v>
       </c>
       <c r="C5" t="n">
-        <v>120.1659189998096</v>
+        <v>156.0978849752429</v>
       </c>
       <c r="D5" t="n">
-        <v>87.05647767408593</v>
+        <v>81.92684591939634</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.98376192404687</v>
+        <v>12.63901994447344</v>
       </c>
       <c r="C6" t="n">
-        <v>164.6695241810218</v>
+        <v>143.2958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>61.42402686390595</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.59745205019235</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>209.0042687571035</v>
+        <v>61.50354842794993</v>
       </c>
       <c r="D7" t="n">
-        <v>45.87314322863646</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.28629478120835</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>201.7786056538469</v>
+        <v>39.30426933952106</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>140.55780056472</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>73.88142348309373</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>42.11403126907541</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.96872602886142</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.5778013896292</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.960907536076775</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.581636609270617</v>
+        <v>0.6813329067472864</v>
       </c>
       <c r="C2" t="n">
-        <v>9.594620313604079</v>
+        <v>4.787983553611694</v>
       </c>
       <c r="D2" t="n">
-        <v>19.78417973598172</v>
+        <v>16.04372098280137</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.69448084199677</v>
+        <v>4.864559874542945</v>
       </c>
       <c r="C3" t="n">
-        <v>59.56263321665398</v>
+        <v>13.15051049838602</v>
       </c>
       <c r="D3" t="n">
-        <v>75.63384313517427</v>
+        <v>72.72296119208248</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.27469373520663</v>
+        <v>16.56601076146068</v>
       </c>
       <c r="C4" t="n">
-        <v>104.2969491083641</v>
+        <v>61.36315850624264</v>
       </c>
       <c r="D4" t="n">
-        <v>98.60477591914113</v>
+        <v>130.7795934304219</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.97414006898687</v>
+        <v>25.13274122871835</v>
       </c>
       <c r="C5" t="n">
-        <v>98.3956636581366</v>
+        <v>146.7958254775043</v>
       </c>
       <c r="D5" t="n">
-        <v>60.08295949990481</v>
+        <v>103.0098778680966</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.04911274740813</v>
+        <v>19.44154978719959</v>
       </c>
       <c r="C6" t="n">
-        <v>137.6606630894878</v>
+        <v>198.6821733946525</v>
       </c>
       <c r="D6" t="n">
-        <v>30.18874190558942</v>
+        <v>53.49445065670446</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>141.8713789930023</v>
+        <v>131.0319025904133</v>
       </c>
       <c r="D7" t="n">
-        <v>27.78738702100172</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>103.5596565824748</v>
+        <v>59.08157684157305</v>
       </c>
       <c r="D8" t="n">
-        <v>26.45319189093031</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>56.35624521458389</v>
+        <v>37.27499683484289</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>24.00864010735575</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.901465376676824</v>
+        <v>0.3652101459798134</v>
       </c>
       <c r="C2" t="n">
-        <v>4.967643383488861</v>
+        <v>3.07483380970101</v>
       </c>
       <c r="D2" t="n">
-        <v>14.16269238146448</v>
+        <v>11.20566829627309</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.79265561242145</v>
+        <v>3.769911184307752</v>
       </c>
       <c r="C3" t="n">
-        <v>49.48990177108171</v>
+        <v>16.39518666092173</v>
       </c>
       <c r="D3" t="n">
-        <v>74.37720607373835</v>
+        <v>69.55191610736527</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.02991976167969</v>
+        <v>14.03899217072939</v>
       </c>
       <c r="C4" t="n">
-        <v>128.9417617280718</v>
+        <v>49.05989627662161</v>
       </c>
       <c r="D4" t="n">
-        <v>111.6099877572986</v>
+        <v>137.0078008661636</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.72932503773092</v>
+        <v>26.62990647769474</v>
       </c>
       <c r="C5" t="n">
-        <v>141.273494641116</v>
+        <v>137.1992416684918</v>
       </c>
       <c r="D5" t="n">
-        <v>74.31830121148356</v>
+        <v>121.810346404423</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.00006641992479</v>
+        <v>23.8692319333527</v>
       </c>
       <c r="C6" t="n">
-        <v>152.4732724511637</v>
+        <v>222.148888769264</v>
       </c>
       <c r="D6" t="n">
-        <v>36.58875518957439</v>
+        <v>66.05296728942966</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.10949807898591</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>170.3175187235536</v>
+        <v>189.9603267901238</v>
       </c>
       <c r="D7" t="n">
-        <v>30.12296480940488</v>
+        <v>41.68108053150257</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>132.1825108997905</v>
+        <v>91.45961612763286</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>60.4609323660398</v>
+        <v>48.03593342109217</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>34.02246669067321</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.61675854244525</v>
+        <v>1.22816637801276</v>
       </c>
       <c r="C2" t="n">
-        <v>7.532950134685777</v>
+        <v>5.931719629059228</v>
       </c>
       <c r="D2" t="n">
-        <v>17.37791611287279</v>
+        <v>15.4968875115359</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.55994034878595</v>
+        <v>2.488730430265664</v>
       </c>
       <c r="C3" t="n">
-        <v>34.16482010778901</v>
+        <v>14.10771451002667</v>
       </c>
       <c r="D3" t="n">
-        <v>68.89414514551991</v>
+        <v>63.48471529511999</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.79866927183395</v>
+        <v>10.79726125130642</v>
       </c>
       <c r="C4" t="n">
-        <v>126.1212005737707</v>
+        <v>44.88648678586841</v>
       </c>
       <c r="D4" t="n">
-        <v>121.5521467582061</v>
+        <v>139.9942773824824</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.1843161931537</v>
+        <v>24.71549845441346</v>
       </c>
       <c r="C5" t="n">
-        <v>186.4584327290755</v>
+        <v>114.1772580039041</v>
       </c>
       <c r="D5" t="n">
-        <v>93.60964359993338</v>
+        <v>138.6964069174682</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.27932473628739</v>
+        <v>29.3032054763588</v>
       </c>
       <c r="C6" t="n">
-        <v>186.7274316000391</v>
+        <v>223.4369417572358</v>
       </c>
       <c r="D6" t="n">
-        <v>48.38249036069132</v>
+        <v>85.69577535599986</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C7" t="n">
-        <v>193.4936367777081</v>
+        <v>250.4458028487698</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>49.94543270585223</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>174.5743767691678</v>
+        <v>163.5591675275186</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>42.14152020479433</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>103.393741220457</v>
+        <v>76.54686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>48.40016181936776</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>42.15820991576653</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.202060100625596</v>
+        <v>0.8148505945248526</v>
       </c>
       <c r="C2" t="n">
-        <v>3.631484758008952</v>
+        <v>3.036545649235384</v>
       </c>
       <c r="D2" t="n">
-        <v>12.13341987678633</v>
+        <v>11.15854440646924</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.81872083207961</v>
+        <v>4.084070449666732</v>
       </c>
       <c r="C3" t="n">
-        <v>34.35135217159589</v>
+        <v>19.64477156197868</v>
       </c>
       <c r="D3" t="n">
-        <v>69.21812188792136</v>
+        <v>69.11503837897546</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.33394275482671</v>
+        <v>17.17862132891069</v>
       </c>
       <c r="C4" t="n">
-        <v>124.1429789497134</v>
+        <v>64.24753326131977</v>
       </c>
       <c r="D4" t="n">
-        <v>129.1204398102448</v>
+        <v>144.4867548771158</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.19060759000669</v>
+        <v>18.33413837680919</v>
       </c>
       <c r="C5" t="n">
-        <v>226.1946710584652</v>
+        <v>179.905266803228</v>
       </c>
       <c r="D5" t="n">
-        <v>99.15651812892787</v>
+        <v>128.4125997154828</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.02773528209295</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>225.2482662715712</v>
+        <v>221.8671271781452</v>
       </c>
       <c r="D6" t="n">
-        <v>47.17494068446774</v>
+        <v>71.60769580005812</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>211.0404134957113</v>
+        <v>114.9822911213864</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>127.5093918275757</v>
+        <v>56.41122308602172</v>
       </c>
       <c r="D8" t="n">
-        <v>30.87596529856218</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>36.94218436310322</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>22.91890015564179</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>35.47545329295849</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.863758053287946</v>
+        <v>0.4034983064454391</v>
       </c>
       <c r="C2" t="n">
-        <v>3.966260725157114</v>
+        <v>1.731802950291373</v>
       </c>
       <c r="D2" t="n">
-        <v>15.92591125829176</v>
+        <v>8.348782476914876</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.93452600345173</v>
+        <v>3.421390749300135</v>
       </c>
       <c r="C3" t="n">
-        <v>24.1166323548229</v>
+        <v>15.31035544772901</v>
       </c>
       <c r="D3" t="n">
-        <v>63.57798132702344</v>
+        <v>62.23789571072654</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.79866927183395</v>
+        <v>11.85656702418873</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6963404975434</v>
+        <v>54.48405234258524</v>
       </c>
       <c r="D4" t="n">
-        <v>133.0003067374281</v>
+        <v>140.1346673041897</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.85453107998479</v>
+        <v>17.45056544298706</v>
       </c>
       <c r="C5" t="n">
-        <v>229.0662830933871</v>
+        <v>135.8493385751524</v>
       </c>
       <c r="D5" t="n">
-        <v>117.6133749687679</v>
+        <v>133.9840179370835</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.68813269188156</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>284.2169421271559</v>
+        <v>208.8658423308047</v>
       </c>
       <c r="D6" t="n">
-        <v>62.51082157250717</v>
+        <v>77.76619914879835</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.10949807898591</v>
+        <v>3.832743037379548</v>
       </c>
       <c r="C7" t="n">
-        <v>262.4830114505399</v>
+        <v>151.8125562462055</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>187.0082114434537</v>
+        <v>63.25400458462199</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>78.21093085882212</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>18.64829764216817</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.915389770985527</v>
+        <v>0.7294385442553801</v>
       </c>
       <c r="C2" t="n">
-        <v>2.265873701401639</v>
+        <v>7.612471698729768</v>
       </c>
       <c r="D2" t="n">
-        <v>12.18152551429442</v>
+        <v>17.76668820375453</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.71715885018568</v>
+        <v>2.30219836645877</v>
       </c>
       <c r="C3" t="n">
-        <v>20.70996782108647</v>
+        <v>10.11200135374215</v>
       </c>
       <c r="D3" t="n">
-        <v>62.01700247727101</v>
+        <v>54.47718010865552</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.42105625859742</v>
+        <v>9.087056750508477</v>
       </c>
       <c r="C4" t="n">
-        <v>89.61982092987432</v>
+        <v>45.02687670757571</v>
       </c>
       <c r="D4" t="n">
-        <v>134.2638160327938</v>
+        <v>140.032565542948</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.14967728606459</v>
+        <v>18.11324514335366</v>
       </c>
       <c r="C5" t="n">
-        <v>224.8202242725196</v>
+        <v>117.3188506574939</v>
       </c>
       <c r="D5" t="n">
-        <v>130.8669689760999</v>
+        <v>154.6252634188727</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.0478943199924</v>
+        <v>17.26796036999715</v>
       </c>
       <c r="C6" t="n">
-        <v>322.6572734869397</v>
+        <v>213.7362926915731</v>
       </c>
       <c r="D6" t="n">
-        <v>72.97625209977816</v>
+        <v>101.1926628675358</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.3727863901733</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>316.500733633608</v>
+        <v>234.2165315498658</v>
       </c>
       <c r="D7" t="n">
-        <v>41.32176087174825</v>
+        <v>49.64599965605695</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>231.4028426294944</v>
+        <v>135.0197617650638</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>84.97811778419538</v>
+        <v>54.80312034646543</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>17.59193711239859</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.581014714464864</v>
+        <v>0.8776824475966484</v>
       </c>
       <c r="C2" t="n">
-        <v>3.677626900108552</v>
+        <v>4.683918296961532</v>
       </c>
       <c r="D2" t="n">
-        <v>15.58033606639688</v>
+        <v>17.79221364406494</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.267698328089891</v>
+        <v>2.390555659840983</v>
       </c>
       <c r="C3" t="n">
-        <v>15.42816517223863</v>
+        <v>20.90631736193583</v>
       </c>
       <c r="D3" t="n">
-        <v>58.02128932098649</v>
+        <v>55.67491230783661</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.76717122984004</v>
+        <v>6.700428081484481</v>
       </c>
       <c r="C4" t="n">
-        <v>73.32182729167303</v>
+        <v>34.37000537797658</v>
       </c>
       <c r="D4" t="n">
-        <v>132.5153233715302</v>
+        <v>134.6977485180709</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.70159942230054</v>
+        <v>16.10066234964769</v>
       </c>
       <c r="C5" t="n">
-        <v>199.9820073550753</v>
+        <v>98.3956636581366</v>
       </c>
       <c r="D5" t="n">
-        <v>143.9978445204009</v>
+        <v>169.7196343716674</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.11080828852221</v>
+        <v>21.09186767803848</v>
       </c>
       <c r="C6" t="n">
-        <v>336.8661080105039</v>
+        <v>201.0167694353514</v>
       </c>
       <c r="D6" t="n">
-        <v>89.68068928753766</v>
+        <v>124.6593782421473</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.12863431145211</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="C7" t="n">
-        <v>374.0517658042602</v>
+        <v>274.3405602224329</v>
       </c>
       <c r="D7" t="n">
-        <v>48.80758711663017</v>
+        <v>64.43799231594365</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.260024272905162</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>301.0823859384118</v>
+        <v>223.0579871433965</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>155.5343617930051</v>
+        <v>109.7171781835107</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>54.52135875534661</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.970588626601601</v>
+        <v>3.334015203622168</v>
       </c>
       <c r="C2" t="n">
-        <v>16.04372098280137</v>
+        <v>6.036766633413637</v>
       </c>
       <c r="D2" t="n">
-        <v>7.829437941368313</v>
+        <v>11.7721367216235</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.88691908756237</v>
+        <v>0.7451465075233291</v>
       </c>
       <c r="C2" t="n">
-        <v>2.148063976892021</v>
+        <v>7.760715602071037</v>
       </c>
       <c r="D2" t="n">
-        <v>11.59149514404209</v>
+        <v>15.35551584212436</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.4976482750619</v>
+        <v>2.64090132442392</v>
       </c>
       <c r="C3" t="n">
-        <v>17.72054606165493</v>
+        <v>19.39933463591697</v>
       </c>
       <c r="D3" t="n">
-        <v>63.9755891472434</v>
+        <v>56.46031047123407</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.48334833232148</v>
+        <v>5.590071427981338</v>
       </c>
       <c r="C4" t="n">
-        <v>107.0919848223548</v>
+        <v>43.24009588584652</v>
       </c>
       <c r="D4" t="n">
-        <v>135.0040538017959</v>
+        <v>132.2345435281156</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.10314992887071</v>
+        <v>13.59720570381833</v>
       </c>
       <c r="C5" t="n">
-        <v>291.7508740095459</v>
+        <v>81.4605157598791</v>
       </c>
       <c r="D5" t="n">
-        <v>130.9896874391307</v>
+        <v>176.6409556866074</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.82519215538184</v>
+        <v>21.53463589265379</v>
       </c>
       <c r="C6" t="n">
-        <v>305.7918296756839</v>
+        <v>179.60288851032</v>
       </c>
       <c r="D6" t="n">
-        <v>71.00392096194632</v>
+        <v>146.5562790376681</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.790928796724434</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C7" t="n">
-        <v>211.699166205261</v>
+        <v>285.1201500150629</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>80.90681005468389</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>114.574865824124</v>
+        <v>289.9837281419016</v>
       </c>
       <c r="D8" t="n">
-        <v>23.94973524510094</v>
+        <v>43.72704274715294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60155896745857</v>
+        <v>183.6015469097172</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>82.70733534427255</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>22.63419332141022</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>36.25005223160922</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>19.90198946049134</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.182065293642165</v>
+        <v>4.606360228326034</v>
       </c>
       <c r="C2" t="n">
-        <v>6.179120050529424</v>
+        <v>7.210936887692822</v>
       </c>
       <c r="D2" t="n">
-        <v>15.95929068023615</v>
+        <v>22.93853510972672</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.56360529769568</v>
+        <v>5.51251335934584</v>
       </c>
       <c r="C3" t="n">
-        <v>40.42837046088366</v>
+        <v>11.91841712955628</v>
       </c>
       <c r="D3" t="n">
-        <v>9.714393533522189</v>
+        <v>11.04957041129785</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39705142259507</v>
+        <v>11.67828756403251</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13750450652715</v>
+        <v>59.94854282870023</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576123696775891</v>
+        <v>0.778552504268834</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.676064315327558</v>
+        <v>2.159844949342983</v>
       </c>
       <c r="C2" t="n">
-        <v>10.33289458719768</v>
+        <v>5.713771638716436</v>
       </c>
       <c r="D2" t="n">
-        <v>22.23658550119025</v>
+        <v>22.57823370226814</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.01859645311846</v>
+        <v>12.10985793188441</v>
       </c>
       <c r="C3" t="n">
-        <v>30.21328559819559</v>
+        <v>22.75200304591983</v>
       </c>
       <c r="D3" t="n">
-        <v>20.76887268334127</v>
+        <v>28.4559572075938</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.36707583039707</v>
+        <v>6.96844520474386</v>
       </c>
       <c r="C4" t="n">
-        <v>62.14168443571036</v>
+        <v>19.93536888243573</v>
       </c>
       <c r="D4" t="n">
-        <v>20.16509784522949</v>
+        <v>20.06299608398782</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43625152363723</v>
+        <v>13.62971119117843</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11803481608139</v>
+        <v>73.76078997578912</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249737162870996</v>
+        <v>1.603495434256285</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.321072557017713</v>
+        <v>2.934443887993716</v>
       </c>
       <c r="C2" t="n">
-        <v>5.574363464713389</v>
+        <v>4.718279466610171</v>
       </c>
       <c r="D2" t="n">
-        <v>24.10386963466769</v>
+        <v>25.53525778745954</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.51790512395258</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="C3" t="n">
-        <v>36.15285920888879</v>
+        <v>22.47711368873073</v>
       </c>
       <c r="D3" t="n">
-        <v>33.73775985644163</v>
+        <v>40.54618018539327</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.67484588791183</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="C4" t="n">
-        <v>69.9779946110084</v>
+        <v>43.24009588584652</v>
       </c>
       <c r="D4" t="n">
-        <v>26.03594911662541</v>
+        <v>30.31146036862027</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.06920536538279</v>
+        <v>6.847690237121504</v>
       </c>
       <c r="C5" t="n">
-        <v>66.66066911835844</v>
+        <v>24.42097414313941</v>
       </c>
       <c r="D5" t="n">
-        <v>30.2132855981956</v>
+        <v>26.97351817418112</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>20.06201433628357</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72089844565903</v>
+        <v>14.84188019736541</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1614355962371</v>
+        <v>87.40218338448517</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180224611414758</v>
+        <v>2.473646699560901</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.223298697220531</v>
+        <v>2.247220495020949</v>
       </c>
       <c r="C2" t="n">
-        <v>5.544911033585985</v>
+        <v>4.687845287778519</v>
       </c>
       <c r="D2" t="n">
-        <v>20.58626761035137</v>
+        <v>26.89792360095411</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5291052593268</v>
+        <v>9.891108120286615</v>
       </c>
       <c r="C3" t="n">
-        <v>27.88163480060942</v>
+        <v>19.95402208881642</v>
       </c>
       <c r="D3" t="n">
-        <v>44.55171081872026</v>
+        <v>51.56629816556372</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.75891633757857</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="C4" t="n">
-        <v>81.1964256274367</v>
+        <v>51.08916878129977</v>
       </c>
       <c r="D4" t="n">
-        <v>36.4886169237412</v>
+        <v>43.5081130091059</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.87472150895069</v>
+        <v>16.71425466480195</v>
       </c>
       <c r="C5" t="n">
-        <v>99.81919782929447</v>
+        <v>56.59775514982863</v>
       </c>
       <c r="D5" t="n">
-        <v>32.71674224402496</v>
+        <v>32.15223731408305</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.42517887139688</v>
+        <v>7.003788122096746</v>
       </c>
       <c r="C6" t="n">
-        <v>59.53219903782235</v>
+        <v>26.20382797405162</v>
       </c>
       <c r="D6" t="n">
-        <v>37.43403996293088</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.95250056176443</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0319019900767</v>
+        <v>16.08744751513785</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7780319357348</v>
+        <v>101.6049316745548</v>
       </c>
       <c r="D21" t="n">
-        <v>6.010633996692233</v>
+        <v>3.386831055818494</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.871252182023426</v>
+        <v>2.057743188101315</v>
       </c>
       <c r="C2" t="n">
-        <v>4.658392856651115</v>
+        <v>8.361545197070084</v>
       </c>
       <c r="D2" t="n">
-        <v>24.96977110981337</v>
+        <v>27.54195009494002</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.38184310368978</v>
+        <v>8.688467182584272</v>
       </c>
       <c r="C3" t="n">
-        <v>22.81090790817464</v>
+        <v>18.92318699935727</v>
       </c>
       <c r="D3" t="n">
-        <v>46.8931790933489</v>
+        <v>60.53947218237957</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.5772519545639</v>
+        <v>18.544232385518</v>
       </c>
       <c r="C4" t="n">
-        <v>61.93748091322701</v>
+        <v>50.45103277353934</v>
       </c>
       <c r="D4" t="n">
-        <v>42.47433267653401</v>
+        <v>58.27458022868218</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.46314823669302</v>
+        <v>22.16295442337175</v>
       </c>
       <c r="C5" t="n">
-        <v>93.65873098514572</v>
+        <v>77.41080647986101</v>
       </c>
       <c r="D5" t="n">
-        <v>30.92505268377453</v>
+        <v>40.57072387799944</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.10945702125691</v>
+        <v>14.81260936167588</v>
       </c>
       <c r="C6" t="n">
-        <v>73.6605302496382</v>
+        <v>59.77370897306707</v>
       </c>
       <c r="D6" t="n">
-        <v>30.14849024971531</v>
+        <v>36.66925850132262</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>7.60559946480004</v>
       </c>
       <c r="C7" t="n">
-        <v>34.07548106670254</v>
+        <v>28.26647990067416</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.040857200889293</v>
+        <v>17.3607885506583</v>
       </c>
       <c r="C21" t="n">
-        <v>66.00803625833711</v>
+        <v>115.4492438618777</v>
       </c>
       <c r="D21" t="n">
-        <v>4.400535750555808</v>
+        <v>4.340197137664575</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.8787052530299</v>
+        <v>2.327723806769188</v>
       </c>
       <c r="C2" t="n">
-        <v>8.612872609357268</v>
+        <v>7.999280294203011</v>
       </c>
       <c r="D2" t="n">
-        <v>20.32119573020473</v>
+        <v>31.48072188437822</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.26956401250715</v>
+        <v>7.770533079113505</v>
       </c>
       <c r="C3" t="n">
-        <v>19.87057353395544</v>
+        <v>26.41392198276044</v>
       </c>
       <c r="D3" t="n">
-        <v>56.53394154905258</v>
+        <v>67.48533718992574</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.25215459573796</v>
+        <v>17.66360469480861</v>
       </c>
       <c r="C4" t="n">
-        <v>59.0786315984603</v>
+        <v>48.7408282727414</v>
       </c>
       <c r="D4" t="n">
-        <v>57.18974901548945</v>
+        <v>73.06657288856887</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.83254741539708</v>
+        <v>24.93639168786899</v>
       </c>
       <c r="C5" t="n">
-        <v>106.3478200625358</v>
+        <v>85.58385611771571</v>
       </c>
       <c r="D5" t="n">
-        <v>39.41717032550945</v>
+        <v>51.68901662859458</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.56230475482195</v>
+        <v>22.29941735426205</v>
       </c>
       <c r="C6" t="n">
-        <v>117.2530735613093</v>
+        <v>91.37125883425065</v>
       </c>
       <c r="D6" t="n">
-        <v>33.65038431076368</v>
+        <v>41.0164373357275</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.82140403328509</v>
+        <v>12.39652826152447</v>
       </c>
       <c r="C7" t="n">
-        <v>75.45712854840984</v>
+        <v>56.47307319138927</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>33.79666471869644</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.85312305945724</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>43.98720588877834</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.256073863931927</v>
+        <v>18.65580222977887</v>
       </c>
       <c r="C21" t="n">
-        <v>75.28176633829375</v>
+        <v>128.8138725389494</v>
       </c>
       <c r="D21" t="n">
-        <v>5.442055397948945</v>
+        <v>5.33022920850825</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.370740779306799</v>
+        <v>2.099958339383927</v>
       </c>
       <c r="C2" t="n">
-        <v>12.03328161095315</v>
+        <v>4.862596379134452</v>
       </c>
       <c r="D2" t="n">
-        <v>26.92344904126453</v>
+        <v>24.68800951869454</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.89159114637213</v>
+        <v>11.21646752101981</v>
       </c>
       <c r="C3" t="n">
-        <v>27.83745615391831</v>
+        <v>39.1520984453628</v>
       </c>
       <c r="D3" t="n">
-        <v>59.40064484545326</v>
+        <v>75.08897315931729</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.5952265128766</v>
+        <v>11.9714315055856</v>
       </c>
       <c r="C4" t="n">
-        <v>53.78210273404877</v>
+        <v>73.60260713508762</v>
       </c>
       <c r="D4" t="n">
-        <v>71.27979206683966</v>
+        <v>67.6041286621396</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.17740290149497</v>
+        <v>12.541826921753</v>
       </c>
       <c r="C5" t="n">
-        <v>106.9368686850839</v>
+        <v>54.58517235612267</v>
       </c>
       <c r="D5" t="n">
-        <v>51.07542431344032</v>
+        <v>39.88350048502668</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.26295382048468</v>
+        <v>7.688066271956774</v>
       </c>
       <c r="C6" t="n">
-        <v>145.5499876408151</v>
+        <v>37.19253002768617</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>25.51954982419159</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.76825078853552</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>125.8217675239755</v>
+        <v>22.15804568485051</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>68.34436643114171</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.457787539084732</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>83.90010981470324</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.52556409669914</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="year_0" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="year_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="year_2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="year_3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="year_4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="year_5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="year_6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="year_7" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="year_8" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="year_9" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="year_10" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="year_11" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="year_12" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="year_13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="year_14" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="year_15" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="year_16" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="year_17" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="year_18" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="year_19" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_8" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_9" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_10" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_11" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_12" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_13" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_14" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_15" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_16" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_17" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_18" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_19" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.007273144557228</v>
+        <v>0.5821763886183585</v>
       </c>
       <c r="C2" t="n">
-        <v>2.93640738340221</v>
+        <v>2.745948328778329</v>
       </c>
       <c r="D2" t="n">
-        <v>16.68283873826605</v>
+        <v>14.24614093632546</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.606401286055039</v>
+        <v>6.175193059712438</v>
       </c>
       <c r="C3" t="n">
-        <v>28.37250865273282</v>
+        <v>26.18812001078367</v>
       </c>
       <c r="D3" t="n">
-        <v>78.58890372495716</v>
+        <v>71.32887945205201</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.92336692580652</v>
+        <v>11.69065166217102</v>
       </c>
       <c r="C4" t="n">
-        <v>89.50495644847746</v>
+        <v>74.95545547153972</v>
       </c>
       <c r="D4" t="n">
-        <v>87.0162260182118</v>
+        <v>76.92091437544184</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.16800203061322</v>
+        <v>10.03837027592364</v>
       </c>
       <c r="C5" t="n">
-        <v>96.13764393836894</v>
+        <v>79.79154466265952</v>
       </c>
       <c r="D5" t="n">
-        <v>52.79348279587224</v>
+        <v>46.16668579220627</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.62643715076748</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>60.01521890831177</v>
+        <v>39.84913931537804</v>
       </c>
       <c r="D6" t="n">
-        <v>30.14849024971531</v>
+        <v>30.63151012020474</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>34.49468733641593</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="D7" t="n">
-        <v>29.58398531977338</v>
+        <v>29.8235317596096</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>28.45595720759379</v>
+        <v>28.87319998189869</v>
       </c>
       <c r="D8" t="n">
         <v>30.95941385342316</v>
@@ -881,10 +881,10 @@
         <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>38.29306920414684</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>37.6716229073586</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>37.75212621910684</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>36.16267668593127</v>
+        <v>35.38218726105505</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>25.80032966760617</v>
+        <v>24.72531593145592</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>21.90573652485908</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.02769422436394</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>26.75262494072559</v>
+        <v>27.28767743954009</v>
       </c>
       <c r="D18" t="n">
-        <v>11.23610247510475</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11.4344155113626</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>85.45721066386785</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>3.009056713516474</v>
+        <v>1.203622685406589</v>
       </c>
     </row>
     <row r="20">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.750456156672063</v>
+        <v>0.776562434059227</v>
       </c>
       <c r="C2" t="n">
-        <v>5.01378552558846</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="D2" t="n">
-        <v>23.54132820013427</v>
+        <v>14.71934332977243</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6.268459091615885</v>
+        <v>3.814089830998858</v>
       </c>
       <c r="C3" t="n">
-        <v>18.25068982194821</v>
+        <v>16.50317890838888</v>
       </c>
       <c r="D3" t="n">
-        <v>74.45574589007809</v>
+        <v>66.74411767321941</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.07201173977529</v>
+        <v>12.21392318853457</v>
       </c>
       <c r="C4" t="n">
-        <v>79.72871280958772</v>
+        <v>70.09285909240528</v>
       </c>
       <c r="D4" t="n">
-        <v>105.7646619262131</v>
+        <v>95.414095880339</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.44489594093983</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C5" t="n">
-        <v>134.2539985557513</v>
+        <v>115.4780737120311</v>
       </c>
       <c r="D5" t="n">
-        <v>70.98035901704441</v>
+        <v>63.32272692391928</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.57739082328414</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="C6" t="n">
-        <v>109.6052589452267</v>
+        <v>87.34609324683873</v>
       </c>
       <c r="D6" t="n">
-        <v>38.9233512302733</v>
+        <v>37.99756314516856</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.102764713776425</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>61.62332164786803</v>
+        <v>42.33983324105218</v>
       </c>
       <c r="D7" t="n">
-        <v>31.62013005838127</v>
+        <v>32.39865598784899</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>37.96909246174539</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>34.72343455150543</v>
+        <v>35.49999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
         <v>39.00483628972578</v>
@@ -1220,10 +1220,10 @@
         <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>38.56010457970196</v>
+        <v>38.73780091417063</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>38.18605870438393</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.821141991377834</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>36.94316611080748</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>28.5776939229204</v>
+        <v>28.27040689149115</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>25.80032966760617</v>
+        <v>24.72531593145592</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>21.49242074137117</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>26.9165768073348</v>
+        <v>27.38879745307752</v>
       </c>
       <c r="D17" t="n">
-        <v>16.99994324673777</v>
+        <v>15.58328130950962</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9.095892479846698</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="C18" t="n">
-        <v>50.82998738737861</v>
+        <v>46.54956739686251</v>
       </c>
       <c r="D18" t="n">
-        <v>9.095892479846698</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>47.54309607356029</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>1.805434028109884</v>
+        <v>0.6018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9149888603580273</v>
+        <v>0.3848451000647496</v>
       </c>
       <c r="C2" t="n">
-        <v>2.029272504678157</v>
+        <v>1.408807955594173</v>
       </c>
       <c r="D2" t="n">
-        <v>15.91805727665778</v>
+        <v>9.815513547059609</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6.720063035569417</v>
+        <v>3.681553890925539</v>
       </c>
       <c r="C3" t="n">
-        <v>20.18473279931442</v>
+        <v>16.46390900021901</v>
       </c>
       <c r="D3" t="n">
-        <v>77.96549393276045</v>
+        <v>65.75255249193013</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.64182631886593</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="C4" t="n">
-        <v>73.47497993353554</v>
+        <v>64.28582142178539</v>
       </c>
       <c r="D4" t="n">
-        <v>117.7360934317987</v>
+        <v>106.8367304192506</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.51852701875834</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="C5" t="n">
-        <v>156.0978849752429</v>
+        <v>136.7329115089746</v>
       </c>
       <c r="D5" t="n">
-        <v>81.92684591939634</v>
+        <v>74.93189352663781</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.63901994447344</v>
+        <v>9.499390786292139</v>
       </c>
       <c r="C6" t="n">
-        <v>143.2958949118645</v>
+        <v>118.2996166140364</v>
       </c>
       <c r="D6" t="n">
-        <v>39.48687441251096</v>
+        <v>38.9233512302733</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.371722527011046</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>61.50354842794993</v>
+        <v>45.09461729916874</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>39.30426933952106</v>
+        <v>37.96909246174539</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.106249736236907</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>26.73593522975338</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>40.93593402397924</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.301797455831271</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>21.51009220004762</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>13.22610507161303</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>43.91652005407257</v>
+        <v>40.13875488813085</v>
       </c>
       <c r="D17" t="n">
-        <v>7.555530331883453</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>41.1990424087174</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6813329067472864</v>
+        <v>0.5478152189697202</v>
       </c>
       <c r="C2" t="n">
-        <v>4.787983553611694</v>
+        <v>2.84412309920301</v>
       </c>
       <c r="D2" t="n">
-        <v>16.04372098280137</v>
+        <v>8.154396431474007</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4.864559874542945</v>
+        <v>2.415099352447154</v>
       </c>
       <c r="C3" t="n">
-        <v>13.15051049838602</v>
+        <v>9.856746950637977</v>
       </c>
       <c r="D3" t="n">
-        <v>72.72296119208248</v>
+        <v>58.35017480190917</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.56601076146068</v>
+        <v>10.24846428463245</v>
       </c>
       <c r="C4" t="n">
-        <v>61.36315850624264</v>
+        <v>51.39547406502477</v>
       </c>
       <c r="D4" t="n">
-        <v>130.7795934304219</v>
+        <v>116.9192793418654</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.13274122871835</v>
+        <v>17.54874021341174</v>
       </c>
       <c r="C5" t="n">
-        <v>146.7958254775043</v>
+        <v>129.4679784975481</v>
       </c>
       <c r="D5" t="n">
-        <v>103.0098778680966</v>
+        <v>95.20498361933444</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.44154978719959</v>
+        <v>14.12833121181585</v>
       </c>
       <c r="C6" t="n">
-        <v>198.6821733946525</v>
+        <v>173.3638818498316</v>
       </c>
       <c r="D6" t="n">
-        <v>53.49445065670446</v>
+        <v>52.44790760397736</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.503898614185871</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>131.0319025904133</v>
+        <v>106.2388460673643</v>
       </c>
       <c r="D7" t="n">
-        <v>37.00992495469625</v>
+        <v>37.72856427420492</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>59.08157684157305</v>
+        <v>49.90223580686537</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.549999698556465</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>41.60155896745857</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
         <v>32.31422568528377</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>31.46010518258904</v>
+        <v>30.59224021203486</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>21.51009220004762</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>37.61173629739955</v>
+        <v>36.37178894693582</v>
       </c>
       <c r="D16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.15952615417349</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>48.16650586575701</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.305544520199011</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.605157496443535</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3652101459798134</v>
+        <v>0.3534291735288517</v>
       </c>
       <c r="C2" t="n">
-        <v>3.07483380970101</v>
+        <v>1.476548547187203</v>
       </c>
       <c r="D2" t="n">
-        <v>11.20566829627309</v>
+        <v>6.465790380169493</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3.769911184307752</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C3" t="n">
-        <v>16.39518666092173</v>
+        <v>10.81395096227862</v>
       </c>
       <c r="D3" t="n">
-        <v>69.55191610736527</v>
+        <v>52.69039928692631</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.03899217072939</v>
+        <v>8.10432729855742</v>
       </c>
       <c r="C4" t="n">
-        <v>49.05989627662161</v>
+        <v>39.1815508764902</v>
       </c>
       <c r="D4" t="n">
-        <v>137.0078008661636</v>
+        <v>120.1610102612884</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.62990647769474</v>
+        <v>18.16233252856599</v>
       </c>
       <c r="C5" t="n">
-        <v>137.1992416684918</v>
+        <v>117.9078992800419</v>
       </c>
       <c r="D5" t="n">
-        <v>121.810346404423</v>
+        <v>112.8028112179585</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.8692319333527</v>
+        <v>17.54972196111598</v>
       </c>
       <c r="C6" t="n">
-        <v>222.148888769264</v>
+        <v>199.0846899533937</v>
       </c>
       <c r="D6" t="n">
-        <v>66.05296728942966</v>
+        <v>65.24793417194728</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.881290643244144</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>189.9603267901238</v>
+        <v>161.0350941799001</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>42.22006002113408</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>91.45961612763286</v>
+        <v>77.35681035612741</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>48.03593342109217</v>
+        <v>46.37187106239383</v>
       </c>
       <c r="D9" t="n">
-        <v>41.3796839862988</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.565887588273662</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>23.43235420496287</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>29.72437524148068</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>24.45533531278805</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>16.59349969717959</v>
+        <v>15.67163860289184</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>31.89207417245764</v>
+        <v>30.81706043630738</v>
       </c>
       <c r="D15" t="n">
-        <v>10.39179944945249</v>
+        <v>9.316785713302231</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>40.91826256530281</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>2.479894700927443</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.22816637801276</v>
+        <v>0.2523091599914303</v>
       </c>
       <c r="C2" t="n">
-        <v>5.931719629059228</v>
+        <v>5.341689258806895</v>
       </c>
       <c r="D2" t="n">
-        <v>15.4968875115359</v>
+        <v>7.110798621859648</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.488730430265664</v>
+        <v>1.688606051304514</v>
       </c>
       <c r="C3" t="n">
-        <v>14.10771451002667</v>
+        <v>7.976700097005335</v>
       </c>
       <c r="D3" t="n">
-        <v>63.48471529511999</v>
+        <v>45.88197895797469</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.79726125130642</v>
+        <v>6.215444715586556</v>
       </c>
       <c r="C4" t="n">
-        <v>44.88648678586841</v>
+        <v>32.8895298399724</v>
       </c>
       <c r="D4" t="n">
-        <v>139.9942773824824</v>
+        <v>119.5739251341488</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.71549845441346</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="C5" t="n">
-        <v>114.1772580039041</v>
+        <v>95.32770208236531</v>
       </c>
       <c r="D5" t="n">
-        <v>138.6964069174682</v>
+        <v>130.891512668706</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.3032054763588</v>
+        <v>21.25287430153496</v>
       </c>
       <c r="C6" t="n">
-        <v>223.4369417572358</v>
+        <v>196.3073256980795</v>
       </c>
       <c r="D6" t="n">
-        <v>85.69577535599986</v>
+        <v>82.75740447718914</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.18745705824891</v>
+        <v>13.95358012045992</v>
       </c>
       <c r="C7" t="n">
-        <v>250.4458028487698</v>
+        <v>223.4369417572358</v>
       </c>
       <c r="D7" t="n">
-        <v>49.94543270585223</v>
+        <v>49.82565948593412</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>163.5591675275186</v>
+        <v>140.7777120504714</v>
       </c>
       <c r="D8" t="n">
-        <v>42.14152020479433</v>
+        <v>43.14290286312608</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.549999698556465</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>76.54686850012379</v>
+        <v>68.78124415953151</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>43.04374634499714</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>43.56014563743098</v>
+        <v>42.70602513473626</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8884816723433632</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.55288818840698</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.28621266575034</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.866703296400686</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>32.25041208450772</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>10.0334615374024</v>
+        <v>8.600109889202059</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>42.15820991576653</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.066578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8148505945248526</v>
+        <v>0.1610066234964769</v>
       </c>
       <c r="C2" t="n">
-        <v>3.036545649235384</v>
+        <v>2.563343255788422</v>
       </c>
       <c r="D2" t="n">
-        <v>11.15854440646924</v>
+        <v>5.062872910800801</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4.084070449666732</v>
+        <v>2.22856728864026</v>
       </c>
       <c r="C3" t="n">
-        <v>19.64477156197868</v>
+        <v>14.51513980728909</v>
       </c>
       <c r="D3" t="n">
-        <v>69.11503837897546</v>
+        <v>47.61476365597031</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.17862132891069</v>
+        <v>10.51648140789183</v>
       </c>
       <c r="C4" t="n">
-        <v>64.24753326131977</v>
+        <v>46.89023385023616</v>
       </c>
       <c r="D4" t="n">
-        <v>144.4867548771158</v>
+        <v>127.359184428826</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.33413837680919</v>
+        <v>13.57266201121216</v>
       </c>
       <c r="C5" t="n">
-        <v>179.905266803228</v>
+        <v>154.9197877301467</v>
       </c>
       <c r="D5" t="n">
-        <v>128.4125997154828</v>
+        <v>122.4975697973958</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.6666888066416</v>
+        <v>8.654106012935635</v>
       </c>
       <c r="C6" t="n">
-        <v>221.8671271781452</v>
+        <v>201.0167694353514</v>
       </c>
       <c r="D6" t="n">
-        <v>71.60769580005812</v>
+        <v>70.52090109145691</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.491495746929157</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>114.9822911213864</v>
+        <v>98.99256626231862</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>38.14777054391831</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.420008090968388</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>56.41122308602172</v>
+        <v>50.65327280061418</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>26.84687272033327</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>8.296749848589794</v>
+        <v>7.067601722872788</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35.47545329295849</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>1.433351648200343</v>
       </c>
     </row>
     <row r="16">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4034983064454391</v>
+        <v>0.1168279768053704</v>
       </c>
       <c r="C2" t="n">
-        <v>1.731802950291373</v>
+        <v>1.449059611468292</v>
       </c>
       <c r="D2" t="n">
-        <v>8.348782476914876</v>
+        <v>4.160646770597983</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3.421390749300135</v>
+        <v>1.330268139254428</v>
       </c>
       <c r="C3" t="n">
-        <v>15.31035544772901</v>
+        <v>12.01659189998096</v>
       </c>
       <c r="D3" t="n">
-        <v>62.23789571072654</v>
+        <v>40.94378800561323</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.85656702418873</v>
+        <v>6.942919764433443</v>
       </c>
       <c r="C4" t="n">
-        <v>54.48405234258524</v>
+        <v>39.81968688425063</v>
       </c>
       <c r="D4" t="n">
-        <v>140.1346673041897</v>
+        <v>117.9785851147477</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.45056544298706</v>
+        <v>12.19821522526662</v>
       </c>
       <c r="C5" t="n">
-        <v>135.8493385751524</v>
+        <v>108.8021893231528</v>
       </c>
       <c r="D5" t="n">
-        <v>133.9840179370835</v>
+        <v>127.283589855599</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.6666888066416</v>
+        <v>8.573602701187397</v>
       </c>
       <c r="C6" t="n">
-        <v>208.8658423308047</v>
+        <v>189.3437892318569</v>
       </c>
       <c r="D6" t="n">
-        <v>77.76619914879835</v>
+        <v>75.83411966684064</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.832743037379548</v>
+        <v>3.593196597543325</v>
       </c>
       <c r="C7" t="n">
-        <v>151.8125562462055</v>
+        <v>136.3618108767692</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>37.72856427420492</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.251728322914683</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>63.25400458462199</v>
+        <v>56.57812019574367</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>21.52187317249857</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>18.64829764216817</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D10" t="n">
         <v>20.07183181332604</v>
@@ -3086,10 +3086,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>13.68261775408779</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>17.76963344686726</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.71617710248143</v>
+        <v>12.15010958775853</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>8.325220532012953</v>
+        <v>7.284567965511334</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="D14" t="n">
-        <v>2.765583282863265</v>
+        <v>1.84372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7294385442553801</v>
+        <v>0.1433351648200343</v>
       </c>
       <c r="C2" t="n">
-        <v>7.612471698729768</v>
+        <v>4.925428232206248</v>
       </c>
       <c r="D2" t="n">
-        <v>17.76668820375453</v>
+        <v>5.43888228152733</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.30219836645877</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="C3" t="n">
-        <v>10.11200135374215</v>
+        <v>7.917795234750526</v>
       </c>
       <c r="D3" t="n">
-        <v>54.47718010865552</v>
+        <v>34.54279297392402</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>9.087056750508477</v>
+        <v>4.607341976030281</v>
       </c>
       <c r="C4" t="n">
-        <v>45.02687670757571</v>
+        <v>34.17856457564846</v>
       </c>
       <c r="D4" t="n">
-        <v>140.032565542948</v>
+        <v>112.0566829627309</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.11324514335366</v>
+        <v>11.65825398793088</v>
       </c>
       <c r="C5" t="n">
-        <v>117.3188506574939</v>
+        <v>90.0508081720387</v>
       </c>
       <c r="D5" t="n">
-        <v>154.6252634188727</v>
+        <v>142.5252229640307</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.26796036999715</v>
+        <v>12.96103319146639</v>
       </c>
       <c r="C6" t="n">
-        <v>213.7362926915731</v>
+        <v>183.1047825713684</v>
       </c>
       <c r="D6" t="n">
-        <v>101.1926628675358</v>
+        <v>98.97882179445919</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.084692344472483</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>234.2165315498658</v>
+        <v>214.4539502633775</v>
       </c>
       <c r="D7" t="n">
-        <v>49.64599965605695</v>
+        <v>50.90361846519711</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.586905200690345</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>135.0197617650638</v>
+        <v>121.1673016581413</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7765624340592268</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>54.80312034646543</v>
+        <v>50.69843319500952</v>
       </c>
       <c r="D9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>21.06830573313655</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.59193711239859</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>18.48041878474196</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>13.88583952886689</v>
+      </c>
+      <c r="D12" t="n">
         <v>13.4519070435898</v>
-      </c>
-      <c r="D12" t="n">
-        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>7.804894248762142</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>3.072870314292517</v>
+        <v>2.151009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>1.791689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8776824475966484</v>
+        <v>0.1688606051304514</v>
       </c>
       <c r="C2" t="n">
-        <v>4.683918296961532</v>
+        <v>7.945284170469436</v>
       </c>
       <c r="D2" t="n">
-        <v>17.79221364406494</v>
+        <v>9.343292901316895</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.390555659840983</v>
+        <v>0.6185010536754906</v>
       </c>
       <c r="C3" t="n">
-        <v>20.90631736193583</v>
+        <v>14.73603304074462</v>
       </c>
       <c r="D3" t="n">
-        <v>55.67491230783661</v>
+        <v>30.87596529856219</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6.700428081484481</v>
+        <v>2.96095107600838</v>
       </c>
       <c r="C4" t="n">
-        <v>34.37000537797658</v>
+        <v>26.08699999724625</v>
       </c>
       <c r="D4" t="n">
-        <v>134.6977485180709</v>
+        <v>104.3735254292954</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.10066234964769</v>
+        <v>9.498409038587893</v>
       </c>
       <c r="C5" t="n">
-        <v>98.3956636581366</v>
+        <v>75.96272861609697</v>
       </c>
       <c r="D5" t="n">
-        <v>169.7196343716674</v>
+        <v>151.4836707652829</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.09186767803848</v>
+        <v>14.81260936167588</v>
       </c>
       <c r="C6" t="n">
-        <v>201.0167694353514</v>
+        <v>163.059457946057</v>
       </c>
       <c r="D6" t="n">
-        <v>124.6593782421473</v>
+        <v>120.8757225899801</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.07335334037803</v>
+        <v>11.13890945238431</v>
       </c>
       <c r="C7" t="n">
-        <v>274.3405602224329</v>
+        <v>245.4153276122092</v>
       </c>
       <c r="D7" t="n">
-        <v>64.43799231594365</v>
+        <v>66.41425044459247</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>223.0579871433965</v>
+        <v>205.8675848420349</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>109.7171781835107</v>
+        <v>99.28905406900114</v>
       </c>
       <c r="D9" t="n">
-        <v>25.62656032395449</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>45.41074005993622</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
         <v>21.78007281871549</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>19.19120412261664</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3725,7 +3725,7 @@
         <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>14.97067074205961</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>3.68744437715102</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>8.958447801252145</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.334015203622168</v>
+        <v>1.518763698469816</v>
       </c>
       <c r="C2" t="n">
-        <v>6.036766633413637</v>
+        <v>2.058724935805561</v>
       </c>
       <c r="D2" t="n">
-        <v>11.7721367216235</v>
+        <v>5.998478472948011</v>
       </c>
     </row>
     <row r="3">
@@ -3932,10 +3932,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7.706719478337463</v>
+        <v>7.780350556155974</v>
       </c>
       <c r="C5" t="n">
-        <v>14.38260386721577</v>
+        <v>14.50532233024663</v>
       </c>
       <c r="D5" t="n">
         <v>27.95526587842793</v>
@@ -3949,10 +3949,10 @@
         <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>19.64280806657019</v>
+        <v>19.84406634594078</v>
       </c>
       <c r="D6" t="n">
-        <v>36.14598697495907</v>
+        <v>36.50825187782615</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.0970952117292</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>23.2360046641135</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>44.31118263117978</v>
+        <v>43.89393985687489</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.08749871886498</v>
+        <v>15.19843620944487</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>49.36718330805084</v>
+        <v>49.81093327037041</v>
       </c>
     </row>
     <row r="10">
@@ -4002,10 +4002,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14.94710879715769</v>
+        <v>14.8047553800419</v>
       </c>
       <c r="C10" t="n">
-        <v>37.72365553568369</v>
+        <v>37.86600895279948</v>
       </c>
       <c r="D10" t="n">
         <v>69.04140730115694</v>
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12.61643974727576</v>
+        <v>12.43874341280708</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>38.38240824523329</v>
       </c>
       <c r="D11" t="n">
-        <v>58.10670137125595</v>
+        <v>58.28439770572462</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.28224461720434</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="C12" t="n">
-        <v>36.66729500591412</v>
+        <v>36.45032876327558</v>
       </c>
       <c r="D12" t="n">
-        <v>59.44875048296136</v>
+        <v>58.79785175504571</v>
       </c>
     </row>
     <row r="13">
@@ -4047,10 +4047,10 @@
         <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>36.94316611080748</v>
+        <v>36.68300296918207</v>
       </c>
       <c r="D13" t="n">
-        <v>60.87817514034472</v>
+        <v>61.39850142359553</v>
       </c>
     </row>
     <row r="14">
@@ -4061,7 +4061,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>39.33274002294421</v>
+        <v>39.64002705437346</v>
       </c>
       <c r="D14" t="n">
         <v>63.60841550585509</v>
@@ -4078,7 +4078,7 @@
         <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>60.91744504851458</v>
       </c>
     </row>
     <row r="16">
@@ -4089,10 +4089,10 @@
         <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>51.25115715250048</v>
+        <v>51.66447293598839</v>
       </c>
       <c r="D16" t="n">
-        <v>57.864209688307</v>
+        <v>58.2775254717949</v>
       </c>
     </row>
     <row r="17">
@@ -4103,10 +4103,10 @@
         <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>56.19425684338318</v>
+        <v>56.6664774891259</v>
       </c>
       <c r="D17" t="n">
-        <v>53.8331536146696</v>
+        <v>52.88871232318417</v>
       </c>
     </row>
     <row r="18">
@@ -4117,7 +4117,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>62.06608986248335</v>
+        <v>61.53103736366884</v>
       </c>
       <c r="D18" t="n">
         <v>45.47946239923349</v>
@@ -4134,7 +4134,7 @@
         <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>34.3032465340878</v>
       </c>
     </row>
     <row r="20">
@@ -4145,10 +4145,10 @@
         <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>20.17491532227195</v>
+        <v>19.50241814486288</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>27.41820207255788</v>
+        <v>24.89822319643705</v>
       </c>
       <c r="C21" t="n">
-        <v>99.77179087514119</v>
+        <v>91.29348505360251</v>
       </c>
       <c r="D21" t="n">
-        <v>0.761616724237719</v>
+        <v>0.7544916120132438</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7451465075233291</v>
+        <v>0.6695519342963246</v>
       </c>
       <c r="C2" t="n">
-        <v>7.760715602071037</v>
+        <v>14.08218906971625</v>
       </c>
       <c r="D2" t="n">
-        <v>15.35551584212436</v>
+        <v>10.3270041009722</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2.64090132442392</v>
+        <v>0.5890486225480862</v>
       </c>
       <c r="C3" t="n">
-        <v>19.39933463591697</v>
+        <v>23.66502841086936</v>
       </c>
       <c r="D3" t="n">
-        <v>56.46031047123407</v>
+        <v>31.02813619272044</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5.590071427981338</v>
+        <v>2.042035224833366</v>
       </c>
       <c r="C4" t="n">
-        <v>43.24009588584652</v>
+        <v>31.88127494771092</v>
       </c>
       <c r="D4" t="n">
-        <v>132.2345435281156</v>
+        <v>96.02670644778902</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.59720570381833</v>
+        <v>7.240389318820228</v>
       </c>
       <c r="C5" t="n">
-        <v>81.4605157598791</v>
+        <v>61.48194997845651</v>
       </c>
       <c r="D5" t="n">
-        <v>176.6409556866074</v>
+        <v>155.386117889664</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.53463589265379</v>
+        <v>14.24908617943821</v>
       </c>
       <c r="C6" t="n">
-        <v>179.60288851032</v>
+        <v>144.4631929322139</v>
       </c>
       <c r="D6" t="n">
-        <v>146.5562790376681</v>
+        <v>140.0355107860608</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.16371518689774</v>
+        <v>14.3727863901733</v>
       </c>
       <c r="C7" t="n">
-        <v>285.1201500150629</v>
+        <v>243.9780489731918</v>
       </c>
       <c r="D7" t="n">
-        <v>80.90681005468389</v>
+        <v>83.48193428292328</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>289.9837281419016</v>
+        <v>267.7864125488812</v>
       </c>
       <c r="D8" t="n">
-        <v>43.72704274715294</v>
+        <v>44.81187396034566</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>183.6015469097172</v>
+        <v>170.9546729836098</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>82.70733534427255</v>
+        <v>76.01672473983054</v>
       </c>
       <c r="D10" t="n">
-        <v>22.63419332141022</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>36.25005223160922</v>
+        <v>34.82848155585983</v>
       </c>
       <c r="D11" t="n">
-        <v>19.90198946049134</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>15.62156946997525</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>3.719842051391165</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.606360228326034</v>
+        <v>2.644828315240907</v>
       </c>
       <c r="C2" t="n">
-        <v>7.210936887692822</v>
+        <v>5.180682635310418</v>
       </c>
       <c r="D2" t="n">
-        <v>22.93853510972672</v>
+        <v>14.52495728433156</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5.51251335934584</v>
+        <v>2.528000338435537</v>
       </c>
       <c r="C3" t="n">
-        <v>11.91841712955628</v>
+        <v>4.064435495581795</v>
       </c>
       <c r="D3" t="n">
-        <v>11.04957041129785</v>
+        <v>7.152032025438015</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.632466505713199</v>
+        <v>3.68155389092554</v>
       </c>
       <c r="C5" t="n">
-        <v>8.197593330460869</v>
+        <v>8.320311793491719</v>
       </c>
       <c r="D5" t="n">
         <v>24.20008090968388</v>
@@ -4571,10 +4571,10 @@
         <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>14.49059611468292</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="D6" t="n">
-        <v>28.6591789823729</v>
+        <v>28.90068891761761</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
         <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>28.14670668075605</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>17.19040230136165</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -4613,10 +4613,10 @@
         <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>18.74843590800133</v>
+        <v>18.85937339858122</v>
       </c>
       <c r="D9" t="n">
-        <v>34.72343455150543</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -4627,10 +4627,10 @@
         <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>46.12250714551515</v>
+        <v>46.26486056263094</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
         <v>39.4878561602152</v>
@@ -4672,7 +4672,7 @@
         <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>40.06512381031234</v>
+        <v>39.80496066868693</v>
       </c>
     </row>
     <row r="14">
@@ -4683,10 +4683,10 @@
         <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>40.86917518009047</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -4697,10 +4697,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>39.77550823755952</v>
+        <v>39.41717032550944</v>
       </c>
     </row>
     <row r="16">
@@ -4711,10 +4711,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>36.78510473042374</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -4728,7 +4728,7 @@
         <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.0554452019901</v>
       </c>
     </row>
     <row r="18">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>36.31484758008951</v>
+        <v>36.98734475749858</v>
       </c>
       <c r="D20" t="n">
-        <v>12.77744637077223</v>
+        <v>12.10494919336317</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.67828756403251</v>
+        <v>9.919770578511182</v>
       </c>
       <c r="C21" t="n">
-        <v>59.94854282870023</v>
+        <v>51.12497144309609</v>
       </c>
       <c r="D21" t="n">
-        <v>0.778552504268834</v>
+        <v>0.7630592752700909</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.159844949342983</v>
+        <v>1.949750940634166</v>
       </c>
       <c r="C2" t="n">
-        <v>5.713771638716436</v>
+        <v>4.906775025825558</v>
       </c>
       <c r="D2" t="n">
-        <v>22.57823370226814</v>
+        <v>17.90118763923634</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.10985793188441</v>
+        <v>6.78387663634546</v>
       </c>
       <c r="C3" t="n">
-        <v>22.75200304591983</v>
+        <v>15.00110492089126</v>
       </c>
       <c r="D3" t="n">
-        <v>28.4559572075938</v>
+        <v>18.13288009743859</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6.96844520474386</v>
+        <v>3.445934441906304</v>
       </c>
       <c r="C4" t="n">
-        <v>19.93536888243573</v>
+        <v>7.300275928779282</v>
       </c>
       <c r="D4" t="n">
-        <v>20.06299608398782</v>
+        <v>17.91885909791278</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.454369260617026</v>
+        <v>2.478912953223197</v>
       </c>
       <c r="C5" t="n">
-        <v>5.056000676871074</v>
+        <v>5.178719139901926</v>
       </c>
       <c r="D5" t="n">
-        <v>25.50089661781091</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.433973543006096</v>
+        <v>5.554728510628454</v>
       </c>
       <c r="C6" t="n">
-        <v>13.68556299720054</v>
+        <v>13.96732458831938</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>30.5510068084565</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.827073535332318</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
         <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>30.48228446915921</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>32.71183350550372</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>20.85624822901923</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -4938,10 +4938,10 @@
         <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D10" t="n">
-        <v>45.26838664282043</v>
+        <v>45.41074005993622</v>
       </c>
     </row>
     <row r="11">
@@ -4952,10 +4952,10 @@
         <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>43.35790561035613</v>
+        <v>43.18020927588745</v>
       </c>
     </row>
     <row r="12">
@@ -4966,7 +4966,7 @@
         <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
         <v>40.57268737340794</v>
@@ -4980,7 +4980,7 @@
         <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
         <v>40.32528695193774</v>
@@ -4994,10 +4994,10 @@
         <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>22.43195329433537</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>41.17646221151972</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5008,10 +5008,10 @@
         <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>40.1338461496096</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -5022,10 +5022,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>37.19842051391164</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>28.80545939030567</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.52766584773283</v>
       </c>
     </row>
     <row r="18">
@@ -5053,7 +5053,7 @@
         <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>36.31484758008951</v>
+        <v>36.98734475749858</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.62971119117843</v>
+        <v>10.8504459466708</v>
       </c>
       <c r="C21" t="n">
-        <v>73.76078997578912</v>
+        <v>58.90242085335579</v>
       </c>
       <c r="D21" t="n">
-        <v>1.603495434256285</v>
+        <v>1.550063706667258</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.934443887993716</v>
+        <v>1.959568417676633</v>
       </c>
       <c r="C2" t="n">
-        <v>4.718279466610171</v>
+        <v>5.270021676396878</v>
       </c>
       <c r="D2" t="n">
-        <v>25.53525778745954</v>
+        <v>19.63495408493621</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.444412914854317</v>
+        <v>6.847690237121502</v>
       </c>
       <c r="C3" t="n">
-        <v>22.47711368873073</v>
+        <v>17.7450897542611</v>
       </c>
       <c r="D3" t="n">
-        <v>40.54618018539327</v>
+        <v>29.32971266437346</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.91060420565131</v>
+        <v>9.393362034233482</v>
       </c>
       <c r="C4" t="n">
-        <v>43.24009588584652</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D4" t="n">
-        <v>30.31146036862027</v>
+        <v>23.53445596620454</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.847690237121504</v>
+        <v>4.025165587411923</v>
       </c>
       <c r="C5" t="n">
-        <v>24.42097414313941</v>
+        <v>10.25926350937917</v>
       </c>
       <c r="D5" t="n">
-        <v>26.97351817418112</v>
+        <v>26.67899386290708</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.467933802027235</v>
+        <v>4.588688769649592</v>
       </c>
       <c r="C6" t="n">
-        <v>10.42517887139688</v>
+        <v>10.82769543013807</v>
       </c>
       <c r="D6" t="n">
-        <v>32.16107304342126</v>
+        <v>32.32207966691774</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.94684675525043</v>
+        <v>7.066619975168541</v>
       </c>
       <c r="C7" t="n">
-        <v>20.06201433628357</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>23.94973524510094</v>
+        <v>24.11663235482289</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>44.69897297435728</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.397068040872215</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>44.42408361716816</v>
+        <v>44.60177995163684</v>
       </c>
     </row>
     <row r="12">
@@ -5280,7 +5280,7 @@
         <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>42.09145107187774</v>
+        <v>41.65751858660066</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.71549845441346</v>
       </c>
       <c r="D13" t="n">
-        <v>41.10577637681396</v>
+        <v>40.84561323518855</v>
       </c>
     </row>
     <row r="14">
@@ -5308,7 +5308,7 @@
         <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>41.17646221151972</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>40.49218406165969</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>37.61173629739955</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>28.80545939030567</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>35.41654843070368</v>
+        <v>33.52766584773283</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
       <c r="D18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -5378,7 +5378,7 @@
         <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>36.31484758008951</v>
+        <v>36.98734475749858</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>14.84188019736541</v>
+        <v>11.80151019270214</v>
       </c>
       <c r="C21" t="n">
-        <v>87.40218338448517</v>
+        <v>66.87522442531215</v>
       </c>
       <c r="D21" t="n">
-        <v>2.473646699560901</v>
+        <v>2.360302038540429</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.247220495020949</v>
+        <v>1.267436286182632</v>
       </c>
       <c r="C2" t="n">
-        <v>4.687845287778519</v>
+        <v>4.174391238457438</v>
       </c>
       <c r="D2" t="n">
-        <v>26.89792360095411</v>
+        <v>28.09172880931823</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.891108120286615</v>
+        <v>6.872233929727672</v>
       </c>
       <c r="C3" t="n">
-        <v>19.95402208881642</v>
+        <v>19.54168805303276</v>
       </c>
       <c r="D3" t="n">
-        <v>51.56629816556372</v>
+        <v>38.73485567105791</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.9443845382232</v>
+        <v>11.9586687854304</v>
       </c>
       <c r="C4" t="n">
-        <v>51.08916878129977</v>
+        <v>37.95632974159018</v>
       </c>
       <c r="D4" t="n">
-        <v>43.5081130091059</v>
+        <v>33.43832680664636</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.71425466480195</v>
+        <v>9.498409038587893</v>
       </c>
       <c r="C5" t="n">
-        <v>56.59775514982863</v>
+        <v>33.28124717396688</v>
       </c>
       <c r="D5" t="n">
-        <v>32.15223731408305</v>
+        <v>29.42788743479815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.003788122096746</v>
+        <v>5.192463607761381</v>
       </c>
       <c r="C6" t="n">
-        <v>26.20382797405162</v>
+        <v>14.04782790006761</v>
       </c>
       <c r="D6" t="n">
-        <v>33.89189424600839</v>
+        <v>33.93214590188251</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.407867265618931</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>17.6066633279623</v>
+        <v>18.26541603751191</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>25.95250056176443</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D8" t="n">
         <v>35.63253292563798</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>27.84531013555227</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>44.12955930589413</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
         <v>45.66795795844887</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>43.39324852770902</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
         <v>41.36593951843936</v>
@@ -5616,10 +5616,10 @@
         <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>41.48374924294897</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3.225041208450772</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
         <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>40.85052197370977</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>37.61173629739955</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>33.99988649347554</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.63820242768521</v>
       </c>
       <c r="D18" t="n">
-        <v>29.96293993361265</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>36.31484758008951</v>
+        <v>36.98734475749858</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.08744751513785</v>
+        <v>11.97253498631802</v>
       </c>
       <c r="C21" t="n">
-        <v>101.6049316745548</v>
+        <v>75.02788591425957</v>
       </c>
       <c r="D21" t="n">
-        <v>3.386831055818494</v>
+        <v>2.394506997263603</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.057743188101315</v>
+        <v>1.467712817848982</v>
       </c>
       <c r="C2" t="n">
-        <v>8.361545197070084</v>
+        <v>3.720823799095411</v>
       </c>
       <c r="D2" t="n">
-        <v>27.54195009494002</v>
+        <v>26.71630027566845</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.688467182584272</v>
+        <v>5.517422097867074</v>
       </c>
       <c r="C3" t="n">
-        <v>18.92318699935727</v>
+        <v>17.53892273636927</v>
       </c>
       <c r="D3" t="n">
-        <v>60.53947218237957</v>
+        <v>52.21916038888784</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.544232385518</v>
+        <v>12.85205919629499</v>
       </c>
       <c r="C4" t="n">
-        <v>50.45103277353934</v>
+        <v>44.43979158043612</v>
       </c>
       <c r="D4" t="n">
-        <v>58.27458022868218</v>
+        <v>45.33318199130072</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.16295442337175</v>
+        <v>14.01444847812322</v>
       </c>
       <c r="C5" t="n">
-        <v>77.41080647986101</v>
+        <v>54.63425974133501</v>
       </c>
       <c r="D5" t="n">
-        <v>40.57072387799944</v>
+        <v>34.87658719336795</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.81260936167588</v>
+        <v>9.177377539299185</v>
       </c>
       <c r="C6" t="n">
-        <v>59.77370897306707</v>
+        <v>34.89818564286137</v>
       </c>
       <c r="D6" t="n">
-        <v>36.66925850132262</v>
+        <v>35.58246379272141</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.60559946480004</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>28.26647990067416</v>
+        <v>19.76258128648829</v>
       </c>
       <c r="D7" t="n">
-        <v>36.71049190490098</v>
+        <v>37.54890444432775</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>24.95111790343269</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>38.60624672180155</v>
+        <v>38.162496759482</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>43.70249905454677</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>30.74146586308036</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>46.55643963079223</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>31.24313893995049</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
         <v>44.04414725562465</v>
@@ -5913,10 +5913,10 @@
         <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>42.40659208494097</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>41.79103627437823</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>40.85052197370977</v>
@@ -5955,10 +5955,10 @@
         <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>38.02505208088746</v>
+        <v>38.85168364786328</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5983,10 +5983,10 @@
         <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>31.56809743005619</v>
+        <v>33.17325492649972</v>
       </c>
       <c r="D18" t="n">
-        <v>29.96293993361265</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -5997,10 +5997,10 @@
         <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -6011,10 +6011,10 @@
         <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>36.31484758008951</v>
+        <v>36.98734475749858</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17.3607885506583</v>
+        <v>12.13685069003768</v>
       </c>
       <c r="C21" t="n">
-        <v>115.4492438618777</v>
+        <v>82.5305846922562</v>
       </c>
       <c r="D21" t="n">
-        <v>4.340197137664575</v>
+        <v>2.427370138007535</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.327723806769188</v>
+        <v>1.383282515283756</v>
       </c>
       <c r="C2" t="n">
-        <v>7.999280294203011</v>
+        <v>9.681014111577797</v>
       </c>
       <c r="D2" t="n">
-        <v>31.48072188437822</v>
+        <v>27.53213261789755</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.770533079113505</v>
+        <v>5.247441479199201</v>
       </c>
       <c r="C3" t="n">
-        <v>26.41392198276044</v>
+        <v>15.72268948351267</v>
       </c>
       <c r="D3" t="n">
-        <v>67.48533718992574</v>
+        <v>60.90762757147212</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.66360469480861</v>
+        <v>11.75446526294706</v>
       </c>
       <c r="C4" t="n">
-        <v>48.7408282727414</v>
+        <v>44.56741878198821</v>
       </c>
       <c r="D4" t="n">
-        <v>73.06657288856887</v>
+        <v>60.44424265506763</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.93639168786899</v>
+        <v>16.8369731278328</v>
       </c>
       <c r="C5" t="n">
-        <v>85.58385611771571</v>
+        <v>69.45865007546185</v>
       </c>
       <c r="D5" t="n">
-        <v>51.68901662859458</v>
+        <v>42.5096755938869</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.29941735426205</v>
+        <v>14.12833121181585</v>
       </c>
       <c r="C6" t="n">
-        <v>91.37125883425065</v>
+        <v>61.82654342264714</v>
       </c>
       <c r="D6" t="n">
-        <v>41.0164373357275</v>
+        <v>38.80259626265094</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.39652826152447</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>56.47307319138927</v>
+        <v>35.69241953559704</v>
       </c>
       <c r="D7" t="n">
-        <v>38.74663664350886</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>26.53664044579129</v>
       </c>
       <c r="D8" t="n">
-        <v>39.13737222979909</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>8.653124265231384</v>
       </c>
       <c r="C9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.9484347022272</v>
       </c>
       <c r="D9" t="n">
         <v>39.38280915586078</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D10" t="n">
-        <v>43.98720588877834</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>47.08952863419825</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>43.1870815098172</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>41.79103627437823</v>
@@ -6252,10 +6252,10 @@
         <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
       <c r="D15" t="n">
-        <v>41.20885988575986</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>38.43836786437537</v>
+        <v>38.85168364786328</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>31.56809743005619</v>
+        <v>33.17325492649972</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>36.31484758008951</v>
+        <v>36.98734475749858</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.65580222977887</v>
+        <v>12.29395362675843</v>
       </c>
       <c r="C21" t="n">
-        <v>128.8138725389494</v>
+        <v>90.15565992956184</v>
       </c>
       <c r="D21" t="n">
-        <v>5.33022920850825</v>
+        <v>2.458790725351686</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.099958339383927</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C2" t="n">
-        <v>4.862596379134452</v>
+        <v>5.575345212417637</v>
       </c>
       <c r="D2" t="n">
-        <v>24.68800951869454</v>
+        <v>21.14390030636355</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.21646752101981</v>
+        <v>7.647814616082653</v>
       </c>
       <c r="C3" t="n">
-        <v>39.1520984453628</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D3" t="n">
-        <v>75.08897315931729</v>
+        <v>69.12485585601792</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.9714315055856</v>
+        <v>8.078801858247003</v>
       </c>
       <c r="C4" t="n">
-        <v>73.60260713508762</v>
+        <v>64.18371966054373</v>
       </c>
       <c r="D4" t="n">
-        <v>67.6041286621396</v>
+        <v>56.20701956353839</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.541826921753</v>
+        <v>7.952156404399165</v>
       </c>
       <c r="C5" t="n">
-        <v>54.58517235612267</v>
+        <v>36.93825737228624</v>
       </c>
       <c r="D5" t="n">
-        <v>39.88350048502668</v>
+        <v>36.22649028670731</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.688066271956774</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>37.19253002768617</v>
+        <v>23.50696703048563</v>
       </c>
       <c r="D6" t="n">
-        <v>25.51954982419159</v>
+        <v>26.12332466230338</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>22.15804568485051</v>
+        <v>18.62473569726624</v>
       </c>
       <c r="D7" t="n">
-        <v>27.48795397120644</v>
+        <v>27.66761380108361</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>23.44904391593506</v>
+        <v>24.28352946454485</v>
       </c>
       <c r="D8" t="n">
         <v>28.95664853675967</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>26.5140602485936</v>
+        <v>26.62499773917349</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.86953503298896</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
         <v>34.60169783617884</v>
@@ -6549,10 +6549,10 @@
         <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>34.41614752007619</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>32.6087499965578</v>
+        <v>32.96708790860789</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>25.21226279276234</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>30.58536797810513</v>
+        <v>29.34542062764141</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>26.9165768073348</v>
+        <v>28.33323874456295</v>
       </c>
       <c r="D17" t="n">
-        <v>25.97213551584937</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>19.26188995732242</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>31.29418982057133</v>
+        <v>31.89600116327462</v>
       </c>
       <c r="D19" t="n">
-        <v>13.23984953947248</v>
+        <v>11.4344155113626</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>14.12244072559037</v>
+        <v>10.08745766113597</v>
       </c>
       <c r="C20" t="n">
-        <v>97.51209072431442</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>4.03498306445439</v>
+        <v>2.017491532227195</v>
       </c>
     </row>
     <row r="21">

--- a/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -475,7 +475,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7193579588281739</v>
+        <v>0.7061868316279986</v>
       </c>
     </row>
     <row r="3">
@@ -483,13 +483,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.150207398749762</v>
+        <v>0.1485875150377547</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.657381656515741</v>
+        <v>4.572107050924863</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4.946830332158828</v>
+        <v>4.893482161910057</v>
       </c>
       <c r="C4" t="n">
-        <v>8.981445241224126</v>
+        <v>9.074102589550941</v>
       </c>
       <c r="D4" t="n">
-        <v>28.05496039429878</v>
+        <v>27.54128643349195</v>
       </c>
     </row>
     <row r="5">
@@ -511,13 +511,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7.9109230008208</v>
+        <v>7.825609125321751</v>
       </c>
       <c r="C5" t="n">
-        <v>12.56146187583794</v>
+        <v>12.69105257279852</v>
       </c>
       <c r="D5" t="n">
-        <v>23.74803517926344</v>
+        <v>23.31321912105253</v>
       </c>
     </row>
     <row r="6">
@@ -525,13 +525,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.607265224034778</v>
+        <v>9.503657461814795</v>
       </c>
       <c r="C6" t="n">
-        <v>19.22741097794928</v>
+        <v>19.42577113809693</v>
       </c>
       <c r="D6" t="n">
-        <v>36.67803336230318</v>
+        <v>36.00647473569937</v>
       </c>
     </row>
     <row r="7">
@@ -539,13 +539,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>12.08511788973739</v>
       </c>
       <c r="C7" t="n">
-        <v>18.90081296917748</v>
+        <v>19.09580377120417</v>
       </c>
       <c r="D7" t="n">
-        <v>32.62933920941127</v>
+        <v>32.03191038845973</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.12950930906094</v>
+        <v>13.9771322478848</v>
       </c>
       <c r="C8" t="n">
-        <v>25.62538222670939</v>
+        <v>25.88974724850897</v>
       </c>
       <c r="D8" t="n">
-        <v>44.68319628875003</v>
+        <v>43.86506665689299</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +567,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.93662373167633</v>
+        <v>14.77554249535433</v>
       </c>
       <c r="C9" t="n">
-        <v>28.38890383939373</v>
+        <v>28.68177881452464</v>
       </c>
       <c r="D9" t="n">
-        <v>48.98089896585167</v>
+        <v>48.08408029200385</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +581,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14.22964757489412</v>
+        <v>14.0761905912433</v>
       </c>
       <c r="C10" t="n">
-        <v>38.85678873592536</v>
+        <v>39.25765595852342</v>
       </c>
       <c r="D10" t="n">
-        <v>70.87520402044251</v>
+        <v>69.577510270015</v>
       </c>
     </row>
     <row r="11">
@@ -595,13 +595,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.60001671411495</v>
+        <v>11.47491849464901</v>
       </c>
       <c r="C11" t="n">
-        <v>32.58861925988222</v>
+        <v>32.92482072469695</v>
       </c>
       <c r="D11" t="n">
-        <v>55.08621907795744</v>
+        <v>54.07761468351326</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.9459469411146</v>
       </c>
       <c r="C12" t="n">
-        <v>35.163718944429</v>
+        <v>35.52648650212065</v>
       </c>
       <c r="D12" t="n">
-        <v>59.10724561704828</v>
+        <v>58.02501799876722</v>
       </c>
     </row>
     <row r="13">
@@ -623,13 +623,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.14538898723234</v>
+        <v>11.0251936158014</v>
       </c>
       <c r="C13" t="n">
-        <v>34.39746977000289</v>
+        <v>34.75233229517995</v>
       </c>
       <c r="D13" t="n">
-        <v>61.09931381072631</v>
+        <v>59.98061230173707</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +637,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12.53731088231347</v>
+        <v>12.4021045884846</v>
       </c>
       <c r="C14" t="n">
-        <v>39.31737567137275</v>
+        <v>39.72299455285937</v>
       </c>
       <c r="D14" t="n">
-        <v>63.50639621142059</v>
+        <v>62.3436220844923</v>
       </c>
     </row>
     <row r="15">
@@ -651,13 +651,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14.6201868116435</v>
+        <v>14.46251813034146</v>
       </c>
       <c r="C15" t="n">
-        <v>45.84933584680847</v>
+        <v>46.32234189071459</v>
       </c>
       <c r="D15" t="n">
-        <v>60.5920742243731</v>
+        <v>59.48266004866603</v>
       </c>
     </row>
     <row r="16">
@@ -665,13 +665,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16.02011976799128</v>
+        <v>15.84735377049333</v>
       </c>
       <c r="C16" t="n">
-        <v>51.1209626807018</v>
+        <v>51.64835362043237</v>
       </c>
       <c r="D16" t="n">
-        <v>58.24032705128099</v>
+        <v>57.1739723298822</v>
       </c>
     </row>
     <row r="17">
@@ -679,13 +679,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18.30327222898767</v>
+        <v>18.10588399906721</v>
       </c>
       <c r="C17" t="n">
-        <v>56.39258951459513</v>
+        <v>56.97436535015014</v>
       </c>
       <c r="D17" t="n">
-        <v>53.23248895328486</v>
+        <v>52.25782554047191</v>
       </c>
     </row>
     <row r="18">
@@ -693,13 +693,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.64712775646887</v>
+        <v>19.43524696693832</v>
       </c>
       <c r="C18" t="n">
-        <v>61.6139705009851</v>
+        <v>62.24961286957674</v>
       </c>
       <c r="D18" t="n">
-        <v>45.2365485647717</v>
+        <v>44.40828729660684</v>
       </c>
     </row>
     <row r="19">
@@ -707,13 +707,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>22.09851250406498</v>
+        <v>21.86019521235448</v>
       </c>
       <c r="C19" t="n">
-        <v>66.73485979236835</v>
+        <v>67.42333196842091</v>
       </c>
       <c r="D19" t="n">
-        <v>33.9204945201285</v>
+        <v>33.2994252144587</v>
       </c>
     </row>
     <row r="20">
@@ -721,13 +721,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>21.95030787063188</v>
+        <v>21.71358886418389</v>
       </c>
       <c r="C20" t="n">
-        <v>74.57321200289121</v>
+        <v>75.34254877384718</v>
       </c>
       <c r="D20" t="n">
-        <v>18.95231545374227</v>
+        <v>18.60530691019919</v>
       </c>
     </row>
     <row r="21">
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>22.86156608971377</v>
+        <v>22.61501978874627</v>
       </c>
       <c r="C21" t="n">
-        <v>79.66060406260559</v>
+        <v>80.48242506583058</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3347759671481623</v>
+        <v>0.3495021827118645</v>
       </c>
     </row>
     <row r="3">
@@ -800,7 +800,7 @@
         <v>0.004908738521234052</v>
       </c>
       <c r="D3" t="n">
-        <v>5.149266708774521</v>
+        <v>5.242532740677968</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4211697651218816</v>
+        <v>0.4084070449666731</v>
       </c>
       <c r="C4" t="n">
         <v>0.2424916829489621</v>
       </c>
       <c r="D4" t="n">
-        <v>19.33552103514093</v>
+        <v>18.31450342272425</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.748893571891069</v>
+        <v>2.478912953223197</v>
       </c>
       <c r="C5" t="n">
-        <v>2.331650797586175</v>
+        <v>2.110757564130643</v>
       </c>
       <c r="D5" t="n">
-        <v>33.87029579651497</v>
+        <v>32.20132469929538</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.573602701187397</v>
+        <v>7.688066271956774</v>
       </c>
       <c r="C6" t="n">
-        <v>10.34467555964864</v>
+        <v>8.855364292306232</v>
       </c>
       <c r="D6" t="n">
-        <v>42.0629803884546</v>
+        <v>40.21140421824511</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88802400845363</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C7" t="n">
-        <v>25.63146906247572</v>
+        <v>22.39759212468673</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>43.71722527011047</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.36559536107409</v>
+        <v>21.02903582496668</v>
       </c>
       <c r="C8" t="n">
-        <v>42.47531442423825</v>
+        <v>38.05254101660637</v>
       </c>
       <c r="D8" t="n">
-        <v>49.4015444776995</v>
+        <v>47.23188205131405</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25.62656032395449</v>
+        <v>24.62812290873548</v>
       </c>
       <c r="C9" t="n">
-        <v>52.36249555370786</v>
+        <v>49.69999577979051</v>
       </c>
       <c r="D9" t="n">
-        <v>58.02030757328223</v>
+        <v>55.46874528994476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="C10" t="n">
-        <v>56.22959976073607</v>
+        <v>53.95194508688347</v>
       </c>
       <c r="D10" t="n">
-        <v>64.34374453633596</v>
+        <v>62.63550353094652</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24.34439782220815</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="C11" t="n">
-        <v>58.63979037466196</v>
+        <v>57.57361236784993</v>
       </c>
       <c r="D11" t="n">
-        <v>65.03685841553418</v>
+        <v>64.50376941212818</v>
       </c>
     </row>
     <row r="12">
@@ -920,7 +920,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>21.26269177857742</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="C12" t="n">
         <v>59.88268296823844</v>
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>17.95125677215293</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="C13" t="n">
-        <v>59.31719629059229</v>
+        <v>61.91882770684634</v>
       </c>
       <c r="D13" t="n">
-        <v>64.26029598147498</v>
+        <v>64.00013283984957</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15.97892563432109</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="C14" t="n">
-        <v>57.76996190869932</v>
+        <v>61.76469331727959</v>
       </c>
       <c r="D14" t="n">
-        <v>64.2229895687136</v>
+        <v>63.91570253728435</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16.12520604225386</v>
+        <v>16.48354395430394</v>
       </c>
       <c r="C15" t="n">
-        <v>57.69240384006381</v>
+        <v>59.48409340031424</v>
       </c>
       <c r="D15" t="n">
-        <v>60.5591071364645</v>
+        <v>61.99245878466483</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>18.18589447346791</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>61.58405173969817</v>
+        <v>60.34410438923444</v>
       </c>
       <c r="D16" t="n">
-        <v>56.62426233784328</v>
+        <v>59.93078860574654</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>19.36104647545135</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="C17" t="n">
-        <v>67.05533169546565</v>
+        <v>62.80534588378121</v>
       </c>
       <c r="D17" t="n">
-        <v>50.05538844872788</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>20.86704745376595</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>72.23208733995907</v>
+        <v>67.41661485062848</v>
       </c>
       <c r="D18" t="n">
-        <v>39.59388491227386</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>22.26701968002191</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>78.83728589413161</v>
+        <v>74.02279515250525</v>
       </c>
       <c r="D19" t="n">
-        <v>25.87788773624167</v>
+        <v>34.3032465340878</v>
       </c>
     </row>
     <row r="20">
@@ -1032,13 +1032,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>39.00483628972577</v>
+        <v>63.21473467645211</v>
       </c>
       <c r="C20" t="n">
-        <v>158.7093338685393</v>
+        <v>244.1164753994906</v>
       </c>
       <c r="D20" t="n">
-        <v>8.06996612890878</v>
+        <v>25.55489274154447</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.14273736431632</v>
+        <v>10.14435225073385</v>
       </c>
       <c r="C21" t="n">
-        <v>10.7136868215816</v>
+        <v>49.16109167663328</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1.560669577035977</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2807798434145878</v>
+        <v>0.2964878066825367</v>
       </c>
     </row>
     <row r="3">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.589670517353839</v>
+        <v>4.717297718905924</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2807798434145877</v>
+        <v>0.2680171232593793</v>
       </c>
       <c r="C4" t="n">
         <v>0.1403899217072939</v>
       </c>
       <c r="D4" t="n">
-        <v>18.56975782582842</v>
+        <v>17.59979109403257</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.086213871524472</v>
+        <v>1.88986433067511</v>
       </c>
       <c r="C5" t="n">
-        <v>1.546252634188727</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="D5" t="n">
-        <v>34.70478134512475</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.205046401467343</v>
+        <v>6.400013283984958</v>
       </c>
       <c r="C6" t="n">
-        <v>7.808821239579131</v>
+        <v>6.561019907481435</v>
       </c>
       <c r="D6" t="n">
-        <v>43.91455655866408</v>
+        <v>41.94222542083224</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.81006502919063</v>
+        <v>13.71403368062369</v>
       </c>
       <c r="C7" t="n">
-        <v>22.0382724649324</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="D7" t="n">
-        <v>47.9691745772034</v>
+        <v>45.93302983859552</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.86628669023996</v>
+        <v>21.11248437982766</v>
       </c>
       <c r="C8" t="n">
-        <v>40.72289477215769</v>
+        <v>35.549084370777</v>
       </c>
       <c r="D8" t="n">
-        <v>51.57120690408495</v>
+        <v>49.06775025825559</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27.5124976638126</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="C9" t="n">
-        <v>54.35937038414588</v>
+        <v>50.03280825153018</v>
       </c>
       <c r="D9" t="n">
-        <v>58.90780749792134</v>
+        <v>56.46718270516377</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28.47068342315751</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="C10" t="n">
-        <v>61.06961594267285</v>
+        <v>58.50725443458867</v>
       </c>
       <c r="D10" t="n">
-        <v>66.19433895884119</v>
+        <v>63.77433086787281</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="C11" t="n">
-        <v>63.6152877397848</v>
+        <v>61.48293172616073</v>
       </c>
       <c r="D11" t="n">
-        <v>66.63612542575224</v>
+        <v>66.2807327568149</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>23.86628669023996</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="C12" t="n">
-        <v>64.65594030628644</v>
+        <v>64.00504157837081</v>
       </c>
       <c r="D12" t="n">
-        <v>65.74077151947915</v>
+        <v>65.30683903420207</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19.77239876353076</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="C13" t="n">
-        <v>64.00013283984957</v>
+        <v>66.34160111447822</v>
       </c>
       <c r="D13" t="n">
-        <v>65.82127483122741</v>
+        <v>66.08143797285281</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>17.20807376003809</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="C14" t="n">
-        <v>62.07198034870884</v>
+        <v>66.06671175728911</v>
       </c>
       <c r="D14" t="n">
         <v>65.14485066300135</v>
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="C15" t="n">
-        <v>60.91744504851458</v>
+        <v>64.85916208106552</v>
       </c>
       <c r="D15" t="n">
-        <v>62.35079669671492</v>
+        <v>63.42581043286518</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>18.18589447346791</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="C16" t="n">
-        <v>63.6506306571377</v>
+        <v>63.23731487364979</v>
       </c>
       <c r="D16" t="n">
-        <v>57.864209688307</v>
+        <v>61.17073595621026</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>19.83326712119407</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="C17" t="n">
-        <v>68.9442142784365</v>
+        <v>64.69422846675207</v>
       </c>
       <c r="D17" t="n">
-        <v>50.99982974021331</v>
+        <v>55.72203619764046</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>20.86704745376595</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>73.3021923375881</v>
+        <v>69.021772347072</v>
       </c>
       <c r="D18" t="n">
-        <v>40.66398990990288</v>
+        <v>47.08461989567702</v>
       </c>
     </row>
     <row r="19">
@@ -1329,13 +1329,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>22.8688310227252</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>80.6427199222415</v>
+        <v>74.62460649520854</v>
       </c>
       <c r="D19" t="n">
-        <v>26.47969907894496</v>
+        <v>36.10868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -1343,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>41.02232782195296</v>
+        <v>67.92221491831556</v>
       </c>
       <c r="C20" t="n">
-        <v>170.1417858844934</v>
+        <v>268.998870963626</v>
       </c>
       <c r="D20" t="n">
-        <v>8.742463306317845</v>
+        <v>29.58987580599885</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.14710804780575</v>
+        <v>11.1981749856567</v>
       </c>
       <c r="C21" t="n">
-        <v>11.80909426293163</v>
+        <v>51.99152671912039</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1.599739283665243</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2385646921319749</v>
+        <v>0.2542726553999239</v>
       </c>
     </row>
     <row r="3">
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.108614142272901</v>
+        <v>4.260785036431157</v>
       </c>
     </row>
     <row r="4">
@@ -1436,7 +1436,7 @@
         <v>0.0765763209312512</v>
       </c>
       <c r="D4" t="n">
-        <v>17.57426565372215</v>
+        <v>16.84679060487526</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.570796326794897</v>
+        <v>1.398990478551705</v>
       </c>
       <c r="C5" t="n">
-        <v>1.006291396852981</v>
+        <v>0.93266031903447</v>
       </c>
       <c r="D5" t="n">
-        <v>35.19565519724816</v>
+        <v>33.08489763311751</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.27296691950962</v>
       </c>
       <c r="C6" t="n">
-        <v>5.796238445873169</v>
+        <v>4.870450360768428</v>
       </c>
       <c r="D6" t="n">
-        <v>46.16864928761476</v>
+        <v>43.63279496754524</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.43267300013236</v>
+        <v>12.39652826152447</v>
       </c>
       <c r="C7" t="n">
-        <v>18.38518925743002</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="D7" t="n">
-        <v>50.18497914568845</v>
+        <v>48.20872101703962</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.53249247079604</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="C8" t="n">
-        <v>37.80219535202343</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>53.99121499505333</v>
+        <v>51.15396412978005</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29.28749751309084</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="C9" t="n">
-        <v>54.80312034646543</v>
+        <v>49.36718330805084</v>
       </c>
       <c r="D9" t="n">
-        <v>60.01718240372024</v>
+        <v>58.242182554442</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="C10" t="n">
-        <v>65.19786503903067</v>
+        <v>60.64255569132548</v>
       </c>
       <c r="D10" t="n">
-        <v>67.90257996423065</v>
+        <v>64.77080478768332</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.852984190737</v>
       </c>
       <c r="C11" t="n">
-        <v>68.76848143937632</v>
+        <v>66.45842909128358</v>
       </c>
       <c r="D11" t="n">
-        <v>68.94617777384498</v>
+        <v>67.87999976703294</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26.4698816019025</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="C12" t="n">
-        <v>69.64616388697297</v>
+        <v>68.12740018850316</v>
       </c>
       <c r="D12" t="n">
         <v>67.25953521794898</v>
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21.853703896534</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="C13" t="n">
-        <v>68.94323253073227</v>
+        <v>70.24404823885929</v>
       </c>
       <c r="D13" t="n">
         <v>67.64241682260524</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>18.74450891718435</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="C14" t="n">
-        <v>66.68128582014761</v>
+        <v>71.2905912915864</v>
       </c>
       <c r="D14" t="n">
         <v>66.68128582014761</v>
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="C15" t="n">
-        <v>64.14248625696536</v>
+        <v>69.15921702566655</v>
       </c>
       <c r="D15" t="n">
-        <v>63.42581043286518</v>
+        <v>64.85916208106552</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>18.59921025695582</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="C16" t="n">
-        <v>66.13052535806514</v>
+        <v>67.78378849201677</v>
       </c>
       <c r="D16" t="n">
-        <v>59.51747282225863</v>
+        <v>63.23731487364979</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>19.83326712119407</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="C17" t="n">
-        <v>70.83309686140737</v>
+        <v>67.05533169546565</v>
       </c>
       <c r="D17" t="n">
-        <v>51.94427103169875</v>
+        <v>57.13869813486862</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>21.40209995258047</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>75.44240233284614</v>
+        <v>70.09187734470103</v>
       </c>
       <c r="D18" t="n">
-        <v>42.26914740634642</v>
+        <v>48.68977739212056</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +1640,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>22.8688310227252</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>82.44815395035138</v>
+        <v>76.43004052331844</v>
       </c>
       <c r="D19" t="n">
-        <v>27.68332176435156</v>
+        <v>37.91411459030757</v>
       </c>
     </row>
     <row r="20">
@@ -1654,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>43.71231653158922</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="C20" t="n">
-        <v>182.9192322552657</v>
+        <v>288.5012891084889</v>
       </c>
       <c r="D20" t="n">
-        <v>9.41496048372691</v>
+        <v>32.95236169304418</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.151849544497283</v>
+        <v>11.90287565822136</v>
       </c>
       <c r="C21" t="n">
-        <v>11.47653090398551</v>
+        <v>57.46215835003414</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.052219941072648</v>
       </c>
     </row>
   </sheetData>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2022400270748429</v>
+        <v>0.2179479903427919</v>
       </c>
     </row>
     <row r="3">
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3.666827675361837</v>
+        <v>3.838633523605029</v>
       </c>
     </row>
     <row r="4">
@@ -1747,7 +1747,7 @@
         <v>0.0382881604656256</v>
       </c>
       <c r="D4" t="n">
-        <v>16.70640068316797</v>
+        <v>16.02997651494192</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.153553552490002</v>
+        <v>1.030835089459151</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6626797003665971</v>
+        <v>0.6135923151542566</v>
       </c>
       <c r="D5" t="n">
-        <v>34.9993056563988</v>
+        <v>33.30579086657305</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.870450360768428</v>
+        <v>4.266675522656639</v>
       </c>
       <c r="C6" t="n">
-        <v>4.22642386678252</v>
+        <v>3.542145716922492</v>
       </c>
       <c r="D6" t="n">
-        <v>48.22148373719484</v>
+        <v>45.00135126726531</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.93550775115597</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>15.03153909972291</v>
+        <v>11.91743538185203</v>
       </c>
       <c r="D7" t="n">
-        <v>53.05953642372311</v>
+        <v>50.36463897556562</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.69800692218626</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="C8" t="n">
-        <v>34.13045893814036</v>
+        <v>27.70492021384499</v>
       </c>
       <c r="D8" t="n">
-        <v>55.82708320199487</v>
+        <v>53.15672944644354</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30.39687241888974</v>
+        <v>26.62499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>53.80468293124643</v>
+        <v>46.48280855297372</v>
       </c>
       <c r="D9" t="n">
-        <v>62.01405723415825</v>
+        <v>59.46249495082079</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="C10" t="n">
-        <v>68.18728679846222</v>
+        <v>62.20844327959914</v>
       </c>
       <c r="D10" t="n">
-        <v>68.89905388404117</v>
+        <v>66.05198554172541</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32.34073287329842</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="C11" t="n">
-        <v>73.92167513896783</v>
+        <v>69.83465944618834</v>
       </c>
       <c r="D11" t="n">
-        <v>71.25623012193772</v>
+        <v>69.479266777251</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="C12" t="n">
-        <v>75.0703199529366</v>
+        <v>72.90065752655116</v>
       </c>
       <c r="D12" t="n">
-        <v>69.42919764433442</v>
+        <v>69.21223140169589</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>24.45533531278805</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="C13" t="n">
-        <v>74.14649536324036</v>
+        <v>74.92698478811657</v>
       </c>
       <c r="D13" t="n">
-        <v>68.68306938910686</v>
+        <v>69.98388509723388</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20.28094407433061</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="C14" t="n">
-        <v>70.98330426015714</v>
+        <v>75.28532270016666</v>
       </c>
       <c r="D14" t="n">
-        <v>68.52500800872312</v>
+        <v>68.21772097729388</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>18.63357142660446</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="C15" t="n">
-        <v>68.44254120156639</v>
+        <v>74.17594779436774</v>
       </c>
       <c r="D15" t="n">
-        <v>64.50082416901544</v>
+        <v>66.29251372926586</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>19.01252604044373</v>
       </c>
       <c r="C16" t="n">
-        <v>69.02373584248051</v>
+        <v>72.74357789387165</v>
       </c>
       <c r="D16" t="n">
-        <v>61.17073595621026</v>
+        <v>64.47726222411352</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20.30548776693678</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="C17" t="n">
-        <v>73.19420009012096</v>
+        <v>70.36087621566466</v>
       </c>
       <c r="D17" t="n">
-        <v>53.36093296892689</v>
+        <v>58.55536007209676</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>21.40209995258047</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>77.04755982928968</v>
+        <v>72.76713983877359</v>
       </c>
       <c r="D18" t="n">
-        <v>42.80419990516094</v>
+        <v>50.2949348885641</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>84.25358797846125</v>
+        <v>77.03185186602173</v>
       </c>
       <c r="D19" t="n">
-        <v>28.88694444975815</v>
+        <v>39.71954861841746</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>45.72980806381642</v>
+        <v>78.00967257945153</v>
       </c>
       <c r="C20" t="n">
-        <v>193.6791870938107</v>
+        <v>310.693695962988</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>36.98734475749858</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.516404689363172</v>
+        <v>12.64777413284112</v>
       </c>
       <c r="C21" t="n">
-        <v>12.58202344681586</v>
+        <v>61.1309083087321</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.107962355473521</v>
       </c>
     </row>
   </sheetData>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1737693436516854</v>
+        <v>0.1894773069196344</v>
       </c>
     </row>
     <row r="3">
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3.293763547748048</v>
+        <v>3.480295611554943</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06381360077604267</v>
+        <v>0.0765763209312512</v>
       </c>
       <c r="C4" t="n">
         <v>0.01276272015520854</v>
       </c>
       <c r="D4" t="n">
-        <v>15.6981457909065</v>
+        <v>15.23868786531899</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8590292412159592</v>
+        <v>0.7608544707912782</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4172427743048945</v>
+        <v>0.3926990816987243</v>
       </c>
       <c r="D5" t="n">
-        <v>34.92567457858028</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.944662275663684</v>
+        <v>3.461642405174254</v>
       </c>
       <c r="C6" t="n">
-        <v>3.059125846433061</v>
+        <v>2.576105975943631</v>
       </c>
       <c r="D6" t="n">
-        <v>49.3887817575443</v>
+        <v>46.249152599363</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.37845589222053</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>12.03720860177014</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="D7" t="n">
-        <v>55.99398031171683</v>
+        <v>52.52055693409162</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.52972715413255</v>
+        <v>18.02488784997144</v>
       </c>
       <c r="C8" t="n">
-        <v>30.12492830481337</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>58.4974369575462</v>
+        <v>55.32639187282899</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30.84062238120929</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="C9" t="n">
-        <v>51.47499562906875</v>
+        <v>43.37655881673681</v>
       </c>
       <c r="D9" t="n">
-        <v>63.34530712111692</v>
+        <v>61.4593697812588</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34.59188035913637</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="C10" t="n">
-        <v>69.75317438673588</v>
+        <v>61.21196935978863</v>
       </c>
       <c r="D10" t="n">
-        <v>70.7496483065464</v>
+        <v>67.19081287865171</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34.65078522139116</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="C11" t="n">
-        <v>78.71947616962197</v>
+        <v>72.50010446321843</v>
       </c>
       <c r="D11" t="n">
-        <v>72.67780079768711</v>
+        <v>70.90083745300038</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31.89403766786613</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="C12" t="n">
-        <v>80.71144226153876</v>
+        <v>77.89088110723767</v>
       </c>
       <c r="D12" t="n">
-        <v>71.81582631335843</v>
+        <v>70.94796134280425</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>26.79680358741669</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="C13" t="n">
-        <v>78.82943191249764</v>
+        <v>79.08959505412305</v>
       </c>
       <c r="D13" t="n">
-        <v>69.98388509723388</v>
+        <v>71.54486394698631</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>22.43195329433537</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="C14" t="n">
-        <v>76.51447082588366</v>
+        <v>79.89462817160543</v>
       </c>
       <c r="D14" t="n">
-        <v>70.06144316586938</v>
+        <v>69.75415613444012</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>19.70858516275472</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="C15" t="n">
-        <v>73.10093405821749</v>
+        <v>79.55101647511904</v>
       </c>
       <c r="D15" t="n">
-        <v>66.29251372926586</v>
+        <v>67.72586537746622</v>
       </c>
     </row>
     <row r="16">
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="C16" t="n">
-        <v>71.50363054340794</v>
+        <v>76.87673572875073</v>
       </c>
       <c r="D16" t="n">
-        <v>61.99736752318607</v>
+        <v>65.71720957457724</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20.30548776693678</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="C17" t="n">
-        <v>75.55530331883453</v>
+        <v>75.08308267309182</v>
       </c>
       <c r="D17" t="n">
-        <v>54.77759490615504</v>
+        <v>60.91646330081034</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>21.93715245139498</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>79.18776982454773</v>
+        <v>74.90734983403163</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33925240397544</v>
+        <v>51.90009238500763</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>86.05902200657115</v>
+        <v>78.23547455142831</v>
       </c>
       <c r="D19" t="n">
-        <v>30.09056713516474</v>
+        <v>41.52498264652733</v>
       </c>
     </row>
     <row r="20">
@@ -2276,13 +2276,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>48.41979677345267</v>
+        <v>82.717152821315</v>
       </c>
       <c r="C20" t="n">
-        <v>204.4391419323557</v>
+        <v>332.8861028174872</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>41.02232782195296</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.522659712619485</v>
+        <v>13.43147764980463</v>
       </c>
       <c r="C21" t="n">
-        <v>13.33405848098871</v>
+        <v>63.69120046842841</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.599640835446057</v>
       </c>
     </row>
   </sheetData>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1492256510455152</v>
+        <v>0.1639518666092173</v>
       </c>
     </row>
     <row r="3">
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.950151851261666</v>
+        <v>3.146501392111027</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0382881604656256</v>
+        <v>0.05105088062083414</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>14.85580626066273</v>
+        <v>14.42187377538565</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6135923151542566</v>
+        <v>0.564504929941916</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2699806186678729</v>
+        <v>0.2454369260617026</v>
       </c>
       <c r="D5" t="n">
-        <v>34.28753857081986</v>
+        <v>32.81491701444964</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.179880814055419</v>
+        <v>2.777364255314227</v>
       </c>
       <c r="C6" t="n">
-        <v>2.173589417202439</v>
+        <v>1.851576170209485</v>
       </c>
       <c r="D6" t="n">
-        <v>50.87809302488671</v>
+        <v>47.17494068446774</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.82140403328509</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="D7" t="n">
-        <v>58.09001166028376</v>
+        <v>54.43692845278139</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.27799883121787</v>
+        <v>16.52281386247382</v>
       </c>
       <c r="C8" t="n">
-        <v>26.11939767148639</v>
+        <v>19.94420461177395</v>
       </c>
       <c r="D8" t="n">
-        <v>61.41813637768045</v>
+        <v>57.41260574435346</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30.50780990946962</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="C9" t="n">
-        <v>48.25780840225195</v>
+        <v>39.04999668412111</v>
       </c>
       <c r="D9" t="n">
-        <v>64.89843198923538</v>
+        <v>62.90155715879737</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36.44247478164161</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="C10" t="n">
-        <v>69.89552780385168</v>
+        <v>59.21902152016762</v>
       </c>
       <c r="D10" t="n">
-        <v>72.60024272905163</v>
+        <v>68.4719936326938</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>36.96083756948391</v>
+        <v>35.53926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>82.62879552793277</v>
+        <v>74.45476414237383</v>
       </c>
       <c r="D11" t="n">
-        <v>74.81015681131117</v>
+        <v>72.32240812874977</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34.49763257952867</v>
+        <v>36.01639627799849</v>
       </c>
       <c r="C12" t="n">
-        <v>85.48469959958676</v>
+        <v>81.36234098945441</v>
       </c>
       <c r="D12" t="n">
-        <v>73.33459001182824</v>
+        <v>72.68369128391259</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>29.65859814529614</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="C13" t="n">
-        <v>85.07334731150736</v>
+        <v>83.77253160338033</v>
       </c>
       <c r="D13" t="n">
-        <v>72.06519023023712</v>
+        <v>73.10584279673874</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>24.27567548291088</v>
+        <v>29.19226798577891</v>
       </c>
       <c r="C14" t="n">
-        <v>81.73835036018095</v>
+        <v>85.11850770590272</v>
       </c>
       <c r="D14" t="n">
-        <v>70.98330426015714</v>
+        <v>72.21245238587414</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21.14193681095506</v>
+        <v>25.083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>77.04265109076844</v>
+        <v>83.85107141972007</v>
       </c>
       <c r="D15" t="n">
-        <v>68.0842032895163</v>
+        <v>69.15921702566655</v>
       </c>
     </row>
     <row r="16">
@@ -2531,13 +2531,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="C16" t="n">
-        <v>75.22347259479911</v>
+        <v>81.42320934711771</v>
       </c>
       <c r="D16" t="n">
-        <v>62.82399909016188</v>
+        <v>66.95715692504096</v>
       </c>
     </row>
     <row r="17">
@@ -2545,13 +2545,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20.77770841267949</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="C17" t="n">
-        <v>77.91640654754811</v>
+        <v>79.80528913051897</v>
       </c>
       <c r="D17" t="n">
-        <v>56.19425684338318</v>
+        <v>62.33312523803849</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>21.93715245139498</v>
+        <v>19.79694245613693</v>
       </c>
       <c r="C18" t="n">
-        <v>80.79292732099125</v>
+        <v>78.1176648269187</v>
       </c>
       <c r="D18" t="n">
-        <v>44.40935740160447</v>
+        <v>53.50524988145117</v>
       </c>
     </row>
     <row r="19">
@@ -2573,13 +2573,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>87.86445603468103</v>
+        <v>80.0409085795382</v>
       </c>
       <c r="D19" t="n">
-        <v>31.29418982057133</v>
+        <v>43.33041667463722</v>
       </c>
     </row>
     <row r="20">
@@ -2587,13 +2587,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>51.10978548308893</v>
+        <v>87.42463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>217.889085480537</v>
+        <v>352.3885209623501</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>45.05731088640735</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.529220636962497</v>
+        <v>13.80749484176391</v>
       </c>
       <c r="C21" t="n">
-        <v>13.00742041866427</v>
+        <v>68.14666808999606</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.672418356470434</v>
       </c>
     </row>
   </sheetData>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1276272015520853</v>
+        <v>0.1433351648200343</v>
       </c>
     </row>
     <row r="3">
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.64090132442392</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="4">
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>13.98794129010856</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4417864669110648</v>
+        <v>0.4172427743048945</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1718058482431918</v>
+        <v>0.1472621556370216</v>
       </c>
       <c r="D5" t="n">
-        <v>33.87029579651497</v>
+        <v>32.20132469929538</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.535854320069512</v>
+        <v>2.213841073076558</v>
       </c>
       <c r="C6" t="n">
-        <v>1.56981457909065</v>
+        <v>1.328304643845935</v>
       </c>
       <c r="D6" t="n">
-        <v>51.4818678629985</v>
+        <v>47.93972214607601</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.384125394267761</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>7.545712854840985</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="D7" t="n">
-        <v>60.7250224984822</v>
+        <v>56.2934133615121</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.77592484372025</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="C8" t="n">
-        <v>22.1138670381594</v>
+        <v>16.6062624173348</v>
       </c>
       <c r="D8" t="n">
-        <v>63.50435024920493</v>
+        <v>59.58226817073891</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29.84218496599028</v>
+        <v>24.73906039931537</v>
       </c>
       <c r="C9" t="n">
-        <v>44.81874619427537</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>67.33905678199295</v>
+        <v>64.45468202691582</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37.43894870145212</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>68.89905388404117</v>
+        <v>56.65666001208344</v>
       </c>
       <c r="D10" t="n">
-        <v>73.59671664886216</v>
+        <v>70.60729488943061</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>39.626282586514</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="C11" t="n">
-        <v>84.58345520708816</v>
+        <v>74.27706780790517</v>
       </c>
       <c r="D11" t="n">
-        <v>77.12020915940391</v>
+        <v>73.74397880449915</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>37.10122749119121</v>
+        <v>38.40302494702248</v>
       </c>
       <c r="C12" t="n">
-        <v>91.34278815082747</v>
+        <v>84.39986838639405</v>
       </c>
       <c r="D12" t="n">
-        <v>74.85335371029807</v>
+        <v>74.20245498238242</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.90251354430586</v>
       </c>
       <c r="C13" t="n">
-        <v>91.05709956889166</v>
+        <v>88.97579443588843</v>
       </c>
       <c r="D13" t="n">
-        <v>74.14649536324036</v>
+        <v>74.40665850486577</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>26.73397173434489</v>
+        <v>31.65056423721292</v>
       </c>
       <c r="C14" t="n">
-        <v>86.65494286304897</v>
+        <v>89.42052614591223</v>
       </c>
       <c r="D14" t="n">
-        <v>71.90516535444489</v>
+        <v>73.7488875430204</v>
       </c>
     </row>
     <row r="15">
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>22.57528845915541</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="C15" t="n">
-        <v>82.41771977151973</v>
+        <v>88.50946427637118</v>
       </c>
       <c r="D15" t="n">
-        <v>69.87589284976671</v>
+        <v>70.59256867386689</v>
       </c>
     </row>
     <row r="16">
@@ -2842,13 +2842,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>21.07910495788326</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="C16" t="n">
-        <v>79.35663042967818</v>
+        <v>86.79631453246051</v>
       </c>
       <c r="D16" t="n">
-        <v>64.47726222411352</v>
+        <v>68.19710427550467</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>21.24992905842221</v>
+        <v>20.77770841267949</v>
       </c>
       <c r="C17" t="n">
-        <v>79.80528913051897</v>
+        <v>83.5830542964607</v>
       </c>
       <c r="D17" t="n">
-        <v>56.6664774891259</v>
+        <v>63.74978717526663</v>
       </c>
     </row>
     <row r="18">
@@ -2870,13 +2870,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>21.93715245139498</v>
+        <v>20.33199495495144</v>
       </c>
       <c r="C18" t="n">
-        <v>83.46818981506381</v>
+        <v>81.86303231862028</v>
       </c>
       <c r="D18" t="n">
-        <v>45.47946239923349</v>
+        <v>55.1104073778947</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>24.07245370813179</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>89.06807872008763</v>
+        <v>83.04996529305467</v>
       </c>
       <c r="D19" t="n">
-        <v>31.89600116327462</v>
+        <v>45.13585070274711</v>
       </c>
     </row>
     <row r="20">
@@ -2898,13 +2898,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>53.12727701531613</v>
+        <v>91.45961612763284</v>
       </c>
       <c r="C20" t="n">
-        <v>229.3215374964911</v>
+        <v>371.8909391072129</v>
       </c>
       <c r="D20" t="n">
-        <v>12.10494919336317</v>
+        <v>49.09229395086174</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.536051576217024</v>
+        <v>14.6529411963389</v>
       </c>
       <c r="C21" t="n">
-        <v>13.76713712803527</v>
+        <v>71.89099274453774</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.747426474313544</v>
       </c>
     </row>
   </sheetData>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1109374905798896</v>
+        <v>0.1256637061435917</v>
       </c>
     </row>
     <row r="3">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.375829444277281</v>
+        <v>2.606540154775281</v>
       </c>
     </row>
     <row r="4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>13.05626271877833</v>
+        <v>12.91587279707104</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3190680038802134</v>
+        <v>0.2945243112740432</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09817477042468106</v>
+        <v>0.07363107781851079</v>
       </c>
       <c r="D5" t="n">
-        <v>33.28124717396688</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.012582793705962</v>
+        <v>1.771072858461246</v>
       </c>
       <c r="C6" t="n">
-        <v>1.127046364475339</v>
+        <v>0.9257880851047423</v>
       </c>
       <c r="D6" t="n">
-        <v>51.96488773348793</v>
+        <v>48.50324532831367</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.126506585127596</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>5.868887775987432</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="D7" t="n">
-        <v>63.18037350680348</v>
+        <v>58.62899114991527</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.02350519163969</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="D8" t="n">
-        <v>65.75746123045136</v>
+        <v>61.58503348740241</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29.06562253193106</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82499653339935</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>69.89061906533041</v>
+        <v>66.00780689503428</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38.00836236991527</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="C10" t="n">
-        <v>66.90610604442013</v>
+        <v>53.09782458418874</v>
       </c>
       <c r="D10" t="n">
-        <v>75.58966448848317</v>
+        <v>71.88847564347269</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>41.5809422656694</v>
+        <v>37.84931924182727</v>
       </c>
       <c r="C11" t="n">
-        <v>85.64963321390022</v>
+        <v>73.03319346662445</v>
       </c>
       <c r="D11" t="n">
-        <v>78.36408350068463</v>
+        <v>75.16554948024852</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>40.13875488813084</v>
+        <v>40.57268737340794</v>
       </c>
       <c r="C12" t="n">
-        <v>96.11604548887547</v>
+        <v>86.35256457014094</v>
       </c>
       <c r="D12" t="n">
-        <v>77.23998237932206</v>
+        <v>75.93818492349077</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>34.86186097780424</v>
+        <v>38.50414496055991</v>
       </c>
       <c r="C13" t="n">
-        <v>96.26036240139976</v>
+        <v>93.65873098514572</v>
       </c>
       <c r="D13" t="n">
-        <v>75.18714792974198</v>
+        <v>75.96763735461819</v>
       </c>
     </row>
     <row r="14">
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>28.88498095434966</v>
+        <v>34.41614752007619</v>
       </c>
       <c r="C14" t="n">
-        <v>93.10797052306326</v>
+        <v>94.02983161735102</v>
       </c>
       <c r="D14" t="n">
-        <v>73.7488875430204</v>
+        <v>75.28532270016666</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>24.36697801940583</v>
+        <v>29.74204670015712</v>
       </c>
       <c r="C15" t="n">
-        <v>87.07611262817085</v>
+        <v>93.1678571330223</v>
       </c>
       <c r="D15" t="n">
-        <v>70.59256867386689</v>
+        <v>72.02592032206724</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>21.90573652485908</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="C16" t="n">
-        <v>83.90310404804515</v>
+        <v>92.16941971780329</v>
       </c>
       <c r="D16" t="n">
-        <v>66.13052535806514</v>
+        <v>70.26368319294421</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>21.72214970416493</v>
+        <v>22.19437034990765</v>
       </c>
       <c r="C17" t="n">
-        <v>83.11083365071798</v>
+        <v>87.83304010814514</v>
       </c>
       <c r="D17" t="n">
-        <v>57.61091878061134</v>
+        <v>65.16644911249479</v>
       </c>
     </row>
     <row r="18">
@@ -3181,13 +3181,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>22.47220495020949</v>
+        <v>20.86704745376595</v>
       </c>
       <c r="C18" t="n">
-        <v>85.07334731150736</v>
+        <v>85.60839981032187</v>
       </c>
       <c r="D18" t="n">
-        <v>46.54956739686251</v>
+        <v>56.71556487433823</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>24.07245370813179</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>91.4753240909008</v>
+        <v>86.05902200657115</v>
       </c>
       <c r="D19" t="n">
-        <v>32.49781250597791</v>
+        <v>46.33947338815369</v>
       </c>
     </row>
     <row r="20">
@@ -3209,13 +3209,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>55.14476854754332</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="C20" t="n">
-        <v>239.4089951576271</v>
+        <v>392.0658544294849</v>
       </c>
       <c r="D20" t="n">
-        <v>12.77744637077223</v>
+        <v>53.12727701531613</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.543123919237478</v>
+        <v>15.06275980415863</v>
       </c>
       <c r="C21" t="n">
-        <v>14.53213668135702</v>
+        <v>75.31379902079314</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.2949787071597</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09621127501618741</v>
+        <v>0.1109374905798896</v>
       </c>
     </row>
     <row r="3">
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.135301256736813</v>
+        <v>2.385646921319749</v>
       </c>
     </row>
     <row r="4">
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>12.29049950946582</v>
+        <v>12.23944862884498</v>
       </c>
     </row>
     <row r="5">
@@ -3316,7 +3316,7 @@
         <v>0.04908738521234053</v>
       </c>
       <c r="D5" t="n">
-        <v>32.29949946972007</v>
+        <v>30.75324683553134</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.56981457909065</v>
+        <v>1.408807955594173</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8050331174823847</v>
+        <v>0.6440264939859077</v>
       </c>
       <c r="D6" t="n">
-        <v>52.76992085097032</v>
+        <v>48.82525857530663</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>4.551382356888213</v>
+        <v>3.53330998758427</v>
       </c>
       <c r="D7" t="n">
-        <v>64.67753875577986</v>
+        <v>60.06626978893259</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.27108553955913</v>
+        <v>12.35038611942487</v>
       </c>
       <c r="C8" t="n">
-        <v>15.52143120414207</v>
+        <v>11.34900346109313</v>
       </c>
       <c r="D8" t="n">
-        <v>68.84505776030758</v>
+        <v>63.75469591378786</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27.73437264497238</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="C9" t="n">
-        <v>36.72030938194344</v>
+        <v>26.84687272033327</v>
       </c>
       <c r="D9" t="n">
-        <v>71.55468142402876</v>
+        <v>67.67186925373262</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38.57777603837842</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="C10" t="n">
-        <v>63.48962403364123</v>
+        <v>48.68486865359933</v>
       </c>
       <c r="D10" t="n">
-        <v>77.72496574521999</v>
+        <v>73.16965639751479</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43.18020927588745</v>
+        <v>38.38240824523329</v>
       </c>
       <c r="C11" t="n">
-        <v>86.71581122071225</v>
+        <v>70.90083745300038</v>
       </c>
       <c r="D11" t="n">
-        <v>79.78565417643402</v>
+        <v>76.76481649046657</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>42.74234979979338</v>
+        <v>42.30841731451629</v>
       </c>
       <c r="C12" t="n">
-        <v>99.15357288581511</v>
+        <v>88.0882945112493</v>
       </c>
       <c r="D12" t="n">
-        <v>79.62661104834605</v>
+        <v>78.32481359251477</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>37.72365553568369</v>
+        <v>40.84561323518855</v>
       </c>
       <c r="C13" t="n">
-        <v>102.5042778004095</v>
+        <v>96.52052554302517</v>
       </c>
       <c r="D13" t="n">
-        <v>76.48796363786902</v>
+        <v>77.26845306274522</v>
       </c>
     </row>
     <row r="14">
@@ -3436,13 +3436,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>31.65056423721292</v>
+        <v>37.18173080293946</v>
       </c>
       <c r="C14" t="n">
-        <v>98.33185005736054</v>
+        <v>98.94642412021904</v>
       </c>
       <c r="D14" t="n">
-        <v>75.59260973159591</v>
+        <v>76.51447082588366</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>26.15866757965626</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>93.1678571330223</v>
+        <v>97.82624998967341</v>
       </c>
       <c r="D15" t="n">
-        <v>71.66758241001716</v>
+        <v>73.45927197026758</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>22.7323680918349</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="C16" t="n">
-        <v>88.44957766641213</v>
+        <v>97.54252490314609</v>
       </c>
       <c r="D16" t="n">
-        <v>67.78378849201677</v>
+        <v>71.50363054340794</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>22.19437034990765</v>
+        <v>23.61103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>85.94415752517428</v>
+        <v>92.55524656557229</v>
       </c>
       <c r="D17" t="n">
-        <v>58.55536007209676</v>
+        <v>66.58311104972293</v>
       </c>
     </row>
     <row r="18">
@@ -3492,13 +3492,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>22.47220495020949</v>
+        <v>21.40209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>87.7486098055799</v>
+        <v>89.35376730202346</v>
       </c>
       <c r="D18" t="n">
-        <v>47.61967239449154</v>
+        <v>58.32072237078177</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>24.07245370813179</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>92.67894677630738</v>
+        <v>89.66989006279091</v>
       </c>
       <c r="D19" t="n">
-        <v>33.09962384868121</v>
+        <v>47.54309607356029</v>
       </c>
     </row>
     <row r="20">
@@ -3520,13 +3520,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
+        <v>100.2020794339507</v>
+      </c>
+      <c r="C20" t="n">
+        <v>412.2407697517568</v>
+      </c>
+      <c r="D20" t="n">
         <v>57.16226007977053</v>
-      </c>
-      <c r="C20" t="n">
-        <v>252.8589387058084</v>
-      </c>
-      <c r="D20" t="n">
-        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.550412451038479</v>
+        <v>15.48006066048286</v>
       </c>
       <c r="C21" t="n">
-        <v>14.20944079864296</v>
+        <v>78.85155898933459</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.386263269480627</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08344855486097888</v>
+        <v>0.09817477042468103</v>
       </c>
     </row>
     <row r="3">
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.919316761802514</v>
+        <v>2.179479903427919</v>
       </c>
     </row>
     <row r="4">
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>11.52473630015331</v>
+        <v>11.56302446061893</v>
       </c>
     </row>
     <row r="5">
@@ -3627,7 +3627,7 @@
         <v>0.02454369260617027</v>
       </c>
       <c r="D5" t="n">
-        <v>31.24412068765475</v>
+        <v>29.94330497952772</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.207549676223577</v>
+        <v>1.127046364475339</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5635231822376693</v>
+        <v>0.4427682146153115</v>
       </c>
       <c r="D6" t="n">
-        <v>53.29319237733387</v>
+        <v>48.98626519880311</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>3.473423377625215</v>
+        <v>2.694897448157494</v>
       </c>
       <c r="D7" t="n">
-        <v>66.17470400475625</v>
+        <v>61.44366181799087</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>12.93452600345173</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="D8" t="n">
-        <v>71.8492057353028</v>
+        <v>65.92435834017331</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26.18124777685393</v>
+        <v>20.74531073843935</v>
       </c>
       <c r="C9" t="n">
-        <v>32.39374724932775</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>73.55155625446676</v>
+        <v>70.22343153707007</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38.15071578703105</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="C10" t="n">
-        <v>60.07314202286233</v>
+        <v>44.4142661401257</v>
       </c>
       <c r="D10" t="n">
-        <v>79.8602670019568</v>
+        <v>74.45083715155687</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>44.60177995163684</v>
+        <v>38.56010457970196</v>
       </c>
       <c r="C11" t="n">
-        <v>85.47193687943154</v>
+        <v>67.70230343256426</v>
       </c>
       <c r="D11" t="n">
-        <v>81.2072248521834</v>
+        <v>78.18638716621597</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>45.56291095409447</v>
+        <v>43.39324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>102.6250327680318</v>
+        <v>88.30526075388785</v>
       </c>
       <c r="D12" t="n">
-        <v>82.01323971737004</v>
+        <v>79.84357729098458</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>40.58545009356315</v>
+        <v>43.70740779306801</v>
       </c>
       <c r="C13" t="n">
-        <v>107.1872143496668</v>
+        <v>99.12215695927921</v>
       </c>
       <c r="D13" t="n">
-        <v>77.78877934599603</v>
+        <v>78.82943191249764</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>34.10886048864694</v>
+        <v>39.64002705437346</v>
       </c>
       <c r="C14" t="n">
-        <v>105.0921647488041</v>
+        <v>103.2484425602286</v>
       </c>
       <c r="D14" t="n">
-        <v>77.43633192017143</v>
+        <v>77.74361895160068</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27.95035713990669</v>
+        <v>34.75877746885832</v>
       </c>
       <c r="C15" t="n">
-        <v>98.1845879017235</v>
+        <v>103.5596565824748</v>
       </c>
       <c r="D15" t="n">
-        <v>72.74259614616741</v>
+        <v>74.89262361846794</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>23.97231544229862</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="C16" t="n">
-        <v>93.82268285175492</v>
+        <v>101.6756827380252</v>
       </c>
       <c r="D16" t="n">
-        <v>69.43705162596841</v>
+        <v>72.74357789387165</v>
       </c>
     </row>
     <row r="17">
@@ -3789,13 +3789,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>22.66659099565036</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="C17" t="n">
-        <v>89.2497020453733</v>
+        <v>97.74967366874218</v>
       </c>
       <c r="D17" t="n">
-        <v>59.4998013635822</v>
+        <v>67.99977298695107</v>
       </c>
     </row>
     <row r="18">
@@ -3803,13 +3803,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>23.007257449024</v>
+        <v>22.47220495020949</v>
       </c>
       <c r="C18" t="n">
-        <v>90.95892479846698</v>
+        <v>93.63418729253954</v>
       </c>
       <c r="D18" t="n">
-        <v>48.68977739212056</v>
+        <v>59.92587986722531</v>
       </c>
     </row>
     <row r="19">
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>24.67426505083508</v>
+        <v>21.66520833731861</v>
       </c>
       <c r="C19" t="n">
-        <v>95.08619214712057</v>
+        <v>93.28075811901068</v>
       </c>
       <c r="D19" t="n">
-        <v>34.3032465340878</v>
+        <v>49.34853010167016</v>
       </c>
     </row>
     <row r="20">
@@ -3831,13 +3831,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>59.17975161199771</v>
+        <v>102.8920681435869</v>
       </c>
       <c r="C20" t="n">
-        <v>262.9463963669444</v>
+        <v>433.0881822514378</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>61.19724314422491</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.557886163354232</v>
+        <v>16.89743923394463</v>
       </c>
       <c r="C21" t="n">
-        <v>14.98190467107479</v>
+        <v>82.00227863531953</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.478884548165071</v>
       </c>
     </row>
   </sheetData>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.650317890838888</v>
+        <v>1.619883712007237</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.899681807717578</v>
+        <v>1.880046853632642</v>
       </c>
       <c r="C3" t="n">
-        <v>3.450843180427539</v>
+        <v>3.485204350076177</v>
       </c>
       <c r="D3" t="n">
-        <v>10.78940726967245</v>
+        <v>10.58814899030185</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4.109595889977149</v>
+        <v>4.058545009356314</v>
       </c>
       <c r="C4" t="n">
-        <v>6.521749999311561</v>
+        <v>6.598326320242813</v>
       </c>
       <c r="D4" t="n">
-        <v>12.34155039008665</v>
+        <v>12.1118214272929</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5.841398840268522</v>
+        <v>5.792311455056182</v>
       </c>
       <c r="C5" t="n">
-        <v>11.70734137314322</v>
+        <v>11.83005983617407</v>
       </c>
       <c r="D5" t="n">
-        <v>22.35930396422111</v>
+        <v>21.94206118991621</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.211337798320324</v>
+        <v>8.090582830697967</v>
       </c>
       <c r="C6" t="n">
-        <v>12.67927160034756</v>
+        <v>12.80002656796992</v>
       </c>
       <c r="D6" t="n">
-        <v>21.89690079552086</v>
+        <v>21.49438423677967</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>18.38518925743002</v>
+        <v>18.56484908730718</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>21.27938148954961</v>
+        <v>21.52972715413255</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.98281156740907</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>55.1359328182051</v>
+        <v>54.1374954029861</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.252972112526189</v>
+        <v>9.110618695410402</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>44.12955930589413</v>
+        <v>43.2754388031994</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>48.33340297547896</v>
+        <v>47.44492130313559</v>
       </c>
     </row>
     <row r="12">
@@ -4033,10 +4033,10 @@
         <v>9.112582190818895</v>
       </c>
       <c r="C12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>50.77010077741955</v>
+        <v>49.90223580686537</v>
       </c>
     </row>
     <row r="13">
@@ -4047,10 +4047,10 @@
         <v>10.40652566501619</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.56104526967722</v>
       </c>
       <c r="D13" t="n">
-        <v>53.59360717483338</v>
+        <v>52.55295460833177</v>
       </c>
     </row>
     <row r="14">
@@ -4061,10 +4061,10 @@
         <v>12.29148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>39.02545299151496</v>
+        <v>39.64002705437346</v>
       </c>
       <c r="D14" t="n">
-        <v>51.93150831154353</v>
+        <v>50.70236018582652</v>
       </c>
     </row>
     <row r="15">
@@ -4075,10 +4075,10 @@
         <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>44.07556318216055</v>
+        <v>44.43390109421063</v>
       </c>
       <c r="D15" t="n">
-        <v>50.16730768701201</v>
+        <v>49.45063186291183</v>
       </c>
     </row>
     <row r="16">
@@ -4089,10 +4089,10 @@
         <v>15.70599977254047</v>
       </c>
       <c r="C16" t="n">
-        <v>49.18457823506095</v>
+        <v>49.59789401854886</v>
       </c>
       <c r="D16" t="n">
-        <v>46.2913677506456</v>
+        <v>45.46473618366979</v>
       </c>
     </row>
     <row r="17">
@@ -4103,10 +4103,10 @@
         <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>54.30537426041232</v>
+        <v>54.77759490615504</v>
       </c>
       <c r="D17" t="n">
-        <v>39.66653424238813</v>
+        <v>38.72209295090269</v>
       </c>
     </row>
     <row r="18">
@@ -4117,10 +4117,10 @@
         <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>58.85577486959629</v>
+        <v>59.92587986722531</v>
       </c>
       <c r="D18" t="n">
-        <v>29.96293993361265</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -4131,10 +4131,10 @@
         <v>19.25796296650543</v>
       </c>
       <c r="C19" t="n">
-        <v>66.19924769736242</v>
+        <v>67.40287038276901</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -4145,7 +4145,7 @@
         <v>20.17491532227195</v>
       </c>
       <c r="C20" t="n">
-        <v>71.28470080536088</v>
+        <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07264933011426397</v>
+        <v>0.08737554567796613</v>
       </c>
     </row>
     <row r="3">
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.737693436516855</v>
+        <v>1.992947839621025</v>
       </c>
     </row>
     <row r="4">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>10.73344765053038</v>
+        <v>10.9121257327033</v>
       </c>
     </row>
     <row r="5">
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>30.4587225242573</v>
+        <v>29.37880004958581</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9257880851047423</v>
+        <v>0.885536429230623</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3622649028670731</v>
+        <v>0.3220132469929539</v>
       </c>
       <c r="D6" t="n">
-        <v>53.05168244208915</v>
+        <v>48.98626519880311</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.311835917051991</v>
+        <v>3.593196597543325</v>
       </c>
       <c r="C7" t="n">
-        <v>2.635010838198439</v>
+        <v>2.036144738607885</v>
       </c>
       <c r="D7" t="n">
-        <v>68.27073535332319</v>
+        <v>62.58150740721292</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="D8" t="n">
-        <v>73.8519710519663</v>
+        <v>67.84367510197582</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24.73906039931537</v>
+        <v>19.30312336090078</v>
       </c>
       <c r="C9" t="n">
-        <v>28.39999758845172</v>
+        <v>20.1906232855399</v>
       </c>
       <c r="D9" t="n">
-        <v>76.43593100954388</v>
+        <v>71.88749389576842</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37.43894870145212</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="C10" t="n">
-        <v>56.22959976073607</v>
+        <v>40.14366362665208</v>
       </c>
       <c r="D10" t="n">
-        <v>81.14144775599888</v>
+        <v>76.01672473983054</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>45.66795795844887</v>
+        <v>38.56010457970196</v>
       </c>
       <c r="C11" t="n">
-        <v>83.69497353474482</v>
+        <v>63.97068040872215</v>
       </c>
       <c r="D11" t="n">
-        <v>83.51727720027614</v>
+        <v>79.60795784196534</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>47.73257338047992</v>
+        <v>44.2611134982632</v>
       </c>
       <c r="C12" t="n">
-        <v>105.0116614370558</v>
+        <v>87.43739578333366</v>
       </c>
       <c r="D12" t="n">
-        <v>83.31503717320132</v>
+        <v>81.36234098945441</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>43.4472446514426</v>
+        <v>46.04887606769665</v>
       </c>
       <c r="C13" t="n">
-        <v>111.6099877572987</v>
+        <v>100.9432989506571</v>
       </c>
       <c r="D13" t="n">
-        <v>80.13024762062467</v>
+        <v>80.39041076225007</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>37.18173080293946</v>
+        <v>42.09832330580748</v>
       </c>
       <c r="C14" t="n">
-        <v>111.5451924088184</v>
+        <v>106.9358869373796</v>
       </c>
       <c r="D14" t="n">
-        <v>78.35819301445918</v>
+        <v>79.28005410874692</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>30.10038461220721</v>
+        <v>37.26714285320892</v>
       </c>
       <c r="C15" t="n">
-        <v>103.5596565824748</v>
+        <v>109.2930631752762</v>
       </c>
       <c r="D15" t="n">
-        <v>74.53428570641785</v>
+        <v>77.04265109076844</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>25.21226279276234</v>
+        <v>32.23863111205676</v>
       </c>
       <c r="C16" t="n">
-        <v>97.95584068663399</v>
+        <v>106.2221563563921</v>
       </c>
       <c r="D16" t="n">
-        <v>70.26368319294421</v>
+        <v>73.57020946084748</v>
       </c>
     </row>
     <row r="17">
@@ -4411,13 +4411,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>23.13881164139307</v>
+        <v>27.38879745307752</v>
       </c>
       <c r="C17" t="n">
-        <v>93.97190850280046</v>
+        <v>102.4718801261693</v>
       </c>
       <c r="D17" t="n">
-        <v>60.91646330081034</v>
+        <v>68.9442142784365</v>
       </c>
     </row>
     <row r="18">
@@ -4428,10 +4428,10 @@
         <v>23.54230994783851</v>
       </c>
       <c r="C18" t="n">
-        <v>93.09913479372503</v>
+        <v>97.91460728305563</v>
       </c>
       <c r="D18" t="n">
-        <v>49.22482989093507</v>
+        <v>60.99598486485433</v>
       </c>
     </row>
     <row r="19">
@@ -4439,13 +4439,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.26701968002191</v>
       </c>
       <c r="C19" t="n">
-        <v>97.49343751793374</v>
+        <v>96.89162617523046</v>
       </c>
       <c r="D19" t="n">
-        <v>35.50686921949439</v>
+        <v>50.55215278707676</v>
       </c>
     </row>
     <row r="20">
@@ -4453,13 +4453,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>61.19724314422491</v>
+        <v>106.9270512080413</v>
       </c>
       <c r="C20" t="n">
-        <v>273.7063512054895</v>
+        <v>453.9355947511189</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>65.23222620867929</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.565517264293077</v>
+        <v>16.84133975878172</v>
       </c>
       <c r="C21" t="n">
-        <v>15.75960605208605</v>
+        <v>85.22738605201657</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4.082749032431932</v>
       </c>
     </row>
   </sheetData>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.319468914507713</v>
+        <v>1.29590696960579</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.040652566501619</v>
+        <v>1.030835089459151</v>
       </c>
       <c r="C3" t="n">
-        <v>1.448077863764045</v>
+        <v>1.462804079327747</v>
       </c>
       <c r="D3" t="n">
-        <v>10.2788984634641</v>
+        <v>10.08745766113598</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4.594579255875073</v>
+        <v>4.505240214788612</v>
       </c>
       <c r="C4" t="n">
-        <v>8.066039138091794</v>
+        <v>8.014988257470959</v>
       </c>
       <c r="D4" t="n">
-        <v>15.59604402966483</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.921321314940014</v>
+        <v>6.749515466696823</v>
       </c>
       <c r="C5" t="n">
-        <v>12.51728322914684</v>
+        <v>12.44365215132832</v>
       </c>
       <c r="D5" t="n">
-        <v>22.82563412373834</v>
+        <v>22.40839134943345</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.976119259928589</v>
+        <v>8.815112636432113</v>
       </c>
       <c r="C6" t="n">
-        <v>16.38242394076653</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>24.75476836258333</v>
+        <v>24.23149683621978</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.19879606234337</v>
+        <v>10.89936301254809</v>
       </c>
       <c r="C7" t="n">
         <v>18.98405535702057</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>12.51728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>24.03318379996192</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -4613,10 +4613,10 @@
         <v>12.64687392610741</v>
       </c>
       <c r="C9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>54.69218285588555</v>
+        <v>52.91718300660731</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11.10356653503143</v>
+        <v>11.388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -4641,10 +4641,10 @@
         <v>9.950994730245668</v>
       </c>
       <c r="C11" t="n">
-        <v>30.74146586308036</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>48.51109930994763</v>
       </c>
     </row>
     <row r="12">
@@ -4655,10 +4655,10 @@
         <v>9.76348091873453</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>51.63796574797373</v>
+        <v>51.20403326269664</v>
       </c>
     </row>
     <row r="13">
@@ -4669,10 +4669,10 @@
         <v>10.6666888066416</v>
       </c>
       <c r="C13" t="n">
-        <v>34.34153469455343</v>
+        <v>34.08137155292803</v>
       </c>
       <c r="D13" t="n">
-        <v>54.89442288296041</v>
+        <v>53.85377031645879</v>
       </c>
     </row>
     <row r="14">
@@ -4683,10 +4683,10 @@
         <v>12.29148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>39.64002705437346</v>
+        <v>39.94731408580272</v>
       </c>
       <c r="D14" t="n">
-        <v>53.77523050011904</v>
+        <v>52.54608237440203</v>
       </c>
     </row>
     <row r="15">
@@ -4697,10 +4697,10 @@
         <v>13.97517856995334</v>
       </c>
       <c r="C15" t="n">
-        <v>45.50891483036089</v>
+        <v>45.15057691831081</v>
       </c>
       <c r="D15" t="n">
-        <v>51.60065933521235</v>
+        <v>50.88398351111218</v>
       </c>
     </row>
     <row r="16">
@@ -4711,10 +4711,10 @@
         <v>15.70599977254047</v>
       </c>
       <c r="C16" t="n">
-        <v>50.42452558552468</v>
+        <v>50.83784136901258</v>
       </c>
       <c r="D16" t="n">
-        <v>47.53131510110933</v>
+        <v>47.94463088459723</v>
       </c>
     </row>
     <row r="17">
@@ -4739,7 +4739,7 @@
         <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>60.99598486485433</v>
+        <v>61.53103736366884</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>19.85977430920873</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
         <v>67.40287038276901</v>
       </c>
       <c r="D19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
     </row>
     <row r="20">
@@ -4764,13 +4764,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>20.84741249968101</v>
+        <v>20.17491532227195</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>0.672497177409065</v>
+        <v>2.68998870963626</v>
       </c>
     </row>
     <row r="21">
@@ -4778,10 +4778,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.417643684932394</v>
+        <v>4.252931054797182</v>
       </c>
       <c r="C21" t="n">
-        <v>6.379396582195773</v>
+        <v>18.42936790412113</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.06814150222053</v>
+        <v>1.04948829583984</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5841398840268521</v>
+        <v>0.5792311455056182</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6185010536754906</v>
+        <v>0.6430447462816609</v>
       </c>
       <c r="D3" t="n">
-        <v>9.576948854927634</v>
+        <v>9.400234268163208</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3.790527886096935</v>
+        <v>3.637375244234433</v>
       </c>
       <c r="C4" t="n">
-        <v>5.845325831085509</v>
+        <v>5.65388502875738</v>
       </c>
       <c r="D4" t="n">
-        <v>17.85504549713674</v>
+        <v>17.28072309015236</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7.903069019186825</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>14.38260386721577</v>
+        <v>14.21079801897258</v>
       </c>
       <c r="D5" t="n">
-        <v>24.1019061392592</v>
+        <v>23.6846633649543</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.14341728027805</v>
+        <v>9.821404033285093</v>
       </c>
       <c r="C6" t="n">
-        <v>18.8377749490878</v>
+        <v>18.6365166697172</v>
       </c>
       <c r="D6" t="n">
-        <v>27.25037102677872</v>
+        <v>26.60634453279281</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.27675504160636</v>
+        <v>11.97732199181109</v>
       </c>
       <c r="C7" t="n">
         <v>22.21793229480956</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.2849121228766</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80496066868692</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.42187377538564</v>
+        <v>14.53281126596553</v>
       </c>
       <c r="C9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>54.1374954029861</v>
+        <v>52.36249555370786</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13.09651437465245</v>
+        <v>13.38122120888403</v>
       </c>
       <c r="C10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.87306111317846</v>
       </c>
       <c r="D10" t="n">
-        <v>52.24370408149402</v>
+        <v>52.10135066437823</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.37256540599505</v>
+        <v>11.72795807493239</v>
       </c>
       <c r="C11" t="n">
-        <v>35.18387422479719</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="D11" t="n">
-        <v>51.70963333038374</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.1485313074443</v>
       </c>
       <c r="D12" t="n">
-        <v>53.15672944644355</v>
+        <v>52.50583071852791</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.18701508989241</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>36.68300296918207</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>56.19523859108743</v>
+        <v>55.67491230783662</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12.59876828859932</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>40.56188814866123</v>
+        <v>39.94731408580272</v>
       </c>
       <c r="D14" t="n">
-        <v>54.6970915944068</v>
+        <v>54.38980456297755</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="C15" t="n">
-        <v>46.58392856651115</v>
+        <v>46.22559065446107</v>
       </c>
       <c r="D15" t="n">
-        <v>53.03401098341269</v>
+        <v>52.31733515931252</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16.11931555602838</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="C16" t="n">
-        <v>52.49110450296421</v>
+        <v>51.66447293598839</v>
       </c>
       <c r="D16" t="n">
-        <v>49.18457823506095</v>
+        <v>49.59789401854886</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>17.47216389248049</v>
       </c>
       <c r="C17" t="n">
-        <v>57.13869813486862</v>
+        <v>56.6664774891259</v>
       </c>
       <c r="D17" t="n">
-        <v>42.02763747110171</v>
+        <v>42.97207876258714</v>
       </c>
     </row>
     <row r="18">
@@ -5053,7 +5053,7 @@
         <v>62.60114236129787</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>34.24335992412875</v>
       </c>
     </row>
     <row r="19">
@@ -5064,10 +5064,10 @@
         <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>69.2083044108789</v>
+        <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>19.25796296650543</v>
+        <v>21.06339699461531</v>
       </c>
     </row>
     <row r="20">
@@ -5075,13 +5075,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>23.53740120931727</v>
+        <v>28.91737862858979</v>
       </c>
       <c r="C20" t="n">
-        <v>86.75213588576938</v>
+        <v>108.9445427402685</v>
       </c>
       <c r="D20" t="n">
-        <v>2.017491532227195</v>
+        <v>5.37997741927252</v>
       </c>
     </row>
     <row r="21">
@@ -5089,10 +5089,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.417908103879842</v>
+        <v>4.26161113987446</v>
       </c>
       <c r="C21" t="n">
-        <v>6.380586467459286</v>
+        <v>18.11184734446645</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.86491972744144</v>
+        <v>0.860010988920206</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3288854809226815</v>
+        <v>0.3337942194439156</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2748893571891069</v>
+        <v>0.2945243112740431</v>
       </c>
       <c r="D3" t="n">
-        <v>8.771915737445251</v>
+        <v>8.6491972744144</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.820561154301086</v>
+        <v>2.667408512438584</v>
       </c>
       <c r="C4" t="n">
-        <v>3.624612524079224</v>
+        <v>3.496985322527139</v>
       </c>
       <c r="D4" t="n">
-        <v>19.36104647545135</v>
+        <v>18.55699510567321</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7.780350556155974</v>
+        <v>7.46128255227576</v>
       </c>
       <c r="C5" t="n">
-        <v>13.13087554430109</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D5" t="n">
-        <v>26.1635763181775</v>
+        <v>25.40272184738622</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.5119735799981</v>
+        <v>11.02895370950867</v>
       </c>
       <c r="C6" t="n">
-        <v>21.57488754852791</v>
+        <v>21.09186767803848</v>
       </c>
       <c r="D6" t="n">
-        <v>29.58496706747763</v>
+        <v>28.77993394999525</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.59426046070558</v>
+        <v>13.11516758103314</v>
       </c>
       <c r="C7" t="n">
-        <v>25.3919226226395</v>
+        <v>25.33203601268044</v>
       </c>
       <c r="D7" t="n">
-        <v>34.31502750653876</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.35453409442011</v>
+        <v>15.10418842983718</v>
       </c>
       <c r="C8" t="n">
-        <v>28.53940576245478</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D8" t="n">
-        <v>41.22358610132356</v>
+        <v>39.80496066868692</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.97499864350409</v>
+        <v>16.08593613408398</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>54.47030787472577</v>
+        <v>52.69530802544753</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.23181563138926</v>
+        <v>15.65887588273663</v>
       </c>
       <c r="C10" t="n">
-        <v>38.15071578703105</v>
+        <v>37.86600895279948</v>
       </c>
       <c r="D10" t="n">
-        <v>55.09077242380977</v>
+        <v>54.6637121724624</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13.14952875068177</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="C11" t="n">
-        <v>39.44858625204532</v>
+        <v>41.22554959673205</v>
       </c>
       <c r="D11" t="n">
-        <v>53.30890034060179</v>
+        <v>52.95350767166445</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.71617710248143</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="C12" t="n">
-        <v>38.18605870438393</v>
+        <v>40.13875488813084</v>
       </c>
       <c r="D12" t="n">
-        <v>54.89245938755191</v>
+        <v>54.02459441699772</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>11.70734137314322</v>
       </c>
       <c r="C13" t="n">
-        <v>39.28463438543612</v>
+        <v>39.80496066868693</v>
       </c>
       <c r="D13" t="n">
-        <v>57.49605429921446</v>
+        <v>56.71556487433823</v>
       </c>
     </row>
     <row r="14">
@@ -5302,10 +5302,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12.90605532002857</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>42.09832330580748</v>
+        <v>41.48374924294897</v>
       </c>
       <c r="D14" t="n">
         <v>56.23352675155306</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="C15" t="n">
-        <v>47.65894230266141</v>
+        <v>46.58392856651115</v>
       </c>
       <c r="D15" t="n">
-        <v>54.10902471956295</v>
+        <v>54.46736263161304</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16.53263133951629</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="C16" t="n">
-        <v>54.14436763691584</v>
+        <v>52.0777887194763</v>
       </c>
       <c r="D16" t="n">
-        <v>50.83784136901258</v>
+        <v>51.25115715250048</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="C17" t="n">
-        <v>58.55536007209676</v>
+        <v>58.08313942635404</v>
       </c>
       <c r="D17" t="n">
-        <v>43.44429940832985</v>
+        <v>44.860961345558</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>64.2062998577414</v>
+        <v>63.13619486011238</v>
       </c>
       <c r="D18" t="n">
-        <v>33.70830742531424</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="19">
@@ -5375,10 +5375,10 @@
         <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>70.41192709628548</v>
+        <v>69.8101157535822</v>
       </c>
       <c r="D19" t="n">
-        <v>20.46158565191202</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5386,13 +5386,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>26.22738991895353</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="C20" t="n">
-        <v>99.52958225654162</v>
+        <v>126.4294693529042</v>
       </c>
       <c r="D20" t="n">
-        <v>3.362485887045325</v>
+        <v>8.06996612890878</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.418670105715117</v>
+        <v>5.715060543117187</v>
       </c>
       <c r="C21" t="n">
-        <v>7.093350528575582</v>
+        <v>26.43215501191699</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.3571912839448242</v>
       </c>
     </row>
   </sheetData>
@@ -5451,7 +5451,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7088218424661971</v>
+        <v>0.7048948516492098</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.186532063806894</v>
+        <v>0.191440802328128</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1276272015520854</v>
+        <v>0.1374446785945534</v>
       </c>
       <c r="D3" t="n">
-        <v>7.966882619962866</v>
+        <v>7.863799111016951</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.990984344212531</v>
+        <v>1.901645303126072</v>
       </c>
       <c r="C4" t="n">
-        <v>2.144136986075034</v>
+        <v>2.067560665143783</v>
       </c>
       <c r="D4" t="n">
-        <v>20.16509784522949</v>
+        <v>19.25894471420968</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.921321314940014</v>
+        <v>6.45499115542278</v>
       </c>
       <c r="C5" t="n">
-        <v>10.234719816773</v>
+        <v>9.621127501618743</v>
       </c>
       <c r="D5" t="n">
-        <v>28.02889695624644</v>
+        <v>27.4889357189107</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.23650338573225</v>
+        <v>11.63272854762046</v>
       </c>
       <c r="C6" t="n">
-        <v>21.9774041072691</v>
+        <v>20.81010608691964</v>
       </c>
       <c r="D6" t="n">
-        <v>32.12082138754715</v>
+        <v>30.95352336719769</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.21119892960008</v>
+        <v>14.49255961009142</v>
       </c>
       <c r="C7" t="n">
-        <v>29.04500583014188</v>
+        <v>28.62579956042849</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>35.33309987584271</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.94005663677871</v>
+        <v>16.35591675275186</v>
       </c>
       <c r="C8" t="n">
-        <v>32.46148784092078</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>42.55876297909923</v>
+        <v>40.97324043674063</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.63906100220244</v>
+        <v>17.86093598336221</v>
       </c>
       <c r="C9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
-        <v>54.47030787472577</v>
+        <v>52.69530802544753</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17.22476347101029</v>
+        <v>17.65182372235765</v>
       </c>
       <c r="C10" t="n">
-        <v>40.71307729511523</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
-        <v>57.65313393189394</v>
+        <v>56.79901342919922</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.28188476430585</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="C11" t="n">
-        <v>43.18020927588745</v>
+        <v>44.42408361716816</v>
       </c>
       <c r="D11" t="n">
-        <v>55.79664902316321</v>
+        <v>55.97434535763188</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.23494080095125</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C12" t="n">
-        <v>42.52538355715483</v>
+        <v>44.91201222617883</v>
       </c>
       <c r="D12" t="n">
-        <v>55.97729060074463</v>
+        <v>55.54335811546754</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.48783079801943</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="C13" t="n">
-        <v>42.66675522656638</v>
+        <v>43.96757093469341</v>
       </c>
       <c r="D13" t="n">
-        <v>59.05703314896688</v>
+        <v>57.75621744083986</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="C14" t="n">
-        <v>44.24933252581224</v>
+        <v>43.94204549438299</v>
       </c>
       <c r="D14" t="n">
-        <v>58.07724894012857</v>
+        <v>57.76996190869932</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="C15" t="n">
-        <v>48.73395603881167</v>
+        <v>47.65894230266141</v>
       </c>
       <c r="D15" t="n">
-        <v>55.5423763677633</v>
+        <v>55.90071427981338</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16.94594712300419</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="C16" t="n">
-        <v>55.38431498737956</v>
+        <v>52.49110450296421</v>
       </c>
       <c r="D16" t="n">
-        <v>51.66447293598839</v>
+        <v>52.90442028645212</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="C17" t="n">
-        <v>60.91646330081034</v>
+        <v>59.02758071783948</v>
       </c>
       <c r="D17" t="n">
-        <v>44.860961345558</v>
+        <v>47.22206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.79694245613693</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>65.81145735418494</v>
+        <v>64.2062998577414</v>
       </c>
       <c r="D18" t="n">
-        <v>34.77841242294325</v>
+        <v>38.52377991464484</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>71.61554978169207</v>
+        <v>71.01373843898878</v>
       </c>
       <c r="D19" t="n">
-        <v>21.66520833731861</v>
+        <v>25.87788773624167</v>
       </c>
     </row>
     <row r="20">
@@ -5697,13 +5697,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>28.91737862858979</v>
+        <v>40.34983064454389</v>
       </c>
       <c r="C20" t="n">
-        <v>110.9620342724957</v>
+        <v>153.3293564492668</v>
       </c>
       <c r="D20" t="n">
-        <v>4.03498306445439</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.774856355571778</v>
+        <v>6.500870333669162</v>
       </c>
       <c r="C21" t="n">
-        <v>8.164339235630177</v>
+        <v>29.61507596449285</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.3611594629816202</v>
       </c>
     </row>
   </sheetData>
@@ -5762,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5811946409141118</v>
+        <v>0.5841398840268521</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1079922474671491</v>
+        <v>0.1129009859883832</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05890486225480862</v>
+        <v>0.06872233929727672</v>
       </c>
       <c r="D3" t="n">
-        <v>7.166758241001716</v>
+        <v>7.12257959431061</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.378373776762522</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C4" t="n">
-        <v>1.237983855055228</v>
+        <v>1.212458414744811</v>
       </c>
       <c r="D4" t="n">
-        <v>20.45864040879928</v>
+        <v>19.45038551653781</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5.718680377237671</v>
+        <v>5.325981295538947</v>
       </c>
       <c r="C5" t="n">
-        <v>7.485826244881931</v>
+        <v>6.872233929727674</v>
       </c>
       <c r="D5" t="n">
-        <v>30.11511082777092</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.11574841810989</v>
+        <v>11.18996033300515</v>
       </c>
       <c r="C6" t="n">
-        <v>19.96482131356314</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>33.32837106377072</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>31.26081039862693</v>
+        <v>30.00319158948677</v>
       </c>
       <c r="D7" t="n">
-        <v>37.90822410408209</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.77592484372025</v>
+        <v>17.85799074024948</v>
       </c>
       <c r="C8" t="n">
-        <v>36.55046702910875</v>
+        <v>35.63253292563798</v>
       </c>
       <c r="D8" t="n">
-        <v>44.14428552145782</v>
+        <v>42.22496875965531</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>19.41406085148067</v>
       </c>
       <c r="C9" t="n">
-        <v>39.60468413702056</v>
+        <v>38.82812170296133</v>
       </c>
       <c r="D9" t="n">
-        <v>55.24687030878498</v>
+        <v>52.91718300660731</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.92947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>43.56014563743098</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>59.21902152016762</v>
+        <v>58.50725443458867</v>
       </c>
     </row>
     <row r="11">
@@ -5882,10 +5882,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17.41424077792992</v>
+        <v>18.30272245027328</v>
       </c>
       <c r="C11" t="n">
-        <v>46.7341359652609</v>
+        <v>47.26722496866692</v>
       </c>
       <c r="D11" t="n">
         <v>58.28439770572462</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C12" t="n">
-        <v>46.86470840992573</v>
+        <v>49.03437083631119</v>
       </c>
       <c r="D12" t="n">
-        <v>57.92998678449154</v>
+        <v>57.49605429921445</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="C13" t="n">
-        <v>46.56920235094746</v>
+        <v>48.39034434232529</v>
       </c>
       <c r="D13" t="n">
-        <v>60.35784885709391</v>
+        <v>59.05703314896688</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>13.52062938288707</v>
       </c>
       <c r="C14" t="n">
-        <v>46.70762877724625</v>
+        <v>47.93677690296326</v>
       </c>
       <c r="D14" t="n">
-        <v>58.99911003441632</v>
+        <v>59.92097112870407</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15.0501923061036</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>50.16730768701201</v>
+        <v>49.09229395086175</v>
       </c>
       <c r="D15" t="n">
-        <v>56.97572801596364</v>
+        <v>57.33406592801372</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16.94594712300419</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="C16" t="n">
-        <v>56.62426233784328</v>
+        <v>53.73105185342793</v>
       </c>
       <c r="D16" t="n">
-        <v>52.90442028645212</v>
+        <v>54.55768342040375</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18.88882582970863</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="C17" t="n">
-        <v>62.33312523803849</v>
+        <v>59.02758071783948</v>
       </c>
       <c r="D17" t="n">
-        <v>45.80540263704344</v>
+        <v>49.11094715724245</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.79694245613693</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>67.41661485062848</v>
+        <v>65.81145735418494</v>
       </c>
       <c r="D18" t="n">
-        <v>36.38356991938679</v>
+        <v>40.66398990990288</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.66520833731861</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>73.42098380980195</v>
+        <v>71.01373843898878</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>28.28513310705485</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>31.60736733822606</v>
+        <v>46.40230524122548</v>
       </c>
       <c r="C20" t="n">
-        <v>123.739480643268</v>
+        <v>176.194260481175</v>
       </c>
       <c r="D20" t="n">
-        <v>4.707480241863455</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.77688956138736</v>
+        <v>7.698808409929637</v>
       </c>
       <c r="C21" t="n">
-        <v>8.529069894659326</v>
+        <v>34.82794280682455</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.7332198485647273</v>
       </c>
     </row>
   </sheetData>
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4820381227851839</v>
+        <v>0.4898921044191584</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.05890486225480862</v>
+        <v>0.06381360077604269</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02945243112740431</v>
+        <v>0.03436116964863836</v>
       </c>
       <c r="D3" t="n">
-        <v>6.440264939859076</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.8933904108645975</v>
       </c>
       <c r="C4" t="n">
         <v>0.714712328691678</v>
       </c>
       <c r="D4" t="n">
-        <v>20.3437759274024</v>
+        <v>19.29723287467531</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.58967051735384</v>
+        <v>4.196971435655115</v>
       </c>
       <c r="C5" t="n">
-        <v>5.178719139901926</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="D5" t="n">
-        <v>31.58773238414113</v>
+        <v>30.43417883165113</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.18996033300515</v>
+        <v>10.30442390377452</v>
       </c>
       <c r="C6" t="n">
-        <v>16.82519215538184</v>
+        <v>14.97361598517235</v>
       </c>
       <c r="D6" t="n">
-        <v>37.35353665118265</v>
+        <v>35.62271544859552</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>16.04961146902685</v>
       </c>
       <c r="C7" t="n">
-        <v>31.20092378866788</v>
+        <v>28.68568617038755</v>
       </c>
       <c r="D7" t="n">
-        <v>40.3036885024443</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.69524160552276</v>
+        <v>19.44351328260808</v>
       </c>
       <c r="C8" t="n">
-        <v>40.22220344299182</v>
+        <v>38.88702656521616</v>
       </c>
       <c r="D8" t="n">
-        <v>45.31256528951153</v>
+        <v>43.81049130201391</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21.41093568191868</v>
+        <v>21.1890607007589</v>
       </c>
       <c r="C9" t="n">
-        <v>43.93124626963626</v>
+        <v>42.71093387325747</v>
       </c>
       <c r="D9" t="n">
-        <v>56.24530772400399</v>
+        <v>53.36093296892687</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="C10" t="n">
-        <v>47.11898106532567</v>
+        <v>46.12250714551515</v>
       </c>
       <c r="D10" t="n">
-        <v>61.21196935978863</v>
+        <v>60.50020227420969</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="C11" t="n">
-        <v>50.28806265463436</v>
+        <v>49.57727731675966</v>
       </c>
       <c r="D11" t="n">
-        <v>60.06136105041135</v>
+        <v>60.4167537193487</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16.92336692580652</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="C12" t="n">
-        <v>51.20403326269664</v>
+        <v>53.37369568908209</v>
       </c>
       <c r="D12" t="n">
-        <v>59.88268296823844</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>14.56913593102267</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="C13" t="n">
-        <v>50.47164947532853</v>
+        <v>52.81311774995717</v>
       </c>
       <c r="D13" t="n">
-        <v>61.91882770684634</v>
+        <v>60.35784885709391</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="C14" t="n">
-        <v>50.39507315439727</v>
+        <v>52.23879534297279</v>
       </c>
       <c r="D14" t="n">
-        <v>60.53554519156258</v>
+        <v>61.15011925442109</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15.40853021815369</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="C15" t="n">
-        <v>52.31733515931252</v>
+        <v>51.95899724726244</v>
       </c>
       <c r="D15" t="n">
-        <v>57.69240384006381</v>
+        <v>59.12575548826415</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="C16" t="n">
-        <v>57.864209688307</v>
+        <v>55.38431498737956</v>
       </c>
       <c r="D16" t="n">
-        <v>54.55768342040375</v>
+        <v>56.62426233784328</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18.88882582970863</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="C17" t="n">
-        <v>63.74978717526663</v>
+        <v>59.97202200932491</v>
       </c>
       <c r="D17" t="n">
-        <v>47.22206457427158</v>
+        <v>50.52760909447059</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>20.33199495495144</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>69.021772347072</v>
+        <v>65.81145735418494</v>
       </c>
       <c r="D18" t="n">
-        <v>37.45367491701582</v>
+        <v>42.26914740634642</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.66520833731861</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>75.22641783791184</v>
+        <v>72.81917246709867</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>30.69237847786803</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>33.62485887045325</v>
+        <v>51.78228266049801</v>
       </c>
       <c r="C20" t="n">
-        <v>134.499435481813</v>
+        <v>198.3866673356742</v>
       </c>
       <c r="D20" t="n">
-        <v>5.37997741927252</v>
+        <v>18.15742379004475</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.135267339532545</v>
+        <v>8.587431170553046</v>
       </c>
       <c r="C21" t="n">
-        <v>9.608703027896452</v>
+        <v>39.95022327170331</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1.120099717898223</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3995713156284518</v>
+        <v>0.4113522880794135</v>
       </c>
     </row>
     <row r="3">
@@ -6398,7 +6398,7 @@
         <v>0.01472621556370216</v>
       </c>
       <c r="D3" t="n">
-        <v>5.753041546886308</v>
+        <v>5.807037670619883</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6381360077604268</v>
+        <v>0.5998478472948012</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4084070449666731</v>
+        <v>0.4211697651218816</v>
       </c>
       <c r="D4" t="n">
-        <v>19.93536888243573</v>
+        <v>18.88882582970863</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.583379120500858</v>
+        <v>3.264311116620645</v>
       </c>
       <c r="C5" t="n">
-        <v>3.485204350076178</v>
+        <v>3.166136346195964</v>
       </c>
       <c r="D5" t="n">
-        <v>33.08489763311751</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.94215900090745</v>
+        <v>8.976119259928589</v>
       </c>
       <c r="C6" t="n">
-        <v>13.4038014060817</v>
+        <v>11.79373517111693</v>
       </c>
       <c r="D6" t="n">
-        <v>39.48687441251096</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>15.92983824910874</v>
       </c>
       <c r="C7" t="n">
-        <v>29.16477905005999</v>
+        <v>25.75124228239384</v>
       </c>
       <c r="D7" t="n">
-        <v>42.93869934064274</v>
+        <v>41.44153409166636</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.28076414788136</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="C8" t="n">
-        <v>42.30841731451629</v>
+        <v>39.72151211382594</v>
       </c>
       <c r="D8" t="n">
-        <v>47.23188205131405</v>
+        <v>45.39601384437251</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23.51874800293658</v>
+        <v>22.85312305945724</v>
       </c>
       <c r="C9" t="n">
-        <v>48.47968338341173</v>
+        <v>46.59374604355361</v>
       </c>
       <c r="D9" t="n">
-        <v>56.68905768632355</v>
+        <v>54.0265579124062</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.91537407545231</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>49.82369599052563</v>
       </c>
       <c r="D10" t="n">
-        <v>63.20491719940966</v>
+        <v>61.639029611136</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22.0343454741154</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="C11" t="n">
-        <v>54.19738201294516</v>
+        <v>53.48659667507046</v>
       </c>
       <c r="D11" t="n">
         <v>62.54910973297276</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18.87606310955342</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="C12" t="n">
-        <v>55.54335811546754</v>
+        <v>56.41122308602172</v>
       </c>
       <c r="D12" t="n">
-        <v>61.18448042406971</v>
+        <v>61.40144666670826</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>16.1301147807751</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="C13" t="n">
-        <v>54.63425974133501</v>
+        <v>58.01638058246527</v>
       </c>
       <c r="D13" t="n">
-        <v>63.47980655659877</v>
+        <v>62.43915399009714</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="C14" t="n">
-        <v>53.77523050011904</v>
+        <v>56.23352675155306</v>
       </c>
       <c r="D14" t="n">
         <v>62.37926738013809</v>
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="C15" t="n">
-        <v>54.82570054366312</v>
+        <v>55.90071427981338</v>
       </c>
       <c r="D15" t="n">
-        <v>58.76741757621406</v>
+        <v>60.5591071364645</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17.77257868998001</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>59.51747282225863</v>
+        <v>57.03757812133119</v>
       </c>
       <c r="D16" t="n">
-        <v>55.79763077086746</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>19.36104647545135</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="C17" t="n">
-        <v>65.16644911249479</v>
+        <v>61.86090459229577</v>
       </c>
       <c r="D17" t="n">
-        <v>48.63872651149973</v>
+        <v>52.41649167744146</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>20.33199495495144</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>70.62692984351554</v>
+        <v>66.34650985299945</v>
       </c>
       <c r="D18" t="n">
-        <v>38.52377991464484</v>
+        <v>43.87430490278995</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>22.26701968002191</v>
+        <v>21.06339699461531</v>
       </c>
       <c r="C19" t="n">
-        <v>77.03185186602173</v>
+        <v>72.81917246709867</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>32.49781250597791</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>36.31484758008951</v>
+        <v>57.16226007977053</v>
       </c>
       <c r="C20" t="n">
-        <v>145.9318874977671</v>
+        <v>223.2690628998096</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>22.19240685449914</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.138774747422649</v>
+        <v>9.531692343365364</v>
       </c>
       <c r="C21" t="n">
-        <v>10.69387373711325</v>
+        <v>43.84578477948068</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1.143803081203844</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3495021827118645</v>
+        <v>0.01767145867644259</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01963495408493621</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004908738521234052</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>5.242532740677968</v>
+        <v>1.025926350937917</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4084070449666731</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2424916829489621</v>
+        <v>0.01276272015520854</v>
       </c>
       <c r="D4" t="n">
-        <v>18.31450342272425</v>
+        <v>7.963937376850126</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.478912953223197</v>
+        <v>0.2699806186678729</v>
       </c>
       <c r="C5" t="n">
-        <v>2.110757564130643</v>
+        <v>0.3190680038802134</v>
       </c>
       <c r="D5" t="n">
-        <v>32.20132469929538</v>
+        <v>22.2856728864026</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.688066271956774</v>
+        <v>1.650317890838888</v>
       </c>
       <c r="C6" t="n">
-        <v>8.855364292306232</v>
+        <v>2.576105975943631</v>
       </c>
       <c r="D6" t="n">
-        <v>40.21140421824511</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.97165248976386</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C7" t="n">
-        <v>22.39759212468673</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="D7" t="n">
-        <v>43.71722527011047</v>
+        <v>47.25053525769474</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.02903582496668</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>38.05254101660637</v>
+        <v>24.70077223884975</v>
       </c>
       <c r="D8" t="n">
-        <v>47.23188205131405</v>
+        <v>49.98568436172635</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24.62812290873548</v>
+        <v>13.42343636016663</v>
       </c>
       <c r="C9" t="n">
-        <v>49.69999577979051</v>
+        <v>41.26874649571891</v>
       </c>
       <c r="D9" t="n">
-        <v>55.46874528994476</v>
+        <v>53.24999547834697</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25.76596849795754</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="C10" t="n">
-        <v>53.95194508688347</v>
+        <v>52.24370408149402</v>
       </c>
       <c r="D10" t="n">
-        <v>62.63550353094652</v>
+        <v>60.21549543997811</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25.41057582902019</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="C11" t="n">
         <v>57.57361236784993</v>
       </c>
       <c r="D11" t="n">
-        <v>64.50376941212818</v>
+        <v>65.74764375340887</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>23.43235420496287</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="C12" t="n">
         <v>59.88268296823844</v>
       </c>
       <c r="D12" t="n">
-        <v>63.35414285045516</v>
+        <v>65.30683903420207</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20.29272504678157</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C13" t="n">
-        <v>61.91882770684634</v>
+        <v>61.65866456522093</v>
       </c>
       <c r="D13" t="n">
-        <v>64.00013283984957</v>
+        <v>63.73996969822417</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>17.8226478228966</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="C14" t="n">
-        <v>61.76469331727959</v>
+        <v>62.07198034870884</v>
       </c>
       <c r="D14" t="n">
-        <v>63.91570253728435</v>
+        <v>63.30112847442584</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16.48354395430394</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>59.48409340031424</v>
+        <v>59.84243131236433</v>
       </c>
       <c r="D15" t="n">
-        <v>61.99245878466483</v>
+        <v>61.63412087261475</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16.53263133951629</v>
+        <v>8.679631453246051</v>
       </c>
       <c r="C16" t="n">
-        <v>60.34410438923444</v>
+        <v>58.2775254717949</v>
       </c>
       <c r="D16" t="n">
-        <v>59.93078860574654</v>
+        <v>59.51747282225863</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.47216389248049</v>
+        <v>8.9721922691116</v>
       </c>
       <c r="C17" t="n">
-        <v>62.80534588378121</v>
+        <v>58.55536007209676</v>
       </c>
       <c r="D17" t="n">
-        <v>53.8331536146696</v>
+        <v>55.24981555189775</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>9.63094497866121</v>
       </c>
       <c r="C18" t="n">
-        <v>67.41661485062848</v>
+        <v>61.53103736366884</v>
       </c>
       <c r="D18" t="n">
-        <v>45.47946239923349</v>
+        <v>48.68977739212056</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>10.23079282595601</v>
       </c>
       <c r="C19" t="n">
-        <v>74.02279515250525</v>
+        <v>66.19924769736242</v>
       </c>
       <c r="D19" t="n">
-        <v>34.3032465340878</v>
+        <v>40.32135996112075</v>
       </c>
     </row>
     <row r="20">
@@ -1032,13 +1032,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>63.21473467645211</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C20" t="n">
-        <v>244.1164753994906</v>
+        <v>70.61220362795183</v>
       </c>
       <c r="D20" t="n">
-        <v>25.55489274154447</v>
+        <v>28.24488145118073</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.14435225073385</v>
+        <v>66.0769682322816</v>
       </c>
       <c r="C21" t="n">
-        <v>49.16109167663328</v>
+        <v>407.3102668646612</v>
       </c>
       <c r="D21" t="n">
-        <v>1.560669577035977</v>
+        <v>22.68313834839518</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2964878066825367</v>
+        <v>0.01178097245096173</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009817477042468103</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.717297718905924</v>
+        <v>0.8443030256522569</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2680171232593793</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1403899217072939</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>17.59979109403257</v>
+        <v>6.955682484588651</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.88986433067511</v>
+        <v>0.1472621556370216</v>
       </c>
       <c r="C5" t="n">
-        <v>1.423534171157875</v>
+        <v>0.1718058482431918</v>
       </c>
       <c r="D5" t="n">
-        <v>32.96217917008666</v>
+        <v>20.44489594093983</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6.400013283984958</v>
+        <v>1.127046364475339</v>
       </c>
       <c r="C6" t="n">
-        <v>6.561019907481435</v>
+        <v>1.690569546713008</v>
       </c>
       <c r="D6" t="n">
-        <v>41.94222542083224</v>
+        <v>37.27303333943441</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.71403368062369</v>
+        <v>3.832743037379548</v>
       </c>
       <c r="C7" t="n">
-        <v>18.50496247734813</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="D7" t="n">
-        <v>45.93302983859552</v>
+        <v>47.60985491744906</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.11248437982766</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>35.549084370777</v>
+        <v>20.27799883121787</v>
       </c>
       <c r="D8" t="n">
-        <v>49.06775025825559</v>
+        <v>51.57120690408495</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25.73749781453438</v>
+        <v>12.31406145436774</v>
       </c>
       <c r="C9" t="n">
-        <v>50.03280825153018</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>56.46718270516377</v>
+        <v>53.80468293124643</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27.61656292046278</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>58.50725443458867</v>
+        <v>51.38958357879929</v>
       </c>
       <c r="D10" t="n">
-        <v>63.77433086787281</v>
+        <v>59.93078860574654</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27.8983245115816</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="C11" t="n">
-        <v>61.48293172616073</v>
+        <v>59.70596838147401</v>
       </c>
       <c r="D11" t="n">
-        <v>66.2807327568149</v>
+        <v>65.5699474189402</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>25.81898287398687</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="C12" t="n">
-        <v>64.00504157837081</v>
+        <v>62.92021036517807</v>
       </c>
       <c r="D12" t="n">
-        <v>65.30683903420207</v>
+        <v>66.3916702473948</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22.63419332141022</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="C13" t="n">
-        <v>66.34160111447822</v>
+        <v>64.52045912310038</v>
       </c>
       <c r="D13" t="n">
-        <v>66.08143797285281</v>
+        <v>64.00013283984957</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>19.97365704290136</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="C14" t="n">
-        <v>66.06671175728911</v>
+        <v>64.2229895687136</v>
       </c>
       <c r="D14" t="n">
-        <v>65.14485066300135</v>
+        <v>63.30112847442584</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>17.5585576904542</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>64.85916208106552</v>
+        <v>63.42581043286518</v>
       </c>
       <c r="D15" t="n">
-        <v>63.42581043286518</v>
+        <v>62.35079669671492</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16.94594712300419</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>63.23731487364979</v>
+        <v>61.17073595621026</v>
       </c>
       <c r="D16" t="n">
-        <v>61.17073595621026</v>
+        <v>59.51747282225863</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.9443845382232</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="C17" t="n">
-        <v>64.69422846675207</v>
+        <v>60.44424265506763</v>
       </c>
       <c r="D17" t="n">
-        <v>55.72203619764046</v>
+        <v>55.24981555189775</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>69.021772347072</v>
+        <v>61.53103736366884</v>
       </c>
       <c r="D18" t="n">
-        <v>47.08461989567702</v>
+        <v>48.68977739212056</v>
       </c>
     </row>
     <row r="19">
@@ -1329,13 +1329,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>9.628981483252716</v>
       </c>
       <c r="C19" t="n">
-        <v>74.62460649520854</v>
+        <v>66.19924769736242</v>
       </c>
       <c r="D19" t="n">
-        <v>36.10868056219768</v>
+        <v>40.92317130382404</v>
       </c>
     </row>
     <row r="20">
@@ -1343,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>67.92221491831556</v>
+        <v>10.08745766113597</v>
       </c>
       <c r="C20" t="n">
-        <v>268.998870963626</v>
+        <v>70.61220362795183</v>
       </c>
       <c r="D20" t="n">
-        <v>29.58987580599885</v>
+        <v>28.91737862858979</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.1981749856567</v>
+        <v>71.21669864648854</v>
       </c>
       <c r="C21" t="n">
-        <v>51.99152671912039</v>
+        <v>450.6999642913489</v>
       </c>
       <c r="D21" t="n">
-        <v>1.599739283665243</v>
+        <v>27.46929804935986</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2542726553999239</v>
+        <v>0.007853981633974483</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004908738521234052</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.260785036431157</v>
+        <v>0.7019496085364695</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1786780821729195</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0765763209312512</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>16.84679060487526</v>
+        <v>6.036766633413637</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.398990478551705</v>
+        <v>0.07363107781851079</v>
       </c>
       <c r="C5" t="n">
-        <v>0.93266031903447</v>
+        <v>0.07363107781851079</v>
       </c>
       <c r="D5" t="n">
-        <v>33.08489763311751</v>
+        <v>18.6532063806894</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.27296691950962</v>
+        <v>0.7647814616082653</v>
       </c>
       <c r="C6" t="n">
-        <v>4.870450360768428</v>
+        <v>1.086794708601219</v>
       </c>
       <c r="D6" t="n">
-        <v>43.63279496754524</v>
+        <v>35.90447703971436</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.39652826152447</v>
+        <v>2.87455727803466</v>
       </c>
       <c r="C7" t="n">
-        <v>14.97165248976386</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="D7" t="n">
-        <v>48.20872101703962</v>
+        <v>48.14883440708056</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.44489594093983</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D8" t="n">
-        <v>51.15396412978005</v>
+        <v>52.40569245269473</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26.40312275801371</v>
+        <v>10.98281156740907</v>
       </c>
       <c r="C9" t="n">
-        <v>49.36718330805084</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>58.242182554442</v>
+        <v>54.58124536530566</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29.60951076008381</v>
+        <v>13.95063487734718</v>
       </c>
       <c r="C10" t="n">
-        <v>60.64255569132548</v>
+        <v>49.68134257340984</v>
       </c>
       <c r="D10" t="n">
-        <v>64.77080478768332</v>
+        <v>59.78843518863076</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29.852984190737</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="C11" t="n">
-        <v>66.45842909128358</v>
+        <v>60.59445005381736</v>
       </c>
       <c r="D11" t="n">
-        <v>67.87999976703294</v>
+        <v>65.92534008787754</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28.42257778564941</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="C12" t="n">
-        <v>68.12740018850316</v>
+        <v>65.74077151947915</v>
       </c>
       <c r="D12" t="n">
-        <v>67.25953521794898</v>
+        <v>66.60863649003335</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>25.49598787928967</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="C13" t="n">
-        <v>70.24404823885929</v>
+        <v>66.86192739772903</v>
       </c>
       <c r="D13" t="n">
-        <v>67.64241682260524</v>
+        <v>64.52045912310038</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>21.81737923147687</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>71.2905912915864</v>
+        <v>67.60314691443537</v>
       </c>
       <c r="D14" t="n">
-        <v>66.68128582014761</v>
+        <v>63.91570253728435</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>18.99190933865455</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>69.15921702566655</v>
+        <v>66.29251372926586</v>
       </c>
       <c r="D15" t="n">
-        <v>64.85916208106552</v>
+        <v>61.99245878466483</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17.77257868998001</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>67.78378849201677</v>
+        <v>64.06394644062561</v>
       </c>
       <c r="D16" t="n">
-        <v>63.23731487364979</v>
+        <v>59.51747282225863</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.9443845382232</v>
+        <v>8.02775097762617</v>
       </c>
       <c r="C17" t="n">
-        <v>67.05533169546565</v>
+        <v>61.86090459229577</v>
       </c>
       <c r="D17" t="n">
-        <v>57.13869813486862</v>
+        <v>55.24981555189775</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="C18" t="n">
-        <v>70.09187734470103</v>
+        <v>62.60114236129787</v>
       </c>
       <c r="D18" t="n">
-        <v>48.68977739212056</v>
+        <v>49.22482989093507</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +1640,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>9.027170140549421</v>
       </c>
       <c r="C19" t="n">
-        <v>76.43004052331844</v>
+        <v>66.19924769736242</v>
       </c>
       <c r="D19" t="n">
-        <v>37.91411459030757</v>
+        <v>40.92317130382404</v>
       </c>
     </row>
     <row r="20">
@@ -1654,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>73.30219233758808</v>
+        <v>9.41496048372691</v>
       </c>
       <c r="C20" t="n">
-        <v>288.5012891084889</v>
+        <v>70.61220362795183</v>
       </c>
       <c r="D20" t="n">
-        <v>32.95236169304418</v>
+        <v>29.58987580599885</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.90287565822136</v>
+        <v>76.54525595093422</v>
       </c>
       <c r="C21" t="n">
-        <v>57.46215835003414</v>
+        <v>494.9227508060404</v>
       </c>
       <c r="D21" t="n">
-        <v>2.052219941072648</v>
+        <v>32.50551965039672</v>
       </c>
     </row>
   </sheetData>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2179479903427919</v>
+        <v>0.004908738521234052</v>
       </c>
     </row>
     <row r="3">
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3.838633523605029</v>
+        <v>0.5792311455056182</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1148644813968768</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0382881604656256</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>16.02997651494192</v>
+        <v>5.219952543480291</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.030835089459151</v>
+        <v>0.02454369260617027</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6135923151542566</v>
+        <v>0.02454369260617027</v>
       </c>
       <c r="D5" t="n">
-        <v>33.30579086657305</v>
+        <v>16.95969159086365</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.266675522656639</v>
+        <v>0.4830198704894308</v>
       </c>
       <c r="C6" t="n">
-        <v>3.542145716922492</v>
+        <v>0.684278149860027</v>
       </c>
       <c r="D6" t="n">
-        <v>45.00135126726531</v>
+        <v>34.69692736349078</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.95924962250714</v>
+        <v>2.09603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>11.91743538185203</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="D7" t="n">
-        <v>50.36463897556562</v>
+        <v>47.84940135728529</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.3600647277471</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>27.70492021384499</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="D8" t="n">
         <v>53.15672944644354</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26.62499773917349</v>
+        <v>9.540624189870499</v>
       </c>
       <c r="C9" t="n">
-        <v>46.48280855297372</v>
+        <v>28.28906009787183</v>
       </c>
       <c r="D9" t="n">
-        <v>59.46249495082079</v>
+        <v>55.35780779936488</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31.17539834835747</v>
+        <v>12.95416095753666</v>
       </c>
       <c r="C10" t="n">
-        <v>62.20844327959914</v>
+        <v>46.40721397974673</v>
       </c>
       <c r="D10" t="n">
-        <v>66.05198554172541</v>
+        <v>60.35784885709391</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31.98534020436108</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="C11" t="n">
-        <v>69.83465944618834</v>
+        <v>60.4167537193487</v>
       </c>
       <c r="D11" t="n">
-        <v>69.479266777251</v>
+        <v>65.5699474189402</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30.8092064546734</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="C12" t="n">
-        <v>72.90065752655116</v>
+        <v>67.04256897531043</v>
       </c>
       <c r="D12" t="n">
-        <v>69.21223140169589</v>
+        <v>66.82560273267188</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>28.35778243716912</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="C13" t="n">
-        <v>74.92698478811657</v>
+        <v>70.24404823885929</v>
       </c>
       <c r="D13" t="n">
-        <v>69.98388509723388</v>
+        <v>64.78062226472579</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>24.27567548291088</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>75.28532270016666</v>
+        <v>70.67601722872789</v>
       </c>
       <c r="D14" t="n">
-        <v>68.21772097729388</v>
+        <v>64.53027660014286</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>20.78359889890498</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>74.17594779436774</v>
+        <v>69.51755493771664</v>
       </c>
       <c r="D15" t="n">
-        <v>66.29251372926586</v>
+        <v>61.99245878466483</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19.01252604044373</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>72.74357789387165</v>
+        <v>66.54384114155305</v>
       </c>
       <c r="D16" t="n">
-        <v>64.47726222411352</v>
+        <v>59.51747282225863</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18.41660518396592</v>
+        <v>7.555530331883453</v>
       </c>
       <c r="C17" t="n">
-        <v>70.36087621566466</v>
+        <v>64.69422846675207</v>
       </c>
       <c r="D17" t="n">
-        <v>58.55536007209676</v>
+        <v>55.72203619764046</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>72.76713983877359</v>
+        <v>64.2062998577414</v>
       </c>
       <c r="D18" t="n">
-        <v>50.2949348885641</v>
+        <v>49.22482989093507</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>77.03185186602173</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>39.71954861841746</v>
+        <v>40.92317130382404</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.00967257945153</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>310.693695962988</v>
+        <v>70.61220362795183</v>
       </c>
       <c r="D20" t="n">
-        <v>36.98734475749858</v>
+        <v>30.26237298340792</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>12.64777413284112</v>
+        <v>82.06085116214253</v>
       </c>
       <c r="C21" t="n">
-        <v>61.1309083087321</v>
+        <v>540.9537688451765</v>
       </c>
       <c r="D21" t="n">
-        <v>2.107962355473521</v>
+        <v>37.79118145624985</v>
       </c>
     </row>
   </sheetData>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1894773069196344</v>
+        <v>0.002945243112740431</v>
       </c>
     </row>
     <row r="3">
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3.480295611554943</v>
+        <v>0.476147636559703</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0765763209312512</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01276272015520854</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>15.23868786531899</v>
+        <v>4.505240214788612</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7608544707912782</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3926990816987243</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>32.96217917008666</v>
+        <v>15.51161372709961</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.461642405174254</v>
+        <v>0.2817615911188346</v>
       </c>
       <c r="C6" t="n">
-        <v>2.576105975943631</v>
+        <v>0.4025165587411924</v>
       </c>
       <c r="D6" t="n">
-        <v>46.249152599363</v>
+        <v>33.04660947265189</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>1.497165248976386</v>
       </c>
       <c r="C7" t="n">
-        <v>9.402197763571703</v>
+        <v>2.694897448157494</v>
       </c>
       <c r="D7" t="n">
-        <v>52.52055693409162</v>
+        <v>47.37030847761284</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.02488784997144</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>23.53249247079604</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="D8" t="n">
-        <v>55.32639187282899</v>
+        <v>53.7408693304704</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26.5140602485936</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>43.37655881673681</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>61.4593697812588</v>
+        <v>56.68905768632355</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>32.02951885105219</v>
+        <v>11.67298020349457</v>
       </c>
       <c r="C10" t="n">
-        <v>61.21196935978863</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>67.19081287865171</v>
+        <v>60.35784885709391</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>33.93999988351647</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="C11" t="n">
-        <v>72.50010446321843</v>
+        <v>58.28439770572462</v>
       </c>
       <c r="D11" t="n">
-        <v>70.90083745300038</v>
+        <v>65.39225108447152</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33.41280136633594</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="C12" t="n">
-        <v>77.89088110723767</v>
+        <v>68.56133267378024</v>
       </c>
       <c r="D12" t="n">
-        <v>70.94796134280425</v>
+        <v>67.04256897531043</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>30.69925071179776</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="C13" t="n">
-        <v>79.08959505412305</v>
+        <v>72.84567965511333</v>
       </c>
       <c r="D13" t="n">
-        <v>71.54486394698631</v>
+        <v>65.82127483122741</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>26.73397173434489</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="C14" t="n">
-        <v>79.89462817160543</v>
+        <v>73.13431348016189</v>
       </c>
       <c r="D14" t="n">
-        <v>69.75415613444012</v>
+        <v>64.53027660014286</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>22.93362637120549</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>79.55101647511904</v>
+        <v>72.74259614616741</v>
       </c>
       <c r="D15" t="n">
-        <v>67.72586537746622</v>
+        <v>61.99245878466483</v>
       </c>
     </row>
     <row r="16">
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20.25247339090745</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>76.87673572875073</v>
+        <v>69.85036740945631</v>
       </c>
       <c r="D16" t="n">
-        <v>65.71720957457724</v>
+        <v>59.93078860574654</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18.88882582970863</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>75.08308267309182</v>
+        <v>67.05533169546565</v>
       </c>
       <c r="D17" t="n">
-        <v>60.91646330081034</v>
+        <v>55.72203619764046</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>74.90734983403163</v>
+        <v>65.27640485537043</v>
       </c>
       <c r="D18" t="n">
-        <v>51.90009238500763</v>
+        <v>49.22482989093507</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>7.221736112439537</v>
       </c>
       <c r="C19" t="n">
-        <v>78.23547455142831</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>41.52498264652733</v>
+        <v>40.92317130382404</v>
       </c>
     </row>
     <row r="20">
@@ -2276,13 +2276,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>82.717152821315</v>
+        <v>8.06996612890878</v>
       </c>
       <c r="C20" t="n">
-        <v>332.8861028174872</v>
+        <v>70.61220362795183</v>
       </c>
       <c r="D20" t="n">
-        <v>41.02232782195296</v>
+        <v>30.93487016081699</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.43147764980463</v>
+        <v>86.64852067731151</v>
       </c>
       <c r="C21" t="n">
-        <v>63.69120046842841</v>
+        <v>587.6547107474075</v>
       </c>
       <c r="D21" t="n">
-        <v>2.599640835446057</v>
+        <v>42.21338186843381</v>
       </c>
     </row>
   </sheetData>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1639518666092173</v>
+        <v>0.001963495408493621</v>
       </c>
     </row>
     <row r="3">
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3.146501392111027</v>
+        <v>0.3926990816987241</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05105088062083414</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>14.42187377538565</v>
+        <v>3.918155087649021</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.564504929941916</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2454369260617026</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>32.81491701444964</v>
+        <v>14.01444847812322</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.777364255314227</v>
+        <v>0.1610066234964769</v>
       </c>
       <c r="C6" t="n">
-        <v>1.851576170209485</v>
+        <v>0.2415099352447154</v>
       </c>
       <c r="D6" t="n">
-        <v>47.17494068446774</v>
+        <v>31.31578827006476</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.204465564390594</v>
+        <v>1.018072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>7.366053024963818</v>
+        <v>1.856484908730718</v>
       </c>
       <c r="D7" t="n">
-        <v>54.43692845278139</v>
+        <v>46.65166915810418</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.52281386247382</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="C8" t="n">
-        <v>19.94420461177395</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="D8" t="n">
-        <v>57.41260574435346</v>
+        <v>54.74225198880214</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25.95937279569415</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>19.74687332322034</v>
       </c>
       <c r="D9" t="n">
-        <v>62.90155715879737</v>
+        <v>57.243745139223</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>32.59893251951534</v>
+        <v>10.53415286656828</v>
       </c>
       <c r="C10" t="n">
-        <v>59.21902152016762</v>
+        <v>37.29659528433633</v>
       </c>
       <c r="D10" t="n">
-        <v>68.4719936326938</v>
+        <v>60.50020227420969</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>35.53926689373453</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="C11" t="n">
-        <v>74.45476414237383</v>
+        <v>55.79664902316321</v>
       </c>
       <c r="D11" t="n">
-        <v>72.32240812874977</v>
+        <v>65.21455475000286</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>36.01639627799849</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C12" t="n">
-        <v>81.36234098945441</v>
+        <v>68.56133267378024</v>
       </c>
       <c r="D12" t="n">
-        <v>72.68369128391259</v>
+        <v>67.69346770322606</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>33.30088212805181</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="C13" t="n">
-        <v>83.77253160338033</v>
+        <v>74.40665850486577</v>
       </c>
       <c r="D13" t="n">
-        <v>73.10584279673874</v>
+        <v>65.82127483122741</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>29.19226798577891</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="C14" t="n">
-        <v>85.11850770590272</v>
+        <v>76.51447082588366</v>
       </c>
       <c r="D14" t="n">
-        <v>72.21245238587414</v>
+        <v>64.53027660014286</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>25.083653843506</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>83.85107141972007</v>
+        <v>75.6092994425681</v>
       </c>
       <c r="D15" t="n">
-        <v>69.15921702566655</v>
+        <v>61.99245878466483</v>
       </c>
     </row>
     <row r="16">
@@ -2531,13 +2531,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>21.90573652485908</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>81.42320934711771</v>
+        <v>73.15689367735958</v>
       </c>
       <c r="D16" t="n">
-        <v>66.95715692504096</v>
+        <v>60.34410438923444</v>
       </c>
     </row>
     <row r="17">
@@ -2545,13 +2545,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>19.83326712119407</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>79.80528913051897</v>
+        <v>69.41643492417923</v>
       </c>
       <c r="D17" t="n">
-        <v>62.33312523803849</v>
+        <v>55.72203619764046</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.79694245613693</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="C18" t="n">
-        <v>78.1176648269187</v>
+        <v>67.41661485062848</v>
       </c>
       <c r="D18" t="n">
-        <v>53.50524988145117</v>
+        <v>49.22482989093507</v>
       </c>
     </row>
     <row r="19">
@@ -2573,13 +2573,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>6.619924769736241</v>
       </c>
       <c r="C19" t="n">
-        <v>80.0409085795382</v>
+        <v>67.40287038276901</v>
       </c>
       <c r="D19" t="n">
-        <v>43.33041667463722</v>
+        <v>41.52498264652733</v>
       </c>
     </row>
     <row r="20">
@@ -2587,13 +2587,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>87.42463306317845</v>
+        <v>7.397468951499714</v>
       </c>
       <c r="C20" t="n">
-        <v>352.3885209623501</v>
+        <v>69.93970645054276</v>
       </c>
       <c r="D20" t="n">
-        <v>45.05731088640735</v>
+        <v>31.60736733822606</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.80749484176391</v>
+        <v>91.35545778226893</v>
       </c>
       <c r="C21" t="n">
-        <v>68.14666808999606</v>
+        <v>636.0623748090475</v>
       </c>
       <c r="D21" t="n">
-        <v>2.672418356470434</v>
+        <v>47.96161533569119</v>
       </c>
     </row>
   </sheetData>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1433351648200343</v>
+        <v>0.0009817477042468104</v>
       </c>
     </row>
     <row r="3">
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.866703296400686</v>
+        <v>0.3288854809226815</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02552544031041707</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>13.66887328622834</v>
+        <v>3.39488356128547</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4172427743048945</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1472621556370216</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>32.20132469929538</v>
+        <v>12.64000169217769</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.213841073076558</v>
+        <v>0.08050331174823847</v>
       </c>
       <c r="C6" t="n">
-        <v>1.328304643845935</v>
+        <v>0.1207549676223577</v>
       </c>
       <c r="D6" t="n">
-        <v>47.93972214607601</v>
+        <v>29.54471541160352</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.006733365209485</v>
+        <v>0.7186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>5.809001166028376</v>
+        <v>1.257618809140164</v>
       </c>
       <c r="D7" t="n">
-        <v>56.2934133615121</v>
+        <v>46.11268966847268</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.18763698469816</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>16.6062624173348</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="D8" t="n">
-        <v>59.58226817073891</v>
+        <v>54.82570054366312</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24.73906039931537</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>34.72343455150543</v>
+        <v>15.97499864350409</v>
       </c>
       <c r="D9" t="n">
-        <v>64.45468202691582</v>
+        <v>57.90937008270233</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
+        <v>9.252972112526189</v>
+      </c>
+      <c r="C10" t="n">
         <v>32.74128593663113</v>
       </c>
-      <c r="C10" t="n">
-        <v>56.65666001208344</v>
-      </c>
       <c r="D10" t="n">
-        <v>70.60729488943061</v>
+        <v>60.78490910844128</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>36.96083756948391</v>
+        <v>12.08335074386974</v>
       </c>
       <c r="C11" t="n">
-        <v>74.27706780790517</v>
+        <v>52.06502599932108</v>
       </c>
       <c r="D11" t="n">
-        <v>73.74397880449915</v>
+        <v>65.74764375340887</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>38.40302494702248</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="C12" t="n">
-        <v>84.39986838639405</v>
+        <v>67.04256897531043</v>
       </c>
       <c r="D12" t="n">
-        <v>74.20245498238242</v>
+        <v>67.47650146058751</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>35.90251354430586</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C13" t="n">
-        <v>88.97579443588843</v>
+        <v>75.96763735461819</v>
       </c>
       <c r="D13" t="n">
-        <v>74.40665850486577</v>
+        <v>66.08143797285281</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>31.65056423721292</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="C14" t="n">
-        <v>89.42052614591223</v>
+        <v>79.28005410874692</v>
       </c>
       <c r="D14" t="n">
-        <v>73.7488875430204</v>
+        <v>64.53027660014286</v>
       </c>
     </row>
     <row r="15">
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27.23368131580652</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>88.50946427637118</v>
+        <v>78.83434065101888</v>
       </c>
       <c r="D15" t="n">
-        <v>70.59256867386689</v>
+        <v>62.70913460876501</v>
       </c>
     </row>
     <row r="16">
@@ -2842,13 +2842,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>23.97231544229862</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>86.79631453246051</v>
+        <v>75.63678837828701</v>
       </c>
       <c r="D16" t="n">
-        <v>68.19710427550467</v>
+        <v>59.93078860574654</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20.77770841267949</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>83.5830542964607</v>
+        <v>72.72197944437823</v>
       </c>
       <c r="D17" t="n">
-        <v>63.74978717526663</v>
+        <v>55.72203619764046</v>
       </c>
     </row>
     <row r="18">
@@ -2870,13 +2870,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>20.33199495495144</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>81.86303231862028</v>
+        <v>69.55682484588651</v>
       </c>
       <c r="D18" t="n">
-        <v>55.1104073778947</v>
+        <v>49.22482989093507</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>83.04996529305467</v>
+        <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>45.13585070274711</v>
+        <v>42.12679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2898,13 +2898,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>91.45961612763284</v>
+        <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>371.8909391072129</v>
+        <v>70.61220362795183</v>
       </c>
       <c r="D20" t="n">
-        <v>49.09229395086174</v>
+        <v>32.27986451563512</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>14.6529411963389</v>
+        <v>96.1771861041782</v>
       </c>
       <c r="C21" t="n">
-        <v>71.89099274453774</v>
+        <v>684.9692278639034</v>
       </c>
       <c r="D21" t="n">
-        <v>2.747426474313544</v>
+        <v>53.95305561941705</v>
       </c>
     </row>
   </sheetData>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1256637061435917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.606540154775281</v>
+        <v>0.2748893571891069</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01276272015520854</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>12.91587279707104</v>
+        <v>2.935425635697963</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2945243112740432</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07363107781851079</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>31.48955761371645</v>
+        <v>11.48644813968768</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.771072858461246</v>
+        <v>0.04025165587411923</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9257880851047423</v>
+        <v>0.04025165587411923</v>
       </c>
       <c r="D6" t="n">
-        <v>48.50324532831367</v>
+        <v>27.85414586489051</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>0.4790928796724435</v>
       </c>
       <c r="C7" t="n">
-        <v>4.551382356888213</v>
+        <v>0.8384125394267761</v>
       </c>
       <c r="D7" t="n">
-        <v>58.62899114991527</v>
+        <v>44.91495746929157</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>13.76901155206151</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="D8" t="n">
-        <v>61.58503348740241</v>
+        <v>54.82570054366312</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23.40781051235669</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>30.50780990946962</v>
+        <v>12.86874890726719</v>
       </c>
       <c r="D9" t="n">
-        <v>66.00780689503428</v>
+        <v>58.46405753560178</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>32.45657910239955</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>53.09782458418874</v>
+        <v>28.18597658892593</v>
       </c>
       <c r="D10" t="n">
-        <v>71.88847564347269</v>
+        <v>61.639029611136</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>37.84931924182727</v>
+        <v>11.0171727370577</v>
       </c>
       <c r="C11" t="n">
-        <v>73.03319346662445</v>
+        <v>47.26722496866692</v>
       </c>
       <c r="D11" t="n">
-        <v>75.16554948024852</v>
+        <v>65.39225108447152</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>40.57268737340794</v>
+        <v>12.58404207303562</v>
       </c>
       <c r="C12" t="n">
-        <v>86.35256457014094</v>
+        <v>65.08987279156352</v>
       </c>
       <c r="D12" t="n">
-        <v>75.93818492349077</v>
+        <v>67.47650146058751</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>38.50414496055991</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>93.65873098514572</v>
+        <v>76.48796363786902</v>
       </c>
       <c r="D13" t="n">
-        <v>75.96763735461819</v>
+        <v>66.34160111447822</v>
       </c>
     </row>
     <row r="14">
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>34.41614752007619</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="C14" t="n">
-        <v>94.02983161735102</v>
+        <v>80.8164892658932</v>
       </c>
       <c r="D14" t="n">
-        <v>75.28532270016666</v>
+        <v>65.14485066300135</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>29.74204670015712</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>93.1678571330223</v>
+        <v>82.05938185946964</v>
       </c>
       <c r="D15" t="n">
-        <v>72.02592032206724</v>
+        <v>62.35079669671492</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>26.03889435973815</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>92.16941971780329</v>
+        <v>79.35663042967818</v>
       </c>
       <c r="D16" t="n">
-        <v>70.26368319294421</v>
+        <v>59.93078860574654</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>22.19437034990765</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>87.83304010814514</v>
+        <v>75.55530331883453</v>
       </c>
       <c r="D17" t="n">
-        <v>65.16644911249479</v>
+        <v>55.72203619764046</v>
       </c>
     </row>
     <row r="18">
@@ -3181,13 +3181,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>20.86704745376595</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>85.60839981032187</v>
+        <v>71.16198234233005</v>
       </c>
       <c r="D18" t="n">
-        <v>56.71556487433823</v>
+        <v>49.75988238974958</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>86.05902200657115</v>
+        <v>69.8101157535822</v>
       </c>
       <c r="D19" t="n">
-        <v>46.33947338815369</v>
+        <v>42.12679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -3209,13 +3209,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>96.16709636949629</v>
+        <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>392.0658544294849</v>
+        <v>71.28470080536088</v>
       </c>
       <c r="D20" t="n">
-        <v>53.12727701531613</v>
+        <v>32.27986451563512</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.06275980415863</v>
+        <v>101.1102812193752</v>
       </c>
       <c r="C21" t="n">
-        <v>75.31379902079314</v>
+        <v>734.2532326645104</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2949787071597</v>
+        <v>60.18469120200906</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1109374905798896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.385646921319749</v>
+        <v>0.2258019719767664</v>
       </c>
     </row>
     <row r="4">
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>12.23944862884498</v>
+        <v>2.565306751196915</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2208932334555324</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04908738521234053</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>30.75324683553134</v>
+        <v>10.33289458719768</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.408807955594173</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6440264939859077</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>48.82525857530663</v>
+        <v>26.1635763181775</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>0.2994330497952771</v>
       </c>
       <c r="C7" t="n">
-        <v>3.53330998758427</v>
+        <v>0.5389794896314989</v>
       </c>
       <c r="D7" t="n">
-        <v>60.06626978893259</v>
+        <v>43.59745205019235</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>1.335176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>11.34900346109313</v>
+        <v>3.087596529856218</v>
       </c>
       <c r="D8" t="n">
-        <v>63.75469591378786</v>
+        <v>54.57535487908019</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22.07656062539802</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>26.84687272033327</v>
+        <v>10.20624913334984</v>
       </c>
       <c r="D9" t="n">
-        <v>67.67186925373262</v>
+        <v>59.46249495082079</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31.74481201682062</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>48.68486865359933</v>
+        <v>23.77302065833652</v>
       </c>
       <c r="D10" t="n">
-        <v>73.16965639751479</v>
+        <v>61.78138302825178</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38.38240824523329</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="C11" t="n">
-        <v>70.90083745300038</v>
+        <v>42.82481660695011</v>
       </c>
       <c r="D11" t="n">
-        <v>76.76481649046657</v>
+        <v>65.21455475000286</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>42.30841731451629</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C12" t="n">
-        <v>88.0882945112493</v>
+        <v>62.0523453946239</v>
       </c>
       <c r="D12" t="n">
-        <v>78.32481359251477</v>
+        <v>67.25953521794898</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>40.84561323518855</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="C13" t="n">
-        <v>96.52052554302517</v>
+        <v>75.18714792974198</v>
       </c>
       <c r="D13" t="n">
-        <v>77.26845306274522</v>
+        <v>67.12209053935443</v>
       </c>
     </row>
     <row r="14">
@@ -3436,13 +3436,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>37.18173080293946</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>98.94642412021904</v>
+        <v>82.66021145446869</v>
       </c>
       <c r="D14" t="n">
-        <v>76.51447082588366</v>
+        <v>64.83756363157211</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>32.25041208450772</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>97.82624998967341</v>
+        <v>84.56774724382024</v>
       </c>
       <c r="D15" t="n">
-        <v>73.45927197026758</v>
+        <v>62.35079669671492</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>28.10547327717769</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>97.54252490314609</v>
+        <v>81.83652513060562</v>
       </c>
       <c r="D16" t="n">
-        <v>71.50363054340794</v>
+        <v>59.51747282225863</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>23.61103228713579</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>92.55524656557229</v>
+        <v>78.86084783903355</v>
       </c>
       <c r="D17" t="n">
-        <v>66.58311104972293</v>
+        <v>56.19425684338318</v>
       </c>
     </row>
     <row r="18">
@@ -3492,13 +3492,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>21.40209995258047</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>89.35376730202346</v>
+        <v>74.37229733521713</v>
       </c>
       <c r="D18" t="n">
-        <v>58.32072237078177</v>
+        <v>49.75988238974958</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>89.66989006279091</v>
+        <v>71.01373843898878</v>
       </c>
       <c r="D19" t="n">
-        <v>47.54309607356029</v>
+        <v>42.12679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -3520,13 +3520,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>100.2020794339507</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>412.2407697517568</v>
+        <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
-        <v>57.16226007977053</v>
+        <v>32.27986451563512</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.48006066048286</v>
+        <v>104.9182205799143</v>
       </c>
       <c r="C21" t="n">
-        <v>78.85155898933459</v>
+        <v>786.2694883459463</v>
       </c>
       <c r="D21" t="n">
-        <v>3.386263269480627</v>
+        <v>66.65392836841617</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09817477042468103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.179479903427919</v>
+        <v>0.186532063806894</v>
       </c>
     </row>
     <row r="4">
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>11.56302446061893</v>
+        <v>2.233476027161494</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1472621556370216</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02454369260617027</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>29.94330497952772</v>
+        <v>9.27751580513236</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.127046364475339</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4427682146153115</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>48.98626519880311</v>
+        <v>24.51325842733861</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.251949307092936</v>
+        <v>0.1796598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>2.694897448157494</v>
+        <v>0.2994330497952771</v>
       </c>
       <c r="D7" t="n">
-        <v>61.44366181799087</v>
+        <v>42.16017341117502</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>0.9179341034707675</v>
       </c>
       <c r="C8" t="n">
-        <v>9.346238144429634</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="D8" t="n">
-        <v>65.92435834017331</v>
+        <v>54.74225198880214</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.74531073843935</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="D9" t="n">
-        <v>70.22343153707007</v>
+        <v>59.68436993198057</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30.89069151412589</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>44.4142661401257</v>
+        <v>19.92947839621025</v>
       </c>
       <c r="D10" t="n">
-        <v>74.45083715155687</v>
+        <v>62.06608986248335</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38.56010457970196</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>67.70230343256426</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>78.18638716621597</v>
+        <v>65.03685841553418</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>43.39324852770902</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="C12" t="n">
-        <v>88.30526075388785</v>
+        <v>57.71302054185299</v>
       </c>
       <c r="D12" t="n">
-        <v>79.84357729098458</v>
+        <v>67.69346770322606</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>43.70740779306801</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="C13" t="n">
-        <v>99.12215695927921</v>
+        <v>74.14649536324036</v>
       </c>
       <c r="D13" t="n">
-        <v>78.82943191249764</v>
+        <v>66.86192739772903</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>39.64002705437346</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="C14" t="n">
-        <v>103.2484425602286</v>
+        <v>83.58207254875646</v>
       </c>
       <c r="D14" t="n">
-        <v>77.74361895160068</v>
+        <v>64.83756363157211</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>34.75877746885832</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>103.5596565824748</v>
+        <v>86.00109889202058</v>
       </c>
       <c r="D15" t="n">
-        <v>74.89262361846794</v>
+        <v>62.35079669671492</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>30.17205219461722</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>101.6756827380252</v>
+        <v>85.14305139850887</v>
       </c>
       <c r="D16" t="n">
-        <v>72.74357789387165</v>
+        <v>59.93078860574654</v>
       </c>
     </row>
     <row r="17">
@@ -3789,13 +3789,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>25.49991487010665</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>97.74967366874218</v>
+        <v>81.69417171348984</v>
       </c>
       <c r="D17" t="n">
-        <v>67.99977298695107</v>
+        <v>55.72203619764046</v>
       </c>
     </row>
     <row r="18">
@@ -3803,13 +3803,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>22.47220495020949</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>93.63418729253954</v>
+        <v>76.51250733047517</v>
       </c>
       <c r="D18" t="n">
-        <v>59.92587986722531</v>
+        <v>49.75988238974958</v>
       </c>
     </row>
     <row r="19">
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.66520833731861</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>93.28075811901068</v>
+        <v>73.42098380980195</v>
       </c>
       <c r="D19" t="n">
-        <v>49.34853010167016</v>
+        <v>42.12679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -3831,13 +3831,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>102.8920681435869</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>433.0881822514378</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>61.19724314422491</v>
+        <v>32.95236169304418</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.89743923394463</v>
+        <v>108.771863673082</v>
       </c>
       <c r="C21" t="n">
-        <v>82.00227863531953</v>
+        <v>838.5551815727138</v>
       </c>
       <c r="D21" t="n">
-        <v>3.478884548165071</v>
+        <v>72.09297941122878</v>
       </c>
     </row>
   </sheetData>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02945243112740431</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.619883712007237</v>
+        <v>0.4682936549257286</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.880046853632642</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
-        <v>3.485204350076177</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>10.58814899030185</v>
+        <v>4.118431619315369</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4.058545009356314</v>
+        <v>2.667408512438584</v>
       </c>
       <c r="C4" t="n">
-        <v>6.598326320242813</v>
+        <v>4.35208757292611</v>
       </c>
       <c r="D4" t="n">
-        <v>12.1118214272929</v>
+        <v>24.14706653365455</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5.792311455056182</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="C5" t="n">
-        <v>11.83005983617407</v>
+        <v>14.57895340806514</v>
       </c>
       <c r="D5" t="n">
-        <v>21.94206118991621</v>
+        <v>27.14532402242431</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.090582830697967</v>
+        <v>10.06291396852981</v>
       </c>
       <c r="C6" t="n">
-        <v>12.80002656796992</v>
+        <v>19.84406634594078</v>
       </c>
       <c r="D6" t="n">
-        <v>21.49438423677967</v>
+        <v>35.82397372796611</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.00106386316226</v>
+        <v>12.15698182168825</v>
       </c>
       <c r="C7" t="n">
-        <v>18.56484908730718</v>
+        <v>23.41566449399068</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C8" t="n">
-        <v>21.52972715413255</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>43.47669708257</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>30.50780990946962</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>54.1374954029861</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.110618695410402</v>
+        <v>14.66240196292611</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>43.2754388031994</v>
+        <v>67.90257996423065</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>12.08335074386974</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>39.626282586514</v>
       </c>
       <c r="D11" t="n">
-        <v>47.44492130313559</v>
+        <v>56.68513069550657</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9.112582190818895</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>36.88426124855266</v>
       </c>
       <c r="D12" t="n">
-        <v>49.90223580686537</v>
+        <v>57.92998678449154</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.40652566501619</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C13" t="n">
-        <v>33.56104526967722</v>
+        <v>37.46349239405829</v>
       </c>
       <c r="D13" t="n">
-        <v>52.55295460833177</v>
+        <v>60.61801199871932</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="C14" t="n">
-        <v>39.64002705437346</v>
+        <v>39.94731408580272</v>
       </c>
       <c r="D14" t="n">
-        <v>50.70236018582652</v>
+        <v>62.07198034870884</v>
       </c>
     </row>
     <row r="15">
@@ -4075,10 +4075,10 @@
         <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>44.43390109421063</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>49.45063186291183</v>
+        <v>59.84243131236433</v>
       </c>
     </row>
     <row r="16">
@@ -4089,10 +4089,10 @@
         <v>15.70599977254047</v>
       </c>
       <c r="C16" t="n">
-        <v>49.59789401854886</v>
+        <v>52.0777887194763</v>
       </c>
       <c r="D16" t="n">
-        <v>45.46473618366979</v>
+        <v>56.62426233784328</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="C17" t="n">
-        <v>54.77759490615504</v>
+        <v>56.6664774891259</v>
       </c>
       <c r="D17" t="n">
-        <v>38.72209295090269</v>
+        <v>52.88871232318417</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="C18" t="n">
-        <v>59.92587986722531</v>
+        <v>62.60114236129787</v>
       </c>
       <c r="D18" t="n">
-        <v>29.42788743479814</v>
+        <v>43.33925240397544</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>19.25796296650543</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>67.40287038276901</v>
+        <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>31.89600116327462</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>20.17491532227195</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>16.43451089120197</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>103.089204681176</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08737554567796613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.992947839621025</v>
+        <v>0.1570796326794897</v>
       </c>
     </row>
     <row r="4">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>10.9121257327033</v>
+        <v>1.939933463591697</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.09817477042468106</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>29.37880004958581</v>
+        <v>8.320311793491719</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.885536429230623</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3220132469929539</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>48.98626519880311</v>
+        <v>22.86294053649972</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.593196597543325</v>
+        <v>0.05988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>2.036144738607885</v>
+        <v>0.1796598298771663</v>
       </c>
       <c r="D7" t="n">
-        <v>62.58150740721292</v>
+        <v>41.02232782195297</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>0.667588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>7.760715602071035</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="D8" t="n">
-        <v>67.84367510197582</v>
+        <v>54.07466354991431</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.30312336090078</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>20.1906232855399</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="D9" t="n">
-        <v>71.88749389576842</v>
+        <v>59.79530742256046</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29.75186417719959</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>40.14366362665208</v>
+        <v>16.65534980254714</v>
       </c>
       <c r="D10" t="n">
-        <v>76.01672473983054</v>
+        <v>62.35079669671494</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38.56010457970196</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>63.97068040872215</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>79.60795784196534</v>
+        <v>65.5699474189402</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>44.2611134982632</v>
+        <v>9.980447161373073</v>
       </c>
       <c r="C12" t="n">
-        <v>87.43739578333366</v>
+        <v>53.59066193172063</v>
       </c>
       <c r="D12" t="n">
-        <v>81.36234098945441</v>
+        <v>67.47650146058751</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>46.04887606769665</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="C13" t="n">
-        <v>100.9432989506571</v>
+        <v>71.80502708861172</v>
       </c>
       <c r="D13" t="n">
-        <v>80.39041076225007</v>
+        <v>66.86192739772903</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>42.09832330580748</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="C14" t="n">
-        <v>106.9358869373796</v>
+        <v>82.96749848589795</v>
       </c>
       <c r="D14" t="n">
-        <v>79.28005410874692</v>
+        <v>64.83756363157211</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>37.26714285320892</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>109.2930631752762</v>
+        <v>88.1511263643211</v>
       </c>
       <c r="D15" t="n">
-        <v>77.04265109076844</v>
+        <v>62.70913460876501</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>32.23863111205676</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>106.2221563563921</v>
+        <v>88.03626188292422</v>
       </c>
       <c r="D16" t="n">
-        <v>73.57020946084748</v>
+        <v>59.51747282225863</v>
       </c>
     </row>
     <row r="17">
@@ -4411,13 +4411,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>27.38879745307752</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>102.4718801261693</v>
+        <v>84.05527494220343</v>
       </c>
       <c r="D17" t="n">
-        <v>68.9442142784365</v>
+        <v>55.72203619764046</v>
       </c>
     </row>
     <row r="18">
@@ -4425,13 +4425,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>23.54230994783851</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>97.91460728305563</v>
+        <v>79.72282232336224</v>
       </c>
       <c r="D18" t="n">
-        <v>60.99598486485433</v>
+        <v>49.75988238974958</v>
       </c>
     </row>
     <row r="19">
@@ -4439,13 +4439,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>22.26701968002191</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>96.89162617523046</v>
+        <v>75.82822918061514</v>
       </c>
       <c r="D19" t="n">
-        <v>50.55215278707676</v>
+        <v>42.12679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -4453,13 +4453,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>106.9270512080413</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>453.9355947511189</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>65.23222620867929</v>
+        <v>33.62485887045325</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.84133975878172</v>
+        <v>112.6693475059312</v>
       </c>
       <c r="C21" t="n">
-        <v>85.22738605201657</v>
+        <v>892.2894302481219</v>
       </c>
       <c r="D21" t="n">
-        <v>4.082749032431932</v>
+        <v>77.70299827995255</v>
       </c>
     </row>
   </sheetData>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01472621556370216</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.29590696960579</v>
+        <v>0.3102322745419921</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.030835089459151</v>
+        <v>0.03436116964863836</v>
       </c>
       <c r="C3" t="n">
-        <v>1.462804079327747</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>10.08745766113598</v>
+        <v>3.59810533606456</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4.505240214788612</v>
+        <v>1.378373776762522</v>
       </c>
       <c r="C4" t="n">
-        <v>8.014988257470959</v>
+        <v>2.080323385298991</v>
       </c>
       <c r="D4" t="n">
-        <v>15.18763698469816</v>
+        <v>20.98191193516283</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.749515466696823</v>
+        <v>6.013204688511715</v>
       </c>
       <c r="C5" t="n">
-        <v>12.44365215132832</v>
+        <v>11.1428364432013</v>
       </c>
       <c r="D5" t="n">
-        <v>22.40839134943345</v>
+        <v>29.20699420134261</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.815112636432113</v>
+        <v>10.34467555964864</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D6" t="n">
-        <v>24.23149683621978</v>
+        <v>36.74976181307086</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.89936301254809</v>
+        <v>12.33664165156542</v>
       </c>
       <c r="C7" t="n">
-        <v>18.98405535702057</v>
+        <v>25.99078872223005</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>36.59071868498287</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>13.93590866178347</v>
       </c>
       <c r="C8" t="n">
-        <v>23.94973524510094</v>
+        <v>28.70630287217673</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>43.22635141798705</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.64687392610741</v>
+        <v>15.30937370002476</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>52.91718300660731</v>
+        <v>50.14374574211007</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11.388273369263</v>
+        <v>15.23181563138926</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>65.76727870749383</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.950994730245668</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>42.46942393801276</v>
       </c>
       <c r="D11" t="n">
-        <v>48.51109930994763</v>
+        <v>59.52827204700533</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9.76348091873453</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>41.44055234396211</v>
       </c>
       <c r="D12" t="n">
-        <v>51.20403326269664</v>
+        <v>58.79785175504571</v>
       </c>
     </row>
     <row r="13">
@@ -4669,10 +4669,10 @@
         <v>10.6666888066416</v>
       </c>
       <c r="C13" t="n">
-        <v>34.08137155292803</v>
+        <v>39.80496066868693</v>
       </c>
       <c r="D13" t="n">
-        <v>53.85377031645879</v>
+        <v>60.61801199871932</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="C14" t="n">
-        <v>39.94731408580272</v>
+        <v>41.17646221151972</v>
       </c>
       <c r="D14" t="n">
-        <v>52.54608237440203</v>
+        <v>62.07198034870884</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.97517856995334</v>
+        <v>12.541826921753</v>
       </c>
       <c r="C15" t="n">
         <v>45.15057691831081</v>
       </c>
       <c r="D15" t="n">
-        <v>50.88398351111218</v>
+        <v>60.20076922441442</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="C16" t="n">
-        <v>50.83784136901258</v>
+        <v>51.66447293598839</v>
       </c>
       <c r="D16" t="n">
-        <v>47.94463088459723</v>
+        <v>57.4508939048191</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="C17" t="n">
-        <v>55.72203619764046</v>
+        <v>57.13869813486862</v>
       </c>
       <c r="D17" t="n">
-        <v>40.61097553387356</v>
+        <v>52.88871232318417</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="C18" t="n">
-        <v>61.53103736366884</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>44.40935740160447</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>20.46158565191202</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="C19" t="n">
-        <v>67.40287038276901</v>
+        <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
     </row>
     <row r="20">
@@ -4764,13 +4764,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>20.17491532227195</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>2.68998870963626</v>
+        <v>18.15742379004475</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>4.252931054797182</v>
+        <v>23.16176878585094</v>
       </c>
       <c r="C21" t="n">
-        <v>18.42936790412113</v>
+        <v>135.1103179174638</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1.544117919056729</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.006872233929727673</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.04948829583984</v>
+        <v>0.2051852701875834</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5792311455056182</v>
+        <v>0.01472621556370216</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6430447462816609</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>9.400234268163208</v>
+        <v>3.077779052813751</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3.637375244234433</v>
+        <v>0.714712328691678</v>
       </c>
       <c r="C4" t="n">
-        <v>5.65388502875738</v>
+        <v>1.008254892261474</v>
       </c>
       <c r="D4" t="n">
-        <v>17.28072309015236</v>
+        <v>18.237927101793</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7.706719478337463</v>
+        <v>4.246058820867455</v>
       </c>
       <c r="C5" t="n">
-        <v>14.21079801897258</v>
+        <v>7.43673885966959</v>
       </c>
       <c r="D5" t="n">
-        <v>23.6846633649543</v>
+        <v>30.11511082777092</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.821404033285093</v>
+        <v>9.45913913041802</v>
       </c>
       <c r="C6" t="n">
-        <v>18.6365166697172</v>
+        <v>19.48180144307371</v>
       </c>
       <c r="D6" t="n">
-        <v>26.60634453279281</v>
+        <v>37.59504658642736</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.97732199181109</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C7" t="n">
-        <v>22.21793229480956</v>
+        <v>28.32636651063322</v>
       </c>
       <c r="D7" t="n">
-        <v>32.63820242768521</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C8" t="n">
-        <v>25.2849121228766</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>43.97738841173587</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>15.30937370002476</v>
       </c>
       <c r="C9" t="n">
-        <v>31.06249736236907</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>52.36249555370786</v>
+        <v>50.14374574211007</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13.38122120888403</v>
+        <v>15.65887588273663</v>
       </c>
       <c r="C10" t="n">
-        <v>35.87306111317846</v>
+        <v>38.72012945549421</v>
       </c>
       <c r="D10" t="n">
-        <v>52.10135066437823</v>
+        <v>64.20139111922018</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.72795807493239</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>43.89099461376214</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>62.19371706403542</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.84831213192725</v>
+        <v>12.15010958775853</v>
       </c>
       <c r="C12" t="n">
-        <v>35.1485313074443</v>
+        <v>45.34594471145593</v>
       </c>
       <c r="D12" t="n">
-        <v>52.50583071852791</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.926851948267</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C13" t="n">
-        <v>36.94316611080748</v>
+        <v>43.4472446514426</v>
       </c>
       <c r="D13" t="n">
-        <v>55.67491230783662</v>
+        <v>60.61801199871932</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12.29148125717007</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="C14" t="n">
-        <v>39.94731408580272</v>
+        <v>43.02018440009523</v>
       </c>
       <c r="D14" t="n">
-        <v>54.38980456297755</v>
+        <v>62.07198034870884</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.97517856995334</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="C15" t="n">
-        <v>46.22559065446107</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>52.31733515931252</v>
+        <v>60.91744504851458</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15.70599977254047</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="C16" t="n">
-        <v>51.66447293598839</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>49.59789401854886</v>
+        <v>57.4508939048191</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.47216389248049</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="C17" t="n">
-        <v>56.6664774891259</v>
+        <v>57.13869813486862</v>
       </c>
       <c r="D17" t="n">
-        <v>42.97207876258714</v>
+        <v>53.36093296892689</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="C18" t="n">
-        <v>62.60114236129787</v>
+        <v>61.53103736366884</v>
       </c>
       <c r="D18" t="n">
-        <v>34.24335992412875</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>20.46158565191202</v>
+        <v>17.45252893839555</v>
       </c>
       <c r="C19" t="n">
-        <v>68.00468172547231</v>
+        <v>67.40287038276901</v>
       </c>
       <c r="D19" t="n">
-        <v>21.06339699461531</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -5075,13 +5075,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>28.91737862858979</v>
+        <v>18.15742379004475</v>
       </c>
       <c r="C20" t="n">
-        <v>108.9445427402685</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>5.37997741927252</v>
+        <v>19.50241814486288</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>4.26161113987446</v>
+        <v>29.66943854726223</v>
       </c>
       <c r="C21" t="n">
-        <v>18.11184734446645</v>
+        <v>169.9978641086376</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4.009383587467869</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002945243112740431</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.860010988920206</v>
+        <v>0.1354811831860598</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3337942194439156</v>
+        <v>0.004908738521234052</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2945243112740431</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8.6491972744144</v>
+        <v>2.59181393921158</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.667408512438584</v>
+        <v>0.3701188845010475</v>
       </c>
       <c r="C4" t="n">
-        <v>3.496985322527139</v>
+        <v>0.4977460860531329</v>
       </c>
       <c r="D4" t="n">
-        <v>18.55699510567321</v>
+        <v>16.0044510746315</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7.46128255227576</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C5" t="n">
-        <v>12.541826921753</v>
+        <v>4.66330159517235</v>
       </c>
       <c r="D5" t="n">
-        <v>25.40272184738622</v>
+        <v>29.64878066825368</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.02895370950867</v>
+        <v>7.808821239579131</v>
       </c>
       <c r="C6" t="n">
-        <v>21.09186767803848</v>
+        <v>15.77864910265474</v>
       </c>
       <c r="D6" t="n">
-        <v>28.77993394999525</v>
+        <v>38.52083467153211</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.11516758103314</v>
+        <v>12.15698182168825</v>
       </c>
       <c r="C7" t="n">
-        <v>25.33203601268044</v>
+        <v>28.32636651063322</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.10418842983718</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>28.20561154301086</v>
+        <v>34.79804737702819</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80496066868692</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.08593613408398</v>
+        <v>15.42031119060464</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>52.69530802544753</v>
+        <v>50.25468323268996</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>15.65887588273663</v>
       </c>
       <c r="C10" t="n">
-        <v>37.86600895279948</v>
+        <v>40.42837046088366</v>
       </c>
       <c r="D10" t="n">
-        <v>54.6637121724624</v>
+        <v>62.92021036517809</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13.68261775408779</v>
+        <v>14.9264920953685</v>
       </c>
       <c r="C11" t="n">
-        <v>41.22554959673205</v>
+        <v>45.31256528951153</v>
       </c>
       <c r="D11" t="n">
-        <v>52.95350767166445</v>
+        <v>64.14837674319081</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12.36707583039707</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="C12" t="n">
-        <v>40.13875488813084</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D12" t="n">
-        <v>54.02459441699772</v>
+        <v>60.31661545351553</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.70734137314322</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>39.80496066868693</v>
+        <v>47.34969177582367</v>
       </c>
       <c r="D13" t="n">
-        <v>56.71556487433823</v>
+        <v>60.61801199871932</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12.29148125717007</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
-        <v>41.48374924294897</v>
+        <v>45.7857676829585</v>
       </c>
       <c r="D14" t="n">
-        <v>56.23352675155306</v>
+        <v>62.68655441156734</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.97517856995334</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="C15" t="n">
         <v>46.58392856651115</v>
       </c>
       <c r="D15" t="n">
-        <v>54.46736263161304</v>
+        <v>60.91744504851458</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15.70599977254047</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="C16" t="n">
-        <v>52.0777887194763</v>
+        <v>50.42452558552468</v>
       </c>
       <c r="D16" t="n">
-        <v>51.25115715250048</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.47216389248049</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="C17" t="n">
-        <v>58.08313942635404</v>
+        <v>56.6664774891259</v>
       </c>
       <c r="D17" t="n">
-        <v>44.860961345558</v>
+        <v>54.30537426041232</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>14.98146996680633</v>
       </c>
       <c r="C18" t="n">
-        <v>63.13619486011238</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>36.38356991938679</v>
+        <v>46.014514898048</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="C19" t="n">
-        <v>69.8101157535822</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>36.10868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -5386,13 +5386,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>34.29735604786232</v>
+        <v>16.81242943522663</v>
       </c>
       <c r="C20" t="n">
-        <v>126.4294693529042</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>8.06996612890878</v>
+        <v>21.51990967709008</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>5.715060543117187</v>
+        <v>35.77790209575883</v>
       </c>
       <c r="C21" t="n">
-        <v>26.43215501191699</v>
+        <v>206.346970226702</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3571912839448242</v>
+        <v>6.656353878280711</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0009817477042468104</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7048948516492098</v>
+        <v>0.09032078879070655</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.191440802328128</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1374446785945534</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>7.863799111016951</v>
+        <v>2.174571164906685</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.901645303126072</v>
+        <v>0.191440802328128</v>
       </c>
       <c r="C4" t="n">
-        <v>2.067560665143783</v>
+        <v>0.2424916829489621</v>
       </c>
       <c r="D4" t="n">
-        <v>19.25894471420968</v>
+        <v>13.93689040948772</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.45499115542278</v>
+        <v>1.86532063806894</v>
       </c>
       <c r="C5" t="n">
-        <v>9.621127501618743</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="D5" t="n">
-        <v>27.4889357189107</v>
+        <v>28.61794557879453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.63272854762046</v>
+        <v>6.078000036992004</v>
       </c>
       <c r="C6" t="n">
-        <v>20.81010608691964</v>
+        <v>11.87423848286517</v>
       </c>
       <c r="D6" t="n">
-        <v>30.95352336719769</v>
+        <v>39.52712606838509</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.49255961009142</v>
+        <v>11.13890945238431</v>
       </c>
       <c r="C7" t="n">
-        <v>28.62579956042849</v>
+        <v>25.87101550231194</v>
       </c>
       <c r="D7" t="n">
-        <v>35.33309987584271</v>
+        <v>42.51949307092936</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.35591675275186</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>36.04977569994287</v>
       </c>
       <c r="D8" t="n">
-        <v>40.97324043674063</v>
+        <v>45.39601384437251</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.86093598336221</v>
+        <v>15.42031119060464</v>
       </c>
       <c r="C9" t="n">
-        <v>35.27812200440487</v>
+        <v>40.49218406165969</v>
       </c>
       <c r="D9" t="n">
-        <v>52.69530802544753</v>
+        <v>50.47655821384974</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17.65182372235765</v>
+        <v>15.9435827169682</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>56.79901342919922</v>
+        <v>62.49315011383072</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="C11" t="n">
-        <v>44.42408361716816</v>
+        <v>46.91183229972957</v>
       </c>
       <c r="D11" t="n">
-        <v>55.97434535763188</v>
+        <v>64.68146574659684</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.10280577150543</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="C12" t="n">
-        <v>44.91201222617883</v>
+        <v>50.33616829214246</v>
       </c>
       <c r="D12" t="n">
-        <v>55.54335811546754</v>
+        <v>61.40144666670826</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.74799393964483</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="C13" t="n">
-        <v>43.96757093469341</v>
+        <v>50.73181261695393</v>
       </c>
       <c r="D13" t="n">
-        <v>57.75621744083986</v>
+        <v>61.39850142359553</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12.90605532002857</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
-        <v>43.94204549438299</v>
+        <v>48.55135096582177</v>
       </c>
       <c r="D14" t="n">
-        <v>57.76996190869932</v>
+        <v>62.37926738013809</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.97517856995334</v>
+        <v>10.39179944945249</v>
       </c>
       <c r="C15" t="n">
-        <v>47.65894230266141</v>
+        <v>48.37561812676158</v>
       </c>
       <c r="D15" t="n">
-        <v>55.90071427981338</v>
+        <v>60.91744504851458</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15.70599977254047</v>
+        <v>11.15952615417349</v>
       </c>
       <c r="C16" t="n">
-        <v>52.49110450296421</v>
+        <v>50.83784136901258</v>
       </c>
       <c r="D16" t="n">
-        <v>52.90442028645212</v>
+        <v>58.69084125528282</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.47216389248049</v>
+        <v>12.74995743505333</v>
       </c>
       <c r="C17" t="n">
-        <v>59.02758071783948</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>47.22206457427158</v>
+        <v>54.30537426041232</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="C18" t="n">
-        <v>64.2062998577414</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>38.52377991464484</v>
+        <v>46.54956739686251</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>15.04528356758237</v>
       </c>
       <c r="C19" t="n">
-        <v>71.01373843898878</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>25.87788773624167</v>
+        <v>37.31230324760427</v>
       </c>
     </row>
     <row r="20">
@@ -5697,13 +5697,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>40.34983064454389</v>
+        <v>15.46743508040849</v>
       </c>
       <c r="C20" t="n">
-        <v>153.3293564492668</v>
+        <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>22.86490403190821</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>6.500870333669162</v>
+        <v>42.26280636718002</v>
       </c>
       <c r="C21" t="n">
-        <v>29.61507596449285</v>
+        <v>243.226763174383</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3611594629816202</v>
+        <v>9.487568776305718</v>
       </c>
     </row>
   </sheetData>
@@ -5762,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5841398840268521</v>
+        <v>0.05988660995905543</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1129009859883832</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>7.12257959431061</v>
+        <v>1.811324514335365</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.301797455831271</v>
+        <v>0.08933904108645975</v>
       </c>
       <c r="C4" t="n">
-        <v>1.212458414744811</v>
+        <v>0.1148644813968768</v>
       </c>
       <c r="D4" t="n">
-        <v>19.45038551653781</v>
+        <v>12.09905870713769</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5.325981295538947</v>
+        <v>1.178097245096173</v>
       </c>
       <c r="C5" t="n">
-        <v>6.872233929727674</v>
+        <v>1.693514789825748</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>27.46439202630453</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.18996033300515</v>
+        <v>4.588688769649592</v>
       </c>
       <c r="C6" t="n">
-        <v>18.31450342272425</v>
+        <v>8.533351045313278</v>
       </c>
       <c r="D6" t="n">
-        <v>33.32837106377072</v>
+        <v>39.64788103600744</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>30.00319158948677</v>
+        <v>21.79872602509618</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>44.01665831990574</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.85799074024948</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C8" t="n">
         <v>35.63253292563798</v>
       </c>
       <c r="D8" t="n">
-        <v>42.22496875965531</v>
+        <v>46.48084505756524</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.41406085148067</v>
+        <v>15.53124868118453</v>
       </c>
       <c r="C9" t="n">
-        <v>38.82812170296133</v>
+        <v>43.15468383557703</v>
       </c>
       <c r="D9" t="n">
-        <v>52.91718300660731</v>
+        <v>51.36405813848885</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19.92947839621025</v>
+        <v>16.08593613408399</v>
       </c>
       <c r="C10" t="n">
-        <v>42.27896488338889</v>
+        <v>46.12250714551515</v>
       </c>
       <c r="D10" t="n">
-        <v>58.50725443458867</v>
+        <v>61.4966761940202</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18.30272245027328</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="C11" t="n">
-        <v>47.26722496866692</v>
+        <v>49.04418831335365</v>
       </c>
       <c r="D11" t="n">
-        <v>58.28439770572462</v>
+        <v>65.21455475000286</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16.27246819789088</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C12" t="n">
-        <v>49.03437083631119</v>
+        <v>52.50583071852791</v>
       </c>
       <c r="D12" t="n">
-        <v>57.49605429921445</v>
+        <v>63.13717660781662</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>14.30897278939726</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="C13" t="n">
-        <v>48.39034434232529</v>
+        <v>53.33344403320798</v>
       </c>
       <c r="D13" t="n">
-        <v>59.05703314896688</v>
+        <v>61.65866456522093</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13.52062938288707</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
-        <v>47.93677690296326</v>
+        <v>52.23879534297279</v>
       </c>
       <c r="D14" t="n">
-        <v>59.92097112870407</v>
+        <v>62.37926738013809</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14.33351648200343</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>49.09229395086175</v>
+        <v>50.88398351111218</v>
       </c>
       <c r="D15" t="n">
-        <v>57.33406592801372</v>
+        <v>61.63412087261475</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15.70599977254047</v>
+        <v>10.33289458719768</v>
       </c>
       <c r="C16" t="n">
-        <v>53.73105185342793</v>
+        <v>52.0777887194763</v>
       </c>
       <c r="D16" t="n">
-        <v>54.55768342040375</v>
+        <v>58.69084125528282</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.47216389248049</v>
+        <v>11.8055161435679</v>
       </c>
       <c r="C17" t="n">
-        <v>59.02758071783948</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>49.11094715724245</v>
+        <v>54.30537426041232</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>12.84125997154828</v>
       </c>
       <c r="C18" t="n">
-        <v>65.81145735418494</v>
+        <v>61.53103736366884</v>
       </c>
       <c r="D18" t="n">
-        <v>40.66398990990288</v>
+        <v>47.08461989567702</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>13.84166088217578</v>
       </c>
       <c r="C19" t="n">
-        <v>71.01373843898878</v>
+        <v>66.19924769736242</v>
       </c>
       <c r="D19" t="n">
-        <v>28.28513310705485</v>
+        <v>38.51592593301086</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>46.40230524122548</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>176.194260481175</v>
+        <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>24.20989838672634</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.698808409929637</v>
+        <v>48.23354029897124</v>
       </c>
       <c r="C21" t="n">
-        <v>34.82794280682455</v>
+        <v>282.2555321199058</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7332198485647273</v>
+        <v>12.50499192936291</v>
       </c>
     </row>
   </sheetData>
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4898921044191584</v>
+        <v>0.03926990816987241</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06381360077604269</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03436116964863836</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>6.450082416901544</v>
+        <v>1.497165248976386</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8933904108645975</v>
+        <v>0.0382881604656256</v>
       </c>
       <c r="C4" t="n">
-        <v>0.714712328691678</v>
+        <v>0.05105088062083414</v>
       </c>
       <c r="D4" t="n">
-        <v>19.29723287467531</v>
+        <v>10.59305772882308</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.196971435655115</v>
+        <v>0.7363107781851078</v>
       </c>
       <c r="C5" t="n">
-        <v>4.736932672990861</v>
+        <v>0.9817477042468106</v>
       </c>
       <c r="D5" t="n">
-        <v>30.43417883165113</v>
+        <v>25.74633354387261</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.30442390377452</v>
+        <v>3.340887437551896</v>
       </c>
       <c r="C6" t="n">
-        <v>14.97361598517235</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="D6" t="n">
-        <v>35.62271544859552</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.04961146902685</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>28.68568617038755</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>45.75337000871835</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.44351328260808</v>
+        <v>12.51728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>38.88702656521616</v>
+        <v>33.04562772494764</v>
       </c>
       <c r="D8" t="n">
-        <v>43.81049130201391</v>
+        <v>47.56567627075796</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21.1890607007589</v>
+        <v>15.19843620944487</v>
       </c>
       <c r="C9" t="n">
-        <v>42.71093387325747</v>
+        <v>44.37499623195582</v>
       </c>
       <c r="D9" t="n">
-        <v>53.36093296892687</v>
+        <v>51.69687061022852</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21.78007281871549</v>
+        <v>15.9435827169682</v>
       </c>
       <c r="C10" t="n">
-        <v>46.12250714551515</v>
+        <v>49.25428232206248</v>
       </c>
       <c r="D10" t="n">
-        <v>60.50020227420969</v>
+        <v>60.78490910844128</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>20.96816746730337</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="C11" t="n">
-        <v>49.57727731675966</v>
+        <v>51.88732966485241</v>
       </c>
       <c r="D11" t="n">
-        <v>60.4167537193487</v>
+        <v>66.10303642234622</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18.44213062427633</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="C12" t="n">
-        <v>53.37369568908209</v>
+        <v>54.24156065963627</v>
       </c>
       <c r="D12" t="n">
-        <v>59.44875048296136</v>
+        <v>63.78807533573226</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>16.1301147807751</v>
+        <v>12.22766765639403</v>
       </c>
       <c r="C13" t="n">
-        <v>52.81311774995717</v>
+        <v>56.45540173271284</v>
       </c>
       <c r="D13" t="n">
-        <v>60.35784885709391</v>
+        <v>62.17899084847173</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14.74977750860408</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
-        <v>52.23879534297279</v>
+        <v>55.61895268869456</v>
       </c>
       <c r="D14" t="n">
-        <v>61.15011925442109</v>
+        <v>62.99384144299659</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14.69185439405351</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>51.95899724726244</v>
+        <v>53.75068680751286</v>
       </c>
       <c r="D15" t="n">
-        <v>59.12575548826415</v>
+        <v>61.63412087261475</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16.11931555602838</v>
+        <v>9.919578803709772</v>
       </c>
       <c r="C16" t="n">
-        <v>55.38431498737956</v>
+        <v>53.73105185342793</v>
       </c>
       <c r="D16" t="n">
-        <v>56.62426233784328</v>
+        <v>58.69084125528282</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.47216389248049</v>
+        <v>10.86107485208246</v>
       </c>
       <c r="C17" t="n">
-        <v>59.97202200932491</v>
+        <v>56.6664774891259</v>
       </c>
       <c r="D17" t="n">
-        <v>50.52760909447059</v>
+        <v>54.30537426041232</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>11.77115497391926</v>
       </c>
       <c r="C18" t="n">
-        <v>65.81145735418494</v>
+        <v>60.99598486485433</v>
       </c>
       <c r="D18" t="n">
-        <v>42.26914740634642</v>
+        <v>48.15472489330605</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>12.63803819676919</v>
       </c>
       <c r="C19" t="n">
-        <v>72.81917246709867</v>
+        <v>66.19924769736242</v>
       </c>
       <c r="D19" t="n">
-        <v>30.69237847786803</v>
+        <v>39.11773727571416</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>51.78228266049801</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>198.3866673356742</v>
+        <v>71.28470080536088</v>
       </c>
       <c r="D20" t="n">
-        <v>18.15742379004475</v>
+        <v>25.55489274154447</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.587431170553046</v>
+        <v>54.52180063630241</v>
       </c>
       <c r="C21" t="n">
-        <v>39.95022327170331</v>
+        <v>322.5103122384668</v>
       </c>
       <c r="D21" t="n">
-        <v>1.120099717898223</v>
+        <v>15.70967136978205</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4113522880794135</v>
+        <v>0.02650718801466388</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03436116964863836</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01472621556370216</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>5.807037670619883</v>
+        <v>1.241910845872215</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5998478472948012</v>
+        <v>0.01276272015520854</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4211697651218816</v>
+        <v>0.02552544031041707</v>
       </c>
       <c r="D4" t="n">
-        <v>18.88882582970863</v>
+        <v>9.201921231905354</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.264311116620645</v>
+        <v>0.4417864669110648</v>
       </c>
       <c r="C5" t="n">
-        <v>3.166136346195964</v>
+        <v>0.564504929941916</v>
       </c>
       <c r="D5" t="n">
-        <v>31.48955761371645</v>
+        <v>23.93010029101601</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.976119259928589</v>
+        <v>2.374847696573035</v>
       </c>
       <c r="C6" t="n">
-        <v>11.79373517111693</v>
+        <v>3.944662275663684</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>39.32586778901449</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.92983824910874</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>25.75124228239384</v>
+        <v>13.59426046070558</v>
       </c>
       <c r="D7" t="n">
-        <v>41.44153409166636</v>
+        <v>46.59178254814513</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.44489594093983</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>39.72151211382594</v>
+        <v>29.12354564648163</v>
       </c>
       <c r="D8" t="n">
-        <v>45.39601384437251</v>
+        <v>48.81740459367264</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22.85312305945724</v>
+        <v>14.53281126596553</v>
       </c>
       <c r="C9" t="n">
-        <v>46.59374604355361</v>
+        <v>43.70937128847648</v>
       </c>
       <c r="D9" t="n">
-        <v>54.0265579124062</v>
+        <v>52.14062057254808</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>23.91537407545231</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="C10" t="n">
-        <v>49.82369599052563</v>
+        <v>51.67429041303087</v>
       </c>
       <c r="D10" t="n">
-        <v>61.639029611136</v>
+        <v>60.78490910844128</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23.10052348092744</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>53.48659667507046</v>
+        <v>54.37507834741383</v>
       </c>
       <c r="D11" t="n">
-        <v>62.54910973297276</v>
+        <v>65.92534008787754</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20.82875929330033</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="C12" t="n">
-        <v>56.41122308602172</v>
+        <v>57.06212181393736</v>
       </c>
       <c r="D12" t="n">
-        <v>61.40144666670826</v>
+        <v>64.65594030628644</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18.21141991377833</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="C13" t="n">
-        <v>58.01638058246527</v>
+        <v>59.05703314896688</v>
       </c>
       <c r="D13" t="n">
-        <v>62.43915399009714</v>
+        <v>62.69931713172255</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15.97892563432109</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="C14" t="n">
-        <v>56.23352675155306</v>
+        <v>58.99911003441632</v>
       </c>
       <c r="D14" t="n">
-        <v>62.37926738013809</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15.40853021815369</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>55.90071427981338</v>
+        <v>56.97572801596364</v>
       </c>
       <c r="D15" t="n">
-        <v>60.5591071364645</v>
+        <v>61.63412087261475</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16.53263133951629</v>
+        <v>9.092947236733956</v>
       </c>
       <c r="C16" t="n">
-        <v>57.03757812133119</v>
+        <v>55.38431498737956</v>
       </c>
       <c r="D16" t="n">
-        <v>57.864209688307</v>
+        <v>58.69084125528282</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.47216389248049</v>
+        <v>9.916633560597033</v>
       </c>
       <c r="C17" t="n">
-        <v>61.86090459229577</v>
+        <v>57.61091878061134</v>
       </c>
       <c r="D17" t="n">
-        <v>52.41649167744146</v>
+        <v>55.24981555189775</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.26188995732242</v>
+        <v>10.70104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>66.34650985299945</v>
+        <v>60.99598486485433</v>
       </c>
       <c r="D18" t="n">
-        <v>43.87430490278995</v>
+        <v>48.15472489330605</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.06339699461531</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>72.81917246709867</v>
+        <v>66.19924769736242</v>
       </c>
       <c r="D19" t="n">
-        <v>32.49781250597791</v>
+        <v>39.71954861841746</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>57.16226007977053</v>
+        <v>12.10494919336317</v>
       </c>
       <c r="C20" t="n">
-        <v>223.2690628998096</v>
+        <v>71.28470080536088</v>
       </c>
       <c r="D20" t="n">
-        <v>22.19240685449914</v>
+        <v>26.8998870963626</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>9.531692343365364</v>
+        <v>60.17208068964722</v>
       </c>
       <c r="C21" t="n">
-        <v>43.84578477948068</v>
+        <v>363.8978213135808</v>
       </c>
       <c r="D21" t="n">
-        <v>1.143803081203844</v>
+        <v>19.10224783798325</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01767145867644259</v>
+        <v>0.01668971097219578</v>
       </c>
     </row>
     <row r="3">
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.025926350937917</v>
+        <v>1.016108873895449</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +814,7 @@
         <v>0.01276272015520854</v>
       </c>
       <c r="D4" t="n">
-        <v>7.963937376850126</v>
+        <v>7.912886496229292</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2699806186678729</v>
+        <v>0.2454369260617026</v>
       </c>
       <c r="C5" t="n">
         <v>0.3190680038802134</v>
       </c>
       <c r="D5" t="n">
-        <v>22.2856728864026</v>
+        <v>22.23658550119026</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.650317890838888</v>
+        <v>1.690569546713008</v>
       </c>
       <c r="C6" t="n">
-        <v>2.576105975943631</v>
+        <v>2.696860943565988</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>39.04410619789565</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>10.24061030299848</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="D7" t="n">
-        <v>47.25053525769474</v>
+        <v>47.37030847761284</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>24.70077223884975</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D8" t="n">
-        <v>49.98568436172635</v>
+        <v>50.40292713603124</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>13.86718632248619</v>
       </c>
       <c r="C9" t="n">
-        <v>41.26874649571891</v>
+        <v>42.04530892977813</v>
       </c>
       <c r="D9" t="n">
-        <v>53.24999547834697</v>
+        <v>53.80468293124643</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.51652246562084</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="C10" t="n">
-        <v>52.24370408149402</v>
+        <v>53.80959166976768</v>
       </c>
       <c r="D10" t="n">
-        <v>60.21549543997811</v>
+        <v>60.64255569132548</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.99267010218054</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="C11" t="n">
-        <v>57.57361236784993</v>
+        <v>57.92900503678727</v>
       </c>
       <c r="D11" t="n">
-        <v>65.74764375340887</v>
+        <v>66.10303642234622</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.97067074205961</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="C12" t="n">
-        <v>59.88268296823844</v>
+        <v>60.09964921087699</v>
       </c>
       <c r="D12" t="n">
-        <v>65.30683903420207</v>
+        <v>65.52380527684062</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="C13" t="n">
         <v>61.65866456522093</v>
       </c>
       <c r="D13" t="n">
-        <v>63.73996969822417</v>
+        <v>62.95948027334796</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="C14" t="n">
-        <v>62.07198034870884</v>
+        <v>61.15011925442109</v>
       </c>
       <c r="D14" t="n">
-        <v>63.30112847442584</v>
+        <v>62.99384144299659</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>59.84243131236433</v>
+        <v>58.76741757621406</v>
       </c>
       <c r="D15" t="n">
-        <v>61.63412087261475</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
       <c r="C16" t="n">
-        <v>58.2775254717949</v>
+        <v>57.864209688307</v>
       </c>
       <c r="D16" t="n">
-        <v>59.51747282225863</v>
+        <v>59.10415703877072</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.9721922691116</v>
+        <v>9.444412914854317</v>
       </c>
       <c r="C17" t="n">
         <v>58.55536007209676</v>
       </c>
       <c r="D17" t="n">
-        <v>55.24981555189775</v>
+        <v>54.30537426041232</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>9.63094497866121</v>
       </c>
       <c r="C18" t="n">
-        <v>61.53103736366884</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>48.68977739212056</v>
+        <v>47.08461989567702</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>10.23079282595601</v>
       </c>
       <c r="C19" t="n">
-        <v>66.19924769736242</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>40.32135996112075</v>
+        <v>38.51592593301086</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>11.43245201595411</v>
       </c>
       <c r="C20" t="n">
-        <v>70.61220362795183</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>28.24488145118073</v>
+        <v>25.55489274154447</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>66.0769682322816</v>
+        <v>55.27189859315163</v>
       </c>
       <c r="C21" t="n">
-        <v>407.3102668646612</v>
+        <v>342.8731336456525</v>
       </c>
       <c r="D21" t="n">
-        <v>22.68313834839518</v>
+        <v>16.86261313011406</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01178097245096173</v>
+        <v>0.01079922474671491</v>
       </c>
     </row>
     <row r="3">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8443030256522569</v>
+        <v>0.8344855486097889</v>
       </c>
     </row>
     <row r="4">
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6.955682484588651</v>
+        <v>6.828055283036567</v>
       </c>
     </row>
     <row r="5">
@@ -1139,7 +1139,7 @@
         <v>0.1718058482431918</v>
       </c>
       <c r="D5" t="n">
-        <v>20.44489594093983</v>
+        <v>20.54307071136451</v>
       </c>
     </row>
     <row r="6">
@@ -1150,10 +1150,10 @@
         <v>1.127046364475339</v>
       </c>
       <c r="C6" t="n">
-        <v>1.690569546713008</v>
+        <v>1.730821202587127</v>
       </c>
       <c r="D6" t="n">
-        <v>37.27303333943441</v>
+        <v>37.79630486579796</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.832743037379548</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="C7" t="n">
-        <v>7.545712854840985</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="D7" t="n">
-        <v>47.60985491744906</v>
+        <v>47.84940135728529</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>20.27799883121787</v>
+        <v>21.11248437982766</v>
       </c>
       <c r="D8" t="n">
-        <v>51.57120690408495</v>
+        <v>51.98844967838984</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.31406145436774</v>
+        <v>12.64687392610741</v>
       </c>
       <c r="C9" t="n">
-        <v>37.60780930658255</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>53.80468293124643</v>
+        <v>54.35937038414588</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14.94710879715769</v>
+        <v>15.23181563138926</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>53.24017800130454</v>
       </c>
       <c r="D10" t="n">
-        <v>59.93078860574654</v>
+        <v>60.35784885709391</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.63727743324319</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="C11" t="n">
-        <v>59.70596838147401</v>
+        <v>60.59445005381736</v>
       </c>
       <c r="D11" t="n">
-        <v>65.5699474189402</v>
+        <v>66.63612542575224</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="C12" t="n">
-        <v>62.92021036517807</v>
+        <v>63.13717660781662</v>
       </c>
       <c r="D12" t="n">
-        <v>66.3916702473948</v>
+        <v>65.9577377621177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C13" t="n">
         <v>64.52045912310038</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="C14" t="n">
         <v>64.2229895687136</v>
       </c>
       <c r="D14" t="n">
-        <v>63.30112847442584</v>
+        <v>62.68655441156734</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>63.42581043286518</v>
+        <v>62.70913460876501</v>
       </c>
       <c r="D15" t="n">
-        <v>62.35079669671492</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
       <c r="C16" t="n">
-        <v>61.17073595621026</v>
+        <v>59.93078860574654</v>
       </c>
       <c r="D16" t="n">
         <v>59.51747282225863</v>
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.499971623368884</v>
+        <v>8.9721922691116</v>
       </c>
       <c r="C17" t="n">
-        <v>60.44424265506763</v>
+        <v>59.97202200932491</v>
       </c>
       <c r="D17" t="n">
-        <v>55.24981555189775</v>
+        <v>54.30537426041232</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>61.53103736366884</v>
+        <v>62.60114236129787</v>
       </c>
       <c r="D18" t="n">
-        <v>48.68977739212056</v>
+        <v>47.61967239449154</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>9.628981483252716</v>
       </c>
       <c r="C19" t="n">
-        <v>66.19924769736242</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>40.92317130382404</v>
+        <v>38.51592593301086</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>10.08745766113597</v>
       </c>
       <c r="C20" t="n">
-        <v>70.61220362795183</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>28.91737862858979</v>
+        <v>26.22738991895353</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>71.21669864648854</v>
+        <v>59.65243764495866</v>
       </c>
       <c r="C21" t="n">
-        <v>450.6999642913489</v>
+        <v>378.1194837817541</v>
       </c>
       <c r="D21" t="n">
-        <v>27.46929804935986</v>
+        <v>20.20485791200213</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007853981633974483</v>
+        <v>0.006872233929727673</v>
       </c>
     </row>
     <row r="3">
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7019496085364695</v>
+        <v>0.6872233929727672</v>
       </c>
     </row>
     <row r="4">
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6.036766633413637</v>
+        <v>5.883613991551135</v>
       </c>
     </row>
     <row r="5">
@@ -1450,7 +1450,7 @@
         <v>0.07363107781851079</v>
       </c>
       <c r="D5" t="n">
-        <v>18.6532063806894</v>
+        <v>18.84955592153876</v>
       </c>
     </row>
     <row r="6">
@@ -1461,10 +1461,10 @@
         <v>0.7647814616082653</v>
       </c>
       <c r="C6" t="n">
-        <v>1.086794708601219</v>
+        <v>1.127046364475339</v>
       </c>
       <c r="D6" t="n">
-        <v>35.90447703971436</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.87455727803466</v>
+        <v>2.934443887993716</v>
       </c>
       <c r="C7" t="n">
-        <v>5.449681506274044</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>48.50815406683489</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.67588438887831</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>16.27246819789088</v>
+        <v>17.02350519163969</v>
       </c>
       <c r="D8" t="n">
-        <v>52.40569245269473</v>
+        <v>52.73948667213865</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.98281156740907</v>
+        <v>11.20468654856884</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>54.58124536530566</v>
+        <v>55.1359328182051</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13.95063487734718</v>
+        <v>14.37769512869454</v>
       </c>
       <c r="C10" t="n">
-        <v>49.68134257340984</v>
+        <v>51.24723016168351</v>
       </c>
       <c r="D10" t="n">
-        <v>59.78843518863076</v>
+        <v>60.92726252555705</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.28188476430585</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="C11" t="n">
-        <v>60.59445005381736</v>
+        <v>62.01602072956675</v>
       </c>
       <c r="D11" t="n">
-        <v>65.92534008787754</v>
+        <v>66.2807327568149</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>14.97067074205961</v>
       </c>
       <c r="C12" t="n">
-        <v>65.74077151947915</v>
+        <v>66.17470400475625</v>
       </c>
       <c r="D12" t="n">
-        <v>66.60863649003335</v>
+        <v>66.3916702473948</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C13" t="n">
-        <v>66.86192739772903</v>
+        <v>67.38225368097983</v>
       </c>
       <c r="D13" t="n">
-        <v>64.52045912310038</v>
+        <v>65.04078540635119</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="C14" t="n">
-        <v>67.60314691443537</v>
+        <v>67.29585988300612</v>
       </c>
       <c r="D14" t="n">
-        <v>63.91570253728435</v>
+        <v>62.68655441156734</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>66.29251372926586</v>
+        <v>65.5758379051657</v>
       </c>
       <c r="D15" t="n">
-        <v>61.99245878466483</v>
+        <v>61.63412087261475</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
       <c r="C16" t="n">
-        <v>64.06394644062561</v>
+        <v>62.82399909016188</v>
       </c>
       <c r="D16" t="n">
-        <v>59.51747282225863</v>
+        <v>59.10415703877072</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.02775097762617</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="C17" t="n">
-        <v>61.86090459229577</v>
+        <v>61.38868394655305</v>
       </c>
       <c r="D17" t="n">
-        <v>55.24981555189775</v>
+        <v>54.30537426041232</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.025787482217675</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>62.60114236129787</v>
+        <v>63.13619486011238</v>
       </c>
       <c r="D18" t="n">
-        <v>49.22482989093507</v>
+        <v>48.15472489330605</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>9.027170140549421</v>
       </c>
       <c r="C19" t="n">
-        <v>66.19924769736242</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>40.92317130382404</v>
+        <v>38.51592593301086</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>9.41496048372691</v>
       </c>
       <c r="C20" t="n">
-        <v>70.61220362795183</v>
+        <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
-        <v>29.58987580599885</v>
+        <v>26.8998870963626</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>76.54525595093422</v>
+        <v>63.20121067346139</v>
       </c>
       <c r="C21" t="n">
-        <v>494.9227508060404</v>
+        <v>414.7579450445904</v>
       </c>
       <c r="D21" t="n">
-        <v>32.50551965039672</v>
+        <v>23.70045400254802</v>
       </c>
     </row>
   </sheetData>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004908738521234052</v>
+        <v>0.003926990816987242</v>
       </c>
     </row>
     <row r="3">
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5792311455056182</v>
+        <v>0.564504929941916</v>
       </c>
     </row>
     <row r="4">
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5.219952543480291</v>
+        <v>5.105088062083414</v>
       </c>
     </row>
     <row r="5">
@@ -1761,7 +1761,7 @@
         <v>0.02454369260617027</v>
       </c>
       <c r="D5" t="n">
-        <v>16.95969159086365</v>
+        <v>17.0824100538945</v>
       </c>
     </row>
     <row r="6">
@@ -1775,7 +1775,7 @@
         <v>0.684278149860027</v>
       </c>
       <c r="D6" t="n">
-        <v>34.69692736349078</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.09603134856694</v>
+        <v>2.155917958525996</v>
       </c>
       <c r="C7" t="n">
-        <v>3.892629647338603</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="D7" t="n">
-        <v>47.84940135728529</v>
+        <v>48.74770050667112</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>12.68418033886879</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="D8" t="n">
-        <v>53.15672944644354</v>
+        <v>53.57397222074844</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.540624189870499</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
-        <v>28.28906009787183</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>55.35780779936488</v>
+        <v>55.91249525226433</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>12.95416095753666</v>
+        <v>13.38122120888403</v>
       </c>
       <c r="C10" t="n">
-        <v>46.40721397974673</v>
+        <v>47.97310156802039</v>
       </c>
       <c r="D10" t="n">
-        <v>60.35784885709391</v>
+        <v>61.4966761940202</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14.57109942643116</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="C11" t="n">
-        <v>60.4167537193487</v>
+        <v>62.01602072956675</v>
       </c>
       <c r="D11" t="n">
-        <v>65.5699474189402</v>
+        <v>66.10303642234622</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>14.97067074205961</v>
       </c>
       <c r="C12" t="n">
-        <v>67.04256897531043</v>
+        <v>68.56133267378024</v>
       </c>
       <c r="D12" t="n">
-        <v>66.82560273267188</v>
+        <v>67.25953521794898</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="C13" t="n">
-        <v>70.24404823885929</v>
+        <v>70.50421138048469</v>
       </c>
       <c r="D13" t="n">
-        <v>64.78062226472579</v>
+        <v>65.3009485479766</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>70.67601722872789</v>
+        <v>70.98330426015714</v>
       </c>
       <c r="D14" t="n">
-        <v>64.53027660014286</v>
+        <v>62.68655441156734</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.0334615374024</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>69.51755493771664</v>
+        <v>68.80087911361647</v>
       </c>
       <c r="D15" t="n">
         <v>61.99245878466483</v>
@@ -1912,10 +1912,10 @@
         <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>66.54384114155305</v>
+        <v>65.71720957457724</v>
       </c>
       <c r="D16" t="n">
-        <v>59.51747282225863</v>
+        <v>58.69084125528282</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.555530331883453</v>
+        <v>8.02775097762617</v>
       </c>
       <c r="C17" t="n">
-        <v>64.69422846675207</v>
+        <v>63.27756652952392</v>
       </c>
       <c r="D17" t="n">
-        <v>55.72203619764046</v>
+        <v>54.30537426041232</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="C18" t="n">
         <v>64.2062998577414</v>
       </c>
       <c r="D18" t="n">
-        <v>49.22482989093507</v>
+        <v>48.68977739212056</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>40.92317130382404</v>
+        <v>39.11773727571416</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>70.61220362795183</v>
+        <v>71.28470080536088</v>
       </c>
       <c r="D20" t="n">
-        <v>30.26237298340792</v>
+        <v>27.57238427377166</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.06085116214253</v>
+        <v>66.85494086459154</v>
       </c>
       <c r="C21" t="n">
-        <v>540.9537688451765</v>
+        <v>451.7773276607247</v>
       </c>
       <c r="D21" t="n">
-        <v>37.79118145624985</v>
+        <v>27.34974853551472</v>
       </c>
     </row>
   </sheetData>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002945243112740431</v>
+        <v>0.001963495408493621</v>
       </c>
     </row>
     <row r="3">
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.476147636559703</v>
+        <v>0.4663301595172349</v>
       </c>
     </row>
     <row r="4">
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4.505240214788612</v>
+        <v>4.403138453546945</v>
       </c>
     </row>
     <row r="5">
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>15.51161372709961</v>
+        <v>15.41343895667493</v>
       </c>
     </row>
     <row r="6">
@@ -2086,7 +2086,7 @@
         <v>0.4025165587411924</v>
       </c>
       <c r="D6" t="n">
-        <v>33.04660947265189</v>
+        <v>33.40887437551896</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.497165248976386</v>
+        <v>1.557051858935441</v>
       </c>
       <c r="C7" t="n">
-        <v>2.694897448157494</v>
+        <v>2.814670668075606</v>
       </c>
       <c r="D7" t="n">
-        <v>47.37030847761284</v>
+        <v>48.14883440708056</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>9.846929473595507</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="D8" t="n">
-        <v>53.7408693304704</v>
+        <v>54.32500921449725</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.85156047467625</v>
+        <v>24.84999788989526</v>
       </c>
       <c r="D9" t="n">
-        <v>56.68905768632355</v>
+        <v>57.243745139223</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11.67298020349457</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C10" t="n">
-        <v>42.27896488338889</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
-        <v>60.35784885709391</v>
+        <v>61.35432277690443</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14.03801042302514</v>
+        <v>14.39340309196248</v>
       </c>
       <c r="C11" t="n">
-        <v>58.28439770572462</v>
+        <v>60.59445005381736</v>
       </c>
       <c r="D11" t="n">
-        <v>65.39225108447152</v>
+        <v>65.92534008787754</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>14.53673825678252</v>
       </c>
       <c r="C12" t="n">
-        <v>68.56133267378024</v>
+        <v>70.08009637225005</v>
       </c>
       <c r="D12" t="n">
-        <v>67.04256897531043</v>
+        <v>68.12740018850316</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="C13" t="n">
-        <v>72.84567965511333</v>
+        <v>73.36600593836414</v>
       </c>
       <c r="D13" t="n">
-        <v>65.82127483122741</v>
+        <v>65.561111689602</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>73.13431348016189</v>
+        <v>74.05617457444966</v>
       </c>
       <c r="D14" t="n">
-        <v>64.53027660014286</v>
+        <v>63.30112847442584</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.0334615374024</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>72.74259614616741</v>
+        <v>72.02592032206724</v>
       </c>
       <c r="D15" t="n">
-        <v>61.99245878466483</v>
+        <v>61.63412087261475</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>69.85036740945631</v>
+        <v>69.02373584248051</v>
       </c>
       <c r="D16" t="n">
-        <v>59.93078860574654</v>
+        <v>58.69084125528282</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>7.555530331883453</v>
       </c>
       <c r="C17" t="n">
-        <v>67.05533169546565</v>
+        <v>65.6386697582375</v>
       </c>
       <c r="D17" t="n">
-        <v>55.72203619764046</v>
+        <v>54.77759490615504</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
         <v>65.27640485537043</v>
       </c>
       <c r="D18" t="n">
-        <v>49.22482989093507</v>
+        <v>48.68977739212056</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>66.80105904006572</v>
+        <v>67.40287038276901</v>
       </c>
       <c r="D19" t="n">
-        <v>40.92317130382404</v>
+        <v>39.11773727571416</v>
       </c>
     </row>
     <row r="20">
@@ -2279,10 +2279,10 @@
         <v>8.06996612890878</v>
       </c>
       <c r="C20" t="n">
-        <v>70.61220362795183</v>
+        <v>71.28470080536088</v>
       </c>
       <c r="D20" t="n">
-        <v>30.93487016081699</v>
+        <v>28.24488145118073</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>86.64852067731151</v>
+        <v>70.61228484862418</v>
       </c>
       <c r="C21" t="n">
-        <v>587.6547107474075</v>
+        <v>489.0939141720881</v>
       </c>
       <c r="D21" t="n">
-        <v>42.21338186843381</v>
+        <v>31.15247860968714</v>
       </c>
     </row>
   </sheetData>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001963495408493621</v>
+        <v>0.0009817477042468104</v>
       </c>
     </row>
     <row r="3">
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3926990816987241</v>
+        <v>0.382881604656256</v>
       </c>
     </row>
     <row r="4">
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3.918155087649021</v>
+        <v>3.790527886096935</v>
       </c>
     </row>
     <row r="5">
@@ -2383,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>14.01444847812322</v>
+        <v>13.98990478551705</v>
       </c>
     </row>
     <row r="6">
@@ -2394,10 +2394,10 @@
         <v>0.1610066234964769</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2415099352447154</v>
+        <v>0.2012582793705962</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>31.63780151705772</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.018072369303942</v>
+        <v>1.077958979262998</v>
       </c>
       <c r="C7" t="n">
-        <v>1.856484908730718</v>
+        <v>1.916371518689774</v>
       </c>
       <c r="D7" t="n">
-        <v>46.65166915810418</v>
+        <v>47.37030847761284</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.337942194439155</v>
+        <v>3.421390749300134</v>
       </c>
       <c r="C8" t="n">
-        <v>7.510369937488099</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="D8" t="n">
-        <v>54.74225198880214</v>
+        <v>55.32639187282899</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>19.74687332322034</v>
+        <v>20.52343575727956</v>
       </c>
       <c r="D9" t="n">
-        <v>57.243745139223</v>
+        <v>57.79843259212245</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.53415286656828</v>
+        <v>10.81885970079985</v>
       </c>
       <c r="C10" t="n">
-        <v>37.29659528433633</v>
+        <v>39.14718970684157</v>
       </c>
       <c r="D10" t="n">
-        <v>60.50020227420969</v>
+        <v>61.4966761940202</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13.14952875068177</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="C11" t="n">
-        <v>55.79664902316321</v>
+        <v>57.92900503678727</v>
       </c>
       <c r="D11" t="n">
-        <v>65.21455475000286</v>
+        <v>66.45842909128358</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.10280577150543</v>
+        <v>14.31977201414398</v>
       </c>
       <c r="C12" t="n">
-        <v>68.56133267378024</v>
+        <v>71.16492758544278</v>
       </c>
       <c r="D12" t="n">
-        <v>67.69346770322606</v>
+        <v>67.91043394586461</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="C13" t="n">
-        <v>74.40665850486577</v>
+        <v>75.70747421299279</v>
       </c>
       <c r="D13" t="n">
         <v>65.82127483122741</v>
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>76.51447082588366</v>
+        <v>76.82175785731292</v>
       </c>
       <c r="D14" t="n">
-        <v>64.53027660014286</v>
+        <v>63.91570253728435</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.0334615374024</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>75.6092994425681</v>
+        <v>75.25096153051801</v>
       </c>
       <c r="D15" t="n">
-        <v>61.99245878466483</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>73.15689367735958</v>
+        <v>71.91694632689584</v>
       </c>
       <c r="D16" t="n">
-        <v>60.34410438923444</v>
+        <v>58.69084125528282</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>69.41643492417923</v>
+        <v>68.4719936326938</v>
       </c>
       <c r="D17" t="n">
-        <v>55.72203619764046</v>
+        <v>55.24981555189775</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>67.41661485062848</v>
+        <v>66.88156235181395</v>
       </c>
       <c r="D18" t="n">
-        <v>49.22482989093507</v>
+        <v>48.68977739212056</v>
       </c>
     </row>
     <row r="19">
@@ -2573,13 +2573,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>7.221736112439537</v>
       </c>
       <c r="C19" t="n">
-        <v>67.40287038276901</v>
+        <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>41.52498264652733</v>
+        <v>39.11773727571416</v>
       </c>
     </row>
     <row r="20">
@@ -2590,10 +2590,10 @@
         <v>7.397468951499714</v>
       </c>
       <c r="C20" t="n">
-        <v>69.93970645054276</v>
+        <v>71.28470080536088</v>
       </c>
       <c r="D20" t="n">
-        <v>31.60736733822606</v>
+        <v>28.91737862858979</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>91.35545778226893</v>
+        <v>74.47304553822951</v>
       </c>
       <c r="C21" t="n">
-        <v>636.0623748090475</v>
+        <v>526.6308220203373</v>
       </c>
       <c r="D21" t="n">
-        <v>47.96161533569119</v>
+        <v>35.10872146802249</v>
       </c>
     </row>
   </sheetData>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009817477042468104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3288854809226815</v>
+        <v>0.3141592653589793</v>
       </c>
     </row>
     <row r="4">
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3.39488356128547</v>
+        <v>3.254493639578176</v>
       </c>
     </row>
     <row r="5">
@@ -2708,7 +2708,7 @@
         <v>0.1207549676223577</v>
       </c>
       <c r="D6" t="n">
-        <v>29.54471541160352</v>
+        <v>29.82647700272235</v>
       </c>
     </row>
     <row r="7">
@@ -2722,7 +2722,7 @@
         <v>1.257618809140164</v>
       </c>
       <c r="D7" t="n">
-        <v>46.11268966847268</v>
+        <v>46.35223610830891</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.503456645829366</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="D8" t="n">
-        <v>54.82570054366312</v>
+        <v>56.07742886657781</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>15.97499864350409</v>
+        <v>16.64062358698343</v>
       </c>
       <c r="D9" t="n">
-        <v>57.90937008270233</v>
+        <v>58.46405753560178</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.252972112526189</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>60.78490910844128</v>
+        <v>61.639029611136</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12.08335074386974</v>
+        <v>12.43874341280708</v>
       </c>
       <c r="C11" t="n">
-        <v>52.06502599932108</v>
+        <v>54.19738201294516</v>
       </c>
       <c r="D11" t="n">
-        <v>65.74764375340887</v>
+        <v>66.99151809468958</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="C12" t="n">
-        <v>67.04256897531043</v>
+        <v>70.2970626148886</v>
       </c>
       <c r="D12" t="n">
-        <v>67.47650146058751</v>
+        <v>67.91043394586461</v>
       </c>
     </row>
     <row r="13">
@@ -2800,10 +2800,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="C13" t="n">
-        <v>75.96763735461819</v>
+        <v>77.78877934599603</v>
       </c>
       <c r="D13" t="n">
         <v>66.08143797285281</v>
@@ -2814,10 +2814,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>79.28005410874692</v>
+        <v>79.58734114017618</v>
       </c>
       <c r="D14" t="n">
         <v>64.53027660014286</v>
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.0334615374024</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>78.83434065101888</v>
+        <v>78.47600273896879</v>
       </c>
       <c r="D15" t="n">
-        <v>62.70913460876501</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>75.63678837828701</v>
+        <v>75.22347259479911</v>
       </c>
       <c r="D16" t="n">
-        <v>59.93078860574654</v>
+        <v>59.10415703877072</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>72.72197944437823</v>
+        <v>71.30531750715009</v>
       </c>
       <c r="D17" t="n">
-        <v>55.72203619764046</v>
+        <v>54.77759490615504</v>
       </c>
     </row>
     <row r="18">
@@ -2870,13 +2870,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="C18" t="n">
-        <v>69.55682484588651</v>
+        <v>69.021772347072</v>
       </c>
       <c r="D18" t="n">
-        <v>49.22482989093507</v>
+        <v>48.68977739212056</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>6.619924769736241</v>
       </c>
       <c r="C19" t="n">
-        <v>68.00468172547231</v>
+        <v>68.6064930681756</v>
       </c>
       <c r="D19" t="n">
-        <v>42.12679398923063</v>
+        <v>39.71954861841746</v>
       </c>
     </row>
     <row r="20">
@@ -2901,10 +2901,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>70.61220362795183</v>
+        <v>71.28470080536088</v>
       </c>
       <c r="D20" t="n">
-        <v>32.27986451563512</v>
+        <v>28.91737862858979</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>96.1771861041782</v>
+        <v>78.43675394656007</v>
       </c>
       <c r="C21" t="n">
-        <v>684.9692278639034</v>
+        <v>565.3982680314539</v>
       </c>
       <c r="D21" t="n">
-        <v>53.95305561941705</v>
+        <v>39.21837697328004</v>
       </c>
     </row>
   </sheetData>
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2748893571891069</v>
+        <v>0.2552544031041707</v>
       </c>
     </row>
     <row r="4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.935425635697963</v>
+        <v>2.820561154301086</v>
       </c>
     </row>
     <row r="5">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>11.48644813968768</v>
+        <v>11.31464229144449</v>
       </c>
     </row>
     <row r="6">
@@ -3019,7 +3019,7 @@
         <v>0.04025165587411923</v>
       </c>
       <c r="D6" t="n">
-        <v>27.85414586489051</v>
+        <v>28.01515248838698</v>
       </c>
     </row>
     <row r="7">
@@ -3033,7 +3033,7 @@
         <v>0.8384125394267761</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>45.57371017884118</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="D8" t="n">
-        <v>54.82570054366312</v>
+        <v>55.91053175685585</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>12.86874890726719</v>
+        <v>13.31249886958674</v>
       </c>
       <c r="D9" t="n">
-        <v>58.46405753560178</v>
+        <v>59.12968247908112</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>28.18597658892593</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>61.639029611136</v>
+        <v>62.49315011383072</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.0171727370577</v>
+        <v>11.37256540599505</v>
       </c>
       <c r="C11" t="n">
-        <v>47.26722496866692</v>
+        <v>49.93266998569701</v>
       </c>
       <c r="D11" t="n">
-        <v>65.39225108447152</v>
+        <v>66.63612542575224</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12.58404207303562</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="C12" t="n">
-        <v>65.08987279156352</v>
+        <v>68.12740018850316</v>
       </c>
       <c r="D12" t="n">
-        <v>67.47650146058751</v>
+        <v>67.91043394586461</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C13" t="n">
-        <v>76.48796363786902</v>
+        <v>78.82943191249764</v>
       </c>
       <c r="D13" t="n">
-        <v>66.34160111447822</v>
+        <v>66.86192739772903</v>
       </c>
     </row>
     <row r="14">
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>80.8164892658932</v>
+        <v>81.43106332875169</v>
       </c>
       <c r="D14" t="n">
-        <v>65.14485066300135</v>
+        <v>64.53027660014286</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.0334615374024</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>82.05938185946964</v>
+        <v>81.70104394741955</v>
       </c>
       <c r="D15" t="n">
-        <v>62.35079669671492</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>79.35663042967818</v>
+        <v>78.52999886270236</v>
       </c>
       <c r="D16" t="n">
-        <v>59.93078860574654</v>
+        <v>59.51747282225863</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>75.55530331883453</v>
+        <v>74.13864138160638</v>
       </c>
       <c r="D17" t="n">
-        <v>55.72203619764046</v>
+        <v>54.77759490615504</v>
       </c>
     </row>
     <row r="18">
@@ -3187,7 +3187,7 @@
         <v>71.16198234233005</v>
       </c>
       <c r="D18" t="n">
-        <v>49.75988238974958</v>
+        <v>48.68977739212056</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>69.8101157535822</v>
       </c>
       <c r="D19" t="n">
-        <v>42.12679398923063</v>
+        <v>40.32135996112075</v>
       </c>
     </row>
     <row r="20">
@@ -3215,7 +3215,7 @@
         <v>71.28470080536088</v>
       </c>
       <c r="D20" t="n">
-        <v>32.27986451563512</v>
+        <v>28.91737862858979</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>101.1102812193752</v>
+        <v>81.38675244194353</v>
       </c>
       <c r="C21" t="n">
-        <v>734.2532326645104</v>
+        <v>605.3836517256896</v>
       </c>
       <c r="D21" t="n">
-        <v>60.18469120200906</v>
+        <v>43.48059377035339</v>
       </c>
     </row>
   </sheetData>
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2258019719767664</v>
+        <v>0.2061670178918302</v>
       </c>
     </row>
     <row r="4">
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.565306751196915</v>
+        <v>2.43767954964483</v>
       </c>
     </row>
     <row r="5">
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33289458719768</v>
+        <v>10.11200135374215</v>
       </c>
     </row>
     <row r="6">
@@ -3344,7 +3344,7 @@
         <v>0.5389794896314989</v>
       </c>
       <c r="D7" t="n">
-        <v>43.59745205019235</v>
+        <v>44.55563780953724</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.335176877775662</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
         <v>3.087596529856218</v>
       </c>
       <c r="D8" t="n">
-        <v>54.57535487908019</v>
+        <v>55.66018609227291</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.549999698556465</v>
+        <v>3.771874679716245</v>
       </c>
       <c r="C9" t="n">
-        <v>10.20624913334984</v>
+        <v>10.53906160508951</v>
       </c>
       <c r="D9" t="n">
-        <v>59.46249495082079</v>
+        <v>59.68436993198057</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="C10" t="n">
-        <v>23.77302065833652</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>61.78138302825178</v>
+        <v>63.34727061652544</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.773298395776996</v>
+        <v>10.12869106471434</v>
       </c>
       <c r="C11" t="n">
-        <v>42.82481660695011</v>
+        <v>45.13486895504285</v>
       </c>
       <c r="D11" t="n">
-        <v>65.21455475000286</v>
+        <v>66.45842909128358</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.93314334511998</v>
+        <v>12.15010958775853</v>
       </c>
       <c r="C12" t="n">
-        <v>62.0523453946239</v>
+        <v>65.08987279156352</v>
       </c>
       <c r="D12" t="n">
-        <v>67.25953521794898</v>
+        <v>67.91043394586461</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.48783079801943</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="C13" t="n">
-        <v>75.18714792974198</v>
+        <v>78.82943191249764</v>
       </c>
       <c r="D13" t="n">
-        <v>67.12209053935443</v>
+        <v>67.64241682260524</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>82.66021145446869</v>
+        <v>83.88935958018571</v>
       </c>
       <c r="D14" t="n">
-        <v>64.83756363157211</v>
+        <v>64.53027660014286</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.0334615374024</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
         <v>84.56774724382024</v>
       </c>
       <c r="D15" t="n">
-        <v>62.35079669671492</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
         <v>81.83652513060562</v>
       </c>
       <c r="D16" t="n">
-        <v>59.51747282225863</v>
+        <v>59.93078860574654</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>78.86084783903355</v>
+        <v>77.44418590180538</v>
       </c>
       <c r="D17" t="n">
-        <v>56.19425684338318</v>
+        <v>54.77759490615504</v>
       </c>
     </row>
     <row r="18">
@@ -3492,13 +3492,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>74.37229733521713</v>
+        <v>73.3021923375881</v>
       </c>
       <c r="D18" t="n">
-        <v>49.75988238974958</v>
+        <v>49.22482989093507</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.814490741626358</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
         <v>71.01373843898878</v>
       </c>
       <c r="D19" t="n">
-        <v>42.12679398923063</v>
+        <v>40.32135996112075</v>
       </c>
     </row>
     <row r="20">
@@ -3526,7 +3526,7 @@
         <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
-        <v>32.27986451563512</v>
+        <v>29.58987580599885</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>104.9182205799143</v>
+        <v>84.38687033394172</v>
       </c>
       <c r="C21" t="n">
-        <v>786.2694883459463</v>
+        <v>645.4455217433921</v>
       </c>
       <c r="D21" t="n">
-        <v>66.65392836841617</v>
+        <v>47.89525073007503</v>
       </c>
     </row>
   </sheetData>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.186532063806894</v>
+        <v>0.1718058482431918</v>
       </c>
     </row>
     <row r="4">
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.0930861054542</v>
       </c>
     </row>
     <row r="5">
@@ -3627,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>9.27751580513236</v>
+        <v>9.007535186464487</v>
       </c>
     </row>
     <row r="6">
@@ -3641,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>24.51325842733861</v>
+        <v>24.59376173908685</v>
       </c>
     </row>
     <row r="7">
@@ -3655,7 +3655,7 @@
         <v>0.2994330497952771</v>
       </c>
       <c r="D7" t="n">
-        <v>42.16017341117502</v>
+        <v>42.99858595060179</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9179341034707675</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
         <v>2.253110981246429</v>
       </c>
       <c r="D8" t="n">
-        <v>54.74225198880214</v>
+        <v>55.24294331796801</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>8.098436812331936</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="D9" t="n">
-        <v>59.68436993198057</v>
+        <v>60.68280734719958</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>19.92947839621025</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>62.06608986248335</v>
+        <v>63.48962403364123</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>40.15937158992001</v>
       </c>
       <c r="D11" t="n">
-        <v>65.03685841553418</v>
+        <v>66.45842909128358</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.0652783745658</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>57.71302054185299</v>
+        <v>60.75054793879262</v>
       </c>
       <c r="D12" t="n">
-        <v>67.69346770322606</v>
+        <v>68.56133267378024</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="C13" t="n">
-        <v>74.14649536324036</v>
+        <v>77.52861620437062</v>
       </c>
       <c r="D13" t="n">
-        <v>66.86192739772903</v>
+        <v>67.38225368097983</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>83.58207254875646</v>
+        <v>85.73308176876121</v>
       </c>
       <c r="D14" t="n">
-        <v>64.83756363157211</v>
+        <v>64.53027660014286</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.0334615374024</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>86.00109889202058</v>
+        <v>87.43445054022092</v>
       </c>
       <c r="D15" t="n">
-        <v>62.35079669671492</v>
+        <v>61.99245878466483</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
         <v>85.14305139850887</v>
       </c>
       <c r="D16" t="n">
-        <v>59.93078860574654</v>
+        <v>59.51747282225863</v>
       </c>
     </row>
     <row r="17">
@@ -3792,10 +3792,10 @@
         <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>81.69417171348984</v>
+        <v>80.7497304220044</v>
       </c>
       <c r="D17" t="n">
-        <v>55.72203619764046</v>
+        <v>54.77759490615504</v>
       </c>
     </row>
     <row r="18">
@@ -3803,10 +3803,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>76.51250733047517</v>
+        <v>75.97745483166067</v>
       </c>
       <c r="D18" t="n">
         <v>49.75988238974958</v>
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>73.42098380980195</v>
+        <v>72.81917246709867</v>
       </c>
       <c r="D19" t="n">
-        <v>42.12679398923063</v>
+        <v>40.32135996112075</v>
       </c>
     </row>
     <row r="20">
@@ -3837,7 +3837,7 @@
         <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>32.95236169304418</v>
+        <v>29.58987580599885</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>108.771863673082</v>
+        <v>87.43499720010826</v>
       </c>
       <c r="C21" t="n">
-        <v>838.5551815727138</v>
+        <v>687.821977974185</v>
       </c>
       <c r="D21" t="n">
-        <v>72.09297941122878</v>
+        <v>52.46099832006495</v>
       </c>
     </row>
   </sheetData>
@@ -3921,7 +3921,7 @@
         <v>2.667408512438584</v>
       </c>
       <c r="C4" t="n">
-        <v>4.35208757292611</v>
+        <v>4.44142661401257</v>
       </c>
       <c r="D4" t="n">
         <v>24.14706653365455</v>
@@ -3935,7 +3935,7 @@
         <v>7.682175785731292</v>
       </c>
       <c r="C5" t="n">
-        <v>14.57895340806514</v>
+        <v>14.5298660228528</v>
       </c>
       <c r="D5" t="n">
         <v>27.14532402242431</v>
@@ -3946,7 +3946,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.06291396852981</v>
+        <v>10.14341728027805</v>
       </c>
       <c r="C6" t="n">
         <v>19.84406634594078</v>
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.15698182168825</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>23.41566449399068</v>
+        <v>23.29589127407256</v>
       </c>
       <c r="D7" t="n">
-        <v>34.31502750653876</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -3974,10 +3974,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C8" t="n">
-        <v>25.86905200690345</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D8" t="n">
         <v>43.47669708257</v>
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.08749871886498</v>
+        <v>14.97656122828509</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>49.36718330805084</v>
+        <v>48.7015583645715</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14.66240196292611</v>
+        <v>14.52004854581033</v>
       </c>
       <c r="C10" t="n">
-        <v>37.72365553568369</v>
+        <v>38.15071578703105</v>
       </c>
       <c r="D10" t="n">
-        <v>67.90257996423065</v>
+        <v>68.61434704980958</v>
       </c>
     </row>
     <row r="11">
@@ -4019,10 +4019,10 @@
         <v>12.08335074386974</v>
       </c>
       <c r="C11" t="n">
-        <v>39.626282586514</v>
+        <v>38.73780091417063</v>
       </c>
       <c r="D11" t="n">
-        <v>56.68513069550657</v>
+        <v>56.32973802656922</v>
       </c>
     </row>
     <row r="12">
@@ -4030,10 +4030,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>36.88426124855266</v>
+        <v>37.10122749119121</v>
       </c>
       <c r="D12" t="n">
         <v>57.92998678449154</v>
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.6666888066416</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
         <v>37.46349239405829</v>
       </c>
       <c r="D13" t="n">
-        <v>60.61801199871932</v>
+        <v>60.35784885709391</v>
       </c>
     </row>
     <row r="14">
@@ -4058,7 +4058,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
         <v>39.94731408580272</v>
@@ -4072,7 +4072,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="C15" t="n">
         <v>45.50891483036089</v>
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="C16" t="n">
         <v>52.0777887194763</v>
       </c>
       <c r="D16" t="n">
-        <v>56.62426233784328</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4103,10 +4103,10 @@
         <v>17.47216389248049</v>
       </c>
       <c r="C17" t="n">
-        <v>56.6664774891259</v>
+        <v>57.13869813486862</v>
       </c>
       <c r="D17" t="n">
-        <v>52.88871232318417</v>
+        <v>51.47205038595602</v>
       </c>
     </row>
     <row r="18">
@@ -4145,10 +4145,10 @@
         <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
-        <v>16.81242943522663</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.43451089120197</v>
+        <v>15.59626222163283</v>
       </c>
       <c r="C21" t="n">
-        <v>103.089204681176</v>
+        <v>97.29096909685239</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1570796326794897</v>
+        <v>0.1423534171157875</v>
       </c>
     </row>
     <row r="4">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.939933463591697</v>
+        <v>1.799543541884403</v>
       </c>
     </row>
     <row r="5">
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8.320311793491719</v>
+        <v>8.099418560036186</v>
       </c>
     </row>
     <row r="6">
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>22.86294053649972</v>
+        <v>22.90319219237384</v>
       </c>
     </row>
     <row r="7">
@@ -4277,7 +4277,7 @@
         <v>0.1796598298771663</v>
       </c>
       <c r="D7" t="n">
-        <v>41.02232782195297</v>
+        <v>41.3816474817073</v>
       </c>
     </row>
     <row r="8">
@@ -4291,7 +4291,7 @@
         <v>1.585522542358599</v>
       </c>
       <c r="D8" t="n">
-        <v>54.07466354991431</v>
+        <v>54.65880343394117</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
         <v>6.323436963053704</v>
       </c>
       <c r="D9" t="n">
-        <v>59.79530742256046</v>
+        <v>61.4593697812588</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>16.65534980254714</v>
+        <v>17.36711688812608</v>
       </c>
       <c r="D10" t="n">
-        <v>62.35079669671494</v>
+        <v>63.63197745075701</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.996335051090269</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
-        <v>65.5699474189402</v>
+        <v>66.45842909128358</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9.980447161373073</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="C12" t="n">
-        <v>53.59066193172063</v>
+        <v>56.41122308602172</v>
       </c>
       <c r="D12" t="n">
-        <v>67.47650146058751</v>
+        <v>69.21223140169589</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="C13" t="n">
-        <v>71.80502708861172</v>
+        <v>75.18714792974198</v>
       </c>
       <c r="D13" t="n">
-        <v>66.86192739772903</v>
+        <v>67.38225368097983</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="C14" t="n">
-        <v>82.96749848589795</v>
+        <v>86.34765583161972</v>
       </c>
       <c r="D14" t="n">
-        <v>64.83756363157211</v>
+        <v>64.53027660014286</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.0334615374024</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>88.1511263643211</v>
+        <v>89.94281592457153</v>
       </c>
       <c r="D15" t="n">
-        <v>62.70913460876501</v>
+        <v>62.35079669671492</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
         <v>88.03626188292422</v>
       </c>
       <c r="D16" t="n">
-        <v>59.51747282225863</v>
+        <v>59.10415703877072</v>
       </c>
     </row>
     <row r="17">
@@ -4417,7 +4417,7 @@
         <v>84.05527494220343</v>
       </c>
       <c r="D17" t="n">
-        <v>55.72203619764046</v>
+        <v>54.77759490615504</v>
       </c>
     </row>
     <row r="18">
@@ -4428,10 +4428,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>79.72282232336224</v>
+        <v>78.65271732573322</v>
       </c>
       <c r="D18" t="n">
-        <v>49.75988238974958</v>
+        <v>50.2949348885641</v>
       </c>
     </row>
     <row r="19">
@@ -4439,13 +4439,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>75.82822918061514</v>
+        <v>74.62460649520854</v>
       </c>
       <c r="D19" t="n">
-        <v>42.12679398923063</v>
+        <v>40.32135996112075</v>
       </c>
     </row>
     <row r="20">
@@ -4459,7 +4459,7 @@
         <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>33.62485887045325</v>
+        <v>29.58987580599885</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>112.6693475059312</v>
+        <v>90.52925034969708</v>
       </c>
       <c r="C21" t="n">
-        <v>892.2894302481219</v>
+        <v>730.1898745311094</v>
       </c>
       <c r="D21" t="n">
-        <v>77.70299827995255</v>
+        <v>57.17636864191395</v>
       </c>
     </row>
   </sheetData>
@@ -4540,10 +4540,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.378373776762522</v>
+        <v>1.403899217072939</v>
       </c>
       <c r="C4" t="n">
-        <v>2.080323385298991</v>
+        <v>2.131374265919825</v>
       </c>
       <c r="D4" t="n">
         <v>20.98191193516283</v>
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.013204688511715</v>
+        <v>6.037748381117885</v>
       </c>
       <c r="C5" t="n">
-        <v>11.1428364432013</v>
+        <v>11.33918598405066</v>
       </c>
       <c r="D5" t="n">
-        <v>29.20699420134261</v>
+        <v>29.45243112740432</v>
       </c>
     </row>
     <row r="6">
@@ -4571,10 +4571,10 @@
         <v>10.34467555964864</v>
       </c>
       <c r="C6" t="n">
-        <v>21.33337761328319</v>
+        <v>21.25287430153496</v>
       </c>
       <c r="D6" t="n">
-        <v>36.74976181307086</v>
+        <v>36.30699359845555</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>12.33664165156542</v>
       </c>
       <c r="C7" t="n">
-        <v>25.99078872223005</v>
+        <v>25.87101550231194</v>
       </c>
       <c r="D7" t="n">
-        <v>36.59071868498287</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.93590866178347</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C8" t="n">
         <v>28.70630287217673</v>
       </c>
       <c r="D8" t="n">
-        <v>43.22635141798705</v>
+        <v>43.72704274715294</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.30937370002476</v>
+        <v>15.19843620944487</v>
       </c>
       <c r="C9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.17187226816797</v>
       </c>
       <c r="D9" t="n">
-        <v>50.14374574211007</v>
+        <v>49.03437083631118</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.23181563138926</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="C10" t="n">
-        <v>37.72365553568369</v>
+        <v>38.57777603837842</v>
       </c>
       <c r="D10" t="n">
-        <v>65.76727870749383</v>
+        <v>66.90610604442013</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13.32722508515045</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="C11" t="n">
-        <v>42.46942393801276</v>
+        <v>41.93633493460674</v>
       </c>
       <c r="D11" t="n">
-        <v>59.52827204700533</v>
+        <v>59.17287937806799</v>
       </c>
     </row>
     <row r="12">
@@ -4655,7 +4655,7 @@
         <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>41.44055234396211</v>
+        <v>40.78965361604648</v>
       </c>
       <c r="D12" t="n">
         <v>58.79785175504571</v>
@@ -4672,7 +4672,7 @@
         <v>39.80496066868693</v>
       </c>
       <c r="D13" t="n">
-        <v>60.61801199871932</v>
+        <v>60.09768571546851</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="C14" t="n">
-        <v>41.17646221151972</v>
+        <v>41.48374924294897</v>
       </c>
       <c r="D14" t="n">
-        <v>62.07198034870884</v>
+        <v>61.76469331727959</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="C15" t="n">
         <v>45.15057691831081</v>
       </c>
       <c r="D15" t="n">
-        <v>60.20076922441442</v>
+        <v>60.5591071364645</v>
       </c>
     </row>
     <row r="16">
@@ -4714,7 +4714,7 @@
         <v>51.66447293598839</v>
       </c>
       <c r="D16" t="n">
-        <v>57.4508939048191</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4728,7 +4728,7 @@
         <v>57.13869813486862</v>
       </c>
       <c r="D17" t="n">
-        <v>52.88871232318417</v>
+        <v>52.41649167744146</v>
       </c>
     </row>
     <row r="18">
@@ -4739,10 +4739,10 @@
         <v>17.65673246087889</v>
       </c>
       <c r="C18" t="n">
-        <v>62.06608986248335</v>
+        <v>63.13619486011238</v>
       </c>
       <c r="D18" t="n">
-        <v>44.40935740160447</v>
+        <v>43.87430490278995</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="C19" t="n">
         <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>33.7014351913845</v>
+        <v>33.09962384868121</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>19.50241814486288</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>18.15742379004475</v>
+        <v>17.48492661263569</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>23.16176878585094</v>
+        <v>21.36757820373163</v>
       </c>
       <c r="C21" t="n">
-        <v>135.1103179174638</v>
+        <v>124.3898302574377</v>
       </c>
       <c r="D21" t="n">
-        <v>1.544117919056729</v>
+        <v>1.52625558598083</v>
       </c>
     </row>
   </sheetData>
@@ -4851,10 +4851,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.714712328691678</v>
+        <v>0.7274750488468864</v>
       </c>
       <c r="C4" t="n">
-        <v>1.008254892261474</v>
+        <v>1.033780332571891</v>
       </c>
       <c r="D4" t="n">
         <v>18.237927101793</v>
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.246058820867455</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C5" t="n">
-        <v>7.43673885966959</v>
+        <v>7.584001015306612</v>
       </c>
       <c r="D5" t="n">
-        <v>30.11511082777092</v>
+        <v>30.31146036862028</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>9.45913913041802</v>
       </c>
       <c r="C6" t="n">
-        <v>19.48180144307371</v>
+        <v>19.80381469006666</v>
       </c>
       <c r="D6" t="n">
-        <v>37.59504658642736</v>
+        <v>37.27303333943441</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.45641487148353</v>
+        <v>12.57618809140164</v>
       </c>
       <c r="C7" t="n">
-        <v>28.32636651063322</v>
+        <v>28.14670668075605</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>39.1059563032632</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.10280577150543</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>43.97738841173587</v>
+        <v>43.89393985687489</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>15.30937370002476</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>50.14374574211007</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.65887588273663</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="C10" t="n">
-        <v>38.72012945549421</v>
+        <v>39.28954312395736</v>
       </c>
       <c r="D10" t="n">
-        <v>64.20139111922018</v>
+        <v>65.62492529037804</v>
       </c>
     </row>
     <row r="11">
@@ -4952,10 +4952,10 @@
         <v>14.03801042302514</v>
       </c>
       <c r="C11" t="n">
-        <v>43.89099461376214</v>
+        <v>44.42408361716816</v>
       </c>
       <c r="D11" t="n">
-        <v>62.19371706403542</v>
+        <v>61.30523539169207</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12.15010958775853</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C12" t="n">
-        <v>45.34594471145593</v>
+        <v>44.2611134982632</v>
       </c>
       <c r="D12" t="n">
-        <v>59.44875048296136</v>
+        <v>59.88268296823844</v>
       </c>
     </row>
     <row r="13">
@@ -4980,10 +4980,10 @@
         <v>10.6666888066416</v>
       </c>
       <c r="C13" t="n">
-        <v>43.4472446514426</v>
+        <v>42.66675522656638</v>
       </c>
       <c r="D13" t="n">
-        <v>60.61801199871932</v>
+        <v>60.09768571546851</v>
       </c>
     </row>
     <row r="14">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="C15" t="n">
-        <v>45.50891483036089</v>
+        <v>46.22559065446107</v>
       </c>
       <c r="D15" t="n">
-        <v>60.91744504851458</v>
+        <v>60.5591071364645</v>
       </c>
     </row>
     <row r="16">
@@ -5025,7 +5025,7 @@
         <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>57.4508939048191</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -5033,7 +5033,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="C17" t="n">
         <v>57.13869813486862</v>
@@ -5050,10 +5050,10 @@
         <v>16.58662746324986</v>
       </c>
       <c r="C18" t="n">
-        <v>61.53103736366884</v>
+        <v>62.60114236129787</v>
       </c>
       <c r="D18" t="n">
-        <v>45.47946239923349</v>
+        <v>44.40935740160447</v>
       </c>
     </row>
     <row r="19">
@@ -5064,10 +5064,10 @@
         <v>17.45252893839555</v>
       </c>
       <c r="C19" t="n">
-        <v>67.40287038276901</v>
+        <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>34.3032465340878</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>18.15742379004475</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>29.66943854726223</v>
+        <v>26.77133874827893</v>
       </c>
       <c r="C21" t="n">
-        <v>169.9978641086376</v>
+        <v>152.754109328415</v>
       </c>
       <c r="D21" t="n">
-        <v>4.009383587467869</v>
+        <v>3.149569264503403</v>
       </c>
     </row>
   </sheetData>
@@ -5162,10 +5162,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3701188845010475</v>
+        <v>0.382881604656256</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4977460860531329</v>
+        <v>0.5105088062083414</v>
       </c>
       <c r="D4" t="n">
         <v>16.0044510746315</v>
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.847068342315751</v>
+        <v>2.871612034921921</v>
       </c>
       <c r="C5" t="n">
-        <v>4.66330159517235</v>
+        <v>4.761476365597031</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>29.82058651649687</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.808821239579131</v>
+        <v>7.929576207201488</v>
       </c>
       <c r="C6" t="n">
-        <v>15.77864910265474</v>
+        <v>16.06041069377357</v>
       </c>
       <c r="D6" t="n">
-        <v>38.52083467153211</v>
+        <v>38.68184129502858</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.15698182168825</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>28.32636651063322</v>
+        <v>28.68568617038755</v>
       </c>
       <c r="D7" t="n">
-        <v>40.96244121199391</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C8" t="n">
-        <v>34.79804737702819</v>
+        <v>34.54770171244525</v>
       </c>
       <c r="D8" t="n">
-        <v>44.47807974090174</v>
+        <v>44.56152829576272</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>15.42031119060464</v>
       </c>
       <c r="C9" t="n">
-        <v>36.83124687252333</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>50.25468323268996</v>
+        <v>50.14374574211007</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.65887588273663</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="C10" t="n">
-        <v>40.42837046088366</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>62.92021036517809</v>
+        <v>63.9166842849886</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14.9264920953685</v>
+        <v>14.74879576089983</v>
       </c>
       <c r="C11" t="n">
-        <v>45.31256528951153</v>
+        <v>45.66795795844887</v>
       </c>
       <c r="D11" t="n">
-        <v>64.14837674319081</v>
+        <v>63.43759140531613</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12.80100831567416</v>
+        <v>12.58404207303562</v>
       </c>
       <c r="C12" t="n">
-        <v>48.16650586575701</v>
+        <v>47.94953962311847</v>
       </c>
       <c r="D12" t="n">
-        <v>60.31661545351553</v>
+        <v>60.53358169615408</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>47.34969177582367</v>
+        <v>46.04887606769665</v>
       </c>
       <c r="D13" t="n">
-        <v>60.61801199871932</v>
+        <v>60.35784885709391</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.1711936201</v>
       </c>
       <c r="D14" t="n">
-        <v>62.68655441156734</v>
+        <v>62.37926738013809</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.75013736150257</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="C15" t="n">
-        <v>46.58392856651115</v>
+        <v>46.94226647856124</v>
       </c>
       <c r="D15" t="n">
-        <v>60.91744504851458</v>
+        <v>60.5591071364645</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="C16" t="n">
-        <v>50.42452558552468</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>57.864209688307</v>
+        <v>58.2775254717949</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>13.69439872653876</v>
       </c>
       <c r="C17" t="n">
-        <v>56.6664774891259</v>
+        <v>57.13869813486862</v>
       </c>
       <c r="D17" t="n">
-        <v>54.30537426041232</v>
+        <v>53.36093296892689</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>14.98146996680633</v>
       </c>
       <c r="C18" t="n">
-        <v>62.06608986248335</v>
+        <v>62.60114236129787</v>
       </c>
       <c r="D18" t="n">
-        <v>46.014514898048</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -5375,10 +5375,10 @@
         <v>16.24890625298896</v>
       </c>
       <c r="C19" t="n">
-        <v>66.80105904006572</v>
+        <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>36.10868056219768</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>16.81242943522663</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>21.51990967709008</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>35.77790209575883</v>
+        <v>31.66326801958617</v>
       </c>
       <c r="C21" t="n">
-        <v>206.346970226702</v>
+        <v>182.6727001129971</v>
       </c>
       <c r="D21" t="n">
-        <v>6.656353878280711</v>
+        <v>4.871272003013257</v>
       </c>
     </row>
   </sheetData>
@@ -5476,7 +5476,7 @@
         <v>0.191440802328128</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2424916829489621</v>
+        <v>0.2552544031041707</v>
       </c>
       <c r="D4" t="n">
         <v>13.93689040948772</v>
@@ -5490,10 +5490,10 @@
         <v>1.86532063806894</v>
       </c>
       <c r="C5" t="n">
-        <v>2.847068342315751</v>
+        <v>2.896155727528091</v>
       </c>
       <c r="D5" t="n">
-        <v>28.61794557879453</v>
+        <v>28.76520773443155</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6.078000036992004</v>
+        <v>6.239006660488481</v>
       </c>
       <c r="C6" t="n">
-        <v>11.87423848286517</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D6" t="n">
-        <v>39.52712606838509</v>
+        <v>39.72838434775569</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.13890945238431</v>
+        <v>11.19879606234337</v>
       </c>
       <c r="C7" t="n">
-        <v>25.87101550231194</v>
+        <v>26.23033516206628</v>
       </c>
       <c r="D7" t="n">
-        <v>42.51949307092936</v>
+        <v>42.33983324105218</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.80081269369168</v>
       </c>
       <c r="D8" t="n">
-        <v>45.39601384437251</v>
+        <v>45.89670517353839</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.42031119060464</v>
+        <v>15.53124868118453</v>
       </c>
       <c r="C9" t="n">
-        <v>40.49218406165969</v>
+        <v>40.38124657107979</v>
       </c>
       <c r="D9" t="n">
-        <v>50.47655821384974</v>
+        <v>50.36562072326985</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>15.9435827169682</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>62.49315011383072</v>
+        <v>62.63550353094652</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.28188476430585</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="C11" t="n">
-        <v>46.91183229972957</v>
+        <v>47.26722496866692</v>
       </c>
       <c r="D11" t="n">
-        <v>64.68146574659684</v>
+        <v>64.85916208106552</v>
       </c>
     </row>
     <row r="12">
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="C12" t="n">
         <v>50.33616829214246</v>
@@ -5602,10 +5602,10 @@
         <v>11.18701508989241</v>
       </c>
       <c r="C13" t="n">
-        <v>50.73181261695393</v>
+        <v>49.69116005045231</v>
       </c>
       <c r="D13" t="n">
-        <v>61.39850142359553</v>
+        <v>61.13833828197012</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.44775906859456</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="C14" t="n">
-        <v>48.55135096582177</v>
+        <v>48.24406393439251</v>
       </c>
       <c r="D14" t="n">
-        <v>62.37926738013809</v>
+        <v>62.07198034870884</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>48.37561812676158</v>
       </c>
       <c r="D15" t="n">
-        <v>60.91744504851458</v>
+        <v>60.5591071364645</v>
       </c>
     </row>
     <row r="16">
@@ -5641,10 +5641,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11.15952615417349</v>
+        <v>11.5728419376614</v>
       </c>
       <c r="C16" t="n">
-        <v>50.83784136901258</v>
+        <v>51.66447293598839</v>
       </c>
       <c r="D16" t="n">
         <v>58.69084125528282</v>
@@ -5658,10 +5658,10 @@
         <v>12.74995743505333</v>
       </c>
       <c r="C17" t="n">
-        <v>56.19425684338318</v>
+        <v>56.6664774891259</v>
       </c>
       <c r="D17" t="n">
-        <v>54.30537426041232</v>
+        <v>53.36093296892689</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>13.9113649691773</v>
       </c>
       <c r="C18" t="n">
-        <v>62.06608986248335</v>
+        <v>62.60114236129787</v>
       </c>
       <c r="D18" t="n">
         <v>46.54956739686251</v>
@@ -5686,10 +5686,10 @@
         <v>15.04528356758237</v>
       </c>
       <c r="C19" t="n">
-        <v>66.80105904006572</v>
+        <v>68.6064930681756</v>
       </c>
       <c r="D19" t="n">
-        <v>37.31230324760427</v>
+        <v>35.50686921949439</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>15.46743508040849</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>22.86490403190821</v>
+        <v>21.51990967709008</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>42.26280636718002</v>
+        <v>36.80881161101543</v>
       </c>
       <c r="C21" t="n">
-        <v>243.226763174383</v>
+        <v>212.4872306635891</v>
       </c>
       <c r="D21" t="n">
-        <v>9.487568776305718</v>
+        <v>6.692511202002806</v>
       </c>
     </row>
   </sheetData>
@@ -5787,7 +5787,7 @@
         <v>0.08933904108645975</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1148644813968768</v>
+        <v>0.1276272015520853</v>
       </c>
       <c r="D4" t="n">
         <v>12.09905870713769</v>
@@ -5801,10 +5801,10 @@
         <v>1.178097245096173</v>
       </c>
       <c r="C5" t="n">
-        <v>1.693514789825748</v>
+        <v>1.742602175038089</v>
       </c>
       <c r="D5" t="n">
-        <v>27.46439202630453</v>
+        <v>27.58711048933538</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.588688769649592</v>
+        <v>4.669192081397831</v>
       </c>
       <c r="C6" t="n">
-        <v>8.533351045313278</v>
+        <v>8.654106012935635</v>
       </c>
       <c r="D6" t="n">
-        <v>39.64788103600744</v>
+        <v>39.84913931537804</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.761517423326035</v>
       </c>
       <c r="C7" t="n">
-        <v>21.79872602509618</v>
+        <v>22.39759212468673</v>
       </c>
       <c r="D7" t="n">
-        <v>44.01665831990574</v>
+        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>35.63253292563798</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="D8" t="n">
-        <v>46.48084505756524</v>
+        <v>47.31533060617502</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>15.53124868118453</v>
       </c>
       <c r="C9" t="n">
-        <v>43.15468383557703</v>
+        <v>43.37655881673681</v>
       </c>
       <c r="D9" t="n">
-        <v>51.36405813848885</v>
+        <v>50.80937068558941</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>16.08593613408399</v>
       </c>
       <c r="C10" t="n">
-        <v>46.12250714551515</v>
+        <v>46.54956739686252</v>
       </c>
       <c r="D10" t="n">
-        <v>61.4966761940202</v>
+        <v>62.20844327959914</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>15.45958109877452</v>
       </c>
       <c r="C11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.22188464782232</v>
       </c>
       <c r="D11" t="n">
         <v>65.21455475000286</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.10280577150543</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="C12" t="n">
         <v>52.50583071852791</v>
       </c>
       <c r="D12" t="n">
-        <v>63.13717660781662</v>
+        <v>62.26931163726244</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>11.70734137314322</v>
       </c>
       <c r="C13" t="n">
-        <v>53.33344403320798</v>
+        <v>52.81311774995717</v>
       </c>
       <c r="D13" t="n">
-        <v>61.65866456522093</v>
+        <v>61.91882770684634</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.44775906859456</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="C14" t="n">
-        <v>52.23879534297279</v>
+        <v>51.31693424868503</v>
       </c>
       <c r="D14" t="n">
-        <v>62.37926738013809</v>
+        <v>61.76469331727959</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>50.88398351111218</v>
+        <v>50.52564559906209</v>
       </c>
       <c r="D15" t="n">
-        <v>61.63412087261475</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -5952,10 +5952,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10.33289458719768</v>
+        <v>10.74621037068559</v>
       </c>
       <c r="C16" t="n">
-        <v>52.0777887194763</v>
+        <v>52.90442028645212</v>
       </c>
       <c r="D16" t="n">
         <v>58.69084125528282</v>
@@ -5969,10 +5969,10 @@
         <v>11.8055161435679</v>
       </c>
       <c r="C17" t="n">
-        <v>56.19425684338318</v>
+        <v>56.6664774891259</v>
       </c>
       <c r="D17" t="n">
-        <v>54.30537426041232</v>
+        <v>53.36093296892689</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>12.84125997154828</v>
       </c>
       <c r="C18" t="n">
-        <v>61.53103736366884</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
         <v>47.08461989567702</v>
@@ -5997,10 +5997,10 @@
         <v>13.84166088217578</v>
       </c>
       <c r="C19" t="n">
-        <v>66.19924769736242</v>
+        <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>38.51592593301086</v>
+        <v>36.10868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -6011,10 +6011,10 @@
         <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>24.20989838672634</v>
+        <v>22.86490403190821</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>48.23354029897124</v>
+        <v>41.34815953363038</v>
       </c>
       <c r="C21" t="n">
-        <v>282.2555321199058</v>
+        <v>243.7818572503625</v>
       </c>
       <c r="D21" t="n">
-        <v>12.50499192936291</v>
+        <v>8.614199902839664</v>
       </c>
     </row>
   </sheetData>
@@ -6098,10 +6098,10 @@
         <v>0.0382881604656256</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05105088062083414</v>
+        <v>0.06381360077604267</v>
       </c>
       <c r="D4" t="n">
-        <v>10.59305772882308</v>
+        <v>10.47819324742621</v>
       </c>
     </row>
     <row r="5">
@@ -6112,10 +6112,10 @@
         <v>0.7363107781851078</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9817477042468106</v>
+        <v>1.030835089459151</v>
       </c>
       <c r="D5" t="n">
-        <v>25.74633354387261</v>
+        <v>26.06540154775282</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.340887437551896</v>
+        <v>3.421390749300135</v>
       </c>
       <c r="C6" t="n">
-        <v>5.916993413495527</v>
+        <v>6.037748381117884</v>
       </c>
       <c r="D6" t="n">
-        <v>39.48687441251096</v>
+        <v>39.68813269188156</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>17.48689010804419</v>
+        <v>18.1456428175938</v>
       </c>
       <c r="D7" t="n">
         <v>45.75337000871835</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>33.04562772494764</v>
+        <v>33.79666471869644</v>
       </c>
       <c r="D8" t="n">
-        <v>47.56567627075796</v>
+        <v>48.23326470964579</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.19843620944487</v>
+        <v>15.30937370002476</v>
       </c>
       <c r="C9" t="n">
-        <v>44.37499623195582</v>
+        <v>44.81874619427537</v>
       </c>
       <c r="D9" t="n">
-        <v>51.69687061022852</v>
+        <v>51.36405813848885</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.9435827169682</v>
+        <v>16.08593613408399</v>
       </c>
       <c r="C10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.53898915629405</v>
       </c>
       <c r="D10" t="n">
-        <v>60.78490910844128</v>
+        <v>61.92373644536757</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="C11" t="n">
-        <v>51.88732966485241</v>
+        <v>52.06502599932108</v>
       </c>
       <c r="D11" t="n">
-        <v>66.10303642234622</v>
+        <v>65.39225108447152</v>
       </c>
     </row>
     <row r="12">
@@ -6207,10 +6207,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.53673825678252</v>
+        <v>14.31977201414398</v>
       </c>
       <c r="C12" t="n">
-        <v>54.24156065963627</v>
+        <v>54.67549314491336</v>
       </c>
       <c r="D12" t="n">
         <v>63.78807533573226</v>
@@ -6238,10 +6238,10 @@
         <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
-        <v>55.61895268869456</v>
+        <v>54.38980456297755</v>
       </c>
       <c r="D14" t="n">
-        <v>62.99384144299659</v>
+        <v>61.76469331727959</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>53.75068680751286</v>
+        <v>53.03401098341269</v>
       </c>
       <c r="D15" t="n">
         <v>61.63412087261475</v>
@@ -6280,10 +6280,10 @@
         <v>10.86107485208246</v>
       </c>
       <c r="C17" t="n">
-        <v>56.6664774891259</v>
+        <v>57.13869813486862</v>
       </c>
       <c r="D17" t="n">
-        <v>54.30537426041232</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>11.77115497391926</v>
       </c>
       <c r="C18" t="n">
-        <v>60.99598486485433</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>48.15472489330605</v>
+        <v>47.08461989567702</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>12.63803819676919</v>
       </c>
       <c r="C19" t="n">
-        <v>66.19924769736242</v>
+        <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>39.11773727571416</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>71.28470080536088</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>25.55489274154447</v>
+        <v>24.20989838672634</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>54.52180063630241</v>
+        <v>46.09442869956224</v>
       </c>
       <c r="C21" t="n">
-        <v>322.5103122384668</v>
+        <v>275.680140876228</v>
       </c>
       <c r="D21" t="n">
-        <v>15.70967136978205</v>
+        <v>10.63717585374513</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02650718801466388</v>
+        <v>0.02552544031041707</v>
       </c>
     </row>
     <row r="3">
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.241910845872215</v>
+        <v>1.232093368829747</v>
       </c>
     </row>
     <row r="4">
@@ -6412,7 +6412,7 @@
         <v>0.02552544031041707</v>
       </c>
       <c r="D4" t="n">
-        <v>9.201921231905354</v>
+        <v>9.138107631129312</v>
       </c>
     </row>
     <row r="5">
@@ -6423,10 +6423,10 @@
         <v>0.4417864669110648</v>
       </c>
       <c r="C5" t="n">
-        <v>0.564504929941916</v>
+        <v>0.5890486225480863</v>
       </c>
       <c r="D5" t="n">
-        <v>23.93010029101601</v>
+        <v>24.15099352447154</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.374847696573035</v>
+        <v>2.415099352447154</v>
       </c>
       <c r="C6" t="n">
-        <v>3.944662275663684</v>
+        <v>4.065417243286043</v>
       </c>
       <c r="D6" t="n">
-        <v>39.32586778901449</v>
+        <v>39.56737772425921</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.347980655659875</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>13.59426046070558</v>
+        <v>14.25301317025519</v>
       </c>
       <c r="D7" t="n">
-        <v>46.59178254814513</v>
+        <v>46.65166915810418</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>11.34900346109313</v>
       </c>
       <c r="C8" t="n">
-        <v>29.12354564648163</v>
+        <v>29.95803119509142</v>
       </c>
       <c r="D8" t="n">
-        <v>48.81740459367264</v>
+        <v>49.31809592283852</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>14.75468624712531</v>
       </c>
       <c r="C9" t="n">
-        <v>43.70937128847648</v>
+        <v>44.37499623195582</v>
       </c>
       <c r="D9" t="n">
-        <v>52.14062057254808</v>
+        <v>52.58437053486764</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.80122929985241</v>
+        <v>16.08593613408399</v>
       </c>
       <c r="C10" t="n">
-        <v>51.67429041303087</v>
+        <v>51.95899724726245</v>
       </c>
       <c r="D10" t="n">
-        <v>60.78490910844128</v>
+        <v>61.06961594267285</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.99267010218054</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="C11" t="n">
-        <v>54.37507834741383</v>
+        <v>55.08586368528852</v>
       </c>
       <c r="D11" t="n">
-        <v>65.92534008787754</v>
+        <v>65.5699474189402</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.97067074205961</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="C12" t="n">
-        <v>57.06212181393736</v>
+        <v>57.2790880565759</v>
       </c>
       <c r="D12" t="n">
-        <v>64.65594030628644</v>
+        <v>65.08987279156352</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>59.05703314896688</v>
       </c>
       <c r="D13" t="n">
-        <v>62.69931713172255</v>
+        <v>62.43915399009714</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>10.75504610002381</v>
       </c>
       <c r="C14" t="n">
-        <v>58.99911003441632</v>
+        <v>57.76996190869932</v>
       </c>
       <c r="D14" t="n">
-        <v>63.60841550585509</v>
+        <v>62.37926738013809</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>56.97572801596364</v>
+        <v>55.90071427981338</v>
       </c>
       <c r="D15" t="n">
-        <v>61.63412087261475</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -6574,10 +6574,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="C16" t="n">
-        <v>55.38431498737956</v>
+        <v>55.79763077086746</v>
       </c>
       <c r="D16" t="n">
         <v>58.69084125528282</v>
@@ -6594,7 +6594,7 @@
         <v>57.61091878061134</v>
       </c>
       <c r="D17" t="n">
-        <v>55.24981555189775</v>
+        <v>54.30537426041232</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>10.70104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>60.99598486485433</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>48.15472489330605</v>
+        <v>47.08461989567702</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>66.19924769736242</v>
+        <v>67.40287038276901</v>
       </c>
       <c r="D19" t="n">
-        <v>39.71954861841746</v>
+        <v>37.91411459030757</v>
       </c>
     </row>
     <row r="20">
@@ -6633,10 +6633,10 @@
         <v>12.10494919336317</v>
       </c>
       <c r="C20" t="n">
-        <v>71.28470080536088</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>26.8998870963626</v>
+        <v>24.8823955641354</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>60.17208068964722</v>
+        <v>51.0480348879363</v>
       </c>
       <c r="C21" t="n">
-        <v>363.8978213135808</v>
+        <v>309.0229254823286</v>
       </c>
       <c r="D21" t="n">
-        <v>19.10224783798325</v>
+        <v>13.67358077355436</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01668971097219578</v>
+        <v>0.01570796326794897</v>
       </c>
     </row>
     <row r="3">
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.016108873895449</v>
+        <v>0.9670214886831081</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +814,7 @@
         <v>0.01276272015520854</v>
       </c>
       <c r="D4" t="n">
-        <v>7.912886496229292</v>
+        <v>7.836310175298041</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2454369260617026</v>
+        <v>0.2699806186678729</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3190680038802134</v>
+        <v>0.3436116964863837</v>
       </c>
       <c r="D5" t="n">
-        <v>22.23658550119026</v>
+        <v>22.67837196810132</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.690569546713008</v>
+        <v>1.771072858461246</v>
       </c>
       <c r="C6" t="n">
-        <v>2.696860943565988</v>
+        <v>2.938370878810704</v>
       </c>
       <c r="D6" t="n">
-        <v>39.04410619789565</v>
+        <v>39.44662275663685</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>10.71970318267092</v>
+        <v>11.85754877189298</v>
       </c>
       <c r="D7" t="n">
-        <v>47.37030847761284</v>
+        <v>48.32849423695774</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>25.53525778745954</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D8" t="n">
-        <v>50.40292713603124</v>
+        <v>52.32224389783376</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.86718632248619</v>
+        <v>14.64374875654542</v>
       </c>
       <c r="C9" t="n">
-        <v>42.04530892977813</v>
+        <v>45.5953086283346</v>
       </c>
       <c r="D9" t="n">
-        <v>53.80468293124643</v>
+        <v>54.0265579124062</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.80122929985241</v>
+        <v>16.22828955119978</v>
       </c>
       <c r="C10" t="n">
-        <v>53.80959166976768</v>
+        <v>56.22959976073607</v>
       </c>
       <c r="D10" t="n">
-        <v>60.64255569132548</v>
+        <v>60.78490910844128</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="C11" t="n">
-        <v>57.92900503678727</v>
+        <v>59.88366471594267</v>
       </c>
       <c r="D11" t="n">
-        <v>66.10303642234622</v>
+        <v>66.81382176022092</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.75370449942107</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C12" t="n">
-        <v>60.09964921087699</v>
+        <v>61.40144666670826</v>
       </c>
       <c r="D12" t="n">
-        <v>65.52380527684062</v>
+        <v>64.87290654892497</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.00815708127024</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="C13" t="n">
+        <v>61.39850142359553</v>
+      </c>
+      <c r="D13" t="n">
         <v>61.65866456522093</v>
-      </c>
-      <c r="D13" t="n">
-        <v>62.95948027334796</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.75504610002381</v>
+        <v>9.525897974306801</v>
       </c>
       <c r="C14" t="n">
-        <v>61.15011925442109</v>
+        <v>58.69182300298707</v>
       </c>
       <c r="D14" t="n">
-        <v>62.99384144299659</v>
+        <v>62.07198034870884</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="C15" t="n">
-        <v>58.76741757621406</v>
+        <v>56.25905219186346</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>61.99245878466483</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>9.092947236733956</v>
       </c>
       <c r="C16" t="n">
-        <v>57.864209688307</v>
+        <v>57.03757812133119</v>
       </c>
       <c r="D16" t="n">
-        <v>59.10415703877072</v>
+        <v>56.62426233784328</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>9.444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>58.55536007209676</v>
+        <v>59.97202200932491</v>
       </c>
       <c r="D17" t="n">
-        <v>54.30537426041232</v>
+        <v>50.05538844872788</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9.63094497866121</v>
+        <v>10.16599747747572</v>
       </c>
       <c r="C18" t="n">
-        <v>62.06608986248335</v>
+        <v>64.2062998577414</v>
       </c>
       <c r="D18" t="n">
-        <v>47.08461989567702</v>
+        <v>44.94440990041898</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10.23079282595601</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>66.80105904006572</v>
+        <v>69.2083044108789</v>
       </c>
       <c r="D19" t="n">
-        <v>38.51592593301086</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -1032,13 +1032,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11.43245201595411</v>
+        <v>12.10494919336317</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>25.55489274154447</v>
+        <v>18.82992096745382</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>55.27189859315163</v>
+        <v>25.71696506362797</v>
       </c>
       <c r="C21" t="n">
-        <v>342.8731336456525</v>
+        <v>184.8406863948261</v>
       </c>
       <c r="D21" t="n">
-        <v>16.86261313011406</v>
+        <v>5.625586107668619</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01079922474671491</v>
+        <v>0.009817477042468103</v>
       </c>
     </row>
     <row r="3">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8344855486097889</v>
+        <v>0.7853981633974483</v>
       </c>
     </row>
     <row r="4">
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6.828055283036567</v>
+        <v>6.700428081484481</v>
       </c>
     </row>
     <row r="5">
@@ -1139,7 +1139,7 @@
         <v>0.1718058482431918</v>
       </c>
       <c r="D5" t="n">
-        <v>20.54307071136451</v>
+        <v>20.81305133003238</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.127046364475339</v>
+        <v>1.207549676223577</v>
       </c>
       <c r="C6" t="n">
-        <v>1.730821202587127</v>
+        <v>1.891827826083604</v>
       </c>
       <c r="D6" t="n">
-        <v>37.79630486579796</v>
+        <v>38.60133798328035</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.892629647338603</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>7.905032514595317</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="D7" t="n">
-        <v>47.84940135728529</v>
+        <v>48.74770050667112</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>21.11248437982766</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>51.98844967838984</v>
+        <v>53.82431788533138</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.64687392610741</v>
+        <v>13.42343636016663</v>
       </c>
       <c r="C9" t="n">
-        <v>38.49530923122167</v>
+        <v>42.48905889209769</v>
       </c>
       <c r="D9" t="n">
-        <v>54.35937038414588</v>
+        <v>55.35780779936488</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.23181563138926</v>
+        <v>15.9435827169682</v>
       </c>
       <c r="C10" t="n">
-        <v>53.24017800130454</v>
+        <v>56.94136684631501</v>
       </c>
       <c r="D10" t="n">
-        <v>60.35784885709391</v>
+        <v>61.06961594267285</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>15.81497376771187</v>
       </c>
       <c r="C11" t="n">
-        <v>60.59445005381736</v>
+        <v>63.25989507084746</v>
       </c>
       <c r="D11" t="n">
-        <v>66.63612542575224</v>
+        <v>66.2807327568149</v>
       </c>
     </row>
     <row r="12">
@@ -1231,10 +1231,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.97067074205961</v>
+        <v>14.31977201414398</v>
       </c>
       <c r="C12" t="n">
-        <v>63.13717660781662</v>
+        <v>64.87290654892497</v>
       </c>
       <c r="D12" t="n">
         <v>65.9577377621177</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.26832022289564</v>
+        <v>12.22766765639403</v>
       </c>
       <c r="C13" t="n">
-        <v>64.52045912310038</v>
+        <v>65.561111689602</v>
       </c>
       <c r="D13" t="n">
-        <v>64.00013283984957</v>
+        <v>62.43915399009714</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.06233313145306</v>
+        <v>9.833185005736054</v>
       </c>
       <c r="C14" t="n">
-        <v>64.2229895687136</v>
+        <v>62.07198034870884</v>
       </c>
       <c r="D14" t="n">
-        <v>62.68655441156734</v>
+        <v>61.76469331727959</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>62.70913460876501</v>
+        <v>59.12575548826415</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>61.99245878466483</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.679631453246051</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>59.93078860574654</v>
+        <v>58.69084125528282</v>
       </c>
       <c r="D16" t="n">
-        <v>59.51747282225863</v>
+        <v>57.03757812133119</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>8.9721922691116</v>
       </c>
       <c r="C17" t="n">
-        <v>59.97202200932491</v>
+        <v>60.91646330081034</v>
       </c>
       <c r="D17" t="n">
-        <v>54.30537426041232</v>
+        <v>50.05538844872788</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9.095892479846698</v>
+        <v>9.63094497866121</v>
       </c>
       <c r="C18" t="n">
-        <v>62.60114236129787</v>
+        <v>64.74135235655591</v>
       </c>
       <c r="D18" t="n">
-        <v>47.61967239449154</v>
+        <v>44.94440990041898</v>
       </c>
     </row>
     <row r="19">
@@ -1329,13 +1329,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9.628981483252716</v>
+        <v>10.23079282595601</v>
       </c>
       <c r="C19" t="n">
-        <v>66.80105904006572</v>
+        <v>69.2083044108789</v>
       </c>
       <c r="D19" t="n">
-        <v>38.51592593301086</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -1343,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>26.22738991895353</v>
+        <v>19.50241814486288</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>59.65243764495866</v>
+        <v>26.8290428117713</v>
       </c>
       <c r="C21" t="n">
-        <v>378.1194837817541</v>
+        <v>198.3723165476424</v>
       </c>
       <c r="D21" t="n">
-        <v>20.20485791200213</v>
+        <v>6.504010378611224</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006872233929727673</v>
+        <v>0.005890486225480863</v>
       </c>
     </row>
     <row r="3">
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6872233929727672</v>
+        <v>0.6381360077604268</v>
       </c>
     </row>
     <row r="4">
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5.883613991551135</v>
+        <v>5.704935909378214</v>
       </c>
     </row>
     <row r="5">
@@ -1450,7 +1450,7 @@
         <v>0.07363107781851079</v>
       </c>
       <c r="D5" t="n">
-        <v>18.84955592153876</v>
+        <v>18.94773069196344</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7647814616082653</v>
+        <v>0.8050331174823847</v>
       </c>
       <c r="C6" t="n">
-        <v>1.127046364475339</v>
+        <v>1.167298020349458</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>37.43403996293088</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.934443887993716</v>
+        <v>3.173990327829938</v>
       </c>
       <c r="C7" t="n">
-        <v>5.689227946110266</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="D7" t="n">
-        <v>48.50815406683489</v>
+        <v>49.40645321622073</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.759332943739289</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>17.02350519163969</v>
+        <v>19.10971906316416</v>
       </c>
       <c r="D8" t="n">
-        <v>52.73948667213865</v>
+        <v>54.49190632421922</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.20468654856884</v>
+        <v>12.09218647320796</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>38.38437174064178</v>
       </c>
       <c r="D9" t="n">
-        <v>55.1359328182051</v>
+        <v>56.79999517690344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14.37769512869454</v>
+        <v>15.37416904850505</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>56.08724634362028</v>
       </c>
       <c r="D10" t="n">
-        <v>60.92726252555705</v>
+        <v>61.4966761940202</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.63727743324319</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="C11" t="n">
-        <v>62.01602072956675</v>
+        <v>65.74764375340887</v>
       </c>
       <c r="D11" t="n">
-        <v>66.2807327568149</v>
+        <v>65.92534008787754</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.97067074205961</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="C12" t="n">
-        <v>66.17470400475625</v>
+        <v>68.56133267378024</v>
       </c>
       <c r="D12" t="n">
-        <v>66.3916702473948</v>
+        <v>66.82560273267188</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.26832022289564</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="C13" t="n">
-        <v>67.38225368097983</v>
+        <v>68.94323253073227</v>
       </c>
       <c r="D13" t="n">
-        <v>65.04078540635119</v>
+        <v>63.21964341497336</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="C14" t="n">
-        <v>67.29585988300612</v>
+        <v>66.06671175728911</v>
       </c>
       <c r="D14" t="n">
-        <v>62.68655441156734</v>
+        <v>61.45740628585034</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>65.5758379051657</v>
+        <v>61.99245878466483</v>
       </c>
       <c r="D15" t="n">
-        <v>61.63412087261475</v>
+        <v>61.99245878466483</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.679631453246051</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="C16" t="n">
-        <v>62.82399909016188</v>
+        <v>60.75742017272236</v>
       </c>
       <c r="D16" t="n">
-        <v>59.10415703877072</v>
+        <v>57.4508939048191</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>8.499971623368884</v>
       </c>
       <c r="C17" t="n">
-        <v>61.38868394655305</v>
+        <v>61.86090459229577</v>
       </c>
       <c r="D17" t="n">
-        <v>54.30537426041232</v>
+        <v>50.52760909447059</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.560839981032187</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>63.13619486011238</v>
+        <v>65.27640485537043</v>
       </c>
       <c r="D18" t="n">
-        <v>48.15472489330605</v>
+        <v>44.40935740160447</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +1640,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
       <c r="C19" t="n">
-        <v>66.80105904006572</v>
+        <v>69.2083044108789</v>
       </c>
       <c r="D19" t="n">
-        <v>38.51592593301086</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -1654,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>9.41496048372691</v>
+        <v>10.08745766113597</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>26.8998870963626</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>63.20121067346139</v>
+        <v>27.96042606337505</v>
       </c>
       <c r="C21" t="n">
-        <v>414.7579450445904</v>
+        <v>212.1702918926695</v>
       </c>
       <c r="D21" t="n">
-        <v>23.70045400254802</v>
+        <v>7.401289252069866</v>
       </c>
     </row>
   </sheetData>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.564504929941916</v>
+        <v>0.5154175447295755</v>
       </c>
     </row>
     <row r="4">
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5.105088062083414</v>
+        <v>4.900884539600077</v>
       </c>
     </row>
     <row r="5">
@@ -1761,7 +1761,7 @@
         <v>0.02454369260617027</v>
       </c>
       <c r="D5" t="n">
-        <v>17.0824100538945</v>
+        <v>17.03332266868216</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4830198704894308</v>
+        <v>0.5232715263635501</v>
       </c>
       <c r="C6" t="n">
-        <v>0.684278149860027</v>
+        <v>0.7245298057341462</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>35.98498035146259</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.155917958525996</v>
+        <v>2.335577788403162</v>
       </c>
       <c r="C7" t="n">
-        <v>4.012402867256713</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="D7" t="n">
-        <v>48.74770050667112</v>
+        <v>49.70588626601601</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>13.35176877775662</v>
+        <v>15.10418842983718</v>
       </c>
       <c r="D8" t="n">
-        <v>53.57397222074844</v>
+        <v>55.15949476310704</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>55.91249525226433</v>
+        <v>58.13124506386212</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13.38122120888403</v>
+        <v>14.37769512869454</v>
       </c>
       <c r="C10" t="n">
-        <v>47.97310156802039</v>
+        <v>53.66723825265189</v>
       </c>
       <c r="D10" t="n">
-        <v>61.4966761940202</v>
+        <v>62.20844327959914</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.10418842983717</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="C11" t="n">
-        <v>62.01602072956675</v>
+        <v>66.99151809468958</v>
       </c>
       <c r="D11" t="n">
-        <v>66.10303642234622</v>
+        <v>65.74764375340887</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.97067074205961</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="C12" t="n">
-        <v>68.56133267378024</v>
+        <v>72.03279255599698</v>
       </c>
       <c r="D12" t="n">
-        <v>67.25953521794898</v>
+        <v>67.47650146058751</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.52848336452105</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="C13" t="n">
-        <v>70.50421138048469</v>
+        <v>72.58551651348793</v>
       </c>
       <c r="D13" t="n">
-        <v>65.3009485479766</v>
+        <v>64.00013283984957</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
-        <v>70.98330426015714</v>
+        <v>70.06144316586938</v>
       </c>
       <c r="D14" t="n">
-        <v>62.68655441156734</v>
+        <v>61.15011925442109</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>68.80087911361647</v>
+        <v>65.5758379051657</v>
       </c>
       <c r="D15" t="n">
         <v>61.99245878466483</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.439684102782329</v>
       </c>
       <c r="C16" t="n">
-        <v>65.71720957457724</v>
+        <v>62.82399909016188</v>
       </c>
       <c r="D16" t="n">
-        <v>58.69084125528282</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.02775097762617</v>
+        <v>7.555530331883453</v>
       </c>
       <c r="C17" t="n">
         <v>63.27756652952392</v>
       </c>
       <c r="D17" t="n">
-        <v>54.30537426041232</v>
+        <v>50.99982974021331</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.025787482217675</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>64.2062998577414</v>
+        <v>65.81145735418494</v>
       </c>
       <c r="D18" t="n">
-        <v>48.68977739212056</v>
+        <v>43.87430490278995</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>9.027170140549421</v>
       </c>
       <c r="C19" t="n">
-        <v>66.80105904006572</v>
+        <v>69.8101157535822</v>
       </c>
       <c r="D19" t="n">
-        <v>39.11773727571416</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>9.41496048372691</v>
       </c>
       <c r="C20" t="n">
-        <v>71.28470080536088</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>27.57238427377166</v>
+        <v>20.84741249968101</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>66.85494086459154</v>
+        <v>29.11117925689335</v>
       </c>
       <c r="C21" t="n">
-        <v>451.7773276607247</v>
+        <v>226.2354502249998</v>
       </c>
       <c r="D21" t="n">
-        <v>27.34974853551472</v>
+        <v>8.317479787683816</v>
       </c>
     </row>
   </sheetData>
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4663301595172349</v>
+        <v>0.4172427743048944</v>
       </c>
     </row>
     <row r="4">
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4.403138453546945</v>
+        <v>4.198934931063608</v>
       </c>
     </row>
     <row r="5">
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>15.41343895667493</v>
+        <v>15.24163310843173</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2817615911188346</v>
+        <v>0.3220132469929539</v>
       </c>
       <c r="C6" t="n">
         <v>0.4025165587411924</v>
       </c>
       <c r="D6" t="n">
-        <v>33.40887437551896</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.557051858935441</v>
+        <v>1.676825078853552</v>
       </c>
       <c r="C7" t="n">
-        <v>2.814670668075606</v>
+        <v>3.114103717870883</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>49.70588626601601</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>10.2641722479004</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="D8" t="n">
-        <v>54.32500921449725</v>
+        <v>55.82708320199487</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>24.84999788989526</v>
+        <v>28.6218725696115</v>
       </c>
       <c r="D9" t="n">
-        <v>57.243745139223</v>
+        <v>59.46249495082079</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>12.10004045484194</v>
+        <v>13.38122120888403</v>
       </c>
       <c r="C10" t="n">
-        <v>43.84485247166256</v>
+        <v>49.96604940764142</v>
       </c>
       <c r="D10" t="n">
-        <v>61.35432277690443</v>
+        <v>62.92021036517809</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14.39340309196248</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="C11" t="n">
-        <v>60.59445005381736</v>
+        <v>66.81382176022092</v>
       </c>
       <c r="D11" t="n">
-        <v>65.92534008787754</v>
+        <v>65.5699474189402</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.53673825678252</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="C12" t="n">
-        <v>70.08009637225005</v>
+        <v>74.85335371029807</v>
       </c>
       <c r="D12" t="n">
         <v>68.12740018850316</v>
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>73.36600593836414</v>
+        <v>76.22780049624359</v>
       </c>
       <c r="D13" t="n">
-        <v>65.561111689602</v>
+        <v>64.78062226472579</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
         <v>74.05617457444966</v>
       </c>
       <c r="D14" t="n">
-        <v>63.30112847442584</v>
+        <v>61.76469331727959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>72.02592032206724</v>
+        <v>69.15921702566655</v>
       </c>
       <c r="D15" t="n">
-        <v>61.63412087261475</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>69.02373584248051</v>
+        <v>65.30389379108934</v>
       </c>
       <c r="D16" t="n">
-        <v>58.69084125528282</v>
+        <v>58.2775254717949</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.555530331883453</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>65.6386697582375</v>
+        <v>64.69422846675207</v>
       </c>
       <c r="D17" t="n">
-        <v>54.77759490615504</v>
+        <v>51.47205038595602</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="C18" t="n">
-        <v>65.27640485537043</v>
+        <v>66.34650985299945</v>
       </c>
       <c r="D18" t="n">
-        <v>48.68977739212056</v>
+        <v>43.33925240397544</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>67.40287038276901</v>
+        <v>70.41192709628548</v>
       </c>
       <c r="D19" t="n">
-        <v>39.11773727571416</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -2276,13 +2276,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.06996612890878</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>71.28470080536088</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>28.24488145118073</v>
+        <v>21.51990967709008</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>70.61228484862418</v>
+        <v>30.28143111541049</v>
       </c>
       <c r="C21" t="n">
-        <v>489.0939141720881</v>
+        <v>240.56914719465</v>
       </c>
       <c r="D21" t="n">
-        <v>31.15247860968714</v>
+        <v>9.252659507486539</v>
       </c>
     </row>
   </sheetData>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.382881604656256</v>
+        <v>0.3337942194439156</v>
       </c>
     </row>
     <row r="4">
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3.790527886096935</v>
+        <v>3.586324363613598</v>
       </c>
     </row>
     <row r="5">
@@ -2383,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>13.98990478551705</v>
+        <v>13.59720570381833</v>
       </c>
     </row>
     <row r="6">
@@ -2397,7 +2397,7 @@
         <v>0.2012582793705962</v>
       </c>
       <c r="D6" t="n">
-        <v>31.63780151705772</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.077958979262998</v>
+        <v>1.197732199181109</v>
       </c>
       <c r="C7" t="n">
-        <v>1.916371518689774</v>
+        <v>2.09603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>47.37030847761284</v>
+        <v>49.34656660626167</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.421390749300134</v>
+        <v>3.75518496874405</v>
       </c>
       <c r="C8" t="n">
-        <v>7.760715602071035</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="D8" t="n">
-        <v>55.32639187282899</v>
+        <v>56.41122308602172</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>20.52343575727956</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>57.79843259212245</v>
+        <v>60.68280734719958</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.81885970079985</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C10" t="n">
-        <v>39.14718970684157</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>61.4966761940202</v>
+        <v>63.77433086787281</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13.50492141961912</v>
+        <v>14.39340309196248</v>
       </c>
       <c r="C11" t="n">
-        <v>57.92900503678727</v>
+        <v>65.21455475000286</v>
       </c>
       <c r="D11" t="n">
-        <v>66.45842909128358</v>
+        <v>66.2807327568149</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.31977201414398</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="C12" t="n">
-        <v>71.16492758544278</v>
+        <v>76.80604989404496</v>
       </c>
       <c r="D12" t="n">
         <v>67.91043394586461</v>
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C13" t="n">
-        <v>75.70747421299279</v>
+        <v>79.87008447899927</v>
       </c>
       <c r="D13" t="n">
-        <v>65.82127483122741</v>
+        <v>65.561111689602</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
-        <v>76.82175785731292</v>
+        <v>78.05090598302992</v>
       </c>
       <c r="D14" t="n">
-        <v>63.91570253728435</v>
+        <v>62.37926738013809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>75.25096153051801</v>
+        <v>73.10093405821749</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>60.5591071364645</v>
       </c>
     </row>
     <row r="16">
@@ -2531,13 +2531,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>71.91694632689584</v>
+        <v>68.19710427550467</v>
       </c>
       <c r="D16" t="n">
-        <v>58.69084125528282</v>
+        <v>58.2775254717949</v>
       </c>
     </row>
     <row r="17">
@@ -2545,13 +2545,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>68.4719936326938</v>
+        <v>66.58311104972293</v>
       </c>
       <c r="D17" t="n">
-        <v>55.24981555189775</v>
+        <v>51.94427103169875</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>66.88156235181395</v>
+        <v>67.41661485062848</v>
       </c>
       <c r="D18" t="n">
-        <v>48.68977739212056</v>
+        <v>43.33925240397544</v>
       </c>
     </row>
     <row r="19">
@@ -2573,13 +2573,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>68.00468172547231</v>
+        <v>71.01373843898878</v>
       </c>
       <c r="D19" t="n">
-        <v>39.11773727571416</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -2587,13 +2587,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>8.06996612890878</v>
       </c>
       <c r="C20" t="n">
-        <v>71.28470080536088</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>28.91737862858979</v>
+        <v>21.51990967709008</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>74.47304553822951</v>
+        <v>31.47143604912085</v>
       </c>
       <c r="C21" t="n">
-        <v>526.6308220203373</v>
+        <v>255.1738058036825</v>
       </c>
       <c r="D21" t="n">
-        <v>35.10872146802249</v>
+        <v>10.2069522321473</v>
       </c>
     </row>
   </sheetData>
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3141592653589793</v>
+        <v>0.2650718801466388</v>
       </c>
     </row>
     <row r="4">
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3.254493639578176</v>
+        <v>3.05029011709484</v>
       </c>
     </row>
     <row r="5">
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>12.64000169217769</v>
+        <v>12.19821522526662</v>
       </c>
     </row>
     <row r="6">
@@ -2705,10 +2705,10 @@
         <v>0.08050331174823847</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1207549676223577</v>
+        <v>0.08050331174823847</v>
       </c>
       <c r="D6" t="n">
-        <v>29.82647700272235</v>
+        <v>30.39000018496002</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7186393195086651</v>
+        <v>0.7785259294677207</v>
       </c>
       <c r="C7" t="n">
-        <v>1.257618809140164</v>
+        <v>1.317505419099219</v>
       </c>
       <c r="D7" t="n">
-        <v>46.35223610830891</v>
+        <v>48.68781389671206</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.586905200690345</v>
+        <v>2.837250865273282</v>
       </c>
       <c r="C8" t="n">
-        <v>5.757950285407543</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D8" t="n">
-        <v>56.07742886657781</v>
+        <v>57.32915718949249</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>16.64062358698343</v>
+        <v>19.41406085148067</v>
       </c>
       <c r="D9" t="n">
-        <v>58.46405753560178</v>
+        <v>61.12655730951914</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>10.81885970079985</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>40.14366362665208</v>
       </c>
       <c r="D10" t="n">
-        <v>61.639029611136</v>
+        <v>64.77080478768332</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12.43874341280708</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="C11" t="n">
-        <v>54.19738201294516</v>
+        <v>62.3714133985041</v>
       </c>
       <c r="D11" t="n">
         <v>66.99151809468958</v>
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.66887328622834</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="C12" t="n">
-        <v>70.2970626148886</v>
+        <v>77.45694862196059</v>
       </c>
       <c r="D12" t="n">
-        <v>67.91043394586461</v>
+        <v>67.69346770322606</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C13" t="n">
-        <v>77.78877934599603</v>
+        <v>83.25220532012953</v>
       </c>
       <c r="D13" t="n">
-        <v>66.08143797285281</v>
+        <v>66.34160111447822</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="C14" t="n">
-        <v>79.58734114017618</v>
+        <v>82.0456373916102</v>
       </c>
       <c r="D14" t="n">
-        <v>64.53027660014286</v>
+        <v>62.99384144299659</v>
       </c>
     </row>
     <row r="15">
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>78.47600273896879</v>
+        <v>77.40098900281852</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>60.20076922441442</v>
       </c>
     </row>
     <row r="16">
@@ -2842,13 +2842,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>75.22347259479911</v>
+        <v>71.50363054340794</v>
       </c>
       <c r="D16" t="n">
-        <v>59.10415703877072</v>
+        <v>58.2775254717949</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>71.30531750715009</v>
+        <v>68.4719936326938</v>
       </c>
       <c r="D17" t="n">
-        <v>54.77759490615504</v>
+        <v>52.41649167744146</v>
       </c>
     </row>
     <row r="18">
@@ -2870,13 +2870,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>69.021772347072</v>
+        <v>68.48671984825749</v>
       </c>
       <c r="D18" t="n">
-        <v>48.68977739212056</v>
+        <v>43.33925240397544</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>7.221736112439537</v>
       </c>
       <c r="C19" t="n">
-        <v>68.6064930681756</v>
+        <v>71.61554978169207</v>
       </c>
       <c r="D19" t="n">
-        <v>39.71954861841746</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -2898,13 +2898,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
       <c r="C20" t="n">
-        <v>71.28470080536088</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>28.91737862858979</v>
+        <v>21.51990967709008</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>78.43675394656007</v>
+        <v>32.68126194065227</v>
       </c>
       <c r="C21" t="n">
-        <v>565.3982680314539</v>
+        <v>270.0504276148635</v>
       </c>
       <c r="D21" t="n">
-        <v>39.21837697328004</v>
+        <v>11.18043171653894</v>
       </c>
     </row>
   </sheetData>
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2552544031041707</v>
+        <v>0.2110757564130642</v>
       </c>
     </row>
     <row r="4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.820561154301086</v>
+        <v>2.590832191507332</v>
       </c>
     </row>
     <row r="5">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>11.31464229144449</v>
+        <v>10.8973995171396</v>
       </c>
     </row>
     <row r="6">
@@ -3019,7 +3019,7 @@
         <v>0.04025165587411923</v>
       </c>
       <c r="D6" t="n">
-        <v>28.01515248838698</v>
+        <v>28.29691407950582</v>
       </c>
     </row>
     <row r="7">
@@ -3033,7 +3033,7 @@
         <v>0.8384125394267761</v>
       </c>
       <c r="D7" t="n">
-        <v>45.57371017884118</v>
+        <v>47.66974152740813</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="D8" t="n">
-        <v>55.91053175685585</v>
+        <v>58.0801941832413</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>13.31249886958674</v>
+        <v>15.53124868118453</v>
       </c>
       <c r="D9" t="n">
-        <v>59.12968247908112</v>
+        <v>61.57030727183869</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>62.49315011383072</v>
+        <v>65.62492529037804</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.37256540599505</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>49.93266998569701</v>
+        <v>58.4620940401933</v>
       </c>
       <c r="D11" t="n">
-        <v>66.63612542575224</v>
+        <v>67.70230343256426</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="C12" t="n">
-        <v>68.12740018850316</v>
+        <v>77.02301613668351</v>
       </c>
       <c r="D12" t="n">
-        <v>67.91043394586461</v>
+        <v>67.69346770322606</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="C13" t="n">
-        <v>78.82943191249764</v>
+        <v>85.85383673638357</v>
       </c>
       <c r="D13" t="n">
         <v>66.86192739772903</v>
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="C14" t="n">
-        <v>81.43106332875169</v>
+        <v>85.11850770590272</v>
       </c>
       <c r="D14" t="n">
-        <v>64.53027660014286</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
         <v>81.70104394741955</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>59.84243131236433</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>78.52999886270236</v>
+        <v>75.22347259479911</v>
       </c>
       <c r="D16" t="n">
-        <v>59.51747282225863</v>
+        <v>58.2775254717949</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>74.13864138160638</v>
+        <v>70.83309686140737</v>
       </c>
       <c r="D17" t="n">
-        <v>54.77759490615504</v>
+        <v>52.41649167744146</v>
       </c>
     </row>
     <row r="18">
@@ -3181,13 +3181,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="C18" t="n">
-        <v>71.16198234233005</v>
+        <v>70.09187734470103</v>
       </c>
       <c r="D18" t="n">
-        <v>48.68977739212056</v>
+        <v>43.33925240397544</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>6.619924769736241</v>
       </c>
       <c r="C19" t="n">
-        <v>69.8101157535822</v>
+        <v>72.21736112439537</v>
       </c>
       <c r="D19" t="n">
-        <v>40.32135996112075</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -3209,13 +3209,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6.052474596681584</v>
+        <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>71.28470080536088</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>28.91737862858979</v>
+        <v>21.51990967709008</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.38675244194353</v>
+        <v>33.91110910230968</v>
       </c>
       <c r="C21" t="n">
-        <v>605.3836517256896</v>
+        <v>285.2011227066045</v>
       </c>
       <c r="D21" t="n">
-        <v>43.48059377035339</v>
+        <v>12.17321865211117</v>
       </c>
     </row>
   </sheetData>
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2061670178918302</v>
+        <v>0.1668971097219578</v>
       </c>
     </row>
     <row r="4">
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.43767954964483</v>
+        <v>2.195187866695868</v>
       </c>
     </row>
     <row r="5">
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10.11200135374215</v>
+        <v>9.694758579437254</v>
       </c>
     </row>
     <row r="6">
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>26.1635763181775</v>
+        <v>26.24407962992574</v>
       </c>
     </row>
     <row r="7">
@@ -3341,10 +3341,10 @@
         <v>0.2994330497952771</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5389794896314989</v>
+        <v>0.4790928796724435</v>
       </c>
       <c r="D7" t="n">
-        <v>44.55563780953724</v>
+        <v>46.41212271826796</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>3.087596529856218</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="D8" t="n">
-        <v>55.66018609227291</v>
+        <v>58.4974369575462</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.771874679716245</v>
+        <v>4.215624642035802</v>
       </c>
       <c r="C9" t="n">
-        <v>10.53906160508951</v>
+        <v>12.20312396378785</v>
       </c>
       <c r="D9" t="n">
-        <v>59.68436993198057</v>
+        <v>62.12499472473814</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>63.34727061652544</v>
+        <v>66.47904579307277</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10.12869106471434</v>
+        <v>11.55026174046372</v>
       </c>
       <c r="C11" t="n">
-        <v>45.13486895504285</v>
+        <v>53.66429300953914</v>
       </c>
       <c r="D11" t="n">
-        <v>66.45842909128358</v>
+        <v>68.41308877043897</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12.15010958775853</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="C12" t="n">
-        <v>65.08987279156352</v>
+        <v>75.28728619557515</v>
       </c>
       <c r="D12" t="n">
-        <v>67.91043394586461</v>
+        <v>67.69346770322606</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>78.82943191249764</v>
+        <v>87.41481558613602</v>
       </c>
       <c r="D13" t="n">
-        <v>67.64241682260524</v>
+        <v>67.38225368097983</v>
       </c>
     </row>
     <row r="14">
@@ -3436,13 +3436,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="C14" t="n">
-        <v>83.88935958018571</v>
+        <v>89.11323911448298</v>
       </c>
       <c r="D14" t="n">
-        <v>64.53027660014286</v>
+        <v>64.2229895687136</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>84.56774724382024</v>
+        <v>85.64276097997049</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>59.48409340031424</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>81.83652513060562</v>
+        <v>78.94331464619027</v>
       </c>
       <c r="D16" t="n">
-        <v>59.93078860574654</v>
+        <v>58.2775254717949</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>77.44418590180538</v>
+        <v>73.66642073586367</v>
       </c>
       <c r="D17" t="n">
-        <v>54.77759490615504</v>
+        <v>52.41649167744146</v>
       </c>
     </row>
     <row r="18">
@@ -3495,10 +3495,10 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>73.3021923375881</v>
+        <v>71.69703484114456</v>
       </c>
       <c r="D18" t="n">
-        <v>49.22482989093507</v>
+        <v>43.33925240397544</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>71.01373843898878</v>
+        <v>72.81917246709867</v>
       </c>
       <c r="D19" t="n">
-        <v>40.32135996112075</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -3520,13 +3520,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>29.58987580599885</v>
+        <v>21.51990967709008</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>84.38687033394172</v>
+        <v>34.28224259865195</v>
       </c>
       <c r="C21" t="n">
-        <v>645.4455217433921</v>
+        <v>299.7498647728285</v>
       </c>
       <c r="D21" t="n">
-        <v>47.89525073007503</v>
+        <v>13.18547792255844</v>
       </c>
     </row>
   </sheetData>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1718058482431918</v>
+        <v>0.1325359400733194</v>
       </c>
     </row>
     <row r="4">
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0930861054542</v>
+        <v>1.850594422505238</v>
       </c>
     </row>
     <row r="5">
@@ -3627,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>9.007535186464487</v>
+        <v>8.590292412159592</v>
       </c>
     </row>
     <row r="6">
@@ -3641,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>24.59376173908685</v>
+        <v>24.23149683621978</v>
       </c>
     </row>
     <row r="7">
@@ -3652,10 +3652,10 @@
         <v>0.1796598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2994330497952771</v>
+        <v>0.2395464398362217</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>44.91495746929157</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.001382658331746</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>2.253110981246429</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="D8" t="n">
-        <v>55.24294331796801</v>
+        <v>58.66433406726815</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>8.209374302911826</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="D9" t="n">
-        <v>60.68280734719958</v>
+        <v>62.67968217763759</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>63.48962403364123</v>
+        <v>67.3331662957675</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>10.48408373365169</v>
       </c>
       <c r="C11" t="n">
-        <v>40.15937158992001</v>
+        <v>48.51109930994763</v>
       </c>
       <c r="D11" t="n">
-        <v>66.45842909128358</v>
+        <v>69.12387410831366</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.28224461720434</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="C12" t="n">
-        <v>60.75054793879262</v>
+        <v>72.24975879863551</v>
       </c>
       <c r="D12" t="n">
-        <v>68.56133267378024</v>
+        <v>67.69346770322606</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.96750451476862</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="C13" t="n">
-        <v>77.52861620437062</v>
+        <v>87.93514186938681</v>
       </c>
       <c r="D13" t="n">
-        <v>67.38225368097983</v>
+        <v>67.90257996423064</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="C14" t="n">
-        <v>85.73308176876121</v>
+        <v>92.49339646020475</v>
       </c>
       <c r="D14" t="n">
-        <v>64.53027660014286</v>
+        <v>64.83756363157211</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="C15" t="n">
-        <v>87.43445054022092</v>
+        <v>89.58447801252143</v>
       </c>
       <c r="D15" t="n">
-        <v>61.99245878466483</v>
+        <v>59.48409340031424</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>7.026368319294422</v>
       </c>
       <c r="C16" t="n">
-        <v>85.14305139850887</v>
+        <v>83.07647248106935</v>
       </c>
       <c r="D16" t="n">
-        <v>59.51747282225863</v>
+        <v>58.2775254717949</v>
       </c>
     </row>
     <row r="17">
@@ -3789,13 +3789,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>80.7497304220044</v>
+        <v>76.49974461031996</v>
       </c>
       <c r="D17" t="n">
-        <v>54.77759490615504</v>
+        <v>52.41649167744146</v>
       </c>
     </row>
     <row r="18">
@@ -3803,13 +3803,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>75.97745483166067</v>
+        <v>73.3021923375881</v>
       </c>
       <c r="D18" t="n">
-        <v>49.75988238974958</v>
+        <v>43.33925240397544</v>
       </c>
     </row>
     <row r="19">
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.814490741626358</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>72.81917246709867</v>
+        <v>73.42098380980195</v>
       </c>
       <c r="D19" t="n">
-        <v>40.32135996112075</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -3831,13 +3831,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>4.707480241863455</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>76.66467822463341</v>
       </c>
       <c r="D20" t="n">
-        <v>29.58987580599885</v>
+        <v>21.51990967709008</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>87.43499720010826</v>
+        <v>34.65506601011424</v>
       </c>
       <c r="C21" t="n">
-        <v>687.821977974185</v>
+        <v>314.5613683994985</v>
       </c>
       <c r="D21" t="n">
-        <v>52.46099832006495</v>
+        <v>14.21746297850841</v>
       </c>
     </row>
   </sheetData>
@@ -3918,10 +3918,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.667408512438584</v>
+        <v>2.718459393059418</v>
       </c>
       <c r="C4" t="n">
-        <v>4.44142661401257</v>
+        <v>4.518002934943822</v>
       </c>
       <c r="D4" t="n">
         <v>24.14706653365455</v>
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7.682175785731292</v>
+        <v>7.731263170943634</v>
       </c>
       <c r="C5" t="n">
-        <v>14.5298660228528</v>
+        <v>14.60349710067131</v>
       </c>
       <c r="D5" t="n">
-        <v>27.14532402242431</v>
+        <v>27.36621725587985</v>
       </c>
     </row>
     <row r="6">
@@ -3946,7 +3946,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.14341728027805</v>
+        <v>10.10316562440393</v>
       </c>
       <c r="C6" t="n">
         <v>19.84406634594078</v>
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.0970952117292</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>23.29589127407256</v>
+        <v>23.47555110394973</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -3980,7 +3980,7 @@
         <v>26.11939767148639</v>
       </c>
       <c r="D8" t="n">
-        <v>43.47669708257</v>
+        <v>43.89393985687489</v>
       </c>
     </row>
     <row r="9">
@@ -3991,10 +3991,10 @@
         <v>14.97656122828509</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>48.7015583645715</v>
+        <v>48.59062087399162</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14.52004854581033</v>
+        <v>14.37769512869454</v>
       </c>
       <c r="C10" t="n">
-        <v>38.15071578703105</v>
+        <v>38.29306920414684</v>
       </c>
       <c r="D10" t="n">
-        <v>68.61434704980958</v>
+        <v>68.75670046692537</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12.08335074386974</v>
+        <v>11.90565440940107</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>38.56010457970196</v>
       </c>
       <c r="D11" t="n">
-        <v>56.32973802656922</v>
+        <v>55.61895268869453</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="C12" t="n">
         <v>37.10122749119121</v>
       </c>
       <c r="D12" t="n">
-        <v>57.92998678449154</v>
+        <v>58.36391926976862</v>
       </c>
     </row>
     <row r="13">
@@ -4047,10 +4047,10 @@
         <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>37.46349239405829</v>
+        <v>36.68300296918207</v>
       </c>
       <c r="D13" t="n">
-        <v>60.35784885709391</v>
+        <v>60.09768571546851</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="C14" t="n">
-        <v>39.94731408580272</v>
+        <v>40.25460111723197</v>
       </c>
       <c r="D14" t="n">
-        <v>62.07198034870884</v>
+        <v>63.30112847442584</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="C15" t="n">
-        <v>45.50891483036089</v>
+        <v>46.58392856651115</v>
       </c>
       <c r="D15" t="n">
-        <v>59.84243131236433</v>
+        <v>58.76741757621406</v>
       </c>
     </row>
     <row r="16">
@@ -4089,10 +4089,10 @@
         <v>15.29268398905256</v>
       </c>
       <c r="C16" t="n">
-        <v>52.0777887194763</v>
+        <v>51.66447293598839</v>
       </c>
       <c r="D16" t="n">
-        <v>57.864209688307</v>
+        <v>56.21094655435537</v>
       </c>
     </row>
     <row r="17">
@@ -4103,7 +4103,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="C17" t="n">
-        <v>57.13869813486862</v>
+        <v>57.61091878061134</v>
       </c>
       <c r="D17" t="n">
         <v>51.47205038595602</v>
@@ -4117,10 +4117,10 @@
         <v>18.72683745850791</v>
       </c>
       <c r="C18" t="n">
-        <v>62.60114236129787</v>
+        <v>63.13619486011238</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33925240397544</v>
+        <v>42.26914740634642</v>
       </c>
     </row>
     <row r="19">
@@ -4134,7 +4134,7 @@
         <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>31.89600116327462</v>
+        <v>30.69237847786803</v>
       </c>
     </row>
     <row r="20">
@@ -4145,10 +4145,10 @@
         <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.59626222163283</v>
+        <v>11.69112140275025</v>
       </c>
       <c r="C21" t="n">
-        <v>97.29096909685239</v>
+        <v>83.29923999459555</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1423534171157875</v>
+        <v>0.1030835089459151</v>
       </c>
     </row>
     <row r="4">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.799543541884403</v>
+        <v>1.557051858935441</v>
       </c>
     </row>
     <row r="5">
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8.099418560036186</v>
+        <v>7.584001015306612</v>
       </c>
     </row>
     <row r="6">
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>22.90319219237384</v>
+        <v>22.29941735426205</v>
       </c>
     </row>
     <row r="7">
@@ -4274,10 +4274,10 @@
         <v>0.05988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1796598298771663</v>
+        <v>0.1197732199181109</v>
       </c>
       <c r="D7" t="n">
-        <v>41.3816474817073</v>
+        <v>43.23813239043802</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.667588438887831</v>
+        <v>0.7510369937488099</v>
       </c>
       <c r="C8" t="n">
         <v>1.585522542358599</v>
       </c>
       <c r="D8" t="n">
-        <v>54.65880343394117</v>
+        <v>58.4974369575462</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>6.323436963053704</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="D9" t="n">
-        <v>61.4593697812588</v>
+        <v>63.12343213995715</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>17.36711688812608</v>
+        <v>20.64124548178919</v>
       </c>
       <c r="D10" t="n">
-        <v>63.63197745075701</v>
+        <v>68.04493338134642</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.996335051090269</v>
+        <v>9.240209392370978</v>
       </c>
       <c r="C11" t="n">
-        <v>35.36157055926586</v>
+        <v>43.00251294141878</v>
       </c>
       <c r="D11" t="n">
-        <v>66.45842909128358</v>
+        <v>70.01235578065702</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.41437964665016</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="C12" t="n">
-        <v>56.41122308602172</v>
+        <v>68.34436643114171</v>
       </c>
       <c r="D12" t="n">
-        <v>69.21223140169589</v>
+        <v>67.91043394586461</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.44717823151781</v>
+        <v>12.22766765639403</v>
       </c>
       <c r="C13" t="n">
-        <v>75.18714792974198</v>
+        <v>87.41481558613602</v>
       </c>
       <c r="D13" t="n">
-        <v>67.38225368097983</v>
+        <v>68.42290624748146</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="C14" t="n">
-        <v>86.34765583161972</v>
+        <v>95.25897974306801</v>
       </c>
       <c r="D14" t="n">
-        <v>64.53027660014286</v>
+        <v>65.4521376944306</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="C15" t="n">
-        <v>89.94281592457153</v>
+        <v>93.52619504507238</v>
       </c>
       <c r="D15" t="n">
-        <v>62.35079669671492</v>
+        <v>59.48409340031424</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="C16" t="n">
-        <v>88.03626188292422</v>
+        <v>87.20963031594842</v>
       </c>
       <c r="D16" t="n">
-        <v>59.10415703877072</v>
+        <v>58.2775254717949</v>
       </c>
     </row>
     <row r="17">
@@ -4411,13 +4411,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>84.05527494220343</v>
+        <v>79.80528913051897</v>
       </c>
       <c r="D17" t="n">
-        <v>54.77759490615504</v>
+        <v>52.41649167744146</v>
       </c>
     </row>
     <row r="18">
@@ -4425,13 +4425,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>78.65271732573322</v>
+        <v>75.44240233284614</v>
       </c>
       <c r="D18" t="n">
-        <v>50.2949348885641</v>
+        <v>43.33925240397544</v>
       </c>
     </row>
     <row r="19">
@@ -4445,7 +4445,7 @@
         <v>74.62460649520854</v>
       </c>
       <c r="D19" t="n">
-        <v>40.32135996112075</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4453,13 +4453,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>4.03498306445439</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>77.33717540204248</v>
       </c>
       <c r="D20" t="n">
-        <v>29.58987580599885</v>
+        <v>21.51990967709008</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>90.52925034969708</v>
+        <v>35.02959045023105</v>
       </c>
       <c r="C21" t="n">
-        <v>730.1898745311094</v>
+        <v>329.6374280829435</v>
       </c>
       <c r="D21" t="n">
-        <v>57.17636864191395</v>
+        <v>15.26930865779303</v>
       </c>
     </row>
   </sheetData>
@@ -4540,10 +4540,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.403899217072939</v>
+        <v>1.429424657383356</v>
       </c>
       <c r="C4" t="n">
-        <v>2.131374265919825</v>
+        <v>2.207950586851076</v>
       </c>
       <c r="D4" t="n">
         <v>20.98191193516283</v>
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.037748381117885</v>
+        <v>6.160466844148737</v>
       </c>
       <c r="C5" t="n">
-        <v>11.33918598405066</v>
+        <v>11.51099183229385</v>
       </c>
       <c r="D5" t="n">
-        <v>29.45243112740432</v>
+        <v>29.62423697564751</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.34467555964864</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="C6" t="n">
-        <v>21.25287430153496</v>
+        <v>21.49438423677967</v>
       </c>
       <c r="D6" t="n">
-        <v>36.30699359845555</v>
+        <v>36.70951015719674</v>
       </c>
     </row>
     <row r="7">
@@ -4582,10 +4582,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.33664165156542</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C7" t="n">
-        <v>25.87101550231194</v>
+        <v>26.11056194214817</v>
       </c>
       <c r="D7" t="n">
         <v>36.83026512481909</v>
@@ -4599,10 +4599,10 @@
         <v>14.10280577150543</v>
       </c>
       <c r="C8" t="n">
-        <v>28.70630287217673</v>
+        <v>29.12354564648163</v>
       </c>
       <c r="D8" t="n">
-        <v>43.72704274715294</v>
+        <v>43.56014563743097</v>
       </c>
     </row>
     <row r="9">
@@ -4613,10 +4613,10 @@
         <v>15.19843620944487</v>
       </c>
       <c r="C9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>49.03437083631118</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.08946221427348</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>38.57777603837842</v>
+        <v>38.72012945549421</v>
       </c>
       <c r="D10" t="n">
-        <v>66.90610604442013</v>
+        <v>67.19081287865171</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13.14952875068177</v>
+        <v>12.79413608174443</v>
       </c>
       <c r="C11" t="n">
-        <v>41.93633493460674</v>
+        <v>41.75863860013807</v>
       </c>
       <c r="D11" t="n">
-        <v>59.17287937806799</v>
+        <v>58.4620940401933</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>40.78965361604648</v>
+        <v>40.35572113076938</v>
       </c>
       <c r="D12" t="n">
-        <v>58.79785175504571</v>
+        <v>58.14695302713008</v>
       </c>
     </row>
     <row r="13">
@@ -4669,10 +4669,10 @@
         <v>10.6666888066416</v>
       </c>
       <c r="C13" t="n">
-        <v>39.80496066868693</v>
+        <v>39.28463438543612</v>
       </c>
       <c r="D13" t="n">
-        <v>60.09768571546851</v>
+        <v>60.35784885709391</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="C14" t="n">
-        <v>41.48374924294897</v>
+        <v>40.86917518009047</v>
       </c>
       <c r="D14" t="n">
-        <v>61.76469331727959</v>
+        <v>63.30112847442584</v>
       </c>
     </row>
     <row r="15">
@@ -4697,10 +4697,10 @@
         <v>12.90016483380309</v>
       </c>
       <c r="C15" t="n">
-        <v>45.15057691831081</v>
+        <v>46.58392856651115</v>
       </c>
       <c r="D15" t="n">
-        <v>60.5591071364645</v>
+        <v>59.48409340031424</v>
       </c>
     </row>
     <row r="16">
@@ -4711,10 +4711,10 @@
         <v>14.46605242207675</v>
       </c>
       <c r="C16" t="n">
-        <v>51.66447293598839</v>
+        <v>52.0777887194763</v>
       </c>
       <c r="D16" t="n">
-        <v>57.864209688307</v>
+        <v>55.79763077086746</v>
       </c>
     </row>
     <row r="17">
@@ -4725,10 +4725,10 @@
         <v>16.05550195525234</v>
       </c>
       <c r="C17" t="n">
-        <v>57.13869813486862</v>
+        <v>57.61091878061134</v>
       </c>
       <c r="D17" t="n">
-        <v>52.41649167744146</v>
+        <v>51.94427103169875</v>
       </c>
     </row>
     <row r="18">
@@ -4739,10 +4739,10 @@
         <v>17.65673246087889</v>
       </c>
       <c r="C18" t="n">
-        <v>63.13619486011238</v>
+        <v>63.67124735892688</v>
       </c>
       <c r="D18" t="n">
-        <v>43.87430490278995</v>
+        <v>42.80419990516094</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="C19" t="n">
         <v>68.00468172547231</v>
       </c>
       <c r="D19" t="n">
-        <v>33.09962384868121</v>
+        <v>31.29418982057133</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>19.50241814486288</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>17.48492661263569</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21.36757820373163</v>
+        <v>14.03373676580476</v>
       </c>
       <c r="C21" t="n">
-        <v>124.3898302574377</v>
+        <v>95.2816864625692</v>
       </c>
       <c r="D21" t="n">
-        <v>1.52625558598083</v>
+        <v>0.7386177245160402</v>
       </c>
     </row>
   </sheetData>
@@ -4851,10 +4851,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7274750488468864</v>
+        <v>0.740237769002095</v>
       </c>
       <c r="C4" t="n">
-        <v>1.033780332571891</v>
+        <v>1.072068493037517</v>
       </c>
       <c r="D4" t="n">
         <v>18.237927101793</v>
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.270602513473626</v>
+        <v>4.417864669110648</v>
       </c>
       <c r="C5" t="n">
-        <v>7.584001015306612</v>
+        <v>7.952156404399165</v>
       </c>
       <c r="D5" t="n">
-        <v>30.31146036862028</v>
+        <v>30.4587225242573</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.45913913041802</v>
+        <v>9.700649065662736</v>
       </c>
       <c r="C6" t="n">
-        <v>19.80381469006666</v>
+        <v>20.12582793705961</v>
       </c>
       <c r="D6" t="n">
-        <v>37.27303333943441</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.57618809140164</v>
+        <v>12.75584792127881</v>
       </c>
       <c r="C7" t="n">
-        <v>28.14670668075605</v>
+        <v>28.62579956042849</v>
       </c>
       <c r="D7" t="n">
-        <v>39.1059563032632</v>
+        <v>39.04606969330414</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>32.04424506661589</v>
       </c>
       <c r="D8" t="n">
-        <v>43.89393985687489</v>
+        <v>43.72704274715294</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.30937370002476</v>
+        <v>15.19843620944487</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>49.36718330805084</v>
+        <v>50.03280825153018</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.51652246562084</v>
+        <v>15.37416904850505</v>
       </c>
       <c r="C10" t="n">
-        <v>39.28954312395736</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
-        <v>65.62492529037804</v>
+        <v>65.90963212460962</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14.03801042302514</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="C11" t="n">
         <v>44.42408361716816</v>
       </c>
       <c r="D11" t="n">
-        <v>61.30523539169207</v>
+        <v>60.77214638828604</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.93314334511998</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>44.2611134982632</v>
+        <v>43.61021477034756</v>
       </c>
       <c r="D12" t="n">
-        <v>59.88268296823844</v>
+        <v>58.36391926976862</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.6666888066416</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="C13" t="n">
-        <v>42.66675522656638</v>
+        <v>41.88626580169016</v>
       </c>
       <c r="D13" t="n">
-        <v>60.09768571546851</v>
+        <v>60.61801199871932</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>10.75504610002381</v>
       </c>
       <c r="C14" t="n">
-        <v>43.02018440009523</v>
+        <v>42.40561033723673</v>
       </c>
       <c r="D14" t="n">
-        <v>62.07198034870884</v>
+        <v>63.30112847442584</v>
       </c>
     </row>
     <row r="15">
@@ -5008,10 +5008,10 @@
         <v>11.82515109765283</v>
       </c>
       <c r="C15" t="n">
-        <v>46.22559065446107</v>
+        <v>46.58392856651115</v>
       </c>
       <c r="D15" t="n">
-        <v>60.5591071364645</v>
+        <v>59.84243131236433</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="C16" t="n">
-        <v>51.25115715250048</v>
+        <v>52.0777887194763</v>
       </c>
       <c r="D16" t="n">
-        <v>57.864209688307</v>
+        <v>55.38431498737956</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="C17" t="n">
-        <v>57.13869813486862</v>
+        <v>58.55536007209676</v>
       </c>
       <c r="D17" t="n">
-        <v>53.36093296892689</v>
+        <v>51.94427103169875</v>
       </c>
     </row>
     <row r="18">
@@ -5050,10 +5050,10 @@
         <v>16.58662746324986</v>
       </c>
       <c r="C18" t="n">
-        <v>62.60114236129787</v>
+        <v>63.67124735892688</v>
       </c>
       <c r="D18" t="n">
-        <v>44.40935740160447</v>
+        <v>43.33925240397544</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>17.45252893839555</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="C19" t="n">
-        <v>68.00468172547231</v>
+        <v>68.6064930681756</v>
       </c>
       <c r="D19" t="n">
-        <v>34.3032465340878</v>
+        <v>31.89600116327462</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>18.15742379004475</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>18.82992096745382</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>26.77133874827893</v>
+        <v>15.70543307910511</v>
       </c>
       <c r="C21" t="n">
-        <v>152.754109328415</v>
+        <v>107.6943982567207</v>
       </c>
       <c r="D21" t="n">
-        <v>3.149569264503403</v>
+        <v>1.495755531343343</v>
       </c>
     </row>
   </sheetData>
@@ -5165,7 +5165,7 @@
         <v>0.382881604656256</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5105088062083414</v>
+        <v>0.5232715263635499</v>
       </c>
       <c r="D4" t="n">
         <v>16.0044510746315</v>
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.871612034921921</v>
+        <v>2.994330497952772</v>
       </c>
       <c r="C5" t="n">
-        <v>4.761476365597031</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>29.94330497952772</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.929576207201488</v>
+        <v>8.171086142446205</v>
       </c>
       <c r="C6" t="n">
-        <v>16.06041069377357</v>
+        <v>16.78494049950772</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68184129502858</v>
+        <v>39.32586778901449</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>12.57618809140164</v>
       </c>
       <c r="C7" t="n">
-        <v>28.68568617038755</v>
+        <v>29.16477905005999</v>
       </c>
       <c r="D7" t="n">
-        <v>40.72289477215769</v>
+        <v>41.20198765183014</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>14.52004854581032</v>
       </c>
       <c r="C8" t="n">
-        <v>34.54770171244525</v>
+        <v>35.21529015133309</v>
       </c>
       <c r="D8" t="n">
-        <v>44.56152829576272</v>
+        <v>44.72842540548468</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>15.42031119060464</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>38.162496759482</v>
       </c>
       <c r="D9" t="n">
-        <v>50.14374574211007</v>
+        <v>50.03280825153018</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.80122929985241</v>
+        <v>15.65887588273663</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>41.42484438069417</v>
       </c>
       <c r="D10" t="n">
-        <v>63.9166842849886</v>
+        <v>64.9131582047991</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14.74879576089983</v>
+        <v>14.21570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>45.66795795844887</v>
+        <v>46.02335062738621</v>
       </c>
       <c r="D11" t="n">
-        <v>63.43759140531613</v>
+        <v>62.54910973297276</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12.58404207303562</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C12" t="n">
-        <v>47.94953962311847</v>
+        <v>46.86470840992573</v>
       </c>
       <c r="D12" t="n">
-        <v>60.53358169615408</v>
+        <v>58.79785175504571</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.926851948267</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="C13" t="n">
-        <v>46.04887606769665</v>
+        <v>45.00822350119503</v>
       </c>
       <c r="D13" t="n">
-        <v>60.35784885709391</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
-        <v>45.1711936201</v>
+        <v>44.24933252581224</v>
       </c>
       <c r="D14" t="n">
-        <v>62.37926738013809</v>
+        <v>63.30112847442584</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>11.10847527355266</v>
       </c>
       <c r="C15" t="n">
-        <v>46.94226647856124</v>
+        <v>47.65894230266141</v>
       </c>
       <c r="D15" t="n">
-        <v>60.5591071364645</v>
+        <v>60.20076922441442</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12.39947350463721</v>
       </c>
       <c r="C16" t="n">
-        <v>51.25115715250048</v>
+        <v>52.0777887194763</v>
       </c>
       <c r="D16" t="n">
-        <v>58.2775254717949</v>
+        <v>54.97099920389165</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>57.13869813486862</v>
+        <v>58.55536007209676</v>
       </c>
       <c r="D17" t="n">
-        <v>53.36093296892689</v>
+        <v>51.94427103169875</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14.98146996680633</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="C18" t="n">
-        <v>62.60114236129787</v>
+        <v>63.67124735892688</v>
       </c>
       <c r="D18" t="n">
-        <v>45.47946239923349</v>
+        <v>43.87430490278995</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="C19" t="n">
-        <v>68.00468172547231</v>
+        <v>68.6064930681756</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>32.49781250597791</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>16.81242943522663</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>20.17491532227195</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>31.66326801958617</v>
+        <v>17.41431485354125</v>
       </c>
       <c r="C21" t="n">
-        <v>182.6727001129971</v>
+        <v>120.3859157266548</v>
       </c>
       <c r="D21" t="n">
-        <v>4.871272003013257</v>
+        <v>2.271432372201033</v>
       </c>
     </row>
   </sheetData>
@@ -5451,7 +5451,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09032078879070655</v>
+        <v>0.08933904108645974</v>
       </c>
     </row>
     <row r="3">
@@ -5465,7 +5465,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.174571164906685</v>
+        <v>2.154936210821749</v>
       </c>
     </row>
     <row r="4">
@@ -5479,7 +5479,7 @@
         <v>0.2552544031041707</v>
       </c>
       <c r="D4" t="n">
-        <v>13.93689040948772</v>
+        <v>14.00070401026376</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.86532063806894</v>
+        <v>1.963495408493621</v>
       </c>
       <c r="C5" t="n">
-        <v>2.896155727528091</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="D5" t="n">
-        <v>28.76520773443155</v>
+        <v>28.86338250485623</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6.239006660488481</v>
+        <v>6.520768251607316</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>13.00128484734051</v>
       </c>
       <c r="D6" t="n">
-        <v>39.72838434775569</v>
+        <v>40.29190752999335</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.19879606234337</v>
+        <v>11.5581157220977</v>
       </c>
       <c r="C7" t="n">
-        <v>26.23033516206628</v>
+        <v>27.36818075128833</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>43.29801900039708</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>14.6034971006713</v>
       </c>
       <c r="C8" t="n">
-        <v>36.80081269369168</v>
+        <v>37.30150402285756</v>
       </c>
       <c r="D8" t="n">
-        <v>45.89670517353839</v>
+        <v>45.98015372839936</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.53124868118453</v>
+        <v>15.64218617176442</v>
       </c>
       <c r="C9" t="n">
-        <v>40.38124657107979</v>
+        <v>41.3796839862988</v>
       </c>
       <c r="D9" t="n">
-        <v>50.36562072326985</v>
+        <v>50.14374574211007</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.9435827169682</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>62.63550353094652</v>
+        <v>64.05903770210438</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.10418842983717</v>
+        <v>14.74879576089983</v>
       </c>
       <c r="C11" t="n">
-        <v>47.26722496866692</v>
+        <v>47.80031397207294</v>
       </c>
       <c r="D11" t="n">
-        <v>64.85916208106552</v>
+        <v>63.97068040872215</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.23494080095125</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="C12" t="n">
-        <v>50.33616829214246</v>
+        <v>49.68526956422682</v>
       </c>
       <c r="D12" t="n">
-        <v>61.40144666670826</v>
+        <v>59.88268296823844</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.18701508989241</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C13" t="n">
-        <v>49.69116005045231</v>
+        <v>48.13018120069988</v>
       </c>
       <c r="D13" t="n">
-        <v>61.13833828197012</v>
+        <v>60.35784885709391</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>10.14047203716531</v>
       </c>
       <c r="C14" t="n">
-        <v>48.24406393439251</v>
+        <v>47.01491580867551</v>
       </c>
       <c r="D14" t="n">
-        <v>62.07198034870884</v>
+        <v>63.30112847442584</v>
       </c>
     </row>
     <row r="15">
@@ -5644,10 +5644,10 @@
         <v>11.5728419376614</v>
       </c>
       <c r="C16" t="n">
-        <v>51.66447293598839</v>
+        <v>52.49110450296421</v>
       </c>
       <c r="D16" t="n">
-        <v>58.69084125528282</v>
+        <v>54.97099920389165</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>12.74995743505333</v>
       </c>
       <c r="C17" t="n">
-        <v>56.6664774891259</v>
+        <v>58.55536007209676</v>
       </c>
       <c r="D17" t="n">
-        <v>53.36093296892689</v>
+        <v>51.94427103169875</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="C18" t="n">
-        <v>62.60114236129787</v>
+        <v>63.67124735892688</v>
       </c>
       <c r="D18" t="n">
-        <v>46.54956739686251</v>
+        <v>44.40935740160447</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>15.04528356758237</v>
+        <v>15.64709491028566</v>
       </c>
       <c r="C19" t="n">
         <v>68.6064930681756</v>
       </c>
       <c r="D19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.09962384868121</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>15.46743508040849</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>21.51990967709008</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>36.80881161101543</v>
+        <v>19.16047884520369</v>
       </c>
       <c r="C21" t="n">
-        <v>212.4872306635891</v>
+        <v>133.3569327626176</v>
       </c>
       <c r="D21" t="n">
-        <v>6.692511202002806</v>
+        <v>3.06567661523259</v>
       </c>
     </row>
   </sheetData>
@@ -5762,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05988660995905543</v>
+        <v>0.05890486225480862</v>
       </c>
     </row>
     <row r="3">
@@ -5776,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.811324514335365</v>
+        <v>1.776963344686727</v>
       </c>
     </row>
     <row r="4">
@@ -5790,7 +5790,7 @@
         <v>0.1276272015520853</v>
       </c>
       <c r="D4" t="n">
-        <v>12.09905870713769</v>
+        <v>12.20116046837936</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.178097245096173</v>
+        <v>1.227184630308513</v>
       </c>
       <c r="C5" t="n">
-        <v>1.742602175038089</v>
+        <v>1.84077694546277</v>
       </c>
       <c r="D5" t="n">
-        <v>27.58711048933538</v>
+        <v>27.68528525976006</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.669192081397831</v>
+        <v>4.950953672516666</v>
       </c>
       <c r="C6" t="n">
-        <v>8.654106012935635</v>
+        <v>9.418887474543901</v>
       </c>
       <c r="D6" t="n">
-        <v>39.84913931537804</v>
+        <v>40.37241084174159</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>22.39759212468673</v>
+        <v>23.95464398362217</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>45.27427712904591</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>36.30012136452581</v>
+        <v>37.55184968744049</v>
       </c>
       <c r="D8" t="n">
-        <v>47.31533060617502</v>
+        <v>47.398779161036</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.53124868118453</v>
+        <v>15.64218617176442</v>
       </c>
       <c r="C9" t="n">
-        <v>43.37655881673681</v>
+        <v>44.48593372253571</v>
       </c>
       <c r="D9" t="n">
-        <v>50.80937068558941</v>
+        <v>50.47655821384974</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>16.08593613408399</v>
       </c>
       <c r="C10" t="n">
-        <v>46.54956739686252</v>
+        <v>47.26133448244146</v>
       </c>
       <c r="D10" t="n">
-        <v>62.20844327959914</v>
+        <v>63.34727061652544</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.45958109877452</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="C11" t="n">
-        <v>49.22188464782232</v>
+        <v>50.11036632016568</v>
       </c>
       <c r="D11" t="n">
-        <v>65.21455475000286</v>
+        <v>65.03685841553418</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.88583952886689</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="C12" t="n">
-        <v>52.50583071852791</v>
+        <v>52.939763203805</v>
       </c>
       <c r="D12" t="n">
-        <v>62.26931163726244</v>
+        <v>61.18448042406971</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.70734137314322</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C13" t="n">
-        <v>52.81311774995717</v>
+        <v>51.25213890020473</v>
       </c>
       <c r="D13" t="n">
-        <v>61.91882770684634</v>
+        <v>60.09768571546851</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.14047203716531</v>
+        <v>9.833185005736054</v>
       </c>
       <c r="C14" t="n">
-        <v>51.31693424868503</v>
+        <v>49.47321206010952</v>
       </c>
       <c r="D14" t="n">
-        <v>61.76469331727959</v>
+        <v>63.30112847442584</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>50.52564559906209</v>
+        <v>49.80896977496192</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>60.91744504851458</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>52.90442028645212</v>
       </c>
       <c r="D16" t="n">
-        <v>58.69084125528282</v>
+        <v>55.38431498737956</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>11.8055161435679</v>
       </c>
       <c r="C17" t="n">
-        <v>56.6664774891259</v>
+        <v>58.55536007209676</v>
       </c>
       <c r="D17" t="n">
-        <v>53.36093296892689</v>
+        <v>51.47205038595602</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12.84125997154828</v>
+        <v>13.37631247036279</v>
       </c>
       <c r="C18" t="n">
-        <v>62.06608986248335</v>
+        <v>63.67124735892688</v>
       </c>
       <c r="D18" t="n">
-        <v>47.08461989567702</v>
+        <v>44.94440990041898</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13.84166088217578</v>
+        <v>14.44347222487907</v>
       </c>
       <c r="C19" t="n">
-        <v>68.00468172547231</v>
+        <v>68.6064930681756</v>
       </c>
       <c r="D19" t="n">
-        <v>36.10868056219768</v>
+        <v>33.7014351913845</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>14.12244072559037</v>
+        <v>14.79493790299943</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>22.86490403190821</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>41.34815953363038</v>
+        <v>20.94414534754896</v>
       </c>
       <c r="C21" t="n">
-        <v>243.7818572503625</v>
+        <v>145.8333083458965</v>
       </c>
       <c r="D21" t="n">
-        <v>8.614199902839664</v>
+        <v>3.878545434731288</v>
       </c>
     </row>
   </sheetData>
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03926990816987241</v>
+        <v>0.0382881604656256</v>
       </c>
     </row>
     <row r="3">
@@ -6087,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.497165248976386</v>
+        <v>1.45298660228528</v>
       </c>
     </row>
     <row r="4">
@@ -6101,7 +6101,7 @@
         <v>0.06381360077604267</v>
       </c>
       <c r="D4" t="n">
-        <v>10.47819324742621</v>
+        <v>10.58029500866788</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7363107781851078</v>
+        <v>0.7608544707912782</v>
       </c>
       <c r="C5" t="n">
-        <v>1.030835089459151</v>
+        <v>1.079922474671491</v>
       </c>
       <c r="D5" t="n">
-        <v>26.06540154775282</v>
+        <v>26.18812001078367</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.421390749300135</v>
+        <v>3.582397372796612</v>
       </c>
       <c r="C6" t="n">
-        <v>6.037748381117884</v>
+        <v>6.561019907481435</v>
       </c>
       <c r="D6" t="n">
-        <v>39.68813269188156</v>
+        <v>40.13090090649688</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.144578954431539</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>18.1456428175938</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="D7" t="n">
-        <v>45.75337000871835</v>
+        <v>46.95110220789945</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>33.79666471869644</v>
+        <v>35.79943003535994</v>
       </c>
       <c r="D8" t="n">
-        <v>48.23326470964579</v>
+        <v>49.06775025825559</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.30937370002476</v>
+        <v>15.64218617176442</v>
       </c>
       <c r="C9" t="n">
-        <v>44.81874619427537</v>
+        <v>46.92655851529327</v>
       </c>
       <c r="D9" t="n">
-        <v>51.36405813848885</v>
+        <v>51.47499562906875</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>16.08593613408399</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>50.67781649322036</v>
       </c>
       <c r="D10" t="n">
-        <v>61.92373644536757</v>
+        <v>62.20844327959914</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.63727743324319</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="C11" t="n">
-        <v>52.06502599932108</v>
+        <v>52.95350767166445</v>
       </c>
       <c r="D11" t="n">
-        <v>65.39225108447152</v>
+        <v>65.92534008787754</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.31977201414398</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="C12" t="n">
-        <v>54.67549314491336</v>
+        <v>55.326391872829</v>
       </c>
       <c r="D12" t="n">
-        <v>63.78807533573226</v>
+        <v>62.48627787990098</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.22766765639403</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="C13" t="n">
-        <v>56.45540173271284</v>
+        <v>54.63425974133501</v>
       </c>
       <c r="D13" t="n">
-        <v>62.17899084847173</v>
+        <v>60.09768571546851</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.44775906859456</v>
+        <v>9.525897974306801</v>
       </c>
       <c r="C14" t="n">
-        <v>54.38980456297755</v>
+        <v>52.23879534297279</v>
       </c>
       <c r="D14" t="n">
-        <v>61.76469331727959</v>
+        <v>63.30112847442584</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>53.03401098341269</v>
+        <v>51.60065933521235</v>
       </c>
       <c r="D15" t="n">
-        <v>61.63412087261475</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>53.73105185342793</v>
       </c>
       <c r="D16" t="n">
-        <v>58.69084125528282</v>
+        <v>55.79763077086746</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>10.86107485208246</v>
       </c>
       <c r="C17" t="n">
-        <v>57.13869813486862</v>
+        <v>58.55536007209676</v>
       </c>
       <c r="D17" t="n">
-        <v>53.8331536146696</v>
+        <v>50.99982974021331</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11.77115497391926</v>
+        <v>12.30620747273377</v>
       </c>
       <c r="C18" t="n">
-        <v>62.06608986248335</v>
+        <v>63.67124735892688</v>
       </c>
       <c r="D18" t="n">
-        <v>47.08461989567702</v>
+        <v>44.94440990041898</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12.63803819676919</v>
+        <v>13.23984953947248</v>
       </c>
       <c r="C19" t="n">
-        <v>68.00468172547231</v>
+        <v>69.2083044108789</v>
       </c>
       <c r="D19" t="n">
-        <v>36.71049190490098</v>
+        <v>34.3032465340878</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>24.20989838672634</v>
+        <v>17.48492661263569</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>46.09442869956224</v>
+        <v>22.7652335355476</v>
       </c>
       <c r="C21" t="n">
-        <v>275.680140876228</v>
+        <v>158.5716266958833</v>
       </c>
       <c r="D21" t="n">
-        <v>10.63717585374513</v>
+        <v>3.925040264749586</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02552544031041707</v>
+        <v>0.02454369260617026</v>
       </c>
     </row>
     <row r="3">
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.232093368829747</v>
+        <v>1.183005983617406</v>
       </c>
     </row>
     <row r="4">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4417864669110648</v>
+        <v>0.466330159517235</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5890486225480863</v>
+        <v>0.6135923151542566</v>
       </c>
       <c r="D5" t="n">
-        <v>24.15099352447154</v>
+        <v>24.49460522095793</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.415099352447154</v>
+        <v>2.576105975943631</v>
       </c>
       <c r="C6" t="n">
-        <v>4.065417243286043</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="D6" t="n">
-        <v>39.56737772425921</v>
+        <v>39.9698942830004</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>14.25301317025519</v>
+        <v>15.57051858935441</v>
       </c>
       <c r="D7" t="n">
-        <v>46.65166915810418</v>
+        <v>47.72962813736718</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C8" t="n">
-        <v>29.95803119509142</v>
+        <v>32.46148784092078</v>
       </c>
       <c r="D8" t="n">
-        <v>49.31809592283852</v>
+        <v>50.73672135547515</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.75468624712531</v>
+        <v>15.30937370002476</v>
       </c>
       <c r="C9" t="n">
-        <v>44.37499623195582</v>
+        <v>47.14843349645305</v>
       </c>
       <c r="D9" t="n">
-        <v>52.58437053486764</v>
+        <v>52.69530802544753</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16.08593613408399</v>
+        <v>16.22828955119978</v>
       </c>
       <c r="C10" t="n">
-        <v>51.95899724726245</v>
+        <v>53.95194508688347</v>
       </c>
       <c r="D10" t="n">
-        <v>61.06961594267285</v>
+        <v>61.35432277690443</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="C11" t="n">
-        <v>55.08586368528852</v>
+        <v>56.32973802656922</v>
       </c>
       <c r="D11" t="n">
-        <v>65.5699474189402</v>
+        <v>66.45842909128358</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.53673825678252</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="C12" t="n">
-        <v>57.2790880565759</v>
+        <v>58.14695302713008</v>
       </c>
       <c r="D12" t="n">
-        <v>65.08987279156352</v>
+        <v>63.78807533573226</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.74799393964483</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="C13" t="n">
-        <v>59.05703314896688</v>
+        <v>58.01638058246527</v>
       </c>
       <c r="D13" t="n">
-        <v>62.43915399009714</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.75504610002381</v>
+        <v>9.525897974306801</v>
       </c>
       <c r="C14" t="n">
-        <v>57.76996190869932</v>
+        <v>55.3116656572653</v>
       </c>
       <c r="D14" t="n">
-        <v>62.37926738013809</v>
+        <v>62.68655441156734</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="C15" t="n">
-        <v>55.90071427981338</v>
+        <v>53.75068680751286</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>61.63412087261475</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>9.506263020221864</v>
       </c>
       <c r="C16" t="n">
-        <v>55.79763077086746</v>
+        <v>54.97099920389165</v>
       </c>
       <c r="D16" t="n">
-        <v>58.69084125528282</v>
+        <v>56.21094655435537</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>9.916633560597033</v>
       </c>
       <c r="C17" t="n">
-        <v>57.61091878061134</v>
+        <v>59.4998013635822</v>
       </c>
       <c r="D17" t="n">
-        <v>54.30537426041232</v>
+        <v>50.52760909447059</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10.70104997629023</v>
+        <v>11.23610247510475</v>
       </c>
       <c r="C18" t="n">
-        <v>62.06608986248335</v>
+        <v>63.67124735892688</v>
       </c>
       <c r="D18" t="n">
-        <v>47.08461989567702</v>
+        <v>44.94440990041898</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11.4344155113626</v>
+        <v>12.03622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>67.40287038276901</v>
+        <v>69.2083044108789</v>
       </c>
       <c r="D19" t="n">
-        <v>37.91411459030757</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>12.10494919336317</v>
+        <v>12.77744637077223</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.99218104722434</v>
       </c>
       <c r="D20" t="n">
-        <v>24.8823955641354</v>
+        <v>18.15742379004475</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>51.0480348879363</v>
+        <v>24.62407338748729</v>
       </c>
       <c r="C21" t="n">
-        <v>309.0229254823286</v>
+        <v>171.5741887644275</v>
       </c>
       <c r="D21" t="n">
-        <v>13.67358077355436</v>
+        <v>4.765949687900765</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -475,7 +475,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7061868316279986</v>
+        <v>0.3530934158139993</v>
       </c>
     </row>
     <row r="3">
@@ -483,13 +483,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1485875150377547</v>
+        <v>0.05713771638716436</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.572107050924863</v>
+        <v>2.286053525462432</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4.893482161910057</v>
+        <v>1.881735459683946</v>
       </c>
       <c r="C4" t="n">
-        <v>9.074102589550941</v>
+        <v>3.729458270154262</v>
       </c>
       <c r="D4" t="n">
-        <v>27.54128643349195</v>
+        <v>13.77064321674597</v>
       </c>
     </row>
     <row r="5">
@@ -511,13 +511,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7.825609125321751</v>
+        <v>3.009253063057324</v>
       </c>
       <c r="C5" t="n">
-        <v>12.69105257279852</v>
+        <v>5.216025552663305</v>
       </c>
       <c r="D5" t="n">
-        <v>23.31321912105253</v>
+        <v>11.65660956052626</v>
       </c>
     </row>
     <row r="6">
@@ -525,13 +525,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.503657461814795</v>
+        <v>3.654528340123033</v>
       </c>
       <c r="C6" t="n">
-        <v>19.42577113809693</v>
+        <v>7.983996445943297</v>
       </c>
       <c r="D6" t="n">
-        <v>36.00647473569937</v>
+        <v>18.00323736784969</v>
       </c>
     </row>
     <row r="7">
@@ -539,13 +539,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.08511788973739</v>
+        <v>4.647200932822702</v>
       </c>
       <c r="C7" t="n">
-        <v>19.09580377120417</v>
+        <v>7.84837978157405</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03191038845973</v>
+        <v>16.01595519422986</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.9771322478848</v>
+        <v>5.374754521485928</v>
       </c>
       <c r="C8" t="n">
-        <v>25.88974724850897</v>
+        <v>10.64069212743314</v>
       </c>
       <c r="D8" t="n">
-        <v>43.86506665689299</v>
+        <v>21.9325333284465</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +567,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.77554249535433</v>
+        <v>5.681774517539622</v>
       </c>
       <c r="C9" t="n">
-        <v>28.68177881452464</v>
+        <v>11.78821774901906</v>
       </c>
       <c r="D9" t="n">
-        <v>48.08408029200385</v>
+        <v>24.04204014600192</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +581,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14.0761905912433</v>
+        <v>5.412846332410704</v>
       </c>
       <c r="C10" t="n">
-        <v>39.25765595852342</v>
+        <v>16.13490570957182</v>
       </c>
       <c r="D10" t="n">
-        <v>69.577510270015</v>
+        <v>34.7887551350075</v>
       </c>
     </row>
     <row r="11">
@@ -595,13 +595,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.47491849464901</v>
+        <v>4.412555377526079</v>
       </c>
       <c r="C11" t="n">
-        <v>32.92482072469695</v>
+        <v>13.53210895879283</v>
       </c>
       <c r="D11" t="n">
-        <v>54.07761468351326</v>
+        <v>27.03880734175663</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.9459469411146</v>
+        <v>4.209145107187775</v>
       </c>
       <c r="C12" t="n">
-        <v>35.52648650212065</v>
+        <v>14.6013941970888</v>
       </c>
       <c r="D12" t="n">
-        <v>58.02501799876722</v>
+        <v>29.01250899938361</v>
       </c>
     </row>
     <row r="13">
@@ -623,13 +623,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.0251936158014</v>
+        <v>4.239618555927597</v>
       </c>
       <c r="C13" t="n">
-        <v>34.75233229517995</v>
+        <v>14.28321663837635</v>
       </c>
       <c r="D13" t="n">
-        <v>59.98061230173707</v>
+        <v>29.99030615086853</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +637,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12.4021045884846</v>
+        <v>4.769094727781986</v>
       </c>
       <c r="C14" t="n">
-        <v>39.72299455285937</v>
+        <v>16.32615997983614</v>
       </c>
       <c r="D14" t="n">
-        <v>62.3436220844923</v>
+        <v>31.17181104224615</v>
       </c>
     </row>
     <row r="15">
@@ -651,13 +651,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14.46251813034146</v>
+        <v>5.561404395017331</v>
       </c>
       <c r="C15" t="n">
-        <v>46.32234189071459</v>
+        <v>19.03849326722106</v>
       </c>
       <c r="D15" t="n">
-        <v>59.48266004866603</v>
+        <v>29.74133002433302</v>
       </c>
     </row>
     <row r="16">
@@ -665,13 +665,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15.84735377049333</v>
+        <v>6.093927911745703</v>
       </c>
       <c r="C16" t="n">
-        <v>51.64835362043237</v>
+        <v>21.22748532415542</v>
       </c>
       <c r="D16" t="n">
-        <v>57.1739723298822</v>
+        <v>28.5869861649411</v>
       </c>
     </row>
     <row r="17">
@@ -679,13 +679,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18.10588399906721</v>
+        <v>6.962421200830602</v>
       </c>
       <c r="C17" t="n">
-        <v>56.97436535015014</v>
+        <v>23.41647738108979</v>
       </c>
       <c r="D17" t="n">
-        <v>52.25782554047191</v>
+        <v>26.12891277023595</v>
       </c>
     </row>
     <row r="18">
@@ -693,13 +693,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.43524696693832</v>
+        <v>7.473613303441098</v>
       </c>
       <c r="C18" t="n">
-        <v>62.24961286957674</v>
+        <v>25.58460533581351</v>
       </c>
       <c r="D18" t="n">
-        <v>44.40828729660684</v>
+        <v>22.20414364830342</v>
       </c>
     </row>
     <row r="19">
@@ -707,13 +707,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.86019521235448</v>
+        <v>8.40610083487962</v>
       </c>
       <c r="C19" t="n">
-        <v>67.42333196842091</v>
+        <v>27.71100508611591</v>
       </c>
       <c r="D19" t="n">
-        <v>33.2994252144587</v>
+        <v>16.64971260722935</v>
       </c>
     </row>
     <row r="20">
@@ -721,13 +721,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>21.71358886418389</v>
+        <v>8.349724954710952</v>
       </c>
       <c r="C20" t="n">
-        <v>75.34254877384718</v>
+        <v>30.96580503097781</v>
       </c>
       <c r="D20" t="n">
-        <v>18.60530691019919</v>
+        <v>9.302653455099595</v>
       </c>
     </row>
     <row r="21">
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>22.61501978874627</v>
+        <v>8.696360434126415</v>
       </c>
       <c r="C21" t="n">
-        <v>80.48242506583058</v>
+        <v>33.07829537980645</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>45.39208685355552</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>142.8138567890793</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01570796326794897</v>
+        <v>377.2444093384709</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>102.7349885109075</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>409.0648159285185</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9670214886831081</v>
+        <v>597.5701926209485</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>132.5280860916854</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01276272015520854</v>
+        <v>554.9485977887775</v>
       </c>
       <c r="D4" t="n">
-        <v>7.836310175298041</v>
+        <v>412.8484715806857</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2699806186678729</v>
+        <v>112.0665004397734</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3436116964863837</v>
+        <v>553.1657439578654</v>
       </c>
       <c r="D5" t="n">
-        <v>22.67837196810132</v>
+        <v>150.9437095279471</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.771072858461246</v>
+        <v>60.33723215530473</v>
       </c>
       <c r="C6" t="n">
-        <v>2.938370878810704</v>
+        <v>370.9995121917569</v>
       </c>
       <c r="D6" t="n">
-        <v>39.44662275663685</v>
+        <v>48.3422387048172</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="C7" t="n">
-        <v>11.85754877189298</v>
+        <v>143.0092245822244</v>
       </c>
       <c r="D7" t="n">
-        <v>48.32849423695774</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -867,10 +867,10 @@
         <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>28.20561154301086</v>
+        <v>40.55599766243574</v>
       </c>
       <c r="D8" t="n">
-        <v>52.32224389783376</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.64374875654542</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>22.85312305945724</v>
       </c>
       <c r="D9" t="n">
-        <v>54.0265579124062</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16.22828955119978</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="C10" t="n">
-        <v>56.22959976073607</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>60.78490910844128</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.63727743324319</v>
+        <v>9.950994730245668</v>
       </c>
       <c r="C11" t="n">
-        <v>59.88366471594267</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>66.81382176022092</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.10280577150543</v>
+        <v>8.678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>61.40144666670826</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>64.87290654892497</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.96750451476862</v>
+        <v>7.544731107136739</v>
       </c>
       <c r="C13" t="n">
-        <v>61.39850142359553</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>61.65866456522093</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9.525897974306801</v>
+        <v>6.145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>58.69182300298707</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>62.07198034870884</v>
+        <v>35.33800861436394</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.600109889202059</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>56.25905219186346</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>61.99245878466483</v>
+        <v>34.04210164475815</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9.092947236733956</v>
+        <v>5.7864209688307</v>
       </c>
       <c r="C16" t="n">
-        <v>57.03757812133119</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>56.62426233784328</v>
+        <v>32.65194689554467</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>59.97202200932491</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="D17" t="n">
-        <v>50.05538844872788</v>
+        <v>30.22212132753381</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10.16599747747572</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>64.2062998577414</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>44.94440990041898</v>
+        <v>26.75262494072559</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10.83260416865931</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>69.2083044108789</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -1032,13 +1032,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>12.10494919336317</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>18.82992096745382</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>25.71696506362797</v>
+        <v>27.64282800432414</v>
       </c>
       <c r="C21" t="n">
-        <v>184.8406863948261</v>
+        <v>124.3927260194586</v>
       </c>
       <c r="D21" t="n">
-        <v>5.625586107668619</v>
+        <v>8.292848401297242</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>46.245225608546</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>145.342838875219</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009817477042468103</v>
+        <v>378.8456398440974</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>105.2188102026519</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>415.1614691718912</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7853981633974483</v>
+        <v>610.4556312391879</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>135.2082573242792</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>565.1204857524788</v>
       </c>
       <c r="D4" t="n">
-        <v>6.700428081484481</v>
+        <v>424.2455806792869</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1472621556370216</v>
+        <v>114.9135687820892</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1718058482431918</v>
+        <v>563.4250074672445</v>
       </c>
       <c r="D5" t="n">
-        <v>20.81305133003238</v>
+        <v>157.3496132981575</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.207549676223577</v>
+        <v>62.792583163626</v>
       </c>
       <c r="C6" t="n">
-        <v>1.891827826083604</v>
+        <v>381.7064526542727</v>
       </c>
       <c r="D6" t="n">
-        <v>38.60133798328035</v>
+        <v>50.31456984264904</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.251949307092936</v>
+        <v>23.77498415374501</v>
       </c>
       <c r="C7" t="n">
-        <v>8.743445054022093</v>
+        <v>151.1538035366559</v>
       </c>
       <c r="D7" t="n">
-        <v>48.74770050667112</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>23.53249247079604</v>
+        <v>43.72704274715294</v>
       </c>
       <c r="D8" t="n">
-        <v>53.82431788533138</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>42.48905889209769</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>55.35780779936488</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.9435827169682</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="C10" t="n">
-        <v>56.94136684631501</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>61.06961594267285</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.81497376771187</v>
+        <v>9.950994730245668</v>
       </c>
       <c r="C11" t="n">
-        <v>63.25989507084746</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>66.2807327568149</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.31977201414398</v>
+        <v>8.678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>64.87290654892497</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>65.9577377621177</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.22766765639403</v>
+        <v>7.544731107136739</v>
       </c>
       <c r="C13" t="n">
-        <v>65.561111689602</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>62.43915399009714</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9.833185005736054</v>
+        <v>6.145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>62.07198034870884</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>61.76469331727959</v>
+        <v>35.33800861436394</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>59.12575548826415</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>61.99245878466483</v>
+        <v>34.04210164475815</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>5.7864209688307</v>
       </c>
       <c r="C16" t="n">
-        <v>58.69084125528282</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>57.03757812133119</v>
+        <v>32.65194689554467</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.9721922691116</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>60.91646330081034</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="D17" t="n">
-        <v>50.05538844872788</v>
+        <v>30.22212132753381</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9.63094497866121</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>64.74135235655591</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>44.94440990041898</v>
+        <v>26.75262494072559</v>
       </c>
     </row>
     <row r="19">
@@ -1329,13 +1329,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10.23079282595601</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>69.2083044108789</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -1343,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>10.75995483854504</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>19.50241814486288</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>26.8290428117713</v>
+        <v>27.6710782261364</v>
       </c>
       <c r="C21" t="n">
-        <v>198.3723165476424</v>
+        <v>124.5198520176138</v>
       </c>
       <c r="D21" t="n">
-        <v>6.504010378611224</v>
+        <v>8.301323467840922</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>46.81758452012189</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>146.6888149777414</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005890486225480863</v>
+        <v>394.3052209428719</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>106.4754472640878</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>418.2736093943536</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6381360077604268</v>
+        <v>623.291982472215</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>136.5866311010417</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>570.2510992548725</v>
       </c>
       <c r="D4" t="n">
-        <v>5.704935909378214</v>
+        <v>435.8724187406819</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.07363107781851079</v>
+        <v>116.3616466458532</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07363107781851079</v>
+        <v>568.6528139923588</v>
       </c>
       <c r="D5" t="n">
-        <v>18.94773069196344</v>
+        <v>163.9273229166112</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8050331174823847</v>
+        <v>64.0403844957237</v>
       </c>
       <c r="C6" t="n">
-        <v>1.167298020349458</v>
+        <v>387.1001745414047</v>
       </c>
       <c r="D6" t="n">
-        <v>37.43403996293088</v>
+        <v>52.36740429222912</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.173990327829938</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="C7" t="n">
-        <v>6.347980655659875</v>
+        <v>155.2859796238307</v>
       </c>
       <c r="D7" t="n">
-        <v>49.40645321622073</v>
+        <v>29.8235317596096</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>19.10971906316416</v>
+        <v>45.39601384437251</v>
       </c>
       <c r="D8" t="n">
-        <v>54.49190632421922</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.09218647320796</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>38.38437174064178</v>
+        <v>23.74062298409636</v>
       </c>
       <c r="D9" t="n">
-        <v>56.79999517690344</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.37416904850505</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="C10" t="n">
-        <v>56.08724634362028</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>61.4966761940202</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.81497376771187</v>
+        <v>9.950994730245668</v>
       </c>
       <c r="C11" t="n">
-        <v>65.74764375340887</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>65.92534008787754</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.53673825678252</v>
+        <v>8.678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>68.56133267378024</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>66.82560273267188</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.48783079801943</v>
+        <v>7.544731107136739</v>
       </c>
       <c r="C13" t="n">
-        <v>68.94323253073227</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>63.21964341497336</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.14047203716531</v>
+        <v>6.145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>66.06671175728911</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>61.45740628585034</v>
+        <v>35.33800861436394</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>61.99245878466483</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>61.99245878466483</v>
+        <v>34.04210164475815</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.852999886270235</v>
+        <v>5.7864209688307</v>
       </c>
       <c r="C16" t="n">
-        <v>60.75742017272236</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>57.4508939048191</v>
+        <v>32.65194689554467</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8.499971623368884</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>61.86090459229577</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="D17" t="n">
-        <v>50.52760909447059</v>
+        <v>30.22212132753381</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9.095892479846698</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>65.27640485537043</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>44.40935740160447</v>
+        <v>26.75262494072559</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +1640,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9.628981483252716</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>69.2083044108789</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -1654,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>10.08745766113597</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>20.17491532227195</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>27.96042606337505</v>
+        <v>27.67982249023297</v>
       </c>
       <c r="C21" t="n">
-        <v>212.1702918926695</v>
+        <v>124.5592012060484</v>
       </c>
       <c r="D21" t="n">
-        <v>7.401289252069866</v>
+        <v>8.303946747069892</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>47.09247387731099</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>151.1204241147115</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003926990816987242</v>
+        <v>397.2475188124996</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>105.9354860267521</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>416.2806615547325</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5154175447295755</v>
+        <v>618.7317643859885</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>135.8208678917292</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>567.4943517013475</v>
       </c>
       <c r="D4" t="n">
-        <v>4.900884539600077</v>
+        <v>432.3626706979995</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02454369260617027</v>
+        <v>115.5762484824558</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02454369260617027</v>
+        <v>565.3148717979196</v>
       </c>
       <c r="D5" t="n">
-        <v>17.03332266868216</v>
+        <v>162.601963515878</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5232715263635501</v>
+        <v>63.55736462523426</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7245298057341462</v>
+        <v>384.2423069743422</v>
       </c>
       <c r="D6" t="n">
-        <v>35.98498035146259</v>
+        <v>52.00513938936205</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.335577788403162</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="C7" t="n">
-        <v>4.491495746929157</v>
+        <v>154.0283608146906</v>
       </c>
       <c r="D7" t="n">
-        <v>49.70588626601601</v>
+        <v>29.70375853969149</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>15.10418842983718</v>
+        <v>45.06221962492859</v>
       </c>
       <c r="D8" t="n">
-        <v>55.15949476310704</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>9.762499171030278</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>23.62968549351647</v>
       </c>
       <c r="D9" t="n">
-        <v>58.13124506386212</v>
+        <v>29.62030998483051</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14.37769512869454</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>53.66723825265189</v>
+        <v>22.49183990429443</v>
       </c>
       <c r="D10" t="n">
-        <v>62.20844327959914</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.63727743324319</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="C11" t="n">
-        <v>66.99151809468958</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>65.74764375340887</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.75370449942107</v>
+        <v>8.461683462903258</v>
       </c>
       <c r="C12" t="n">
-        <v>72.03279255599698</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>67.47650146058751</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.74799393964483</v>
+        <v>7.284567965511334</v>
       </c>
       <c r="C13" t="n">
-        <v>72.58551651348793</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>64.00013283984957</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.44775906859456</v>
+        <v>5.838453597155781</v>
       </c>
       <c r="C14" t="n">
-        <v>70.06144316586938</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>61.15011925442109</v>
+        <v>35.03072158293469</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>65.5758379051657</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>61.99245878466483</v>
+        <v>33.68376373270807</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.439684102782329</v>
+        <v>5.7864209688307</v>
       </c>
       <c r="C16" t="n">
-        <v>62.82399909016188</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
-        <v>57.864209688307</v>
+        <v>32.23863111205676</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.555530331883453</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>63.27756652952392</v>
+        <v>25.02769422436394</v>
       </c>
       <c r="D17" t="n">
-        <v>50.99982974021331</v>
+        <v>29.7499006817911</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.560839981032187</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>65.81145735418494</v>
+        <v>27.82272993835461</v>
       </c>
       <c r="D18" t="n">
-        <v>43.87430490278995</v>
+        <v>26.21757244191107</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9.027170140549421</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>69.8101157535822</v>
+        <v>29.48875579246144</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>21.06339699461531</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>9.41496048372691</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>20.84741249968101</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>29.11117925689335</v>
+        <v>26.75016515294236</v>
       </c>
       <c r="C21" t="n">
-        <v>226.2354502249998</v>
+        <v>122.6817919083219</v>
       </c>
       <c r="D21" t="n">
-        <v>8.317479787683816</v>
+        <v>7.379355904259961</v>
       </c>
     </row>
   </sheetData>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>154.5202164145182</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001963495408493621</v>
+        <v>401.9756157561523</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>105.3955247894163</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>414.2975311921539</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4172427743048944</v>
+        <v>614.2059074694107</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>135.0551046824167</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>564.7503668679777</v>
       </c>
       <c r="D4" t="n">
-        <v>4.198934931063608</v>
+        <v>428.8784480956276</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>114.7908503190583</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>562.0014732960867</v>
       </c>
       <c r="D5" t="n">
-        <v>15.24163310843173</v>
+        <v>161.2766041151448</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3220132469929539</v>
+        <v>63.07434475474484</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4025165587411924</v>
+        <v>381.4246910631538</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>51.6831261423691</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.676825078853552</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="C7" t="n">
-        <v>3.114103717870883</v>
+        <v>152.7707420055504</v>
       </c>
       <c r="D7" t="n">
-        <v>49.70588626601601</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>11.68279768053704</v>
+        <v>44.72842540548468</v>
       </c>
       <c r="D8" t="n">
-        <v>55.82708320199487</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>59.46249495082079</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13.38122120888403</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>22.34948648717864</v>
       </c>
       <c r="D10" t="n">
-        <v>62.92021036517809</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.10418842983717</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="C11" t="n">
-        <v>66.81382176022092</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>65.5699474189402</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.75370449942107</v>
+        <v>8.244717220264713</v>
       </c>
       <c r="C12" t="n">
-        <v>74.85335371029807</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>68.12740018850316</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.00815708127024</v>
+        <v>7.024404823885929</v>
       </c>
       <c r="C13" t="n">
-        <v>76.22780049624359</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>64.78062226472579</v>
+        <v>35.64235040268046</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.44775906859456</v>
+        <v>5.53116656572653</v>
       </c>
       <c r="C14" t="n">
-        <v>74.05617457444966</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>61.76469331727959</v>
+        <v>34.72343455150544</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>69.15921702566655</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>33.32542582065798</v>
       </c>
     </row>
     <row r="16">
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>5.7864209688307</v>
       </c>
       <c r="C16" t="n">
-        <v>65.30389379108934</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>58.2775254717949</v>
+        <v>31.82531532856885</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>64.69422846675207</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>51.47205038595602</v>
+        <v>29.27768003604838</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.025787482217675</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>66.34650985299945</v>
+        <v>27.28767743954009</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33925240397544</v>
+        <v>25.68251994309656</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>70.41192709628548</v>
+        <v>28.88694444975815</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>20.46158565191202</v>
       </c>
     </row>
     <row r="20">
@@ -2279,10 +2279,10 @@
         <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>21.51990967709008</v>
+        <v>12.10494919336317</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>30.28143111541049</v>
+        <v>25.82668722485405</v>
       </c>
       <c r="C21" t="n">
-        <v>240.56914719465</v>
+        <v>120.8320009448529</v>
       </c>
       <c r="D21" t="n">
-        <v>9.252659507486539</v>
+        <v>6.456671806213513</v>
       </c>
     </row>
   </sheetData>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>50.05538844872788</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>161.4876798715578</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009817477042468104</v>
+        <v>404.7873411811152</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>106.7699715753619</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>417.8760015741336</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3337942194439156</v>
+        <v>628.1614510852792</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>136.4334784591792</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>569.8682176502163</v>
       </c>
       <c r="D4" t="n">
-        <v>3.586324363613598</v>
+        <v>440.5563370376434</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>116.2389281828224</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>567.229279821201</v>
       </c>
       <c r="D5" t="n">
-        <v>13.59720570381833</v>
+        <v>167.9034011188108</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1610066234964769</v>
+        <v>64.32214608684252</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2012582793705962</v>
+        <v>386.8184129502858</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>53.7762122478233</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.197732199181109</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="C7" t="n">
-        <v>2.09603134856694</v>
+        <v>156.9029180927252</v>
       </c>
       <c r="D7" t="n">
-        <v>49.34656660626167</v>
+        <v>30.00319158948677</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>8.845546815263761</v>
+        <v>46.39739650270425</v>
       </c>
       <c r="D8" t="n">
-        <v>56.41122308602172</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
         <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>60.68280734719958</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>12.10004045484194</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>22.34948648717864</v>
       </c>
       <c r="D10" t="n">
-        <v>63.77433086787281</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14.39340309196248</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="C11" t="n">
-        <v>65.21455475000286</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>66.2807327568149</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.75370449942107</v>
+        <v>8.244717220264713</v>
       </c>
       <c r="C12" t="n">
-        <v>76.80604989404496</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>67.91043394586461</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.26832022289564</v>
+        <v>7.024404823885929</v>
       </c>
       <c r="C13" t="n">
-        <v>79.87008447899927</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>65.561111689602</v>
+        <v>35.64235040268046</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.44775906859456</v>
+        <v>5.53116656572653</v>
       </c>
       <c r="C14" t="n">
-        <v>78.05090598302992</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>62.37926738013809</v>
+        <v>34.72343455150544</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>73.10093405821749</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>60.5591071364645</v>
+        <v>33.32542582065798</v>
       </c>
     </row>
     <row r="16">
@@ -2531,13 +2531,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>5.7864209688307</v>
       </c>
       <c r="C16" t="n">
-        <v>68.19710427550467</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>58.2775254717949</v>
+        <v>31.82531532856885</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>66.58311104972293</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>51.94427103169875</v>
+        <v>29.27768003604838</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>67.41661485062848</v>
+        <v>27.28767743954009</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33925240397544</v>
+        <v>25.68251994309656</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>71.01373843898878</v>
+        <v>28.88694444975815</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>20.46158565191202</v>
       </c>
     </row>
     <row r="20">
@@ -2587,13 +2587,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.06996612890878</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>31.60736733822606</v>
       </c>
       <c r="D20" t="n">
-        <v>21.51990967709008</v>
+        <v>12.10494919336317</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>31.47143604912085</v>
+        <v>25.83085541606944</v>
       </c>
       <c r="C21" t="n">
-        <v>255.1738058036825</v>
+        <v>120.851502125182</v>
       </c>
       <c r="D21" t="n">
-        <v>10.2069522321473</v>
+        <v>6.45771385401736</v>
       </c>
     </row>
   </sheetData>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>50.5236821036536</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>165.0160811206209</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>405.8240667567998</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>106.2251015995049</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>415.8879624730338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2650718801466388</v>
+        <v>623.5717805679253</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>135.6677152498667</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>567.1114700966913</v>
       </c>
       <c r="D4" t="n">
-        <v>3.05029011709484</v>
+        <v>437.0210635546507</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>115.4535300194249</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>563.8913376267618</v>
       </c>
       <c r="D5" t="n">
-        <v>12.19821522526662</v>
+        <v>166.5289543328652</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.08050331174823847</v>
+        <v>63.83912621635311</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08050331174823847</v>
+        <v>384.0007970390975</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>53.41394734495622</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7785259294677207</v>
+        <v>24.55351008321272</v>
       </c>
       <c r="C7" t="n">
-        <v>1.317505419099219</v>
+        <v>155.6452992835851</v>
       </c>
       <c r="D7" t="n">
-        <v>48.68781389671206</v>
+        <v>29.88341836956866</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.837250865273282</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>6.508987279156353</v>
+        <v>46.06360228326034</v>
       </c>
       <c r="D8" t="n">
-        <v>57.32915718949249</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>9.540624189870499</v>
       </c>
       <c r="C9" t="n">
-        <v>19.41406085148067</v>
+        <v>23.74062298409636</v>
       </c>
       <c r="D9" t="n">
-        <v>61.12655730951914</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.81885970079985</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>40.14366362665208</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
-        <v>64.77080478768332</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13.50492141961912</v>
+        <v>9.417905726839649</v>
       </c>
       <c r="C11" t="n">
-        <v>62.3714133985041</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>66.99151809468958</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.53673825678252</v>
+        <v>8.027750977626168</v>
       </c>
       <c r="C12" t="n">
-        <v>77.45694862196059</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>67.69346770322606</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.26832022289564</v>
+        <v>6.764241682260525</v>
       </c>
       <c r="C13" t="n">
-        <v>83.25220532012953</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>66.34160111447822</v>
+        <v>35.38218726105505</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.75504610002381</v>
+        <v>5.223879534297279</v>
       </c>
       <c r="C14" t="n">
-        <v>82.0456373916102</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>62.99384144299659</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>77.40098900281852</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>60.20076922441442</v>
+        <v>32.96708790860789</v>
       </c>
     </row>
     <row r="16">
@@ -2842,13 +2842,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>5.7864209688307</v>
       </c>
       <c r="C16" t="n">
-        <v>71.50363054340794</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>58.2775254717949</v>
+        <v>31.41199954508094</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>68.4719936326938</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D17" t="n">
-        <v>52.41649167744146</v>
+        <v>28.80545939030567</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>68.48671984825749</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33925240397544</v>
+        <v>25.14746744428205</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>71.61554978169207</v>
+        <v>28.28513310705485</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>19.85977430920873</v>
       </c>
     </row>
     <row r="20">
@@ -2898,13 +2898,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>31.60736733822606</v>
       </c>
       <c r="D20" t="n">
-        <v>21.51990967709008</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>32.68126194065227</v>
+        <v>24.89886993334683</v>
       </c>
       <c r="C21" t="n">
-        <v>270.0504276148635</v>
+        <v>118.9612674593238</v>
       </c>
       <c r="D21" t="n">
-        <v>11.18043171653894</v>
+        <v>5.533082207410407</v>
       </c>
     </row>
   </sheetData>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>50.81820641492764</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>167.9907766644887</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>413.7850588905371</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>105.6802316236479</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>413.9097408489765</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2110757564130642</v>
+        <v>619.0164712202202</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>134.9019520405542</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>564.3674852633214</v>
       </c>
       <c r="D4" t="n">
-        <v>2.590832191507332</v>
+        <v>433.5113155119683</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>114.6681318560275</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>560.5779391249288</v>
       </c>
       <c r="D5" t="n">
-        <v>10.8973995171396</v>
+        <v>165.1790512395259</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.04025165587411923</v>
+        <v>63.35610634586367</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04025165587411923</v>
+        <v>381.1831811279092</v>
       </c>
       <c r="D6" t="n">
-        <v>28.29691407950582</v>
+        <v>53.05168244208915</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4790928796724435</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8384125394267761</v>
+        <v>154.3876804744449</v>
       </c>
       <c r="D7" t="n">
-        <v>47.66974152740813</v>
+        <v>29.76364514965055</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.086213871524472</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>4.756567627075796</v>
+        <v>45.72980806381643</v>
       </c>
       <c r="D8" t="n">
-        <v>58.0801941832413</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>15.53124868118453</v>
+        <v>23.62968549351647</v>
       </c>
       <c r="D9" t="n">
-        <v>61.57030727183869</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.680032363873552</v>
       </c>
       <c r="C10" t="n">
-        <v>35.01894061048373</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="D10" t="n">
-        <v>65.62492529037804</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12.61643974727576</v>
+        <v>9.240209392370978</v>
       </c>
       <c r="C11" t="n">
-        <v>58.4620940401933</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>67.70230343256426</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.88583952886689</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="C12" t="n">
-        <v>77.02301613668351</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>67.69346770322606</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.26832022289564</v>
+        <v>6.50407854063512</v>
       </c>
       <c r="C13" t="n">
-        <v>85.85383673638357</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>66.86192739772903</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.06233313145306</v>
+        <v>4.916592502868027</v>
       </c>
       <c r="C14" t="n">
-        <v>85.11850770590272</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>63.60841550585509</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>81.70104394741955</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>59.84243131236433</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>75.22347259479911</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>58.2775254717949</v>
+        <v>30.99868376159304</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>70.83309686140737</v>
+        <v>23.61103228713579</v>
       </c>
       <c r="D17" t="n">
-        <v>52.41649167744146</v>
+        <v>28.33323874456295</v>
       </c>
     </row>
     <row r="18">
@@ -3181,13 +3181,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>70.09187734470103</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33925240397544</v>
+        <v>24.61241494546753</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>72.21736112439537</v>
+        <v>27.68332176435156</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>19.25796296650543</v>
       </c>
     </row>
     <row r="20">
@@ -3209,13 +3209,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6.724971774090649</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>31.60736733822606</v>
       </c>
       <c r="D20" t="n">
-        <v>21.51990967709008</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>33.91110910230968</v>
+        <v>23.97323731068273</v>
       </c>
       <c r="C21" t="n">
-        <v>285.2011227066045</v>
+        <v>117.1000437867964</v>
       </c>
       <c r="D21" t="n">
-        <v>12.17321865211117</v>
+        <v>4.610237944362063</v>
       </c>
     </row>
   </sheetData>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>51.18832529942869</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>171.3375545882661</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>421.2306334795449</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>107.1626706570606</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>418.1656171468865</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1668971097219578</v>
+        <v>633.5119760734243</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>136.2930885374719</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>569.4853360455601</v>
       </c>
       <c r="D4" t="n">
-        <v>2.195187866695868</v>
+        <v>445.2657807749154</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>116.0916660271854</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>565.805745650043</v>
       </c>
       <c r="D5" t="n">
-        <v>9.694758579437254</v>
+        <v>171.8549356284042</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>64.56365602208724</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>386.536651359167</v>
       </c>
       <c r="D6" t="n">
-        <v>26.24407962992574</v>
+        <v>55.2252718592916</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2994330497952771</v>
+        <v>25.03260296288517</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4790928796724435</v>
+        <v>158.4599699516607</v>
       </c>
       <c r="D7" t="n">
-        <v>46.41212271826796</v>
+        <v>30.24273802932299</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>3.337942194439155</v>
+        <v>47.398779161036</v>
       </c>
       <c r="D8" t="n">
-        <v>58.4974369575462</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>12.20312396378785</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>62.12499472473814</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>9.680032363873552</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="D10" t="n">
-        <v>66.47904579307277</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.55026174046372</v>
+        <v>9.240209392370978</v>
       </c>
       <c r="C11" t="n">
-        <v>53.66429300953914</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>68.41308877043897</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.23494080095125</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="C12" t="n">
-        <v>75.28728619557515</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>67.69346770322606</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.00815708127024</v>
+        <v>6.50407854063512</v>
       </c>
       <c r="C13" t="n">
-        <v>87.41481558613602</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>67.38225368097983</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -3436,13 +3436,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.06233313145306</v>
+        <v>4.916592502868027</v>
       </c>
       <c r="C14" t="n">
-        <v>89.11323911448298</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>64.2229895687136</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>85.64276097997049</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>59.48409340031424</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>78.94331464619027</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>58.2775254717949</v>
+        <v>30.99868376159304</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>73.66642073586367</v>
+        <v>23.61103228713579</v>
       </c>
       <c r="D17" t="n">
-        <v>52.41649167744146</v>
+        <v>28.33323874456295</v>
       </c>
     </row>
     <row r="18">
@@ -3492,13 +3492,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>71.69703484114456</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33925240397544</v>
+        <v>24.61241494546753</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>72.81917246709867</v>
+        <v>27.68332176435156</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>19.25796296650543</v>
       </c>
     </row>
     <row r="20">
@@ -3520,13 +3520,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6.052474596681584</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>30.93487016081699</v>
       </c>
       <c r="D20" t="n">
-        <v>21.51990967709008</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>34.28224259865195</v>
+        <v>23.97437005250219</v>
       </c>
       <c r="C21" t="n">
-        <v>299.7498647728285</v>
+        <v>117.1055767949146</v>
       </c>
       <c r="D21" t="n">
-        <v>13.18547792255844</v>
+        <v>4.610455779327345</v>
       </c>
     </row>
   </sheetData>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>51.39449231732052</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>174.1806959397649</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>422.7219082422959</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>106.6128919426824</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>416.1726693072654</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1325359400733194</v>
+        <v>628.8879443864219</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>135.5273253281594</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>566.728588492035</v>
       </c>
       <c r="D4" t="n">
-        <v>1.850594422505238</v>
+        <v>441.7049818516122</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>115.3062678637879</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>562.4923471482101</v>
       </c>
       <c r="D5" t="n">
-        <v>8.590292412159592</v>
+        <v>170.4559451498525</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>64.08063615159783</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>383.7190354479787</v>
       </c>
       <c r="D6" t="n">
-        <v>24.23149683621978</v>
+        <v>54.86300695642451</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1796598298771663</v>
+        <v>24.852943133008</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2395464398362217</v>
+        <v>157.2023511425205</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>30.12296480940488</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.084831213192726</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>2.336559536107409</v>
+        <v>47.06498494159209</v>
       </c>
       <c r="D8" t="n">
-        <v>58.66433406726815</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.328124717396686</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>9.429686699290611</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>62.67968217763759</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>67.3331662957675</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10.48408373365169</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>48.51109930994763</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>69.12387410831366</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12.36707583039707</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C12" t="n">
-        <v>72.24975879863551</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>67.69346770322606</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.74799393964483</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="C13" t="n">
-        <v>87.93514186938681</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>67.90257996423064</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.06233313145306</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>92.49339646020475</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>64.83756363157211</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.241771977151972</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>89.58447801252143</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>59.48409340031424</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7.026368319294422</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>83.07647248106935</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>58.2775254717949</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -3789,13 +3789,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>76.49974461031996</v>
+        <v>23.13881164139307</v>
       </c>
       <c r="D17" t="n">
-        <v>52.41649167744146</v>
+        <v>27.86101809882023</v>
       </c>
     </row>
     <row r="18">
@@ -3803,13 +3803,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>73.3021923375881</v>
+        <v>25.68251994309656</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33925240397544</v>
+        <v>24.07736244665303</v>
       </c>
     </row>
     <row r="19">
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>73.42098380980195</v>
+        <v>27.68332176435156</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>18.65615162380213</v>
       </c>
     </row>
     <row r="20">
@@ -3831,13 +3831,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>76.66467822463341</v>
+        <v>30.93487016081699</v>
       </c>
       <c r="D20" t="n">
-        <v>21.51990967709008</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>34.65506601011424</v>
+        <v>23.04069277500962</v>
       </c>
       <c r="C21" t="n">
-        <v>314.5613683994985</v>
+        <v>115.2034638750481</v>
       </c>
       <c r="D21" t="n">
-        <v>14.21746297850841</v>
+        <v>3.686510844001539</v>
       </c>
     </row>
   </sheetData>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>11.66905321267759</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>48.37267288364884</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4682936549257286</v>
+        <v>94.19280173625597</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.07363107781851078</v>
+        <v>0.01963495408493621</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.118431619315369</v>
+        <v>2.154936210821749</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.718459393059418</v>
+        <v>0.8423395302437633</v>
       </c>
       <c r="C4" t="n">
-        <v>4.518002934943822</v>
+        <v>1.033780332571891</v>
       </c>
       <c r="D4" t="n">
-        <v>24.14706653365455</v>
+        <v>11.94590606527519</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7.731263170943634</v>
+        <v>3.387029579651497</v>
       </c>
       <c r="C5" t="n">
-        <v>14.60349710067131</v>
+        <v>6.724971774090653</v>
       </c>
       <c r="D5" t="n">
-        <v>27.36621725587985</v>
+        <v>15.19254572321939</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.10316562440393</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>19.84406634594078</v>
+        <v>8.533351045313278</v>
       </c>
       <c r="D6" t="n">
-        <v>35.82397372796611</v>
+        <v>18.43525839034661</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>23.47555110394973</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>18.44507586738907</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.10280577150543</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>26.11939767148639</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="D8" t="n">
-        <v>43.89393985687489</v>
+        <v>22.19731559302038</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.97656122828509</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>31.06249736236907</v>
+        <v>13.53437385074652</v>
       </c>
       <c r="D9" t="n">
-        <v>48.59062087399162</v>
+        <v>25.4046853427947</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14.37769512869454</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>38.29306920414684</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="D10" t="n">
-        <v>68.75670046692537</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.90565440940107</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>17.59193711239859</v>
       </c>
       <c r="D11" t="n">
-        <v>55.61895268869453</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.63134588928871</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>37.10122749119121</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>58.36391926976862</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.926851948267</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>36.68300296918207</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>60.09768571546851</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.98419422574081</v>
+        <v>4.916592502868027</v>
       </c>
       <c r="C14" t="n">
-        <v>40.25460111723197</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>63.30112847442584</v>
+        <v>31.95785126864218</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.97517856995334</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>46.58392856651115</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>58.76741757621406</v>
+        <v>31.17539834835746</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15.29268398905256</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>51.66447293598839</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>56.21094655435537</v>
+        <v>29.75873641112932</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.47216389248049</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>57.61091878061134</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D17" t="n">
-        <v>51.47205038595602</v>
+        <v>26.9165768073348</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>18.72683745850791</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>63.13619486011238</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>42.26914740634642</v>
+        <v>23.54230994783851</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>20.46158565191202</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>68.00468172547231</v>
+        <v>28.28513310705485</v>
       </c>
       <c r="D19" t="n">
-        <v>30.69237847786803</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>20.84741249968101</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>30.93487016081699</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.69112140275025</v>
+        <v>12.45010474215894</v>
       </c>
       <c r="C21" t="n">
-        <v>83.29923999459555</v>
+        <v>49.80041896863577</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1.556263092769868</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>52.36053205829938</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>175.2861438547468</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>427.1692253425339</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>106.0680219668254</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>414.1895389446868</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1030835089459151</v>
+        <v>624.2933651305467</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>134.7615621188469</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>563.9846036586652</v>
       </c>
       <c r="D4" t="n">
-        <v>1.557051858935441</v>
+        <v>438.1697083686194</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>114.5208697003904</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>559.2034923389833</v>
       </c>
       <c r="D5" t="n">
-        <v>7.584001015306612</v>
+        <v>169.0814983639069</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>63.59761628110839</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>380.9014195367903</v>
       </c>
       <c r="D6" t="n">
-        <v>22.29941735426205</v>
+        <v>54.50074205355744</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.05988660995905543</v>
+        <v>24.67328330313084</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1197732199181109</v>
+        <v>155.9447323333803</v>
       </c>
       <c r="D7" t="n">
-        <v>43.23813239043802</v>
+        <v>30.00319158948677</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7510369937488099</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>1.585522542358599</v>
+        <v>46.73119072214817</v>
       </c>
       <c r="D8" t="n">
-        <v>58.4974369575462</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>9.207811718130833</v>
       </c>
       <c r="C9" t="n">
-        <v>7.09999939711293</v>
+        <v>23.74062298409636</v>
       </c>
       <c r="D9" t="n">
-        <v>63.12343213995715</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>20.64124548178919</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>68.04493338134642</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.240209392370978</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>43.00251294141878</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>70.01235578065702</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.71617710248143</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>68.34436643114171</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>67.91043394586461</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.22766765639403</v>
+        <v>5.983752257384309</v>
       </c>
       <c r="C13" t="n">
-        <v>87.41481558613602</v>
+        <v>24.71549845441346</v>
       </c>
       <c r="D13" t="n">
-        <v>68.42290624748146</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.06233313145306</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>95.25897974306801</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>65.4521376944306</v>
+        <v>33.49428642578843</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.600109889202059</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>93.52619504507238</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>59.48409340031424</v>
+        <v>31.89207417245764</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.613052535806514</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>87.20963031594842</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>58.2775254717949</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -4411,13 +4411,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>79.80528913051897</v>
+        <v>22.66659099565036</v>
       </c>
       <c r="D17" t="n">
-        <v>52.41649167744146</v>
+        <v>27.38879745307752</v>
       </c>
     </row>
     <row r="18">
@@ -4425,13 +4425,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>75.44240233284614</v>
+        <v>25.14746744428205</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33925240397544</v>
+        <v>23.54230994783851</v>
       </c>
     </row>
     <row r="19">
@@ -4439,13 +4439,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.814490741626358</v>
+        <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>74.62460649520854</v>
+        <v>27.68332176435156</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>18.05434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -4453,13 +4453,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>4.707480241863455</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>77.33717540204248</v>
+        <v>30.93487016081699</v>
       </c>
       <c r="D20" t="n">
-        <v>21.51990967709008</v>
+        <v>9.41496048372691</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>35.02959045023105</v>
+        <v>22.11312885678554</v>
       </c>
       <c r="C21" t="n">
-        <v>329.6374280829435</v>
+        <v>113.3297853910259</v>
       </c>
       <c r="D21" t="n">
-        <v>15.26930865779303</v>
+        <v>2.764141107098192</v>
       </c>
     </row>
   </sheetData>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>9.662360905197108</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>22.72156886708818</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3102322745419921</v>
+        <v>132.1589489548886</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03436116964863836</v>
+        <v>33.26161221988194</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>164.4623754154257</v>
       </c>
       <c r="D3" t="n">
-        <v>3.59810533606456</v>
+        <v>109.9802865682489</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.429424657383356</v>
+        <v>0.3956443248114646</v>
       </c>
       <c r="C4" t="n">
-        <v>2.207950586851076</v>
+        <v>0.3445934441906304</v>
       </c>
       <c r="D4" t="n">
-        <v>20.98191193516283</v>
+        <v>10.60582044897829</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.160466844148737</v>
+        <v>2.429825568010856</v>
       </c>
       <c r="C5" t="n">
-        <v>11.51099183229385</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="D5" t="n">
-        <v>29.62423697564751</v>
+        <v>16.88606051304514</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.42517887139688</v>
+        <v>5.071708640139024</v>
       </c>
       <c r="C6" t="n">
-        <v>21.49438423677967</v>
+        <v>10.30442390377452</v>
       </c>
       <c r="D6" t="n">
-        <v>36.70951015719674</v>
+        <v>20.04532462531138</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.45641487148353</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>26.11056194214817</v>
+        <v>12.03720860177014</v>
       </c>
       <c r="D7" t="n">
-        <v>36.83026512481909</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.10280577150543</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>29.12354564648163</v>
+        <v>13.60211444233956</v>
       </c>
       <c r="D8" t="n">
-        <v>43.56014563743097</v>
+        <v>23.11524969649115</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.19843620944487</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>32.39374724932775</v>
+        <v>14.42187377538564</v>
       </c>
       <c r="D9" t="n">
-        <v>49.36718330805084</v>
+        <v>26.18124777685393</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14.94710879715769</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>38.72012945549421</v>
+        <v>16.79770321966293</v>
       </c>
       <c r="D10" t="n">
-        <v>67.19081287865171</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12.79413608174443</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>41.75863860013807</v>
+        <v>19.01350778814797</v>
       </c>
       <c r="D11" t="n">
-        <v>58.4620940401933</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.84831213192725</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>40.35572113076938</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>58.14695302713008</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.6666888066416</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>39.28463438543612</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>60.35784885709391</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.36962016288231</v>
+        <v>4.916592502868027</v>
       </c>
       <c r="C14" t="n">
-        <v>40.86917518009047</v>
+        <v>18.12993485432585</v>
       </c>
       <c r="D14" t="n">
-        <v>63.30112847442584</v>
+        <v>32.87971236292993</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12.90016483380309</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>46.58392856651115</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>59.48409340031424</v>
+        <v>31.89207417245764</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14.46605242207675</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>52.0777887194763</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>55.79763077086746</v>
+        <v>30.99868376159304</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16.05550195525234</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>57.61091878061134</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>51.94427103169875</v>
+        <v>27.86101809882023</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17.65673246087889</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>63.67124735892688</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>42.80419990516094</v>
+        <v>24.61241494546753</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>19.25796296650543</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>68.00468172547231</v>
+        <v>28.88694444975815</v>
       </c>
       <c r="D19" t="n">
-        <v>31.29418982057133</v>
+        <v>18.65615162380213</v>
       </c>
     </row>
     <row r="20">
@@ -4764,13 +4764,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>19.50241814486288</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>30.93487016081699</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>14.03373676580476</v>
+        <v>16.26644818593689</v>
       </c>
       <c r="C21" t="n">
-        <v>95.2816864625692</v>
+        <v>66.69243756234124</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7386177245160402</v>
+        <v>3.253289637187378</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>12.27282805078938</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>38.34706532788041</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2051852701875834</v>
+        <v>153.9193868195192</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01472621556370216</v>
+        <v>40.63453747877548</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>134.4552568351219</v>
       </c>
       <c r="D3" t="n">
-        <v>3.077779052813751</v>
+        <v>220.1421964617836</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.740237769002095</v>
+        <v>42.57643443777567</v>
       </c>
       <c r="C4" t="n">
-        <v>1.072068493037517</v>
+        <v>252.4210792297144</v>
       </c>
       <c r="D4" t="n">
-        <v>18.237927101793</v>
+        <v>65.66419519854792</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.417864669110648</v>
+        <v>1.644427404613408</v>
       </c>
       <c r="C5" t="n">
-        <v>7.952156404399165</v>
+        <v>1.988039101099791</v>
       </c>
       <c r="D5" t="n">
-        <v>30.4587225242573</v>
+        <v>17.7450897542611</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.700649065662736</v>
+        <v>4.588688769649592</v>
       </c>
       <c r="C6" t="n">
-        <v>20.12582793705961</v>
+        <v>7.969827863075609</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>21.49438423677967</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.75584792127881</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>28.62579956042849</v>
+        <v>13.95358012045992</v>
       </c>
       <c r="D7" t="n">
-        <v>39.04606969330414</v>
+        <v>22.27781890476862</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>32.04424506661589</v>
+        <v>15.52143120414207</v>
       </c>
       <c r="D8" t="n">
-        <v>43.72704274715294</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.19843620944487</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.83437204208531</v>
+        <v>16.41874860582365</v>
       </c>
       <c r="D9" t="n">
-        <v>50.03280825153018</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.37416904850505</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>17.79417713947344</v>
       </c>
       <c r="D10" t="n">
-        <v>65.90963212460962</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13.68261775408779</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>44.42408361716816</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>60.77214638828604</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.28224461720434</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>43.61021477034756</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>58.36391926976862</v>
+        <v>32.76190263842031</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.40652566501619</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>41.88626580169016</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>60.61801199871932</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.75504610002381</v>
+        <v>5.223879534297279</v>
       </c>
       <c r="C14" t="n">
-        <v>42.40561033723673</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>63.30112847442584</v>
+        <v>33.49428642578843</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11.82515109765283</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>46.58392856651115</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>59.84243131236433</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13.63942085510094</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>52.0777887194763</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>55.38431498737956</v>
+        <v>31.82531532856885</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15.11106066376691</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>58.55536007209676</v>
+        <v>25.02769422436394</v>
       </c>
       <c r="D17" t="n">
-        <v>51.94427103169875</v>
+        <v>28.80545939030567</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>16.58662746324986</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>63.67124735892688</v>
+        <v>27.28767743954009</v>
       </c>
       <c r="D18" t="n">
-        <v>43.33925240397544</v>
+        <v>25.68251994309656</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>18.05434028109884</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>68.6064930681756</v>
+        <v>29.48875579246144</v>
       </c>
       <c r="D19" t="n">
-        <v>31.89600116327462</v>
+        <v>19.25796296650543</v>
       </c>
     </row>
     <row r="20">
@@ -5075,13 +5075,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>18.15742379004475</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>31.60736733822606</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>12.10494919336317</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.70543307910511</v>
+        <v>19.43726220944859</v>
       </c>
       <c r="C21" t="n">
-        <v>107.6943982567207</v>
+        <v>82.81963897938964</v>
       </c>
       <c r="D21" t="n">
-        <v>1.495755531343343</v>
+        <v>5.070590141595284</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>18.59135627532185</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>84.11319805675397</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1354811831860598</v>
+        <v>240.7412267922901</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004908738521234052</v>
+        <v>49.13156385903162</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>162.518514961017</v>
       </c>
       <c r="D3" t="n">
-        <v>2.59181393921158</v>
+        <v>313.545673043825</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.382881604656256</v>
+        <v>68.85487523735006</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5232715263635499</v>
+        <v>302.5530439993736</v>
       </c>
       <c r="D4" t="n">
-        <v>16.0044510746315</v>
+        <v>152.4506922539659</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.994330497952772</v>
+        <v>33.74757733348411</v>
       </c>
       <c r="C5" t="n">
-        <v>5.056000676871074</v>
+        <v>234.0731963850458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.94330497952772</v>
+        <v>35.09748042682348</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.171086142446205</v>
+        <v>3.864158963915446</v>
       </c>
       <c r="C6" t="n">
-        <v>16.78494049950772</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="D6" t="n">
-        <v>39.32586778901449</v>
+        <v>22.90319219237384</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.57618809140164</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>29.16477905005999</v>
+        <v>13.11516758103314</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20198765183014</v>
+        <v>23.71509754378595</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>35.21529015133309</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D8" t="n">
-        <v>44.72842540548468</v>
+        <v>25.03456645829366</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.42031119060464</v>
+        <v>8.653124265231384</v>
       </c>
       <c r="C9" t="n">
-        <v>38.162496759482</v>
+        <v>18.30468594568177</v>
       </c>
       <c r="D9" t="n">
-        <v>50.03280825153018</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.65887588273663</v>
+        <v>9.110618695410402</v>
       </c>
       <c r="C10" t="n">
-        <v>41.42484438069417</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="D10" t="n">
-        <v>64.9131582047991</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14.21570675749381</v>
+        <v>8.529424054496287</v>
       </c>
       <c r="C11" t="n">
-        <v>46.02335062738621</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>62.54910973297276</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.93314334511998</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>46.86470840992573</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>58.79785175504571</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.40652566501619</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="C13" t="n">
-        <v>45.00822350119503</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>60.87817514034472</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.44775906859456</v>
+        <v>5.53116656572653</v>
       </c>
       <c r="C14" t="n">
-        <v>44.24933252581224</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>63.30112847442584</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11.10847527355266</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>47.65894230266141</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>60.20076922441442</v>
+        <v>33.32542582065798</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12.39947350463721</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>52.0777887194763</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>54.97099920389165</v>
+        <v>32.23863111205676</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14.16661937228147</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>58.55536007209676</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="D17" t="n">
-        <v>51.94427103169875</v>
+        <v>29.7499006817911</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>15.51652246562084</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>63.67124735892688</v>
+        <v>27.82272993835461</v>
       </c>
       <c r="D18" t="n">
-        <v>43.87430490278995</v>
+        <v>26.21757244191107</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>16.85071759569225</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>68.6064930681756</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>32.49781250597791</v>
+        <v>20.46158565191202</v>
       </c>
     </row>
     <row r="20">
@@ -5386,13 +5386,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>16.81242943522663</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17.41431485354125</v>
+        <v>22.67029837303515</v>
       </c>
       <c r="C21" t="n">
-        <v>120.3859157266548</v>
+        <v>96.78473536180393</v>
       </c>
       <c r="D21" t="n">
-        <v>2.271432372201033</v>
+        <v>6.10354186966331</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>31.66921744359361</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>112.8401176307199</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08933904108645974</v>
+        <v>238.5352397008475</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>62.27716561889642</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>255.4114827368502</v>
       </c>
       <c r="D3" t="n">
-        <v>2.154936210821749</v>
+        <v>420.3647320043992</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.191440802328128</v>
+        <v>87.20766682053993</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2552544031041707</v>
+        <v>348.7668536813836</v>
       </c>
       <c r="D4" t="n">
-        <v>14.00070401026376</v>
+        <v>231.9752015410703</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.963495408493621</v>
+        <v>62.34097921967247</v>
       </c>
       <c r="C5" t="n">
-        <v>3.067961575771283</v>
+        <v>358.1170188166303</v>
       </c>
       <c r="D5" t="n">
-        <v>28.86338250485623</v>
+        <v>66.04707680320418</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6.520768251607316</v>
+        <v>18.79752329321368</v>
       </c>
       <c r="C6" t="n">
-        <v>13.00128484734051</v>
+        <v>134.4405306195582</v>
       </c>
       <c r="D6" t="n">
-        <v>40.29190752999335</v>
+        <v>27.29062268265284</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.5581157220977</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>27.36818075128833</v>
+        <v>11.79766216193392</v>
       </c>
       <c r="D7" t="n">
-        <v>43.29801900039708</v>
+        <v>24.852943133008</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>37.30150402285756</v>
+        <v>17.60764507566654</v>
       </c>
       <c r="D8" t="n">
-        <v>45.98015372839936</v>
+        <v>25.86905200690345</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.64218617176442</v>
+        <v>9.207811718130833</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3796839862988</v>
+        <v>19.96874830438012</v>
       </c>
       <c r="D9" t="n">
-        <v>50.14374574211007</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.80122929985241</v>
+        <v>9.680032363873552</v>
       </c>
       <c r="C10" t="n">
-        <v>44.12955930589413</v>
+        <v>20.64124548178919</v>
       </c>
       <c r="D10" t="n">
-        <v>64.05903770210438</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14.74879576089983</v>
+        <v>9.240209392370978</v>
       </c>
       <c r="C11" t="n">
-        <v>47.80031397207294</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>63.97068040872215</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12.36707583039707</v>
+        <v>8.027750977626168</v>
       </c>
       <c r="C12" t="n">
-        <v>49.68526956422682</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>59.88268296823844</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.6666888066416</v>
+        <v>6.764241682260525</v>
       </c>
       <c r="C13" t="n">
-        <v>48.13018120069988</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
-        <v>60.35784885709391</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10.14047203716531</v>
+        <v>5.838453597155781</v>
       </c>
       <c r="C14" t="n">
-        <v>47.01491580867551</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>63.30112847442584</v>
+        <v>34.72343455150544</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.39179944945249</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>48.37561812676158</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>60.5591071364645</v>
+        <v>33.68376373270807</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11.5728419376614</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>52.49110450296421</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
-        <v>54.97099920389165</v>
+        <v>32.65194689554467</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12.74995743505333</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>58.55536007209676</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="D17" t="n">
-        <v>51.94427103169875</v>
+        <v>30.22212132753381</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14.44641746799181</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>63.67124735892688</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>44.40935740160447</v>
+        <v>26.75262494072559</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>15.64709491028566</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>68.6064930681756</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>33.09962384868121</v>
+        <v>21.06339699461531</v>
       </c>
     </row>
     <row r="20">
@@ -5697,13 +5697,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>15.46743508040849</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19.16047884520369</v>
+        <v>24.97755918552569</v>
       </c>
       <c r="C21" t="n">
-        <v>133.3569327626176</v>
+        <v>107.9387379088789</v>
       </c>
       <c r="D21" t="n">
-        <v>3.06567661523259</v>
+        <v>7.136445481578768</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>30.21328559819559</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>125.4820828183061</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05890486225480862</v>
+        <v>284.8275891991973</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>82.44717220264714</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>332.6063047217769</v>
       </c>
       <c r="D3" t="n">
-        <v>1.776963344686727</v>
+        <v>489.8724694650734</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.08933904108645975</v>
+        <v>103.7609148618454</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1276272015520853</v>
+        <v>431.0736359623235</v>
       </c>
       <c r="D4" t="n">
-        <v>12.20116046837936</v>
+        <v>311.7804906715893</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.227184630308513</v>
+        <v>83.39946747576656</v>
       </c>
       <c r="C5" t="n">
-        <v>1.84077694546277</v>
+        <v>433.1225434210867</v>
       </c>
       <c r="D5" t="n">
-        <v>27.68528525976006</v>
+        <v>96.43216824964297</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.950953672516666</v>
+        <v>35.66296710446964</v>
       </c>
       <c r="C6" t="n">
-        <v>9.418887474543901</v>
+        <v>244.4483061235261</v>
       </c>
       <c r="D6" t="n">
-        <v>40.37241084174159</v>
+        <v>33.77113927838603</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.24061030299848</v>
+        <v>10.59992996275281</v>
       </c>
       <c r="C7" t="n">
-        <v>23.95464398362217</v>
+        <v>55.15556777229006</v>
       </c>
       <c r="D7" t="n">
-        <v>45.27427712904591</v>
+        <v>26.11056194214817</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>37.55184968744049</v>
+        <v>17.27385085622263</v>
       </c>
       <c r="D8" t="n">
-        <v>47.398779161036</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.64218617176442</v>
+        <v>9.540624189870499</v>
       </c>
       <c r="C9" t="n">
-        <v>44.48593372253571</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>50.47655821384974</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16.08593613408399</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>47.26133448244146</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>63.34727061652544</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.10418842983717</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="C11" t="n">
-        <v>50.11036632016568</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>65.03685841553418</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.0179745583127</v>
+        <v>8.461683462903258</v>
       </c>
       <c r="C12" t="n">
-        <v>52.939763203805</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>61.18448042406971</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.6666888066416</v>
+        <v>7.024404823885929</v>
       </c>
       <c r="C13" t="n">
-        <v>51.25213890020473</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>60.09768571546851</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9.833185005736054</v>
+        <v>6.145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>49.47321206010952</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>63.30112847442584</v>
+        <v>35.33800861436394</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.0334615374024</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>49.80896977496192</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>60.91744504851458</v>
+        <v>34.04210164475815</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10.74621037068559</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>52.90442028645212</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>55.38431498737956</v>
+        <v>32.65194689554467</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11.8055161435679</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>58.55536007209676</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="D17" t="n">
-        <v>51.47205038595602</v>
+        <v>30.22212132753381</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13.37631247036279</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>63.67124735892688</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>44.94440990041898</v>
+        <v>26.75262494072559</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14.44347222487907</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>68.6064930681756</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>33.7014351913845</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>14.79493790299943</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>16.81242943522663</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20.94414534754896</v>
+        <v>26.27511810493557</v>
       </c>
       <c r="C21" t="n">
-        <v>145.8333083458965</v>
+        <v>115.9729350838535</v>
       </c>
       <c r="D21" t="n">
-        <v>3.878545434731288</v>
+        <v>8.154346998083451</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>37.11202671593792</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>131.6828013183289</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0382881604656256</v>
+        <v>344.1467489851981</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>91.36635009572942</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>376.8242213210532</v>
       </c>
       <c r="D3" t="n">
-        <v>1.45298660228528</v>
+        <v>536.5840252331367</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0382881604656256</v>
+        <v>119.1655180891821</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06381360077604267</v>
+        <v>496.1252205934214</v>
       </c>
       <c r="D4" t="n">
-        <v>10.58029500866788</v>
+        <v>359.8704202164151</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7608544707912782</v>
+        <v>97.31574118346511</v>
       </c>
       <c r="C5" t="n">
-        <v>1.079922474671491</v>
+        <v>496.8134257340985</v>
       </c>
       <c r="D5" t="n">
-        <v>26.18812001078367</v>
+        <v>121.5894531709675</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.582397372796612</v>
+        <v>47.77871552257953</v>
       </c>
       <c r="C6" t="n">
-        <v>6.561019907481435</v>
+        <v>309.6559886395993</v>
       </c>
       <c r="D6" t="n">
-        <v>40.13090090649688</v>
+        <v>39.9698942830004</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>19.70269467652924</v>
+        <v>98.333813552769</v>
       </c>
       <c r="D7" t="n">
-        <v>46.95110220789945</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.35176877775662</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>35.79943003535994</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>49.06775025825559</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.64218617176442</v>
+        <v>9.762499171030278</v>
       </c>
       <c r="C9" t="n">
-        <v>46.92655851529327</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>51.47499562906875</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16.08593613408399</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="C10" t="n">
-        <v>50.67781649322036</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
-        <v>62.20844327959914</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.45958109877452</v>
+        <v>9.950994730245668</v>
       </c>
       <c r="C11" t="n">
-        <v>52.95350767166445</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>65.92534008787754</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.4519070435898</v>
+        <v>8.678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>55.326391872829</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>62.48627787990098</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.18701508989241</v>
+        <v>7.284567965511334</v>
       </c>
       <c r="C13" t="n">
-        <v>54.63425974133501</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>60.09768571546851</v>
+        <v>35.38218726105505</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9.525897974306801</v>
+        <v>6.145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>52.23879534297279</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>63.30112847442584</v>
+        <v>35.33800861436394</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9.675123625352315</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>51.60065933521235</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>61.27578296056467</v>
+        <v>34.04210164475815</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9.919578803709772</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>53.73105185342793</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>55.79763077086746</v>
+        <v>32.65194689554467</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10.86107485208246</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>58.55536007209676</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="D17" t="n">
-        <v>50.99982974021331</v>
+        <v>30.22212132753381</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12.30620747273377</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>63.67124735892688</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>44.94440990041898</v>
+        <v>26.75262494072559</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13.23984953947248</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>69.2083044108789</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>34.3032465340878</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
+        <v>8.742463306317845</v>
+      </c>
+      <c r="C20" t="n">
+        <v>32.27986451563512</v>
+      </c>
+      <c r="D20" t="n">
         <v>13.4499435481813</v>
-      </c>
-      <c r="C20" t="n">
-        <v>75.99218104722434</v>
-      </c>
-      <c r="D20" t="n">
-        <v>17.48492661263569</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>22.7652335355476</v>
+        <v>27.43624379723887</v>
       </c>
       <c r="C21" t="n">
-        <v>158.5716266958833</v>
+        <v>120.719472707851</v>
       </c>
       <c r="D21" t="n">
-        <v>3.925040264749586</v>
+        <v>8.230873139171662</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>43.48455106420397</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>128.4626688483994</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02454369260617026</v>
+        <v>369.1292828151667</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>97.95878592974674</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>399.3504223949963</v>
       </c>
       <c r="D3" t="n">
-        <v>1.183005983617406</v>
+        <v>572.1036571727863</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01276272015520854</v>
+        <v>127.4485234699124</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02552544031041707</v>
+        <v>534.8090253838584</v>
       </c>
       <c r="D4" t="n">
-        <v>9.138107631129312</v>
+        <v>390.9221183540374</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.466330159517235</v>
+        <v>106.5441696033851</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6135923151542566</v>
+        <v>533.3835277172922</v>
       </c>
       <c r="D5" t="n">
-        <v>24.49460522095793</v>
+        <v>138.6964069174682</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.576105975943631</v>
+        <v>55.58753676215866</v>
       </c>
       <c r="C6" t="n">
-        <v>4.467933802027235</v>
+        <v>350.0283994813408</v>
       </c>
       <c r="D6" t="n">
-        <v>39.9698942830004</v>
+        <v>44.71958967614647</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.006733365209485</v>
+        <v>19.76258128648829</v>
       </c>
       <c r="C7" t="n">
-        <v>15.57051858935441</v>
+        <v>127.3189327729519</v>
       </c>
       <c r="D7" t="n">
-        <v>47.72962813736718</v>
+        <v>28.26647990067416</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>32.46148784092078</v>
+        <v>34.88149593188918</v>
       </c>
       <c r="D8" t="n">
-        <v>50.73672135547515</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.30937370002476</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>47.14843349645305</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>52.69530802544753</v>
+        <v>29.62030998483051</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16.22828955119978</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="C10" t="n">
-        <v>53.95194508688347</v>
+        <v>22.49183990429443</v>
       </c>
       <c r="D10" t="n">
-        <v>61.35432277690443</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.45958109877452</v>
+        <v>9.950994730245668</v>
       </c>
       <c r="C11" t="n">
-        <v>56.32973802656922</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>66.45842909128358</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.88583952886689</v>
+        <v>8.678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>58.14695302713008</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>63.78807533573226</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.44717823151781</v>
+        <v>7.544731107136739</v>
       </c>
       <c r="C13" t="n">
-        <v>58.01638058246527</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>60.87817514034472</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9.525897974306801</v>
+        <v>6.145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>55.3116656572653</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>62.68655441156734</v>
+        <v>35.33800861436394</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8.958447801252145</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>53.75068680751286</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>61.63412087261475</v>
+        <v>34.04210164475815</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9.506263020221864</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>54.97099920389165</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>56.21094655435537</v>
+        <v>32.65194689554467</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.916633560597033</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>59.4998013635822</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="D17" t="n">
-        <v>50.52760909447059</v>
+        <v>30.22212132753381</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11.23610247510475</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>63.67124735892688</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>44.94440990041898</v>
+        <v>26.75262494072559</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12.03622685406589</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>69.2083044108789</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9050578767911</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>12.77744637077223</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>75.99218104722434</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>18.15742379004475</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>24.62407338748729</v>
+        <v>27.57372025309666</v>
       </c>
       <c r="C21" t="n">
-        <v>171.5741887644275</v>
+        <v>123.1626171304984</v>
       </c>
       <c r="D21" t="n">
-        <v>4.765949687900765</v>
+        <v>8.272116075928999</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -475,7 +475,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3530934158139993</v>
+        <v>0.7233399275165989</v>
       </c>
     </row>
     <row r="3">
@@ -483,13 +483,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.05713771638716436</v>
+        <v>0.1518272824617692</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.286053525462432</v>
+        <v>4.683162351229262</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.881735459683946</v>
+        <v>5.000178502407599</v>
       </c>
       <c r="C4" t="n">
-        <v>3.729458270154262</v>
+        <v>8.871941102292437</v>
       </c>
       <c r="D4" t="n">
-        <v>13.77064321674597</v>
+        <v>28.21025717314736</v>
       </c>
     </row>
     <row r="5">
@@ -511,13 +511,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.009253063057324</v>
+        <v>7.996236876319848</v>
       </c>
       <c r="C5" t="n">
-        <v>5.216025552663305</v>
+        <v>12.40830923397544</v>
       </c>
       <c r="D5" t="n">
-        <v>11.65660956052626</v>
+        <v>23.87949119686208</v>
       </c>
     </row>
     <row r="6">
@@ -525,13 +525,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.654528340123033</v>
+        <v>9.710872986254762</v>
       </c>
       <c r="C6" t="n">
-        <v>7.983996445943297</v>
+        <v>18.9929853341384</v>
       </c>
       <c r="D6" t="n">
-        <v>18.00323736784969</v>
+        <v>36.88106271453223</v>
       </c>
     </row>
     <row r="7">
@@ -539,13 +539,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.647200932822702</v>
+        <v>12.34861897355723</v>
       </c>
       <c r="C7" t="n">
-        <v>7.84837978157405</v>
+        <v>18.67036929405504</v>
       </c>
       <c r="D7" t="n">
-        <v>16.01595519422986</v>
+        <v>32.80995722504777</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.374754521485928</v>
+        <v>14.28188637023709</v>
       </c>
       <c r="C8" t="n">
-        <v>10.64069212743314</v>
+        <v>25.31295083730989</v>
       </c>
       <c r="D8" t="n">
-        <v>21.9325333284465</v>
+        <v>44.93053780535797</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +567,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.681774517539622</v>
+        <v>15.09770496799833</v>
       </c>
       <c r="C9" t="n">
-        <v>11.78821774901906</v>
+        <v>28.04277886878448</v>
       </c>
       <c r="D9" t="n">
-        <v>24.04204014600192</v>
+        <v>49.25203019282893</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +581,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.412846332410704</v>
+        <v>14.38310455854494</v>
       </c>
       <c r="C10" t="n">
-        <v>16.13490570957182</v>
+        <v>38.38303656376402</v>
       </c>
       <c r="D10" t="n">
-        <v>34.7887551350075</v>
+        <v>71.26753003801363</v>
       </c>
     </row>
     <row r="11">
@@ -595,13 +595,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.412555377526079</v>
+        <v>11.7251149335809</v>
       </c>
       <c r="C11" t="n">
-        <v>13.53210895879283</v>
+        <v>32.19129025601027</v>
       </c>
       <c r="D11" t="n">
-        <v>27.03880734175663</v>
+        <v>55.3911459879057</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.209145107187775</v>
+        <v>11.184609808017</v>
       </c>
       <c r="C12" t="n">
-        <v>14.6013941970888</v>
+        <v>34.73499364897523</v>
       </c>
       <c r="D12" t="n">
-        <v>29.01250899938361</v>
+        <v>59.4344307109472</v>
       </c>
     </row>
     <row r="13">
@@ -623,13 +623,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.239618555927597</v>
+        <v>11.26558435866328</v>
       </c>
       <c r="C13" t="n">
-        <v>14.28321663837635</v>
+        <v>33.97808678570274</v>
       </c>
       <c r="D13" t="n">
-        <v>29.99030615086853</v>
+        <v>61.43752589483933</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +637,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.769094727781986</v>
+        <v>12.67251717614234</v>
       </c>
       <c r="C14" t="n">
-        <v>16.32615997983614</v>
+        <v>38.83800790234312</v>
       </c>
       <c r="D14" t="n">
-        <v>31.17181104224615</v>
+        <v>63.85793257537565</v>
       </c>
     </row>
     <row r="15">
@@ -651,13 +651,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.561404395017331</v>
+        <v>14.77785549294554</v>
       </c>
       <c r="C15" t="n">
-        <v>19.03849326722106</v>
+        <v>45.29032870401034</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74133002433302</v>
+        <v>60.92747851005198</v>
       </c>
     </row>
     <row r="16">
@@ -665,13 +665,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.093927911745703</v>
+        <v>16.19288576548923</v>
       </c>
       <c r="C16" t="n">
-        <v>21.22748532415542</v>
+        <v>50.49768247920203</v>
       </c>
       <c r="D16" t="n">
-        <v>28.5869861649411</v>
+        <v>58.56271336240157</v>
       </c>
     </row>
     <row r="17">
@@ -679,13 +679,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.962421200830602</v>
+        <v>18.50066045890812</v>
       </c>
       <c r="C17" t="n">
-        <v>23.41647738108979</v>
+        <v>55.70503625439373</v>
       </c>
       <c r="D17" t="n">
-        <v>26.12891277023595</v>
+        <v>53.52715463622832</v>
       </c>
     </row>
     <row r="18">
@@ -693,13 +693,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.473613303441098</v>
+        <v>19.85900854599942</v>
       </c>
       <c r="C18" t="n">
-        <v>25.58460533581351</v>
+        <v>60.86275679264952</v>
       </c>
       <c r="D18" t="n">
-        <v>22.20414364830342</v>
+        <v>45.4869531342169</v>
       </c>
     </row>
     <row r="19">
@@ -707,13 +707,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.40610083487962</v>
+        <v>22.33682979577549</v>
       </c>
       <c r="C19" t="n">
-        <v>27.71100508611591</v>
+        <v>65.92121085703351</v>
       </c>
       <c r="D19" t="n">
-        <v>16.64971260722935</v>
+        <v>34.10825965905193</v>
       </c>
     </row>
     <row r="20">
@@ -721,13 +721,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.349724954710952</v>
+        <v>22.18702687707988</v>
       </c>
       <c r="C20" t="n">
-        <v>30.96580503097781</v>
+        <v>73.66399581903417</v>
       </c>
       <c r="D20" t="n">
-        <v>9.302653455099595</v>
+        <v>19.05722501341808</v>
       </c>
     </row>
     <row r="21">
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.696360434126415</v>
+        <v>23.10811239068127</v>
       </c>
       <c r="C21" t="n">
-        <v>33.07829537980645</v>
+        <v>78.68936105879422</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.39208685355552</v>
+        <v>37.45465666472006</v>
       </c>
       <c r="C2" t="n">
-        <v>142.8138567890793</v>
+        <v>107.7752812245106</v>
       </c>
       <c r="D2" t="n">
-        <v>377.2444093384709</v>
+        <v>275.3331071514265</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>102.7349885109075</v>
+        <v>96.80523237725674</v>
       </c>
       <c r="C3" t="n">
-        <v>409.0648159285185</v>
+        <v>346.0415220543945</v>
       </c>
       <c r="D3" t="n">
-        <v>597.5701926209485</v>
+        <v>354.3765600634499</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>132.5280860916854</v>
+        <v>105.330729440936</v>
       </c>
       <c r="C4" t="n">
-        <v>554.9485977887775</v>
+        <v>512.1807225486738</v>
       </c>
       <c r="D4" t="n">
-        <v>412.8484715806857</v>
+        <v>50.71904989679872</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>112.0665004397734</v>
+        <v>53.16163818496479</v>
       </c>
       <c r="C5" t="n">
-        <v>553.1657439578654</v>
+        <v>474.5032091550897</v>
       </c>
       <c r="D5" t="n">
-        <v>150.9437095279471</v>
+        <v>25.28000338435537</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.33723215530473</v>
+        <v>13.4038014060817</v>
       </c>
       <c r="C6" t="n">
-        <v>370.9995121917569</v>
+        <v>257.7313525619854</v>
       </c>
       <c r="D6" t="n">
-        <v>48.3422387048172</v>
+        <v>33.00635781677777</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.45747873464579</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>143.0092245822244</v>
+        <v>92.28526594690442</v>
       </c>
       <c r="D7" t="n">
-        <v>28.98511922018283</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>40.55599766243574</v>
+        <v>45.89670517353839</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>41.0566889916016</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>22.85312305945724</v>
+        <v>42.93280885441725</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.2494460323367</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>45.69544689416779</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>39.57424995818893</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.950994730245668</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>47.44492130313559</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.678649705541803</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>42.95931604243193</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.544731107136739</v>
+        <v>6.764241682260525</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>40.84561323518855</v>
       </c>
       <c r="D13" t="n">
-        <v>36.16267668593127</v>
+        <v>20.03256190515617</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.145740628585034</v>
+        <v>7.067601722872788</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>44.24933252581224</v>
       </c>
       <c r="D14" t="n">
-        <v>35.33800861436394</v>
+        <v>9.21861094287755</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>5.733406592801372</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>50.16730768701201</v>
       </c>
       <c r="D15" t="n">
-        <v>34.04210164475815</v>
+        <v>1.791689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>53.73105185342793</v>
       </c>
       <c r="D16" t="n">
-        <v>32.65194689554467</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>25.49991487010665</v>
+        <v>59.02758071783948</v>
       </c>
       <c r="D17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>58.32072237078177</v>
       </c>
       <c r="D18" t="n">
-        <v>26.75262494072559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30.09056713516474</v>
+        <v>40.32135996112075</v>
       </c>
       <c r="D19" t="n">
-        <v>21.66520833731861</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1032,13 +1032,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27986451563512</v>
+        <v>12.10494919336317</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>27.64282800432414</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>124.3927260194586</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.292848401297242</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46.245225608546</v>
+        <v>33.35291475637689</v>
       </c>
       <c r="C2" t="n">
-        <v>145.342838875219</v>
+        <v>105.12358067534</v>
       </c>
       <c r="D2" t="n">
-        <v>378.8456398440974</v>
+        <v>252.9129348295421</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>105.2188102026519</v>
+        <v>94.67974859756239</v>
       </c>
       <c r="C3" t="n">
-        <v>415.1614691718912</v>
+        <v>356.6443972602601</v>
       </c>
       <c r="D3" t="n">
-        <v>610.4556312391879</v>
+        <v>363.1632020164589</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>135.2082573242792</v>
+        <v>102.9568634920673</v>
       </c>
       <c r="C4" t="n">
-        <v>565.1204857524788</v>
+        <v>565.9628252827224</v>
       </c>
       <c r="D4" t="n">
-        <v>424.2455806792869</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>114.9135687820892</v>
+        <v>52.94074495150926</v>
       </c>
       <c r="C5" t="n">
-        <v>563.4250074672445</v>
+        <v>532.8926538651688</v>
       </c>
       <c r="D5" t="n">
-        <v>157.3496132981575</v>
+        <v>24.98547907308133</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.792583163626</v>
+        <v>12.43776166510284</v>
       </c>
       <c r="C6" t="n">
-        <v>381.7064526542727</v>
+        <v>307.0396310077815</v>
       </c>
       <c r="D6" t="n">
-        <v>50.31456984264904</v>
+        <v>32.32207966691774</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.77498415374501</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>151.1538035366559</v>
+        <v>115.9404768807313</v>
       </c>
       <c r="D7" t="n">
-        <v>29.40432548989622</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>43.72704274715294</v>
+        <v>50.31947858117027</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>44.26405874137593</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>39.04999668412111</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.2494460323367</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>45.55309347705201</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.950994730245668</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>46.37874329632356</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>31.98534020436108</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.678649705541803</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>42.30841731451629</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.544731107136739</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>40.58545009356315</v>
       </c>
       <c r="D13" t="n">
-        <v>36.16267668593127</v>
+        <v>13.52848336452105</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.145740628585034</v>
+        <v>5.53116656572653</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>44.24933252581224</v>
       </c>
       <c r="D14" t="n">
-        <v>35.33800861436394</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>49.80896977496192</v>
       </c>
       <c r="D15" t="n">
-        <v>34.04210164475815</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>53.73105185342793</v>
       </c>
       <c r="D16" t="n">
-        <v>32.65194689554467</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>25.49991487010665</v>
+        <v>57.61091878061134</v>
       </c>
       <c r="D17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>52.43514488382214</v>
       </c>
       <c r="D18" t="n">
-        <v>26.75262494072559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1329,13 +1329,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30.09056713516474</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>21.66520833731861</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1343,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27986451563512</v>
+        <v>7.397468951499714</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>27.6710782261364</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>124.5198520176138</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.301323467840922</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46.81758452012189</v>
+        <v>28.44024924432585</v>
       </c>
       <c r="C2" t="n">
-        <v>146.6888149777414</v>
+        <v>177.824943417929</v>
       </c>
       <c r="D2" t="n">
-        <v>394.3052209428719</v>
+        <v>270.5470870932233</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>106.4754472640878</v>
+        <v>90.49750337747099</v>
       </c>
       <c r="C3" t="n">
-        <v>418.2736093943536</v>
+        <v>362.5054310546135</v>
       </c>
       <c r="D3" t="n">
-        <v>623.291982472215</v>
+        <v>359.6289102811704</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>136.5866311010417</v>
+        <v>99.67684441217867</v>
       </c>
       <c r="C4" t="n">
-        <v>570.2510992548725</v>
+        <v>611.6406007182138</v>
       </c>
       <c r="D4" t="n">
-        <v>435.8724187406819</v>
+        <v>44.69504598354029</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>116.3616466458532</v>
+        <v>50.5109193834984</v>
       </c>
       <c r="C5" t="n">
-        <v>568.6528139923588</v>
+        <v>590.9139431861553</v>
       </c>
       <c r="D5" t="n">
-        <v>163.9273229166112</v>
+        <v>24.42097414313941</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.0403844957237</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="C6" t="n">
-        <v>387.1001745414047</v>
+        <v>358.3202405914095</v>
       </c>
       <c r="D6" t="n">
-        <v>52.36740429222912</v>
+        <v>31.87931145230244</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.43373686329462</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>155.2859796238307</v>
+        <v>137.0205635863188</v>
       </c>
       <c r="D7" t="n">
-        <v>29.8235317596096</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>45.39601384437251</v>
+        <v>53.82431788533138</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>23.74062298409636</v>
+        <v>44.92968368485526</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.2494460323367</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.950994730245668</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>45.31256528951153</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>26.83214650476957</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.678649705541803</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>41.65751858660066</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>18.00819813899924</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.544731107136739</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>40.32528695193774</v>
       </c>
       <c r="D13" t="n">
-        <v>36.16267668593127</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.145740628585034</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>44.24933252581224</v>
       </c>
       <c r="D14" t="n">
-        <v>35.33800861436394</v>
+        <v>1.84372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>1.791689560250429</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>49.45063186291183</v>
       </c>
       <c r="D15" t="n">
-        <v>34.04210164475815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>53.31773606994002</v>
       </c>
       <c r="D16" t="n">
-        <v>32.65194689554467</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>25.49991487010665</v>
+        <v>54.77759490615504</v>
       </c>
       <c r="D17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>44.94440990041898</v>
       </c>
       <c r="D18" t="n">
-        <v>26.75262494072559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +1640,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30.09056713516474</v>
+        <v>23.47064236542849</v>
       </c>
       <c r="D19" t="n">
-        <v>21.66520833731861</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1654,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27986451563512</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>27.67982249023297</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>124.5592012060484</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.303946747069892</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.09247387731099</v>
+        <v>31.15281815115979</v>
       </c>
       <c r="C2" t="n">
-        <v>151.1204241147115</v>
+        <v>165.302751450261</v>
       </c>
       <c r="D2" t="n">
-        <v>397.2475188124996</v>
+        <v>264.6075134825301</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>105.9354860267521</v>
+        <v>84.25358797846127</v>
       </c>
       <c r="C3" t="n">
-        <v>416.2806615547325</v>
+        <v>405.825048504504</v>
       </c>
       <c r="D3" t="n">
-        <v>618.7317643859885</v>
+        <v>357.0518225575225</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>135.8208678917292</v>
+        <v>93.66560321907544</v>
       </c>
       <c r="C4" t="n">
-        <v>567.4943517013475</v>
+        <v>637.0256511069236</v>
       </c>
       <c r="D4" t="n">
-        <v>432.3626706979995</v>
+        <v>41.67028130675587</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>115.5762484824558</v>
+        <v>45.77398671050754</v>
       </c>
       <c r="C5" t="n">
-        <v>565.3148717979196</v>
+        <v>640.467658558013</v>
       </c>
       <c r="D5" t="n">
-        <v>162.601963515878</v>
+        <v>24.1019061392592</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.55736462523426</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>384.2423069743422</v>
+        <v>402.1945454941994</v>
       </c>
       <c r="D6" t="n">
-        <v>52.00513938936205</v>
+        <v>31.03402667894593</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.25407703341745</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>154.0283608146906</v>
+        <v>153.7888143748544</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>45.06221962492859</v>
+        <v>55.57673753741193</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>35.13184159647211</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.62968549351647</v>
+        <v>44.70780870369548</v>
       </c>
       <c r="D9" t="n">
-        <v>29.62030998483051</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>22.49183990429443</v>
+        <v>44.4142661401257</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.773298395776996</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>44.42408361716816</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>21.85664913964673</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.461683462903258</v>
+        <v>4.556291095409447</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>40.78965361604648</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>12.36707583039707</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.284567965511334</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>40.06512381031234</v>
       </c>
       <c r="D13" t="n">
-        <v>35.90251354430586</v>
+        <v>4.422773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5.838453597155781</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>44.24933252581224</v>
       </c>
       <c r="D14" t="n">
-        <v>35.03072158293469</v>
+        <v>0.6145740628585034</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>48.73395603881167</v>
       </c>
       <c r="D15" t="n">
-        <v>33.68376373270807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>52.49110450296421</v>
       </c>
       <c r="D16" t="n">
-        <v>32.23863111205676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>25.02769422436394</v>
+        <v>50.99982974021331</v>
       </c>
       <c r="D17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27.82272993835461</v>
+        <v>37.98872741583033</v>
       </c>
       <c r="D18" t="n">
-        <v>26.21757244191107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>29.48875579246144</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>21.06339699461531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27986451563512</v>
+        <v>2.68998870963626</v>
       </c>
       <c r="D20" t="n">
-        <v>12.77744637077223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>26.75016515294236</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>122.6817919083219</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.379355904259961</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48.63872651149973</v>
+        <v>28.70335762906399</v>
       </c>
       <c r="C2" t="n">
-        <v>154.5202164145182</v>
+        <v>262.0166812910227</v>
       </c>
       <c r="D2" t="n">
-        <v>401.9756157561523</v>
+        <v>234.5954861637051</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>105.3955247894163</v>
+        <v>79.59519512181015</v>
       </c>
       <c r="C3" t="n">
-        <v>414.2975311921539</v>
+        <v>432.690574431218</v>
       </c>
       <c r="D3" t="n">
-        <v>614.2059074694107</v>
+        <v>340.263936814902</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>135.0551046824167</v>
+        <v>86.05902200657115</v>
       </c>
       <c r="C4" t="n">
-        <v>564.7503668679777</v>
+        <v>667.9241966026835</v>
       </c>
       <c r="D4" t="n">
-        <v>428.8784480956276</v>
+        <v>39.0411609547829</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>114.7908503190583</v>
+        <v>41.55247158224626</v>
       </c>
       <c r="C5" t="n">
-        <v>562.0014732960867</v>
+        <v>683.7872760079035</v>
       </c>
       <c r="D5" t="n">
-        <v>161.2766041151448</v>
+        <v>23.51285751671111</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.07434475474484</v>
+        <v>9.45913913041802</v>
       </c>
       <c r="C6" t="n">
-        <v>381.4246910631538</v>
+        <v>442.8084662711856</v>
       </c>
       <c r="D6" t="n">
-        <v>51.6831261423691</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.07441720354028</v>
+        <v>7.066619975168541</v>
       </c>
       <c r="C7" t="n">
-        <v>152.7707420055504</v>
+        <v>168.6406936447001</v>
       </c>
       <c r="D7" t="n">
-        <v>29.58398531977338</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>44.72842540548468</v>
+        <v>55.15949476310704</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>44.37499623195582</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>30.50780990946962</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.595602061308321</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>43.5356019448248</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.244717220264713</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>39.92178864549229</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>8.027750977626168</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.024404823885929</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>39.54479752706153</v>
       </c>
       <c r="D13" t="n">
-        <v>35.64235040268046</v>
+        <v>2.081305133003238</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5.53116656572653</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>43.94204549438299</v>
       </c>
       <c r="D14" t="n">
-        <v>34.72343455150544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>48.37561812676158</v>
       </c>
       <c r="D15" t="n">
-        <v>33.32542582065798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>50.83784136901258</v>
       </c>
       <c r="D16" t="n">
-        <v>31.82531532856885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>24.55547357862122</v>
+        <v>45.80540263704344</v>
       </c>
       <c r="D17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27.28767743954009</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>25.68251994309656</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28.88694444975815</v>
+        <v>12.03622685406589</v>
       </c>
       <c r="D19" t="n">
-        <v>20.46158565191202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2276,13 +2276,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27986451563512</v>
+        <v>1.34499435481813</v>
       </c>
       <c r="D20" t="n">
-        <v>12.10494919336317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>25.82668722485405</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>120.8320009448529</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.456671806213513</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50.05538844872788</v>
+        <v>29.80978729175015</v>
       </c>
       <c r="C2" t="n">
-        <v>161.4876798715578</v>
+        <v>214.7720365195535</v>
       </c>
       <c r="D2" t="n">
-        <v>404.7873411811152</v>
+        <v>209.9271115990954</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>106.7699715753619</v>
+        <v>74.49501579824798</v>
       </c>
       <c r="C3" t="n">
-        <v>417.8760015741336</v>
+        <v>499.6114066912018</v>
       </c>
       <c r="D3" t="n">
-        <v>628.1614510852792</v>
+        <v>324.3939851757523</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>136.4334784591792</v>
+        <v>77.83983022661685</v>
       </c>
       <c r="C4" t="n">
-        <v>569.8682176502163</v>
+        <v>704.310711765183</v>
       </c>
       <c r="D4" t="n">
-        <v>440.5563370376434</v>
+        <v>36.25888796094745</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>116.2389281828224</v>
+        <v>36.98734475749859</v>
       </c>
       <c r="C5" t="n">
-        <v>567.229279821201</v>
+        <v>716.4794745593223</v>
       </c>
       <c r="D5" t="n">
-        <v>167.9034011188108</v>
+        <v>23.12015843501239</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.32214608684252</v>
+        <v>8.493099389439159</v>
       </c>
       <c r="C6" t="n">
-        <v>386.8184129502858</v>
+        <v>468.3280160953773</v>
       </c>
       <c r="D6" t="n">
-        <v>53.7762122478233</v>
+        <v>29.42396044398116</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>156.9029180927252</v>
+        <v>178.9411905576576</v>
       </c>
       <c r="D7" t="n">
-        <v>30.00319158948677</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>46.39739650270425</v>
+        <v>54.57535487908019</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>3.882812170296134</v>
       </c>
       <c r="C9" t="n">
-        <v>23.85156047467625</v>
+        <v>43.93124626963626</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>42.56367171762047</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.595602061308321</v>
+        <v>3.37623035490478</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>42.46942393801276</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>12.26104707833841</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.244717220264713</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>39.05392367493812</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>4.773257338047991</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.024404823885929</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>39.02447124381072</v>
       </c>
       <c r="D13" t="n">
-        <v>35.64235040268046</v>
+        <v>0.7804894248762143</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5.53116656572653</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>43.63475846295374</v>
       </c>
       <c r="D14" t="n">
-        <v>34.72343455150544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>47.65894230266141</v>
       </c>
       <c r="D15" t="n">
-        <v>33.32542582065798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2531,13 +2531,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>48.35794666808513</v>
       </c>
       <c r="D16" t="n">
-        <v>31.82531532856885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2545,13 +2545,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>24.55547357862122</v>
+        <v>40.13875488813085</v>
       </c>
       <c r="D17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27.28767743954009</v>
+        <v>24.61241494546753</v>
       </c>
       <c r="D18" t="n">
-        <v>25.68251994309656</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2573,13 +2573,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28.88694444975815</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="D19" t="n">
-        <v>20.46158565191202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2587,13 +2587,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>31.60736733822606</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="D20" t="n">
-        <v>12.10494919336317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>25.83085541606944</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>120.851502125182</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.45771385401736</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50.5236821036536</v>
+        <v>28.07994783686727</v>
       </c>
       <c r="C2" t="n">
-        <v>165.0160811206209</v>
+        <v>312.4608418306324</v>
       </c>
       <c r="D2" t="n">
-        <v>405.8240667567998</v>
+        <v>202.4815370100876</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>106.2251015995049</v>
+        <v>70.54348128865456</v>
       </c>
       <c r="C3" t="n">
-        <v>415.8879624730338</v>
+        <v>539.548903299962</v>
       </c>
       <c r="D3" t="n">
-        <v>623.5717805679253</v>
+        <v>309.2407093607028</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>135.6677152498667</v>
+        <v>70.50126613737194</v>
       </c>
       <c r="C4" t="n">
-        <v>567.1114700966913</v>
+        <v>741.0290576517179</v>
       </c>
       <c r="D4" t="n">
-        <v>437.0210635546507</v>
+        <v>33.74463209037137</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>115.4535300194249</v>
+        <v>32.93763547748049</v>
       </c>
       <c r="C5" t="n">
-        <v>563.8913376267618</v>
+        <v>751.3069743674779</v>
       </c>
       <c r="D5" t="n">
-        <v>166.5289543328652</v>
+        <v>22.67837196810132</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.83912621635311</v>
+        <v>7.647814616082655</v>
       </c>
       <c r="C6" t="n">
-        <v>384.0007970390975</v>
+        <v>494.894108972296</v>
       </c>
       <c r="D6" t="n">
-        <v>53.41394734495622</v>
+        <v>28.33716573537994</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.55351008321272</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>155.6452992835851</v>
+        <v>190.139986620001</v>
       </c>
       <c r="D7" t="n">
-        <v>29.88341836956866</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>46.06360228326034</v>
+        <v>53.49052366588747</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.540624189870499</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>23.74062298409636</v>
+        <v>43.4874963073167</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>23.62968549351647</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>16.65534980254714</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.417905726839649</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>41.04785326226338</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>8.351727720027615</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.027750977626168</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>38.18605870438393</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>2.603594911662541</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.764241682260525</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>38.76430810218531</v>
       </c>
       <c r="D13" t="n">
-        <v>35.38218726105505</v>
+        <v>0.2601631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5.223879534297279</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>43.02018440009523</v>
       </c>
       <c r="D14" t="n">
-        <v>34.41614752007619</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>46.58392856651115</v>
       </c>
       <c r="D15" t="n">
-        <v>32.96708790860789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2842,13 +2842,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>45.05142040018188</v>
       </c>
       <c r="D16" t="n">
-        <v>31.41199954508094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>24.0832529328785</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
-        <v>28.80545939030567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2870,13 +2870,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26.75262494072559</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>25.14746744428205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28.28513310705485</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="D19" t="n">
-        <v>19.85977430920873</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2898,13 +2898,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>31.60736733822606</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>24.89886993334683</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>118.9612674593238</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>5.533082207410407</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50.81820641492764</v>
+        <v>24.58492600974862</v>
       </c>
       <c r="C2" t="n">
-        <v>167.9907766644887</v>
+        <v>281.4209246654609</v>
       </c>
       <c r="D2" t="n">
-        <v>413.7850588905371</v>
+        <v>184.8601474665616</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>105.6802316236479</v>
+        <v>65.94890203277949</v>
       </c>
       <c r="C3" t="n">
-        <v>413.9097408489765</v>
+        <v>601.5119096534994</v>
       </c>
       <c r="D3" t="n">
-        <v>619.0164712202202</v>
+        <v>291.8048701332795</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>134.9019520405542</v>
+        <v>60.40595449460199</v>
       </c>
       <c r="C4" t="n">
-        <v>564.3674852633214</v>
+        <v>783.5544412088727</v>
       </c>
       <c r="D4" t="n">
-        <v>433.5113155119683</v>
+        <v>31.58773238414112</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>114.6681318560275</v>
+        <v>29.10881943091793</v>
       </c>
       <c r="C5" t="n">
-        <v>560.5779391249288</v>
+        <v>775.2125309658878</v>
       </c>
       <c r="D5" t="n">
-        <v>165.1790512395259</v>
+        <v>21.96660488252239</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.35610634586367</v>
+        <v>6.802529842726151</v>
       </c>
       <c r="C6" t="n">
-        <v>381.1831811279092</v>
+        <v>511.1557779454401</v>
       </c>
       <c r="D6" t="n">
-        <v>53.05168244208915</v>
+        <v>27.4113776502752</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.37385025333556</v>
+        <v>4.910702016642545</v>
       </c>
       <c r="C7" t="n">
-        <v>154.3876804744449</v>
+        <v>184.0914390141364</v>
       </c>
       <c r="D7" t="n">
-        <v>29.76364514965055</v>
+        <v>27.78738702100172</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>3.75518496874405</v>
       </c>
       <c r="C8" t="n">
-        <v>45.72980806381643</v>
+        <v>52.48914100755572</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>25.70215489718149</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>23.62968549351647</v>
+        <v>42.48905889209769</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.680032363873552</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>22.06477965294707</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>12.66945412330509</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.240209392370978</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>39.98167525545134</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>5.508586368528851</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.810784734987623</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>37.10122749119121</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>1.301797455831271</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.50407854063512</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>38.50414496055991</v>
       </c>
       <c r="D13" t="n">
-        <v>35.12202411942965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>42.09832330580748</v>
       </c>
       <c r="D14" t="n">
-        <v>34.10886048864694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>45.15057691831081</v>
       </c>
       <c r="D15" t="n">
-        <v>32.6087499965578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>30.99868376159304</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>23.61103228713579</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>28.33323874456295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3181,13 +3181,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26.21757244191107</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>24.61241494546753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27.68332176435156</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3209,13 +3209,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>31.60736733822606</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>23.97323731068273</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>117.1000437867964</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4.610237944362063</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>51.18832529942869</v>
+        <v>21.86548486898496</v>
       </c>
       <c r="C2" t="n">
-        <v>171.3375545882661</v>
+        <v>339.2281929869217</v>
       </c>
       <c r="D2" t="n">
-        <v>421.2306334795449</v>
+        <v>163.1173810606075</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>107.1626706570606</v>
+        <v>61.30032665317084</v>
       </c>
       <c r="C3" t="n">
-        <v>418.1656171468865</v>
+        <v>643.8203269680158</v>
       </c>
       <c r="D3" t="n">
-        <v>633.5119760734243</v>
+        <v>275.3458698715817</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>136.2930885374719</v>
+        <v>51.77835566968103</v>
       </c>
       <c r="C4" t="n">
-        <v>569.4853360455601</v>
+        <v>834.7074235909486</v>
       </c>
       <c r="D4" t="n">
-        <v>445.2657807749154</v>
+        <v>29.62227348023901</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>116.0916660271854</v>
+        <v>25.72178985126644</v>
       </c>
       <c r="C5" t="n">
-        <v>565.805745650043</v>
+        <v>801.6460879027333</v>
       </c>
       <c r="D5" t="n">
-        <v>171.8549356284042</v>
+        <v>21.27938148954962</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.56365602208724</v>
+        <v>6.037748381117884</v>
       </c>
       <c r="C6" t="n">
-        <v>386.536651359167</v>
+        <v>527.7394601655773</v>
       </c>
       <c r="D6" t="n">
-        <v>55.2252718592916</v>
+        <v>26.40508625342222</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.03260296288517</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>158.4599699516607</v>
+        <v>178.222551238149</v>
       </c>
       <c r="D7" t="n">
-        <v>30.24273802932299</v>
+        <v>25.930902112271</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C8" t="n">
-        <v>47.398779161036</v>
+        <v>51.57120690408495</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>22.94835258676919</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>23.96249796525614</v>
+        <v>41.49062147687869</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>16.9734360587231</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.680032363873552</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>22.06477965294707</v>
+        <v>40.57072387799944</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>9.395325529641976</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.240209392370978</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>38.91549724863931</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>3.37623035490478</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.810784734987623</v>
+        <v>0.6508987279156353</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>36.23336252063703</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>0.4339324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.50407854063512</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>38.24398181893451</v>
       </c>
       <c r="D13" t="n">
-        <v>35.12202411942965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3436,13 +3436,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>41.17646221151972</v>
       </c>
       <c r="D14" t="n">
-        <v>34.10886048864694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>43.00054944601029</v>
       </c>
       <c r="D15" t="n">
-        <v>32.6087499965578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>30.99868376159304</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D17" t="n">
-        <v>28.33323874456295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3492,13 +3492,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26.21757244191107</v>
+        <v>10.70104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>24.61241494546753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27.68332176435156</v>
+        <v>1.805434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3520,13 +3520,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>30.93487016081699</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>23.97437005250219</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>117.1055767949146</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4.610455779327345</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>51.39449231732052</v>
+        <v>19.91573392835079</v>
       </c>
       <c r="C2" t="n">
-        <v>174.1806959397649</v>
+        <v>273.9802588149744</v>
       </c>
       <c r="D2" t="n">
-        <v>422.7219082422959</v>
+        <v>150.2329241900724</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>106.6128919426824</v>
+        <v>56.06270265101411</v>
       </c>
       <c r="C3" t="n">
-        <v>416.1726693072654</v>
+        <v>696.9230602907257</v>
       </c>
       <c r="D3" t="n">
-        <v>628.8879443864219</v>
+        <v>259.9177046993431</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>135.5273253281594</v>
+        <v>44.09519813624549</v>
       </c>
       <c r="C4" t="n">
-        <v>566.728588492035</v>
+        <v>881.7508100830473</v>
       </c>
       <c r="D4" t="n">
-        <v>441.7049818516122</v>
+        <v>27.54195009494002</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>115.3062678637879</v>
+        <v>22.50656611985813</v>
       </c>
       <c r="C5" t="n">
-        <v>562.4923471482101</v>
+        <v>823.514518014831</v>
       </c>
       <c r="D5" t="n">
-        <v>170.4559451498525</v>
+        <v>20.76396394482004</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.08063615159783</v>
+        <v>5.353470231257858</v>
       </c>
       <c r="C6" t="n">
-        <v>383.7190354479787</v>
+        <v>533.2941886762057</v>
       </c>
       <c r="D6" t="n">
-        <v>54.86300695642451</v>
+        <v>25.03652995370216</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.852943133008</v>
+        <v>3.712969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>157.2023511425205</v>
+        <v>171.2158178729395</v>
       </c>
       <c r="D7" t="n">
-        <v>30.12296480940488</v>
+        <v>23.95464398362217</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>2.753802310412303</v>
       </c>
       <c r="C8" t="n">
-        <v>47.06498494159209</v>
+        <v>50.40292713603124</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>20.27799883121787</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>23.85156047467625</v>
+        <v>40.49218406165969</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>13.64531134132641</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>6.690610604442014</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>1.066178006812036</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>1.954659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.593818492349078</v>
+        <v>0.2169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>35.79943003535993</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.243915399009714</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D13" t="n">
-        <v>34.86186097780424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>39.94731408580272</v>
       </c>
       <c r="D14" t="n">
-        <v>33.80157345721769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>40.49218406165969</v>
       </c>
       <c r="D15" t="n">
-        <v>32.25041208450772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>32.65194689554467</v>
       </c>
       <c r="D16" t="n">
-        <v>30.58536797810513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3789,13 +3789,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>23.13881164139307</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>27.86101809882023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3803,13 +3803,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>25.68251994309656</v>
+        <v>7.490734983403163</v>
       </c>
       <c r="D18" t="n">
-        <v>24.07736244665303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27.68332176435156</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="D19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3831,13 +3831,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>30.93487016081699</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>23.04069277500962</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>115.2034638750481</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3.686510844001539</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.66905321267759</v>
+        <v>18.12208087269187</v>
       </c>
       <c r="C2" t="n">
-        <v>48.37267288364884</v>
+        <v>31.76837396172254</v>
       </c>
       <c r="D2" t="n">
-        <v>94.19280173625597</v>
+        <v>35.77488634275377</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01963495408493621</v>
+        <v>0.08344855486097889</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.154936210821749</v>
+        <v>4.525856916577796</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8423395302437633</v>
+        <v>3.216205479112551</v>
       </c>
       <c r="C4" t="n">
-        <v>1.033780332571891</v>
+        <v>4.849833658979244</v>
       </c>
       <c r="D4" t="n">
-        <v>11.94590606527519</v>
+        <v>27.74615361742335</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.387029579651497</v>
+        <v>8.099418560036186</v>
       </c>
       <c r="C5" t="n">
-        <v>6.724971774090653</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D5" t="n">
-        <v>15.19254572321939</v>
+        <v>24.51914891356409</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.467933802027235</v>
+        <v>10.10316562440393</v>
       </c>
       <c r="C6" t="n">
-        <v>8.533351045313278</v>
+        <v>19.68305972244431</v>
       </c>
       <c r="D6" t="n">
-        <v>18.43525839034661</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>12.33664165156542</v>
       </c>
       <c r="C7" t="n">
-        <v>10.65981657271187</v>
+        <v>22.27781890476862</v>
       </c>
       <c r="D7" t="n">
-        <v>18.44507586738907</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>14.43659999094934</v>
       </c>
       <c r="C8" t="n">
-        <v>11.01520924164921</v>
+        <v>25.95250056176443</v>
       </c>
       <c r="D8" t="n">
-        <v>22.19731559302038</v>
+        <v>44.81187396034566</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>14.64374875654542</v>
       </c>
       <c r="C9" t="n">
-        <v>13.53437385074652</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>25.4046853427947</v>
+        <v>52.91718300660731</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>13.38122120888403</v>
       </c>
       <c r="C10" t="n">
-        <v>15.80122929985241</v>
+        <v>38.43542262126263</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>64.48609795345175</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>11.0171727370577</v>
       </c>
       <c r="C11" t="n">
-        <v>17.59193711239859</v>
+        <v>35.7169632282032</v>
       </c>
       <c r="D11" t="n">
-        <v>30.74146586308036</v>
+        <v>54.19738201294516</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.773257338047991</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>36.01639627799849</v>
       </c>
       <c r="D12" t="n">
-        <v>29.72437524148068</v>
+        <v>57.92998678449154</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.422773407631881</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>35.38218726105505</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>59.8375225738431</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>39.02545299151496</v>
       </c>
       <c r="D14" t="n">
-        <v>31.95785126864218</v>
+        <v>59.61368409727482</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>46.94226647856124</v>
       </c>
       <c r="D15" t="n">
-        <v>31.17539834835746</v>
+        <v>56.61739010391356</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>51.66447293598839</v>
       </c>
       <c r="D16" t="n">
-        <v>29.75873641112932</v>
+        <v>52.49110450296421</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="C17" t="n">
-        <v>24.0832529328785</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>26.9165768073348</v>
+        <v>44.860961345558</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="C18" t="n">
-        <v>26.21757244191107</v>
+        <v>60.99598486485433</v>
       </c>
       <c r="D18" t="n">
-        <v>23.54230994783851</v>
+        <v>34.77841242294325</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>19.85977430920873</v>
       </c>
       <c r="C19" t="n">
-        <v>28.28513310705485</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>20.46158565191202</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>21.51990967709008</v>
       </c>
       <c r="C20" t="n">
-        <v>30.93487016081699</v>
+        <v>125.7569721754952</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>2.017491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>12.45010474215894</v>
+        <v>4.965748707180583</v>
       </c>
       <c r="C21" t="n">
-        <v>49.80041896863577</v>
+        <v>4.965748707180583</v>
       </c>
       <c r="D21" t="n">
-        <v>1.556263092769868</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>52.36053205829938</v>
+        <v>16.03684874887164</v>
       </c>
       <c r="C2" t="n">
-        <v>175.2861438547468</v>
+        <v>231.544214298906</v>
       </c>
       <c r="D2" t="n">
-        <v>427.1692253425339</v>
+        <v>145.5539146316321</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>106.0680219668254</v>
+        <v>52.03753706360218</v>
       </c>
       <c r="C3" t="n">
-        <v>414.1895389446868</v>
+        <v>720.8433431046993</v>
       </c>
       <c r="D3" t="n">
-        <v>624.2933651305467</v>
+        <v>245.3436600297991</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>134.7615621188469</v>
+        <v>37.57344813693393</v>
       </c>
       <c r="C4" t="n">
-        <v>563.9846036586652</v>
+        <v>934.3842680031272</v>
       </c>
       <c r="D4" t="n">
-        <v>438.1697083686194</v>
+        <v>25.66583023212436</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>114.5208697003904</v>
+        <v>19.68404147014855</v>
       </c>
       <c r="C5" t="n">
-        <v>559.2034923389833</v>
+        <v>839.8606172905403</v>
       </c>
       <c r="D5" t="n">
-        <v>169.0814983639069</v>
+        <v>20.02765316663493</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.59761628110839</v>
+        <v>4.70944373727195</v>
       </c>
       <c r="C6" t="n">
-        <v>380.9014195367903</v>
+        <v>550.8036589814476</v>
       </c>
       <c r="D6" t="n">
-        <v>54.50074205355744</v>
+        <v>23.8692319333527</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.67328330313084</v>
+        <v>3.233876937788993</v>
       </c>
       <c r="C7" t="n">
-        <v>155.9447323333803</v>
+        <v>166.1853426363788</v>
       </c>
       <c r="D7" t="n">
-        <v>30.00319158948677</v>
+        <v>21.91849924501429</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>46.73119072214817</v>
+        <v>48.9843017033946</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>17.60764507566654</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.207811718130833</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>23.74062298409636</v>
+        <v>39.93749660876023</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>10.6499990956694</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>38.43542262126263</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>4.555309347705201</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>36.60544490054656</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>0.8884816723433632</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>35.36549755008285</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.983752257384309</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>24.71549845441346</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>34.60169783617884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.02545299151496</v>
       </c>
       <c r="D14" t="n">
-        <v>33.49428642578843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>37.26714285320892</v>
       </c>
       <c r="D15" t="n">
-        <v>31.89207417245764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>30.17205219461722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4411,13 +4411,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>22.66659099565036</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>27.38879745307752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4425,13 +4425,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>25.14746744428205</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="D18" t="n">
-        <v>23.54230994783851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4439,13 +4439,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27.68332176435156</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>18.05434028109884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4453,13 +4453,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>30.93487016081699</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>9.41496048372691</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>22.11312885678554</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113.3297853910259</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2.764141107098192</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.662360905197108</v>
+        <v>19.0999015861217</v>
       </c>
       <c r="C2" t="n">
-        <v>22.72156886708818</v>
+        <v>40.01799992050848</v>
       </c>
       <c r="D2" t="n">
-        <v>132.1589489548886</v>
+        <v>158.0388001865388</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>33.26161221988194</v>
+        <v>27.59201922785661</v>
       </c>
       <c r="C3" t="n">
-        <v>164.4623754154257</v>
+        <v>62.26243940333271</v>
       </c>
       <c r="D3" t="n">
-        <v>109.9802865682489</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3956443248114646</v>
+        <v>2.054797944988574</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3445934441906304</v>
+        <v>2.641883072128167</v>
       </c>
       <c r="D4" t="n">
-        <v>10.60582044897829</v>
+        <v>27.15906849028376</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.429825568010856</v>
+        <v>7.314020396638739</v>
       </c>
       <c r="C5" t="n">
-        <v>3.657010198319369</v>
+        <v>12.22275891787279</v>
       </c>
       <c r="D5" t="n">
-        <v>16.88606051304514</v>
+        <v>25.35363446217388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.071708640139024</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>10.30442390377452</v>
+        <v>21.09186767803848</v>
       </c>
       <c r="D6" t="n">
-        <v>20.04532462531138</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>12.39652826152447</v>
       </c>
       <c r="C7" t="n">
-        <v>12.03720860177014</v>
+        <v>25.15237618280328</v>
       </c>
       <c r="D7" t="n">
-        <v>20.30156077611979</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>14.43659999094934</v>
       </c>
       <c r="C8" t="n">
-        <v>13.60211444233956</v>
+        <v>28.03871443328891</v>
       </c>
       <c r="D8" t="n">
-        <v>23.11524969649115</v>
+        <v>45.31256528951153</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>14.42187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>14.42187377538564</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>26.18124777685393</v>
+        <v>54.1374954029861</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>12.5271007061893</v>
       </c>
       <c r="C10" t="n">
-        <v>16.79770321966293</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>59.07666810305182</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.574764375340887</v>
+        <v>10.30638739918301</v>
       </c>
       <c r="C11" t="n">
-        <v>19.01350778814797</v>
+        <v>38.73780091417063</v>
       </c>
       <c r="D11" t="n">
-        <v>32.87382187670443</v>
+        <v>53.48659667507046</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>9.76348091873453</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>37.5351599764683</v>
       </c>
       <c r="D12" t="n">
-        <v>31.46010518258904</v>
+        <v>56.41122308602172</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95125677215293</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>57.23589115758905</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>18.12993485432585</v>
+        <v>39.94731408580272</v>
       </c>
       <c r="D14" t="n">
-        <v>32.87971236292993</v>
+        <v>55.3116656572653</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>48.37561812676158</v>
       </c>
       <c r="D15" t="n">
-        <v>31.89207417245764</v>
+        <v>51.60065933521235</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>52.49110450296421</v>
       </c>
       <c r="D16" t="n">
-        <v>30.99868376159304</v>
+        <v>44.63810461669397</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="C17" t="n">
-        <v>24.55547357862122</v>
+        <v>56.6664774891259</v>
       </c>
       <c r="D17" t="n">
-        <v>27.86101809882023</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="C18" t="n">
-        <v>26.75262494072559</v>
+        <v>61.53103736366884</v>
       </c>
       <c r="D18" t="n">
-        <v>24.61241494546753</v>
+        <v>22.47220495020949</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="C19" t="n">
-        <v>28.88694444975815</v>
+        <v>75.22641783791184</v>
       </c>
       <c r="D19" t="n">
-        <v>18.65615162380213</v>
+        <v>4.814490741626358</v>
       </c>
     </row>
     <row r="20">
@@ -4764,13 +4764,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>10.08745766113597</v>
       </c>
       <c r="C20" t="n">
-        <v>30.93487016081699</v>
+        <v>106.9270512080413</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.26644818593689</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>66.69243756234124</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3.253289637187378</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12.27282805078938</v>
+        <v>24.89908527510761</v>
       </c>
       <c r="C2" t="n">
-        <v>38.34706532788041</v>
+        <v>61.98656829843936</v>
       </c>
       <c r="D2" t="n">
-        <v>153.9193868195192</v>
+        <v>160.5324393553257</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>40.63453747877548</v>
+        <v>43.72213400863171</v>
       </c>
       <c r="C3" t="n">
-        <v>134.4552568351219</v>
+        <v>107.1037657948058</v>
       </c>
       <c r="D3" t="n">
-        <v>220.1421964617836</v>
+        <v>88.67636138609315</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.57643443777567</v>
+        <v>20.25443688631594</v>
       </c>
       <c r="C4" t="n">
-        <v>252.4210792297144</v>
+        <v>69.86313012961152</v>
       </c>
       <c r="D4" t="n">
-        <v>65.66419519854792</v>
+        <v>29.36701907713484</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.644427404613408</v>
+        <v>6.381360077604269</v>
       </c>
       <c r="C5" t="n">
-        <v>1.988039101099791</v>
+        <v>9.375690575557041</v>
       </c>
       <c r="D5" t="n">
-        <v>17.7450897542611</v>
+        <v>25.59907138823559</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.588688769649592</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>7.969827863075609</v>
+        <v>20.930861054542</v>
       </c>
       <c r="D6" t="n">
-        <v>21.49438423677967</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.707300315414209</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C7" t="n">
-        <v>13.95358012045992</v>
+        <v>27.60772719112455</v>
       </c>
       <c r="D7" t="n">
-        <v>22.27781890476862</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.42692138262712</v>
+        <v>14.43659999094934</v>
       </c>
       <c r="C8" t="n">
-        <v>15.52143120414207</v>
+        <v>30.29182541453534</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>45.89670517353839</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>13.86718632248619</v>
       </c>
       <c r="C9" t="n">
-        <v>16.41874860582365</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>53.24999547834697</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>11.67298020349457</v>
       </c>
       <c r="C10" t="n">
-        <v>17.79417713947344</v>
+        <v>40.00131020953629</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>55.51783267515713</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>9.595602061308321</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>41.22554959673205</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>52.42041866825843</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>9.112582190818895</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>39.05392367493812</v>
       </c>
       <c r="D12" t="n">
-        <v>32.76190263842031</v>
+        <v>54.45852690227482</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="C13" t="n">
-        <v>20.55288818840698</v>
+        <v>38.50414496055991</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>53.85377031645879</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5.223879534297279</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>40.86917518009047</v>
       </c>
       <c r="D14" t="n">
-        <v>33.49428642578843</v>
+        <v>50.39507315439727</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>49.80896977496192</v>
       </c>
       <c r="D15" t="n">
-        <v>32.6087499965578</v>
+        <v>45.15057691831081</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>52.90442028645212</v>
       </c>
       <c r="D16" t="n">
-        <v>31.82531532856885</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="C17" t="n">
+        <v>57.13869813486862</v>
+      </c>
+      <c r="D17" t="n">
         <v>25.02769422436394</v>
-      </c>
-      <c r="D17" t="n">
-        <v>28.80545939030567</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="C18" t="n">
-        <v>27.28767743954009</v>
+        <v>63.13619486011238</v>
       </c>
       <c r="D18" t="n">
-        <v>25.68251994309656</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>29.48875579246144</v>
+        <v>79.43909723683491</v>
       </c>
       <c r="D19" t="n">
-        <v>19.25796296650543</v>
+        <v>0.6018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -5075,13 +5075,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>2.68998870963626</v>
       </c>
       <c r="C20" t="n">
-        <v>31.60736733822606</v>
+        <v>85.40714153095125</v>
       </c>
       <c r="D20" t="n">
-        <v>12.10494919336317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19.43726220944859</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>82.81963897938964</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>5.070590141595284</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.59135627532185</v>
+        <v>37.47232812339651</v>
       </c>
       <c r="C2" t="n">
-        <v>84.11319805675397</v>
+        <v>82.48153337229579</v>
       </c>
       <c r="D2" t="n">
-        <v>240.7412267922901</v>
+        <v>249.0605568380776</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>49.13156385903162</v>
+        <v>59.68535167968484</v>
       </c>
       <c r="C3" t="n">
-        <v>162.518514961017</v>
+        <v>169.7589042798372</v>
       </c>
       <c r="D3" t="n">
-        <v>313.545673043825</v>
+        <v>145.0826757335936</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>68.85487523735006</v>
+        <v>40.57268737340794</v>
       </c>
       <c r="C4" t="n">
-        <v>302.5530439993736</v>
+        <v>151.1871829586003</v>
       </c>
       <c r="D4" t="n">
-        <v>152.4506922539659</v>
+        <v>39.51338160052563</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.74757733348411</v>
+        <v>12.24730261047896</v>
       </c>
       <c r="C5" t="n">
-        <v>234.0731963850458</v>
+        <v>54.92878405260905</v>
       </c>
       <c r="D5" t="n">
-        <v>35.09748042682348</v>
+        <v>25.79542092908495</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.864158963915446</v>
+        <v>10.34467555964864</v>
       </c>
       <c r="C6" t="n">
-        <v>5.876741757621407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D6" t="n">
-        <v>22.90319219237384</v>
+        <v>35.82397372796611</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C7" t="n">
-        <v>13.11516758103314</v>
+        <v>28.86534600026472</v>
       </c>
       <c r="D7" t="n">
-        <v>23.71509754378595</v>
+        <v>36.59071868498287</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C8" t="n">
-        <v>17.35729941108361</v>
+        <v>32.96217917008666</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>45.72980806381643</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.653124265231384</v>
+        <v>13.20156137900685</v>
       </c>
       <c r="C9" t="n">
-        <v>18.30468594568177</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>52.25155806312797</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.110618695410402</v>
+        <v>10.67650628368406</v>
       </c>
       <c r="C10" t="n">
-        <v>19.21771131063132</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>52.67076433284138</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.529424054496287</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>43.35790561035613</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>50.99884799250905</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>8.461683462903258</v>
       </c>
       <c r="C12" t="n">
-        <v>22.99842171968578</v>
+        <v>41.00661985868502</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>51.42099950533518</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.243915399009714</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>39.28463438543612</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>49.95132319207772</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5.53116656572653</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>42.09832330580748</v>
       </c>
       <c r="D14" t="n">
-        <v>34.41614752007619</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>50.88398351111218</v>
       </c>
       <c r="D15" t="n">
-        <v>33.32542582065798</v>
+        <v>37.9838186773091</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>53.31773606994002</v>
       </c>
       <c r="D16" t="n">
-        <v>32.23863111205676</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="C17" t="n">
-        <v>25.49991487010665</v>
+        <v>57.13869813486862</v>
       </c>
       <c r="D17" t="n">
-        <v>29.7499006817911</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>12.30620747273377</v>
       </c>
       <c r="C18" t="n">
-        <v>27.82272993835461</v>
+        <v>65.27640485537043</v>
       </c>
       <c r="D18" t="n">
-        <v>26.21757244191107</v>
+        <v>2.140209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>30.09056713516474</v>
+        <v>80.0409085795382</v>
       </c>
       <c r="D19" t="n">
-        <v>20.46158565191202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5386,13 +5386,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27986451563512</v>
+        <v>66.57722056349743</v>
       </c>
       <c r="D20" t="n">
-        <v>12.77744637077223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>22.67029837303515</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.78473536180393</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.10354186966331</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.66921744359361</v>
+        <v>41.85190463204152</v>
       </c>
       <c r="C2" t="n">
-        <v>112.8401176307199</v>
+        <v>67.36752746541613</v>
       </c>
       <c r="D2" t="n">
-        <v>238.5352397008475</v>
+        <v>221.389016046177</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>62.27716561889642</v>
+        <v>81.12181280191395</v>
       </c>
       <c r="C3" t="n">
-        <v>255.4114827368502</v>
+        <v>231.2997591205485</v>
       </c>
       <c r="D3" t="n">
-        <v>420.3647320043992</v>
+        <v>214.7965802121597</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.20766682053993</v>
+        <v>58.74680087442488</v>
       </c>
       <c r="C4" t="n">
-        <v>348.7668536813836</v>
+        <v>246.9841604435956</v>
       </c>
       <c r="D4" t="n">
-        <v>231.9752015410703</v>
+        <v>49.30238795957057</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.34097921967247</v>
+        <v>21.91751749731004</v>
       </c>
       <c r="C5" t="n">
-        <v>358.1170188166303</v>
+        <v>127.2590461629928</v>
       </c>
       <c r="D5" t="n">
-        <v>66.04707680320418</v>
+        <v>25.89359569950963</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.79752329321368</v>
+        <v>11.18996033300515</v>
       </c>
       <c r="C6" t="n">
-        <v>134.4405306195582</v>
+        <v>38.44033135978387</v>
       </c>
       <c r="D6" t="n">
-        <v>27.29062268265284</v>
+        <v>35.17994723398021</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>12.51630148144259</v>
       </c>
       <c r="C7" t="n">
-        <v>11.79766216193392</v>
+        <v>29.10489244010094</v>
       </c>
       <c r="D7" t="n">
-        <v>24.852943133008</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>17.60764507566654</v>
+        <v>35.13184159647211</v>
       </c>
       <c r="D8" t="n">
-        <v>25.86905200690345</v>
+        <v>45.72980806381643</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.207811718130833</v>
+        <v>12.20312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>19.96874830438012</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>50.58749570442963</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.680032363873552</v>
       </c>
       <c r="C10" t="n">
-        <v>20.64124548178919</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.240209392370978</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>44.42408361716816</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>8.027750977626168</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>42.52538355715483</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>48.6004383510341</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6.764241682260525</v>
+        <v>8.845546815263763</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>40.58545009356315</v>
       </c>
       <c r="D13" t="n">
-        <v>34.86186097780424</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5.838453597155781</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>43.02018440009523</v>
       </c>
       <c r="D14" t="n">
-        <v>34.72343455150544</v>
+        <v>39.33274002294421</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>51.24232142316227</v>
       </c>
       <c r="D15" t="n">
-        <v>33.68376373270807</v>
+        <v>30.10038461220721</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>53.31773606994002</v>
       </c>
       <c r="D16" t="n">
-        <v>32.65194689554467</v>
+        <v>16.11931555602838</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>11.8055161435679</v>
       </c>
       <c r="C17" t="n">
-        <v>25.49991487010665</v>
+        <v>58.08313942635404</v>
       </c>
       <c r="D17" t="n">
-        <v>30.22212132753381</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>66.88156235181395</v>
       </c>
       <c r="D18" t="n">
-        <v>26.75262494072559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>1.805434028109884</v>
       </c>
       <c r="C19" t="n">
-        <v>30.09056713516474</v>
+        <v>75.82822918061514</v>
       </c>
       <c r="D19" t="n">
-        <v>21.06339699461531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5697,13 +5697,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27986451563512</v>
+        <v>50.43728830567987</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>24.97755918552569</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.9387379088789</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.136445481578768</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.21328559819559</v>
+        <v>40.55992465325272</v>
       </c>
       <c r="C2" t="n">
-        <v>125.4820828183061</v>
+        <v>63.88035961993146</v>
       </c>
       <c r="D2" t="n">
-        <v>284.8275891991973</v>
+        <v>210.1656762912274</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>82.44717220264714</v>
+        <v>97.1439353352219</v>
       </c>
       <c r="C3" t="n">
-        <v>332.6063047217769</v>
+        <v>242.1333450369121</v>
       </c>
       <c r="D3" t="n">
-        <v>489.8724694650734</v>
+        <v>264.0655887497858</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>103.7609148618454</v>
+        <v>78.97571232043042</v>
       </c>
       <c r="C4" t="n">
-        <v>431.0736359623235</v>
+        <v>349.6857695325587</v>
       </c>
       <c r="D4" t="n">
-        <v>311.7804906715893</v>
+        <v>58.69574999380406</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>83.39946747576656</v>
+        <v>32.10314992887071</v>
       </c>
       <c r="C5" t="n">
-        <v>433.1225434210867</v>
+        <v>219.2978934361313</v>
       </c>
       <c r="D5" t="n">
-        <v>96.43216824964297</v>
+        <v>25.9181393921158</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.66296710446964</v>
+        <v>12.7597749120958</v>
       </c>
       <c r="C6" t="n">
-        <v>244.4483061235261</v>
+        <v>79.81903359837844</v>
       </c>
       <c r="D6" t="n">
-        <v>33.77113927838603</v>
+        <v>34.81768233111314</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.59992996275281</v>
+        <v>12.27675504160636</v>
       </c>
       <c r="C7" t="n">
-        <v>55.15556777229006</v>
+        <v>35.15344004596554</v>
       </c>
       <c r="D7" t="n">
-        <v>26.11056194214817</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C8" t="n">
-        <v>17.27385085622263</v>
+        <v>36.38356991938679</v>
       </c>
       <c r="D8" t="n">
-        <v>26.53664044579129</v>
+        <v>45.39601384437251</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.540624189870499</v>
+        <v>11.20468654856884</v>
       </c>
       <c r="C9" t="n">
-        <v>20.85624822901923</v>
+        <v>39.38280915586078</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>48.59062087399162</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>47.11898106532567</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.595602061308321</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>45.84565429291754</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.461683462903258</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>43.61021477034756</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.024404823885929</v>
+        <v>8.325220532012953</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>41.10577637681396</v>
       </c>
       <c r="D13" t="n">
-        <v>35.12202411942965</v>
+        <v>39.80496066868693</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.145740628585034</v>
+        <v>9.525897974306801</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>43.63475846295374</v>
       </c>
       <c r="D14" t="n">
-        <v>35.33800861436394</v>
+        <v>32.57242533150067</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>50.88398351111218</v>
       </c>
       <c r="D15" t="n">
-        <v>34.04210164475815</v>
+        <v>20.42526098685489</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>11.15952615417349</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>53.31773606994002</v>
       </c>
       <c r="D16" t="n">
-        <v>32.65194689554467</v>
+        <v>7.439684102782329</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>8.02775097762617</v>
       </c>
       <c r="C17" t="n">
-        <v>25.49991487010665</v>
+        <v>59.02758071783948</v>
       </c>
       <c r="D17" t="n">
-        <v>30.22212132753381</v>
+        <v>0.9444412914854317</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>67.41661485062848</v>
       </c>
       <c r="D18" t="n">
-        <v>26.75262494072559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30.09056713516474</v>
+        <v>69.2083044108789</v>
       </c>
       <c r="D19" t="n">
-        <v>21.66520833731861</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27986451563512</v>
+        <v>36.98734475749858</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>26.27511810493557</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>115.9729350838535</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.154346998083451</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.11202671593792</v>
+        <v>37.77470641630452</v>
       </c>
       <c r="C2" t="n">
-        <v>131.6828013183289</v>
+        <v>138.9467525820511</v>
       </c>
       <c r="D2" t="n">
-        <v>344.1467489851981</v>
+        <v>252.4377689406866</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>91.36635009572942</v>
+        <v>102.7644409420349</v>
       </c>
       <c r="C3" t="n">
-        <v>376.8242213210532</v>
+        <v>243.787589918568</v>
       </c>
       <c r="D3" t="n">
-        <v>536.5840252331367</v>
+        <v>304.1552562527043</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>119.1655180891821</v>
+        <v>96.46063893306611</v>
       </c>
       <c r="C4" t="n">
-        <v>496.1252205934214</v>
+        <v>418.2981530869597</v>
       </c>
       <c r="D4" t="n">
-        <v>359.8704202164151</v>
+        <v>56.6792402092811</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>97.31574118346511</v>
+        <v>42.41150082346221</v>
       </c>
       <c r="C5" t="n">
-        <v>496.8134257340985</v>
+        <v>321.2523925221626</v>
       </c>
       <c r="D5" t="n">
-        <v>121.5894531709675</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.77871552257953</v>
+        <v>14.4503444588088</v>
       </c>
       <c r="C6" t="n">
-        <v>309.6559886395993</v>
+        <v>137.4191531542431</v>
       </c>
       <c r="D6" t="n">
-        <v>39.9698942830004</v>
+        <v>34.41516577237194</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>11.67788894201581</v>
       </c>
       <c r="C7" t="n">
-        <v>98.333813552769</v>
+        <v>49.40645321622073</v>
       </c>
       <c r="D7" t="n">
-        <v>27.30829414132927</v>
+        <v>37.60879105428681</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>12.01659189998096</v>
       </c>
       <c r="C8" t="n">
-        <v>25.78560345204247</v>
+        <v>38.38633523605029</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>44.14428552145782</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>21.07812321017901</v>
+        <v>40.71405904281946</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>46.37187106239383</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.2494460323367</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.950994730245668</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>47.44492130313559</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>43.89099461376214</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.678649705541803</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>44.04414725562465</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.284567965511334</v>
+        <v>7.804894248762142</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>41.10577637681396</v>
       </c>
       <c r="D13" t="n">
-        <v>35.38218726105505</v>
+        <v>34.08137155292803</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.145740628585034</v>
+        <v>8.911323911448299</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>43.94204549438299</v>
       </c>
       <c r="D14" t="n">
-        <v>35.33800861436394</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>50.52564559906209</v>
       </c>
       <c r="D15" t="n">
-        <v>34.04210164475815</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>53.73105185342793</v>
       </c>
       <c r="D16" t="n">
-        <v>32.65194689554467</v>
+        <v>2.479894700927443</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>25.49991487010665</v>
+        <v>59.4998013635822</v>
       </c>
       <c r="D17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>66.34650985299945</v>
       </c>
       <c r="D18" t="n">
-        <v>26.75262494072559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30.09056713516474</v>
+        <v>60.18113427032947</v>
       </c>
       <c r="D19" t="n">
-        <v>21.66520833731861</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27986451563512</v>
+        <v>26.22738991895353</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>27.43624379723887</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>120.719472707851</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.230873139171662</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.48455106420397</v>
+        <v>30.63543711102172</v>
       </c>
       <c r="C2" t="n">
-        <v>128.4626688483994</v>
+        <v>115.8815720184765</v>
       </c>
       <c r="D2" t="n">
-        <v>369.1292828151667</v>
+        <v>282.5077193740622</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>97.95878592974674</v>
+        <v>102.7349885109075</v>
       </c>
       <c r="C3" t="n">
-        <v>399.3504223949963</v>
+        <v>315.9362287036661</v>
       </c>
       <c r="D3" t="n">
-        <v>572.1036571727863</v>
+        <v>333.0039125419969</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>127.4485234699124</v>
+        <v>103.7481521416902</v>
       </c>
       <c r="C4" t="n">
-        <v>534.8090253838584</v>
+        <v>459.1260948634718</v>
       </c>
       <c r="D4" t="n">
-        <v>390.9221183540374</v>
+        <v>53.79486545420397</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>106.5441696033851</v>
+        <v>49.92187076095032</v>
       </c>
       <c r="C5" t="n">
-        <v>533.3835277172922</v>
+        <v>405.780869857813</v>
       </c>
       <c r="D5" t="n">
-        <v>138.6964069174682</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.58753676215866</v>
+        <v>14.28933783531233</v>
       </c>
       <c r="C6" t="n">
-        <v>350.0283994813408</v>
+        <v>198.0783985565407</v>
       </c>
       <c r="D6" t="n">
-        <v>44.71958967614647</v>
+        <v>33.6906359666378</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.76258128648829</v>
+        <v>11.07902284242525</v>
       </c>
       <c r="C7" t="n">
-        <v>127.3189327729519</v>
+        <v>69.58824077242241</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>37.60879105428681</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>34.88149593188918</v>
+        <v>41.72427743048944</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>42.97600575340412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>41.71249645803847</v>
       </c>
       <c r="D9" t="n">
-        <v>29.62030998483051</v>
+        <v>43.59843379789659</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.2494460323367</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="C10" t="n">
-        <v>22.49183990429443</v>
+        <v>45.12603322570465</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>42.27896488338889</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.950994730245668</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>47.97801030654161</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>40.15937158992001</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.678649705541803</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>43.61021477034756</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7.544731107136739</v>
+        <v>7.284567965511334</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>41.10577637681396</v>
       </c>
       <c r="D13" t="n">
-        <v>35.90251354430586</v>
+        <v>27.3171298706675</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6.145740628585034</v>
+        <v>8.296749848589794</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>44.24933252581224</v>
       </c>
       <c r="D14" t="n">
-        <v>35.33800861436394</v>
+        <v>15.97892563432109</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>7.883434065101886</v>
+      </c>
+      <c r="C15" t="n">
+        <v>50.52564559906209</v>
+      </c>
+      <c r="D15" t="n">
         <v>5.375068680751286</v>
-      </c>
-      <c r="C15" t="n">
-        <v>23.29196428325557</v>
-      </c>
-      <c r="D15" t="n">
-        <v>34.04210164475815</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>53.73105185342793</v>
       </c>
       <c r="D16" t="n">
-        <v>32.65194689554467</v>
+        <v>0.4133157834879072</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>25.49991487010665</v>
+        <v>59.4998013635822</v>
       </c>
       <c r="D17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>63.67124735892688</v>
       </c>
       <c r="D18" t="n">
-        <v>26.75262494072559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8.425358797846126</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30.09056713516474</v>
+        <v>49.95034144437346</v>
       </c>
       <c r="D19" t="n">
-        <v>21.66520833731861</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>32.27986451563512</v>
+        <v>18.15742379004475</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>27.57372025309666</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>123.1626171304984</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.272116075928999</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -27,6 +27,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_17" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_18" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_19" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_20" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,13 +470,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.0124956847796534</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.1541343895667492</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5425432337979148</v>
+        <v>51.13398360050323</v>
       </c>
     </row>
     <row r="3">
@@ -483,13 +484,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3504102993382928</v>
+        <v>0.3512300586713388</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1.364629308903067</v>
       </c>
       <c r="D3" t="n">
-        <v>3.512619654717269</v>
+        <v>132.8861883842865</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +498,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.54017919154111</v>
+        <v>1.031738297347058</v>
       </c>
       <c r="C4" t="n">
-        <v>29.1660062346903</v>
+        <v>3.203442758957343</v>
       </c>
       <c r="D4" t="n">
-        <v>21.15918611811868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -511,13 +512,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.45494243181676</v>
+        <v>1.258011508221863</v>
       </c>
       <c r="C5" t="n">
-        <v>40.79161711145498</v>
+        <v>2.675262494072558</v>
       </c>
       <c r="D5" t="n">
-        <v>17.91088239781578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -525,13 +526,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.41224274567721</v>
+        <v>1.606202076000854</v>
       </c>
       <c r="C6" t="n">
-        <v>62.43836859193375</v>
+        <v>3.300635781677777</v>
       </c>
       <c r="D6" t="n">
-        <v>27.66274924120907</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -539,13 +540,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.50003767951448</v>
+        <v>1.709882487550951</v>
       </c>
       <c r="C7" t="n">
-        <v>61.37778654703591</v>
+        <v>3.233876937788993</v>
       </c>
       <c r="D7" t="n">
-        <v>24.60920463047465</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +554,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.96192882442208</v>
+        <v>1.808497080947134</v>
       </c>
       <c r="C8" t="n">
-        <v>83.21489890736814</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="D8" t="n">
-        <v>33.70028163783202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +568,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>34.84480016619982</v>
+        <v>1.640987360657726</v>
       </c>
       <c r="C9" t="n">
-        <v>92.1890546718882</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94162967565032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +582,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33.19553569064761</v>
+        <v>1.175269811707942</v>
       </c>
       <c r="C10" t="n">
-        <v>126.182068931434</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="D10" t="n">
-        <v>53.45441989406379</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -595,13 +596,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27.06101938356522</v>
+        <v>0.2445101562288935</v>
       </c>
       <c r="C11" t="n">
-        <v>105.827051992818</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>41.54629148044801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +610,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>25.8135587179209</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>114.1893335006663</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>44.57896904372867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -623,13 +624,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>26.00044421090132</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>111.7010448568676</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>46.08139646039982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +638,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>29.24757965143618</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>127.6777615588541</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>47.89682958887746</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -651,13 +652,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>34.10660246892716</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>148.8894024568106</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>45.69883392374744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -665,13 +666,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>37.37242645876005</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>166.0082844379179</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>43.92513489017734</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -679,13 +680,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>42.69866300870211</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>183.1271664190252</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>40.14819930104569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -693,13 +694,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>45.83366715344869</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>200.0828819316866</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>34.11762258690734</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -707,13 +708,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>51.55236323864963</v>
+        <v>1.2421386113396</v>
       </c>
       <c r="C19" t="n">
-        <v>216.7122645074564</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>25.58300017831706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -721,13 +722,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>51.20662507663585</v>
+        <v>3.007407377373338</v>
       </c>
       <c r="C20" t="n">
-        <v>242.1662335850043</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>14.29392750582968</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -735,10 +736,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>53.33244755928816</v>
+        <v>5.140116820170939</v>
       </c>
       <c r="C21" t="n">
-        <v>258.6868385151436</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +781,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>109.503157183985</v>
+        <v>3.39782880439821</v>
       </c>
       <c r="C2" t="n">
-        <v>671.2925729759543</v>
+        <v>0.3033600406122644</v>
       </c>
       <c r="D2" t="n">
-        <v>538.009522899703</v>
+        <v>21.82916020392783</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8737554567796613</v>
+        <v>8.850455553784995</v>
       </c>
       <c r="C3" t="n">
-        <v>2.611448893296516</v>
+        <v>1.349903093339364</v>
       </c>
       <c r="D3" t="n">
-        <v>4.933282213840222</v>
+        <v>96.53525175858886</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +809,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4.122358610132356</v>
+        <v>14.56226369709294</v>
       </c>
       <c r="C4" t="n">
-        <v>21.16059001733575</v>
+        <v>2.909900195387546</v>
       </c>
       <c r="D4" t="n">
-        <v>12.50746575210436</v>
+        <v>88.17763355233576</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +823,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8.860273030827464</v>
+        <v>18.13778883595982</v>
       </c>
       <c r="C5" t="n">
-        <v>32.17678100668922</v>
+        <v>4.368777283898307</v>
       </c>
       <c r="D5" t="n">
-        <v>14.38260386721577</v>
+        <v>29.35425635697964</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.74719211838983</v>
+        <v>19.24029150782899</v>
       </c>
       <c r="C6" t="n">
-        <v>48.50324532831367</v>
+        <v>5.594980166502573</v>
       </c>
       <c r="D6" t="n">
-        <v>20.0855762811855</v>
+        <v>4.950953672516666</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +851,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.61800233205675</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="C7" t="n">
-        <v>56.35329997147116</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="D7" t="n">
-        <v>23.29589127407256</v>
+        <v>0.3593196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +865,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>69.9298889735003</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="D8" t="n">
-        <v>26.45319189093031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +879,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>78.65468082114168</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="D9" t="n">
-        <v>26.29218526743382</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +893,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>80.71438750465153</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +907,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.19486907152638</v>
+        <v>3.37623035490478</v>
       </c>
       <c r="C11" t="n">
-        <v>80.31874317984003</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +921,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.0179745583127</v>
+        <v>2.603594911662541</v>
       </c>
       <c r="C12" t="n">
-        <v>91.99368687874312</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +935,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>14.56913593102267</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>104.5855829334127</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +949,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14.44249047717483</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>119.8419422574081</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>8.911323911448299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +963,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.39179944945249</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>135.8100686669825</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2.866703296400686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -976,10 +977,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>150.8602609730861</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -990,10 +991,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>149.2217240546982</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1007,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>111.2909197534184</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1021,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>49.95034144437346</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1035,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>9.41496048372691</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1046,7 +1047,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.84761314347087</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1091,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>94.31355670387833</v>
+        <v>3.754203221039802</v>
       </c>
       <c r="C2" t="n">
-        <v>627.2327177570617</v>
+        <v>0.2513274122871835</v>
       </c>
       <c r="D2" t="n">
-        <v>505.7610743106038</v>
+        <v>19.48278319077795</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1106,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8246680715673208</v>
+        <v>10.44088683466483</v>
       </c>
       <c r="C3" t="n">
-        <v>2.768528525976005</v>
+        <v>1.281180754042087</v>
       </c>
       <c r="D3" t="n">
-        <v>4.913647259755287</v>
+        <v>92.45609004744337</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1120,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3.7394770054761</v>
+        <v>15.97892563432108</v>
       </c>
       <c r="C4" t="n">
-        <v>20.45864040879928</v>
+        <v>2.897137475232337</v>
       </c>
       <c r="D4" t="n">
-        <v>11.92038062496477</v>
+        <v>90.89609294539518</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1134,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8.148505945248528</v>
+        <v>20.42035224833366</v>
       </c>
       <c r="C5" t="n">
-        <v>31.34229545807943</v>
+        <v>4.344233591292137</v>
       </c>
       <c r="D5" t="n">
-        <v>14.01444847812322</v>
+        <v>33.55122779263475</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1148,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.740900721536855</v>
+        <v>22.29941735426205</v>
       </c>
       <c r="C6" t="n">
-        <v>47.41645061971246</v>
+        <v>5.715735134124931</v>
       </c>
       <c r="D6" t="n">
-        <v>19.64280806657019</v>
+        <v>6.520768251607316</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1162,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.30049691295753</v>
+        <v>20.48122060599696</v>
       </c>
       <c r="C7" t="n">
-        <v>55.57477404200344</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="D7" t="n">
-        <v>22.57725195456389</v>
+        <v>0.5389794896314989</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1176,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C8" t="n">
-        <v>68.34436643114171</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1190,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.653124265231384</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
-        <v>76.10311853780424</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="D9" t="n">
-        <v>24.62812290873548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1204,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.110618695410402</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>77.72496574521999</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1218,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10.48408373365169</v>
+        <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>78.54177983515331</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="D11" t="n">
-        <v>21.85664913964673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1232,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.93314334511998</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>90.90885566555039</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>18.00819813899924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1246,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12.74799393964483</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>103.8050935085365</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>11.96750451476862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1260,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.06233313145306</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>118.9200811631204</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1274,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>134.3767170187822</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1288,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.066578917439536</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>144.6605242207675</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1304,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>133.6384427451886</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1318,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>89.35376730202346</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1332,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1346,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1402,13 +1403,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>77.01221691193679</v>
+        <v>4.094869674413446</v>
       </c>
       <c r="C2" t="n">
-        <v>760.133867976361</v>
+        <v>0.2905973204570559</v>
       </c>
       <c r="D2" t="n">
-        <v>550.8458741327302</v>
+        <v>20.35064816133213</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1417,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7755806863549802</v>
+        <v>11.64843651088841</v>
       </c>
       <c r="C3" t="n">
-        <v>2.905973204570559</v>
+        <v>1.197732199181109</v>
       </c>
       <c r="D3" t="n">
-        <v>4.874377351585414</v>
+        <v>88.3229322125643</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1431,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3.407646281440679</v>
+        <v>18.02096085915445</v>
       </c>
       <c r="C4" t="n">
-        <v>19.78221624057323</v>
+        <v>2.858849314766712</v>
       </c>
       <c r="D4" t="n">
-        <v>11.38434637844601</v>
+        <v>93.86980674155878</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1445,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7.46128255227576</v>
+        <v>22.26112919379643</v>
       </c>
       <c r="C5" t="n">
-        <v>30.53235360207581</v>
+        <v>4.319689898685966</v>
       </c>
       <c r="D5" t="n">
-        <v>13.67083678163684</v>
+        <v>36.27557767191965</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1459,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.774860980557992</v>
+        <v>25.43904651244335</v>
       </c>
       <c r="C6" t="n">
-        <v>46.41015922285948</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="D6" t="n">
-        <v>19.20003985195487</v>
+        <v>7.768569583705012</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1473,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.102764713776425</v>
+        <v>23.89475737366311</v>
       </c>
       <c r="C7" t="n">
-        <v>54.73636150257666</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="D7" t="n">
-        <v>21.79872602509618</v>
+        <v>0.7785259294677207</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1487,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>19.02627050830318</v>
       </c>
       <c r="C8" t="n">
-        <v>66.7588438887831</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="D8" t="n">
-        <v>23.699389580518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1501,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>12.09218647320796</v>
       </c>
       <c r="C9" t="n">
-        <v>73.55155625446676</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="D9" t="n">
-        <v>22.96406055003713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1515,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>75.02025082002002</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="D10" t="n">
-        <v>22.20713307006285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1529,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.773298395776996</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>76.94251282493525</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>19.01350778814797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1543,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10.84831213192725</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>89.82402445235766</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>14.31977201414398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1557,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.6666888066416</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>103.0246040836603</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>8.065057390387548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1571,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7.682175785731292</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>117.6909330374034</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2.765583282863265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1585,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3.583379120500858</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>131.8683516344315</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1599,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>136.3942085510093</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1615,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>116.6384994984508</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1629,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>70.62692984351554</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1643,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>24.67426505083508</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1657,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>3.362485887045325</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1713,13 +1714,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>72.46083455504858</v>
+        <v>4.62599518241097</v>
       </c>
       <c r="C2" t="n">
-        <v>712.6997458979721</v>
+        <v>0.2415099352447153</v>
       </c>
       <c r="D2" t="n">
-        <v>559.8622450485328</v>
+        <v>19.87450052477243</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1728,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7264933011426398</v>
+        <v>12.63509295365645</v>
       </c>
       <c r="C3" t="n">
-        <v>3.023782929080176</v>
+        <v>1.148644813968768</v>
       </c>
       <c r="D3" t="n">
-        <v>4.82038122785184</v>
+        <v>84.68555696832988</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1742,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3.101340997715674</v>
+        <v>19.8843180018149</v>
       </c>
       <c r="C4" t="n">
-        <v>19.1440802328128</v>
+        <v>2.795035713990669</v>
       </c>
       <c r="D4" t="n">
-        <v>10.89936301254809</v>
+        <v>94.02295938342127</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1756,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.823146544515334</v>
+        <v>24.44551783574558</v>
       </c>
       <c r="C5" t="n">
-        <v>29.74695543867836</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="D5" t="n">
-        <v>13.35176877775663</v>
+        <v>38.97538385859838</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1770,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.889324551327369</v>
+        <v>28.05540414426111</v>
       </c>
       <c r="C6" t="n">
-        <v>45.44411948188061</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="D6" t="n">
-        <v>18.71701998146544</v>
+        <v>9.096874227550947</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1784,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.024805734513427</v>
+        <v>27.18852092141116</v>
       </c>
       <c r="C7" t="n">
-        <v>53.89794896314989</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="D7" t="n">
-        <v>20.90042687571034</v>
+        <v>1.077958979262998</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1798,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>22.61455836732527</v>
       </c>
       <c r="C8" t="n">
-        <v>65.08987279156352</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="D8" t="n">
-        <v>22.36421270274234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1812,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>15.75312366234431</v>
       </c>
       <c r="C9" t="n">
-        <v>71.1109314617092</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="D9" t="n">
-        <v>21.29999819133879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1826,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>72.60024272905163</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>19.92947839621025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1840,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>75.52094214918587</v>
+        <v>2.132356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1854,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9.546514676095983</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>88.95615948180348</v>
+        <v>0.2169662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>10.84831213192725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1868,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8.325220532012953</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>101.9839515171587</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>5.203262832508096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1882,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>116.4617849116864</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1.229148125717007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1896,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>127.9266346018806</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1912,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>126.4746297472996</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1926,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>99.63855625171304</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1940,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54.57535487908019</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1954,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1968,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2.017491532227195</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2024,13 +2025,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>60.46976809537804</v>
+        <v>4.884194828627882</v>
       </c>
       <c r="C2" t="n">
-        <v>901.614511383073</v>
+        <v>0.2856885819358218</v>
       </c>
       <c r="D2" t="n">
-        <v>504.4062624787433</v>
+        <v>17.25519764984194</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2039,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6774059159302992</v>
+        <v>13.77882902910398</v>
       </c>
       <c r="C3" t="n">
-        <v>3.126866438026091</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="D3" t="n">
-        <v>4.756567627075796</v>
+        <v>81.23962252642356</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2053,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.820561154301086</v>
+        <v>21.41584442043992</v>
       </c>
       <c r="C4" t="n">
-        <v>18.5314696653628</v>
+        <v>2.692933952749001</v>
       </c>
       <c r="D4" t="n">
-        <v>10.45266780711579</v>
+        <v>93.89533218186919</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2067,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.234097921967248</v>
+        <v>26.60536278508857</v>
       </c>
       <c r="C5" t="n">
-        <v>29.01064466049325</v>
+        <v>4.246058820867455</v>
       </c>
       <c r="D5" t="n">
-        <v>13.03270077387641</v>
+        <v>41.47884050442774</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2081,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.084291433844984</v>
+        <v>30.26924521733767</v>
       </c>
       <c r="C6" t="n">
-        <v>44.51833139677587</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="D6" t="n">
-        <v>18.19374845510189</v>
+        <v>10.465430527271</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2095,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.066619975168541</v>
+        <v>30.42239785920016</v>
       </c>
       <c r="C7" t="n">
-        <v>52.99964981376406</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="D7" t="n">
-        <v>20.00212772632452</v>
+        <v>1.377392029058275</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2109,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>63.42090169434395</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="D8" t="n">
-        <v>20.9455872701057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2123,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>18.97031088916111</v>
       </c>
       <c r="C9" t="n">
-        <v>68.78124415953151</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2137,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>11.67298020349457</v>
       </c>
       <c r="C10" t="n">
-        <v>70.32258805519903</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="D10" t="n">
-        <v>17.50947030524187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2151,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.996335051090269</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>74.09937147343649</v>
+        <v>2.132356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>13.14952875068177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2165,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8.027750977626168</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>88.0882945112493</v>
+        <v>0.2169662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>7.810784734987623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2179,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.983752257384309</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>100.9432989506571</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3.121957699504857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2193,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.765583282863265</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>114.6180627231109</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2210,7 @@
         <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>122.9099038331794</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -2223,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>114.9017878096382</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2237,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>83.5830542964607</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2251,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>41.7340949075319</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2265,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>11.4344155113626</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2279,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2335,13 +2336,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>53.9882697519406</v>
+        <v>5.250386722311942</v>
       </c>
       <c r="C2" t="n">
-        <v>791.6990201633043</v>
+        <v>0.2228567288640259</v>
       </c>
       <c r="D2" t="n">
-        <v>459.6748918301458</v>
+        <v>15.33293564492668</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2350,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6283185307179586</v>
+        <v>14.62313205475624</v>
       </c>
       <c r="C3" t="n">
-        <v>3.215223731408304</v>
+        <v>1.050470043544087</v>
       </c>
       <c r="D3" t="n">
-        <v>4.682936549257286</v>
+        <v>77.72005700669875</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2364,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.565306751196915</v>
+        <v>22.96013355922015</v>
       </c>
       <c r="C4" t="n">
-        <v>17.9443845382232</v>
+        <v>2.590832191507332</v>
       </c>
       <c r="D4" t="n">
-        <v>10.03149804199391</v>
+        <v>93.51245057721293</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2378,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5.669592992025331</v>
+        <v>28.59340188618836</v>
       </c>
       <c r="C5" t="n">
-        <v>28.29887757491431</v>
+        <v>4.172427743048945</v>
       </c>
       <c r="D5" t="n">
-        <v>12.7136327699962</v>
+        <v>43.81049130201392</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2392,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6.31950997223672</v>
+        <v>32.56358960216246</v>
       </c>
       <c r="C6" t="n">
-        <v>43.59254331167113</v>
+        <v>5.796238445873169</v>
       </c>
       <c r="D6" t="n">
-        <v>17.63022527286423</v>
+        <v>11.87423848286517</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2406,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.228207435741766</v>
+        <v>33.23706852727577</v>
       </c>
       <c r="C7" t="n">
-        <v>52.04146405441917</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="D7" t="n">
-        <v>19.04394196697963</v>
+        <v>1.736711688812608</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2420,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>28.95664853675967</v>
       </c>
       <c r="C8" t="n">
-        <v>61.75193059712436</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="D8" t="n">
-        <v>19.61041039233004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2434,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="C9" t="n">
-        <v>66.45155685735384</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="D9" t="n">
-        <v>17.86093598336221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2448,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>14.37769512869454</v>
       </c>
       <c r="C10" t="n">
-        <v>68.32964021557801</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="D10" t="n">
-        <v>15.08946221427348</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2462,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.107853378746905</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>72.85549713215578</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="D11" t="n">
-        <v>10.30638739918301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2476,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.292021036517808</v>
+        <v>4.556291095409447</v>
       </c>
       <c r="C12" t="n">
-        <v>87.22042954069512</v>
+        <v>0.2169662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>5.424156065963627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2490,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.902447124381071</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>99.90264638415543</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1.560978849752429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2503,10 +2504,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.229148125717007</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>112.1597664716769</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -2517,10 +2518,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>116.4598214162779</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -2534,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>102.9156300884889</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2548,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>68.9442142784365</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2562,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2576,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>7.221736112439537</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2646,13 +2647,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.13152280130262</v>
+        <v>5.402557616470197</v>
       </c>
       <c r="C2" t="n">
-        <v>964.3550619183738</v>
+        <v>0.2503456645829367</v>
       </c>
       <c r="D2" t="n">
-        <v>455.141180931934</v>
+        <v>15.00306841629976</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2661,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5841398840268521</v>
+        <v>15.44780012632356</v>
       </c>
       <c r="C3" t="n">
-        <v>3.288854809226815</v>
+        <v>0.9915651812892785</v>
       </c>
       <c r="D3" t="n">
-        <v>4.599487994396307</v>
+        <v>74.21030896401639</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2675,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.335577788403162</v>
+        <v>24.23640557474101</v>
       </c>
       <c r="C4" t="n">
-        <v>17.38282485139402</v>
+        <v>2.514255870576081</v>
       </c>
       <c r="D4" t="n">
-        <v>9.648616437337653</v>
+        <v>92.88707728960772</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2689,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5.154175447295755</v>
+        <v>30.48326621686347</v>
       </c>
       <c r="C5" t="n">
-        <v>27.61165418194155</v>
+        <v>4.074252972624264</v>
       </c>
       <c r="D5" t="n">
-        <v>12.37002107350981</v>
+        <v>45.9703362513569</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2703,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.635231822376692</v>
+        <v>34.73717901936489</v>
       </c>
       <c r="C6" t="n">
-        <v>42.7070068824405</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="D6" t="n">
-        <v>17.02645043475243</v>
+        <v>13.32329809433347</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2717,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>35.81219275551515</v>
       </c>
       <c r="C7" t="n">
-        <v>51.08327829507428</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="D7" t="n">
-        <v>18.08575620763474</v>
+        <v>2.155917958525996</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2731,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="C8" t="n">
-        <v>60.0829594999048</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="D8" t="n">
-        <v>18.19178495969339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2745,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
+        <v>24.96093538047515</v>
+      </c>
+      <c r="C9" t="n">
         <v>5.324999547834698</v>
       </c>
-      <c r="C9" t="n">
-        <v>64.34374453633593</v>
-      </c>
       <c r="D9" t="n">
-        <v>15.97499864350409</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2759,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>16.94005663677871</v>
       </c>
       <c r="C10" t="n">
-        <v>66.47904579307277</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>12.66945412330509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2773,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>9.950994730245668</v>
       </c>
       <c r="C11" t="n">
-        <v>71.78931912534375</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="D11" t="n">
-        <v>7.818638716621595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2787,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.556291095409447</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C12" t="n">
-        <v>86.35256457014094</v>
+        <v>0.2169662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>3.471459882216721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2801,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>98.6018306760284</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2814,10 +2815,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>109.0868961573843</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -2828,10 +2829,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>108.9347252632261</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -2845,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>90.51615658385167</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2859,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>56.19425684338318</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2873,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>23.007257449024</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2887,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2957,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.9476328809722</v>
+        <v>5.404521111878692</v>
       </c>
       <c r="C2" t="n">
-        <v>894.6715916186395</v>
+        <v>0.2081305133003238</v>
       </c>
       <c r="D2" t="n">
-        <v>425.6072647450772</v>
+        <v>13.80926320793563</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2972,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5399612373357457</v>
+        <v>15.94849145548944</v>
       </c>
       <c r="C3" t="n">
-        <v>3.347759671481623</v>
+        <v>0.9522952731194061</v>
       </c>
       <c r="D3" t="n">
-        <v>4.511130701014094</v>
+        <v>70.90181920070465</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2986,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.131374265919825</v>
+        <v>25.33399950808894</v>
       </c>
       <c r="C4" t="n">
-        <v>16.84679060487526</v>
+        <v>2.412154109334413</v>
       </c>
       <c r="D4" t="n">
-        <v>9.291260272991813</v>
+        <v>92.04473775936395</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +3000,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.66330159517235</v>
+        <v>32.12769362147687</v>
       </c>
       <c r="C5" t="n">
-        <v>26.94897448157495</v>
+        <v>4.000621894805753</v>
       </c>
       <c r="D5" t="n">
-        <v>12.02640937702343</v>
+        <v>48.37561812676159</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3014,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.031456984264904</v>
+        <v>36.74976181307086</v>
       </c>
       <c r="C6" t="n">
-        <v>41.861722109084</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="D6" t="n">
-        <v>16.38242394076653</v>
+        <v>14.20883452356409</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3028,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.850815406683489</v>
+        <v>38.14777054391831</v>
       </c>
       <c r="C7" t="n">
-        <v>50.12509253572939</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="D7" t="n">
-        <v>17.0676838383308</v>
+        <v>2.455351008321272</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3042,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="C8" t="n">
-        <v>58.41398840268521</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="D8" t="n">
-        <v>16.77315952705676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3056,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="C9" t="n">
-        <v>62.34686970589792</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="D9" t="n">
-        <v>14.08906130364597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3070,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="C10" t="n">
-        <v>64.77080478768332</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>10.39179944945249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3084,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>11.72795807493239</v>
       </c>
       <c r="C11" t="n">
-        <v>70.72314111853171</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="D11" t="n">
-        <v>5.686282702997524</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3098,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>85.26773335694821</v>
+        <v>0.2169662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>1.952696183746906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3111,10 +3112,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.040652566501619</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="C13" t="n">
-        <v>97.04085182627598</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -3125,10 +3126,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>105.0921647488041</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -3139,10 +3140,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>100.6929532860741</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3156,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>78.52999886270236</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3170,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>44.860961345558</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3184,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3198,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>2.407245370813179</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3268,13 +3269,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.50045464945439</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C2" t="n">
-        <v>987.6126650319808</v>
+        <v>0.2100940087088174</v>
       </c>
       <c r="D2" t="n">
-        <v>380.7129239775749</v>
+        <v>12.14716434464579</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3283,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4957825906446393</v>
+        <v>16.07611865704152</v>
       </c>
       <c r="C3" t="n">
-        <v>3.396847056693964</v>
+        <v>0.9032078879070655</v>
       </c>
       <c r="D3" t="n">
-        <v>4.422773407631881</v>
+        <v>67.67677799225388</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3297,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.939933463591697</v>
+        <v>26.04871183678062</v>
       </c>
       <c r="C4" t="n">
-        <v>16.32351907851172</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="D4" t="n">
-        <v>8.946666828801183</v>
+        <v>91.90434783765667</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3311,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.221515128261285</v>
+        <v>33.52668410002858</v>
       </c>
       <c r="C5" t="n">
-        <v>26.31083847381452</v>
+        <v>3.877903431774902</v>
       </c>
       <c r="D5" t="n">
-        <v>11.68279768053704</v>
+        <v>48.89103567149117</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3325,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.467933802027235</v>
+        <v>38.56108632740622</v>
       </c>
       <c r="C6" t="n">
-        <v>41.0164373357275</v>
+        <v>5.594980166502573</v>
       </c>
       <c r="D6" t="n">
-        <v>15.73839744678062</v>
+        <v>15.13462260866883</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3339,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.311835917051991</v>
+        <v>39.82459562277186</v>
       </c>
       <c r="C7" t="n">
-        <v>49.10702016642545</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="D7" t="n">
-        <v>16.04961146902685</v>
+        <v>2.75478405811655</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3353,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>36.63391558396972</v>
       </c>
       <c r="C8" t="n">
-        <v>56.74501730546564</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="D8" t="n">
-        <v>15.27108553955913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3367,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="C9" t="n">
-        <v>60.34999487545991</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="D9" t="n">
-        <v>12.20312396378785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3381,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.555309347705201</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="C10" t="n">
-        <v>63.20491719940966</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="D10" t="n">
-        <v>8.256498192715677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3395,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="C11" t="n">
-        <v>69.83465944618834</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="D11" t="n">
-        <v>3.909319358310797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3409,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C12" t="n">
-        <v>84.18290214375548</v>
+        <v>0.2169662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3422,10 +3423,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>94.95954669327276</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -3436,10 +3437,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>100.175572245936</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -3450,10 +3451,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>91.73450548482195</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3467,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66.95715692504096</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3481,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41654843070368</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3495,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>11.77115497391926</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3509,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.203622685406589</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3579,13 +3580,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.94470333339269</v>
+        <v>5.505641125416113</v>
       </c>
       <c r="C2" t="n">
-        <v>845.1345659577539</v>
+        <v>0.1619883712007237</v>
       </c>
       <c r="D2" t="n">
-        <v>359.1733793463998</v>
+        <v>11.58658640552086</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3594,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4565126824747668</v>
+        <v>16.02703127182918</v>
       </c>
       <c r="C3" t="n">
-        <v>3.436116964863836</v>
+        <v>0.8639379797371931</v>
       </c>
       <c r="D3" t="n">
-        <v>4.329507375728434</v>
+        <v>64.63826884760999</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3608,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.761255381418778</v>
+        <v>26.30396623988479</v>
       </c>
       <c r="C4" t="n">
-        <v>15.82577299245858</v>
+        <v>2.220713307006285</v>
       </c>
       <c r="D4" t="n">
-        <v>8.62759882492097</v>
+        <v>89.83678717251287</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3622,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.804272353956391</v>
+        <v>34.23845118560752</v>
       </c>
       <c r="C5" t="n">
-        <v>25.69724615866027</v>
+        <v>3.755184968744051</v>
       </c>
       <c r="D5" t="n">
-        <v>11.31464229144449</v>
+        <v>49.38190952361457</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3636,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.984913931537804</v>
+        <v>40.21140421824511</v>
       </c>
       <c r="C6" t="n">
-        <v>40.21140421824511</v>
+        <v>5.554728510628454</v>
       </c>
       <c r="D6" t="n">
-        <v>15.05411929692059</v>
+        <v>16.06041069377357</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3650,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.832743037379548</v>
+        <v>41.50142070162541</v>
       </c>
       <c r="C7" t="n">
-        <v>48.08894779712151</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="D7" t="n">
-        <v>14.97165248976386</v>
+        <v>3.054217107911827</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3664,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>38.63668090063322</v>
       </c>
       <c r="C8" t="n">
-        <v>55.15949476310704</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D8" t="n">
-        <v>13.76901155206151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3678,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.882812170296134</v>
+        <v>32.28280975874785</v>
       </c>
       <c r="C9" t="n">
-        <v>58.57499502618167</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="D9" t="n">
-        <v>10.31718662392973</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3692,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>23.91537407545231</v>
       </c>
       <c r="C10" t="n">
-        <v>61.78138302825178</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="D10" t="n">
-        <v>6.405903770210439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3706,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.665445017030089</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="C11" t="n">
-        <v>68.94617777384498</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="D11" t="n">
-        <v>2.487748682561417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3720,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>8.895615948180348</v>
       </c>
       <c r="C12" t="n">
-        <v>83.09807093056276</v>
+        <v>0.2169662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4339324852770902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3733,10 +3734,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>92.6180784186441</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -3747,10 +3748,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>94.64440568020952</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -3761,10 +3762,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>82.77605768356982</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3778,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>56.62426233784328</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3792,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>27.38879745307752</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3806,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3820,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6018113427032947</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3890,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.483682823024189</v>
+        <v>0.8982991493858314</v>
       </c>
       <c r="C2" t="n">
-        <v>19.26483520043516</v>
+        <v>0.3730641276137879</v>
       </c>
       <c r="D2" t="n">
-        <v>162.7659153824872</v>
+        <v>41.10184938599696</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3905,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6234097921967247</v>
+        <v>0.1178097245096172</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4270602513473625</v>
+        <v>1.153553552490002</v>
       </c>
       <c r="D3" t="n">
-        <v>3.902447124381071</v>
+        <v>131.416747690478</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3919,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.09531164276995</v>
+        <v>0.8168140899333463</v>
       </c>
       <c r="C4" t="n">
-        <v>28.09074706161399</v>
+        <v>3.177917318646925</v>
       </c>
       <c r="D4" t="n">
-        <v>19.73116535995239</v>
+        <v>16.57877348161589</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3933,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.95969159086365</v>
+        <v>1.546252634188727</v>
       </c>
       <c r="C5" t="n">
-        <v>39.785325714602</v>
+        <v>3.288854809226816</v>
       </c>
       <c r="D5" t="n">
-        <v>17.7450897542611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3947,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.89060939866788</v>
+        <v>1.811324514335366</v>
       </c>
       <c r="C6" t="n">
-        <v>60.33723215530473</v>
+        <v>3.421390749300135</v>
       </c>
       <c r="D6" t="n">
-        <v>25.92206638293279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3961,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.23033516206628</v>
+        <v>1.976258128648829</v>
       </c>
       <c r="C7" t="n">
-        <v>61.14422876819559</v>
+        <v>3.473423377625215</v>
       </c>
       <c r="D7" t="n">
-        <v>24.91282974296706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3975,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.0414797499524</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>81.19544387973245</v>
+        <v>3.421390749300134</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7952820603647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3989,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30.61874740004951</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>93.07655459652732</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4003,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27.75891633757857</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>118.7227498745668</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="D10" t="n">
-        <v>46.83427423109409</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4017,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23.63361248433346</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>102.3530886539554</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="D11" t="n">
-        <v>39.98167525545134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4031,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>22.99842171968578</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>109.7849187751038</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>42.30841731451629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4045,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>24.19517217116264</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>110.8294983324224</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>44.48789721794422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4059,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>28.27040689149115</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>127.5241180431394</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>43.63475846295374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4073,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>31.53373626040754</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>147.2768818525853</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4087,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>35.54515737996002</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>164.0863660446991</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>38.85168364786328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4101,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>39.19431359664542</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>180.8605073194601</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4115,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>43.87430490278995</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>197.4343720625548</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>26.21757244191107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4129,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>45.7376620454504</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>216.0502720304828</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4143,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>46.40230524122548</v>
+        <v>2.017491532227195</v>
       </c>
       <c r="C20" t="n">
-        <v>381.9783967683489</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2.017491532227195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4156,7 +4157,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>9.132205934201133</v>
+        <v>5.315511026478704</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -4201,13 +4202,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>5.425137813667874</v>
       </c>
       <c r="C2" t="n">
-        <v>732.855026266159</v>
+        <v>0.1286089492563322</v>
       </c>
       <c r="D2" t="n">
-        <v>357.6173092351686</v>
+        <v>11.76919147851076</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4216,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4172427743048944</v>
+        <v>15.99757884070178</v>
       </c>
       <c r="C3" t="n">
-        <v>3.465569395991241</v>
+        <v>0.8099418560036185</v>
       </c>
       <c r="D3" t="n">
-        <v>4.231332605303753</v>
+        <v>61.73720438156067</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4230,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.595340019401067</v>
+        <v>26.29120351972959</v>
       </c>
       <c r="C4" t="n">
-        <v>15.35355234671587</v>
+        <v>2.144136986075034</v>
       </c>
       <c r="D4" t="n">
-        <v>8.321293541195963</v>
+        <v>87.74370106705868</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4244,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.436116964863837</v>
+        <v>35.02384934900497</v>
       </c>
       <c r="C5" t="n">
-        <v>25.10819753611218</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="D5" t="n">
-        <v>10.94648690235194</v>
+        <v>49.7746086053133</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4258,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.542145716922492</v>
+        <v>40.97618567985338</v>
       </c>
       <c r="C6" t="n">
-        <v>39.40637110076273</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="D6" t="n">
-        <v>14.32958949118645</v>
+        <v>16.9459471230042</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4272,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.413536767666159</v>
+        <v>43.11835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>47.01098881785852</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="D7" t="n">
-        <v>13.89369351050086</v>
+        <v>3.353650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4286,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.421390749300134</v>
+        <v>40.47254910757476</v>
       </c>
       <c r="C8" t="n">
-        <v>53.57397222074844</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="D8" t="n">
-        <v>12.2669375645639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4300,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.328124717396686</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="C9" t="n">
-        <v>56.91093266748334</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="D9" t="n">
-        <v>8.542186774651494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4314,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="C10" t="n">
-        <v>60.50020227420969</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="D10" t="n">
-        <v>4.697662764820988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4328,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>17.23654444346124</v>
       </c>
       <c r="C11" t="n">
-        <v>68.05769610150162</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="D11" t="n">
-        <v>1.421570675749381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4342,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4339324852770902</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="C12" t="n">
-        <v>81.79627347473149</v>
+        <v>0.2169662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2169662426385451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4355,10 +4356,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>89.75628386076465</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -4369,10 +4370,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>88.80595208305373</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -4383,10 +4384,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>73.81760988231767</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -4400,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>47.11799931762141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4414,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>20.77770841267949</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -4428,7 +4429,318 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>5.350524988145117</v>
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Branching</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Foliose</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>5.459498983316512</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1158462291011236</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12.6822168434603</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>15.80613803837365</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.755945732270044</v>
+      </c>
+      <c r="D3" t="n">
+        <v>59.02267197931824</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>26.13805087786708</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.054797944988574</v>
+      </c>
+      <c r="D4" t="n">
+        <v>85.62508952129406</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>35.14656781203582</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.509748042682348</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50.04458922398117</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>42.18373535607696</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.353470231257858</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17.83148355223482</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>44.31609136970101</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6.587527095496098</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.712969817461437</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>42.05807164993335</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6.592435834017332</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.08344855486097888</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>36.0546844384641</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.657812019574366</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>27.75891633757857</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.270602513473626</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>19.01350778814797</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.487748682561417</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>11.49921085984289</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.2169662426385451</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5.983752257384309</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2.765583282863265</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.7166758241001715</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -4512,13 +4824,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.71692217047421</v>
+        <v>0.9954921721062657</v>
       </c>
       <c r="C2" t="n">
-        <v>199.7640593647325</v>
+        <v>0.3652101459798134</v>
       </c>
       <c r="D2" t="n">
-        <v>361.2900273967559</v>
+        <v>38.13402607605885</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4838,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8001243789611504</v>
+        <v>2.577087723647877</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8148505945248528</v>
+        <v>1.187914722138641</v>
       </c>
       <c r="D3" t="n">
-        <v>4.211697651218817</v>
+        <v>128.0689880189964</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4852,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>8.882853228025139</v>
+        <v>0.3956443248114646</v>
       </c>
       <c r="C4" t="n">
-        <v>27.0697294491973</v>
+        <v>3.012001956629214</v>
       </c>
       <c r="D4" t="n">
-        <v>18.46765606458675</v>
+        <v>31.51115606320987</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4866,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.63433219013046</v>
+        <v>1.374446785945535</v>
       </c>
       <c r="C5" t="n">
-        <v>38.77903431774902</v>
+        <v>3.755184968744051</v>
       </c>
       <c r="D5" t="n">
-        <v>17.42602175038089</v>
+        <v>1.521708941582556</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4880,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.44154978719959</v>
+        <v>2.13333776132832</v>
       </c>
       <c r="C6" t="n">
-        <v>58.40515267334701</v>
+        <v>3.743403996293088</v>
       </c>
       <c r="D6" t="n">
-        <v>24.59376173908685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4894,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.07441720354028</v>
+        <v>2.275691178444106</v>
       </c>
       <c r="C7" t="n">
-        <v>60.7250224984822</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="D7" t="n">
-        <v>24.97271635292611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4908,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.12078032981814</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>79.60992133737385</v>
+        <v>3.588287859022091</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4922,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26.5140602485936</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>92.85467961536754</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="D9" t="n">
-        <v>38.93905919354123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4936,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>23.48831382410494</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>112.1744926872406</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="D10" t="n">
-        <v>42.13661146627311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4950,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>20.7904711328347</v>
+        <v>1.243874341280709</v>
       </c>
       <c r="C11" t="n">
-        <v>98.97685829905066</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>38.38240824523329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4964,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20.82875929330033</v>
+        <v>0.2169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>106.0964926502485</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>40.57268737340794</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4978,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22.89435646303562</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>110.0490089075462</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>41.62610266006477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4992,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>26.73397173434489</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>126.9095439802809</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>40.25460111723197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +5006,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>29.74204670015712</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>145.8435302043849</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>37.9838186773091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +5020,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>33.06526267903257</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>162.0197871272596</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>33.47857846252048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +5034,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>37.30543101367455</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>178.4994040907466</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>26.9165768073348</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +5048,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>39.59388491227386</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>195.2941620672968</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>17.12167996206437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +5062,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>40.92317130382404</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>258.7788773624167</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.814490741626358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4764,10 +5076,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>18.15742379004475</v>
+        <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>242.7714810446724</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4778,7 +5090,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>5.400691548333707</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -4823,13 +5135,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>62.75724024627311</v>
+        <v>1.151590057081509</v>
       </c>
       <c r="C2" t="n">
-        <v>391.0880337160552</v>
+        <v>0.4427682146153115</v>
       </c>
       <c r="D2" t="n">
-        <v>362.8166450768597</v>
+        <v>31.5013385861674</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +5149,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9081166264282996</v>
+        <v>3.406664533736432</v>
       </c>
       <c r="C3" t="n">
-        <v>1.16337102953247</v>
+        <v>1.207549676223577</v>
       </c>
       <c r="D3" t="n">
-        <v>4.452225838759285</v>
+        <v>124.4217952977195</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +5163,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7.861835615608458</v>
+        <v>3.994731408580271</v>
       </c>
       <c r="C4" t="n">
-        <v>26.09976271740145</v>
+        <v>2.935425635697963</v>
       </c>
       <c r="D4" t="n">
-        <v>17.3445366909284</v>
+        <v>44.72057142385071</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +5177,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.40714755982195</v>
+        <v>0.8835729338221295</v>
       </c>
       <c r="C5" t="n">
-        <v>37.77274292089604</v>
+        <v>4.025165587411923</v>
       </c>
       <c r="D5" t="n">
-        <v>17.00877897607599</v>
+        <v>4.295146206079796</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +5191,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.03274183160542</v>
+        <v>2.052834449580081</v>
       </c>
       <c r="C6" t="n">
-        <v>56.63407981488576</v>
+        <v>4.065417243286043</v>
       </c>
       <c r="D6" t="n">
-        <v>23.50696703048563</v>
+        <v>0.08050331174823847</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +5205,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.0382724649324</v>
+        <v>2.635010838198439</v>
       </c>
       <c r="C7" t="n">
-        <v>60.24592961880976</v>
+        <v>3.952516257297658</v>
       </c>
       <c r="D7" t="n">
-        <v>25.03260296288517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +5219,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.28352946454485</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>78.1912959047372</v>
+        <v>3.75518496874405</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +5233,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22.85312305945724</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>91.85624220014853</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +5247,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20.07183181332604</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>106.1956491683775</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="D10" t="n">
-        <v>38.72012945549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +5261,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18.48041878474196</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>95.60062794414587</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +5275,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19.09302935219197</v>
+        <v>0.6508987279156353</v>
       </c>
       <c r="C12" t="n">
-        <v>103.0589652533089</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>38.40302494702248</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +5289,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21.853703896534</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>109.26851948267</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>38.76430810218531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +5303,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>25.19753657719863</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>126.2949699174224</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>36.56715674008095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5317,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27.95035713990669</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>144.0518406441345</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33.32542582065798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5331,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>31.41199954508094</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>159.9532082098201</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5345,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>176.138300862033</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>19.36104647545135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5359,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>35.84851742057228</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>205.995212043587</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5373,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>22.26701968002191</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>244.3354051375377</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5075,10 +5387,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3.362485887045325</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>154.0018536266759</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5089,7 +5401,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>5.484060644689134</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -5134,13 +5446,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>110.3661134160179</v>
+        <v>1.517781950765569</v>
       </c>
       <c r="C2" t="n">
-        <v>569.7749516183129</v>
+        <v>0.5046183199828606</v>
       </c>
       <c r="D2" t="n">
-        <v>484.9195522971482</v>
+        <v>31.12140222462389</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5460,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9621127501618741</v>
+        <v>4.025165587411922</v>
       </c>
       <c r="C3" t="n">
-        <v>1.47753029489145</v>
+        <v>1.281180754042087</v>
       </c>
       <c r="D3" t="n">
-        <v>4.633849164044945</v>
+        <v>119.7683111795896</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5474,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6.993970645054278</v>
+        <v>6.202681995431348</v>
       </c>
       <c r="C4" t="n">
-        <v>25.18084686622644</v>
+        <v>2.884374755077129</v>
       </c>
       <c r="D4" t="n">
-        <v>16.33628179866692</v>
+        <v>56.30912132478006</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5488,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.30268139254428</v>
+        <v>4.491495746929158</v>
       </c>
       <c r="C5" t="n">
-        <v>36.79099521664922</v>
+        <v>4.147884050442775</v>
       </c>
       <c r="D5" t="n">
-        <v>16.56699250916493</v>
+        <v>8.025787482217677</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5502,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.66418553188536</v>
+        <v>1.56981457909065</v>
       </c>
       <c r="C6" t="n">
-        <v>55.02401357992099</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="D6" t="n">
-        <v>22.66168225712913</v>
+        <v>0.4025165587411924</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5516,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.06201433628357</v>
+        <v>2.694897448157494</v>
       </c>
       <c r="C7" t="n">
-        <v>59.70695012917827</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="D7" t="n">
-        <v>25.03260296288517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5530,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.52972715413255</v>
+        <v>3.00414797499524</v>
       </c>
       <c r="C8" t="n">
-        <v>76.85611902696155</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5544,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.63593583264045</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>90.30311733203008</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5558,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17.36711688812608</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>100.9285727350934</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5572,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16.52575910558656</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>92.40209392370977</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5586,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17.7912318963607</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>100.4553703416464</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5600,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20.55288818840698</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>108.4880300577938</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>35.64235040268046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5614,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>23.66110142005238</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>125.3731088231347</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>32.57242533150067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5628,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>26.15866757965626</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>142.260151083884</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5642,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>157.8866292923805</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5656,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>31.16656261901925</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>177.5549627992612</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5670,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>23.54230994783851</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>209.2055270364741</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.140209995258047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5372,10 +5684,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>207.6249132326367</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -5386,10 +5698,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>97.51209072431442</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5400,7 +5712,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>4.770818137655528</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -5445,13 +5757,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>133.5569576857361</v>
+        <v>1.770091110756999</v>
       </c>
       <c r="C2" t="n">
-        <v>567.1605574819037</v>
+        <v>0.4172427743048944</v>
       </c>
       <c r="D2" t="n">
-        <v>446.2671634332471</v>
+        <v>25.69528266325177</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5771,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9817477042468105</v>
+        <v>5.090361846519713</v>
       </c>
       <c r="C3" t="n">
-        <v>1.757328390601791</v>
+        <v>1.379355524466769</v>
       </c>
       <c r="D3" t="n">
-        <v>4.766385104118265</v>
+        <v>115.4486212809037</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5785,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6.240970155896973</v>
+        <v>7.67039481328033</v>
       </c>
       <c r="C4" t="n">
-        <v>24.30021917551705</v>
+        <v>2.846086594611503</v>
       </c>
       <c r="D4" t="n">
-        <v>15.41736594749191</v>
+        <v>66.28956848615313</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5799,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.27184630308513</v>
+        <v>7.878525326580655</v>
       </c>
       <c r="C5" t="n">
-        <v>35.80924751240241</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="D5" t="n">
-        <v>16.10066234964769</v>
+        <v>12.59091430696535</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5813,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.37613254391355</v>
+        <v>4.628940425523712</v>
       </c>
       <c r="C6" t="n">
-        <v>53.53470231257858</v>
+        <v>4.789947049020189</v>
       </c>
       <c r="D6" t="n">
-        <v>21.9774041072691</v>
+        <v>0.845284773356504</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5827,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>2.335577788403162</v>
       </c>
       <c r="C7" t="n">
-        <v>59.10808402958771</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="D7" t="n">
-        <v>24.97271635292611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5841,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.94282195344221</v>
+        <v>3.171045084717197</v>
       </c>
       <c r="C8" t="n">
-        <v>75.52094214918588</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5855,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.86249856814321</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>88.41717999217197</v>
+        <v>3.660937189136355</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5869,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.23181563138926</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>96.08855655315658</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5883,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15.10418842983717</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="C11" t="n">
-        <v>89.55895257221101</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="D11" t="n">
-        <v>33.22921454564179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5897,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16.70640068316797</v>
+        <v>1.518763698469816</v>
       </c>
       <c r="C12" t="n">
-        <v>98.28570791526093</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5911,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19.25207248027995</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>107.7075406329176</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5925,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>22.12466626290612</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>124.4512477288469</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>28.27040689149115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5939,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>24.36697801940583</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>140.4684615236336</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5953,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>26.45221014322606</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>157.0599977254047</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>13.63942085510094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5967,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>23.13881164139307</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>179.443845382232</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5981,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11.23610247510475</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>200.6446870554419</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5683,10 +5995,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.407245370813179</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>166.0999305861093</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -5700,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>61.86974032163398</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5711,7 +6023,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>4.032183322181856</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -5756,13 +6068,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>136.122264436933</v>
+        <v>2.038108234016379</v>
       </c>
       <c r="C2" t="n">
-        <v>554.1278567080271</v>
+        <v>0.3504839304161113</v>
       </c>
       <c r="D2" t="n">
-        <v>425.8036142859266</v>
+        <v>22.13546548765283</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +6082,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9768389657255764</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C3" t="n">
-        <v>2.007674055184727</v>
+        <v>1.384264262988003</v>
       </c>
       <c r="D3" t="n">
-        <v>4.854742397500477</v>
+        <v>110.4269817736812</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +6096,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5.602834148136547</v>
+        <v>9.546514676095985</v>
       </c>
       <c r="C4" t="n">
-        <v>23.45787964527329</v>
+        <v>2.858849314766712</v>
       </c>
       <c r="D4" t="n">
-        <v>14.58778913740336</v>
+        <v>75.49148971805847</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +6110,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.31464229144449</v>
+        <v>10.52924412804704</v>
       </c>
       <c r="C5" t="n">
-        <v>34.85204350076177</v>
+        <v>4.344233591292137</v>
       </c>
       <c r="D5" t="n">
-        <v>15.63433219013046</v>
+        <v>16.49336143134642</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +6124,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.12833121181585</v>
+        <v>8.694357668809754</v>
       </c>
       <c r="C6" t="n">
-        <v>52.1258943569844</v>
+        <v>5.031456984264904</v>
       </c>
       <c r="D6" t="n">
-        <v>21.41388092503143</v>
+        <v>1.56981457909065</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +6138,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.40893112878119</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>58.4493313200381</v>
+        <v>4.850815406683489</v>
       </c>
       <c r="D7" t="n">
-        <v>24.79305652304895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +6152,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.6062624173348</v>
+        <v>3.00414797499524</v>
       </c>
       <c r="C8" t="n">
-        <v>74.18576527141022</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +6166,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>86.19843018057416</v>
+        <v>3.882812170296134</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +6180,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13.52357462599982</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>91.67560062256716</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="D10" t="n">
-        <v>31.74481201682062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +6194,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13.86031408855647</v>
+        <v>2.487748682561417</v>
       </c>
       <c r="C11" t="n">
-        <v>86.89350755518092</v>
+        <v>1.066178006812036</v>
       </c>
       <c r="D11" t="n">
-        <v>31.27455486648638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +6208,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15.62156946997525</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>96.33301173151402</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>31.02617269731195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +6222,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18.21141991377833</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>106.9270512080414</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>28.61794557879453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +6236,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20.58823110575986</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>123.2220996031299</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +6250,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>22.57528845915541</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>139.0351098754333</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>16.48354395430394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +6264,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>21.49242074137117</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>156.6466819419168</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.439684102782329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +6278,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13.69439872653876</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>178.4994040907466</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1.416661937228147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +6292,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>182.987954594563</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -5994,10 +6306,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>127.5840046530985</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6011,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -6022,7 +6334,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>3.269630630596206</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -6067,13 +6379,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>128.1455643399277</v>
+        <v>2.383683425911256</v>
       </c>
       <c r="C2" t="n">
-        <v>771.1834383876587</v>
+        <v>0.4673119072214817</v>
       </c>
       <c r="D2" t="n">
-        <v>485.837486400619</v>
+        <v>22.80207217883641</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6393,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9522952731194061</v>
+        <v>6.877142668248907</v>
       </c>
       <c r="C3" t="n">
-        <v>2.233476027161494</v>
+        <v>1.340085616296896</v>
       </c>
       <c r="D3" t="n">
-        <v>4.908738521234052</v>
+        <v>105.3071674960341</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6407,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5.041274461307371</v>
+        <v>11.29500733735955</v>
       </c>
       <c r="C4" t="n">
-        <v>22.65382827549515</v>
+        <v>2.897137475232337</v>
       </c>
       <c r="D4" t="n">
-        <v>13.83478864824605</v>
+        <v>80.5965777801419</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6421,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.43106935762236</v>
+        <v>13.22905031472577</v>
       </c>
       <c r="C5" t="n">
-        <v>33.91938318172731</v>
+        <v>4.393320976504477</v>
       </c>
       <c r="D5" t="n">
-        <v>15.19254572321939</v>
+        <v>20.76396394482004</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6435,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.96103319146639</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>50.83784136901259</v>
+        <v>5.2327152636355</v>
       </c>
       <c r="D6" t="n">
-        <v>20.930861054542</v>
+        <v>2.495602664195392</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6449,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.67221943996858</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>57.79057861048849</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="D7" t="n">
-        <v>24.43373686329462</v>
+        <v>0.05988660995905543</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6463,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>72.85058839363457</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6477,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.64687392610741</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>83.75780538781659</v>
+        <v>4.104687151455913</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6491,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>12.10004045484194</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>87.68970494332511</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6505,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12.79413608174443</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>84.4057588726195</v>
+        <v>1.243874341280709</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6519,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.75370449942107</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>94.81424803304421</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6533,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>16.91060420565131</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>106.1465617831651</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6547,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>19.0517959486136</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>121.9929514774129</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6561,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>19.35024725070463</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>137.960096139283</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>10.75013736150257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6575,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14.87936820556466</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>156.2333661584289</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -6277,10 +6589,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.083309686140737</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>172.832756341834</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -6291,10 +6603,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>159.980697145539</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -6308,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>95.68800348982387</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6322,7 +6634,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>24.20989838672634</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -6333,7 +6645,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>2.483947543108285</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -6378,13 +6690,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>106.1082736226995</v>
+        <v>2.706678420608456</v>
       </c>
       <c r="C2" t="n">
-        <v>715.512453070639</v>
+        <v>0.3701188845010475</v>
       </c>
       <c r="D2" t="n">
-        <v>539.178784415461</v>
+        <v>23.35479613632737</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6704,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9179341034707678</v>
+        <v>7.878525326580654</v>
       </c>
       <c r="C3" t="n">
-        <v>2.43473430653209</v>
+        <v>1.384264262988003</v>
       </c>
       <c r="D3" t="n">
-        <v>4.933282213840222</v>
+        <v>100.6978620245953</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6718,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4.556291095409446</v>
+        <v>12.89034735676062</v>
       </c>
       <c r="C4" t="n">
-        <v>21.88806506618264</v>
+        <v>2.897137475232337</v>
       </c>
       <c r="D4" t="n">
-        <v>13.14560175986479</v>
+        <v>84.7827499910503</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6732,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.621127501618743</v>
+        <v>15.78159434576748</v>
       </c>
       <c r="C5" t="n">
-        <v>33.03581024790518</v>
+        <v>4.393320976504477</v>
       </c>
       <c r="D5" t="n">
-        <v>14.7753029489145</v>
+        <v>25.08365384350601</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6746,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.83398682699105</v>
+        <v>15.8994040702771</v>
       </c>
       <c r="C6" t="n">
-        <v>49.63029169278902</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="D6" t="n">
-        <v>20.48809283992669</v>
+        <v>3.622649028670731</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6760,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.11516758103314</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C7" t="n">
-        <v>57.07193929097983</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="D7" t="n">
-        <v>23.95464398362217</v>
+        <v>0.1796598298771663</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6774,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>71.43196296099792</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6788,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.09374905798895</v>
+        <v>4.215624642035802</v>
       </c>
       <c r="C9" t="n">
-        <v>81.20624310447914</v>
+        <v>4.215624642035802</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6802,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.96121311791564</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>83.98851609831463</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="D10" t="n">
-        <v>28.04362317181014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6816,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.90565440940107</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>82.27340285899542</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="D11" t="n">
-        <v>26.83214650476957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6830,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.88583952886689</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>93.29548433457438</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>24.95111790343269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6844,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>15.86995163914969</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>105.3660723582889</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>20.55288818840698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6858,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>17.20807376003809</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>120.7638033516959</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>13.52062938288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6872,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15.0501923061036</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>136.8850824031328</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6886,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>154.5801030244773</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -6588,10 +6900,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.833323874456295</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>162.916122781237</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -6605,7 +6917,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>135.3682822000715</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -6619,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>69.8101157535822</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6633,7 +6945,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>14.79493790299943</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -6644,7 +6956,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1.676122699438934</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
